--- a/Financial Analysis/STNE.xlsx
+++ b/Financial Analysis/STNE.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Desktop\Financial Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CD95A12-E16A-4B00-BD31-FA47948A26A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EF69E5E-475C-4982-825E-7BA0B0E09635}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{739ADCDA-92AA-4302-8B1F-47F1B6FD860D}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="131">
   <si>
     <t>Price</t>
   </si>
@@ -415,7 +415,10 @@
     <t>Impairment</t>
   </si>
   <si>
-    <t>Slightly undervalued</t>
+    <t>Q125 6K</t>
+  </si>
+  <si>
+    <t>Undervalued</t>
   </si>
 </sst>
 </file>
@@ -546,14 +549,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>26</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>26</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
       <xdr:row>122</xdr:row>
       <xdr:rowOff>106680</xdr:rowOff>
     </xdr:to>
@@ -570,7 +573,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="16710660" y="7620"/>
+          <a:off x="17312640" y="7620"/>
           <a:ext cx="0" cy="22410420"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -967,17 +970,17 @@
         <v>0</v>
       </c>
       <c r="D3" s="2">
-        <v>13.77</v>
+        <v>13.28</v>
       </c>
       <c r="E3" s="6">
-        <v>45780</v>
+        <v>45804</v>
       </c>
       <c r="F3" s="6">
         <f ca="1">TODAY()</f>
-        <v>45780</v>
+        <v>45804</v>
       </c>
       <c r="G3" s="6">
-        <v>45832</v>
+        <v>45882</v>
       </c>
     </row>
     <row r="4" spans="3:9" x14ac:dyDescent="0.3">
@@ -985,10 +988,11 @@
         <v>1</v>
       </c>
       <c r="D4" s="1">
-        <v>293.10000000000002</v>
+        <f>279.8</f>
+        <v>279.8</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>36</v>
+        <v>129</v>
       </c>
     </row>
     <row r="5" spans="3:9" x14ac:dyDescent="0.3">
@@ -997,7 +1001,7 @@
       </c>
       <c r="D5" s="1">
         <f>D3*D4</f>
-        <v>4035.9870000000001</v>
+        <v>3715.7440000000001</v>
       </c>
     </row>
     <row r="6" spans="3:9" x14ac:dyDescent="0.3">
@@ -1005,11 +1009,11 @@
         <v>5</v>
       </c>
       <c r="D6" s="1">
-        <f>5227.7+517.9+32.6</f>
-        <v>5778.2</v>
+        <f>5650.4+146.2+32.1</f>
+        <v>5828.7</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>36</v>
+        <v>123</v>
       </c>
     </row>
     <row r="7" spans="3:9" x14ac:dyDescent="0.3">
@@ -1017,11 +1021,11 @@
         <v>6</v>
       </c>
       <c r="D7" s="1">
-        <f>3066+1903.8+5430+2496.1</f>
-        <v>12895.9</v>
+        <f>2853+2086.1+6025+2471.7</f>
+        <v>13435.8</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>36</v>
+        <v>123</v>
       </c>
     </row>
     <row r="8" spans="3:9" x14ac:dyDescent="0.3">
@@ -1030,10 +1034,10 @@
       </c>
       <c r="D8" s="1">
         <f>D6/D13</f>
-        <v>1020.8833922261483</v>
+        <v>1029.8056537102473</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>36</v>
+        <v>123</v>
       </c>
       <c r="I8" t="s">
         <v>78</v>
@@ -1045,10 +1049,10 @@
       </c>
       <c r="D9" s="1">
         <f>D7/D13</f>
-        <v>2278.4275618374559</v>
+        <v>2373.8162544169609</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>36</v>
+        <v>123</v>
       </c>
     </row>
     <row r="10" spans="3:9" x14ac:dyDescent="0.3">
@@ -1057,7 +1061,7 @@
       </c>
       <c r="D10" s="1">
         <f>D8-D9</f>
-        <v>-1257.5441696113076</v>
+        <v>-1344.0106007067136</v>
       </c>
       <c r="E10" s="5"/>
     </row>
@@ -1067,7 +1071,7 @@
       </c>
       <c r="D11" s="1">
         <f>D5-D10</f>
-        <v>5293.5311696113076</v>
+        <v>5059.754600706714</v>
       </c>
     </row>
     <row r="13" spans="3:9" x14ac:dyDescent="0.3">
@@ -1278,20 +1282,19 @@
         <v>829.8</v>
       </c>
       <c r="AA3" s="1">
-        <f>W3*0.96</f>
-        <v>719.80799999999988</v>
+        <v>684.4</v>
       </c>
       <c r="AB3" s="1">
-        <f t="shared" ref="AB3" si="0">X3*0.96</f>
-        <v>775.19999999999993</v>
+        <f>X3*0.92</f>
+        <v>742.9</v>
       </c>
       <c r="AC3" s="1">
-        <f>Y3*0.97</f>
-        <v>804.0329999999999</v>
+        <f>Y3*0.94</f>
+        <v>779.16599999999994</v>
       </c>
       <c r="AD3" s="1">
-        <f>Z3*0.98</f>
-        <v>813.20399999999995</v>
+        <f>Z3*0.97</f>
+        <v>804.90599999999995</v>
       </c>
       <c r="AH3" s="1">
         <v>770.3</v>
@@ -1316,47 +1319,47 @@
       </c>
       <c r="AN3" s="1">
         <f>SUM(AA3:AD3)</f>
-        <v>3112.2449999999999</v>
+        <v>3011.3719999999998</v>
       </c>
       <c r="AO3" s="1">
-        <f t="shared" ref="AO3:AX4" si="1">AN3*1.01</f>
-        <v>3143.3674499999997</v>
+        <f t="shared" ref="AO3:AX4" si="0">AN3*1.01</f>
+        <v>3041.4857199999997</v>
       </c>
       <c r="AP3" s="1">
-        <f t="shared" si="1"/>
-        <v>3174.8011244999998</v>
+        <f t="shared" si="0"/>
+        <v>3071.9005771999996</v>
       </c>
       <c r="AQ3" s="1">
-        <f t="shared" si="1"/>
-        <v>3206.5491357449996</v>
+        <f t="shared" si="0"/>
+        <v>3102.6195829719995</v>
       </c>
       <c r="AR3" s="1">
-        <f t="shared" si="1"/>
-        <v>3238.6146271024495</v>
+        <f t="shared" si="0"/>
+        <v>3133.6457788017196</v>
       </c>
       <c r="AS3" s="1">
-        <f t="shared" si="1"/>
-        <v>3271.0007733734742</v>
+        <f t="shared" si="0"/>
+        <v>3164.9822365897367</v>
       </c>
       <c r="AT3" s="1">
-        <f t="shared" si="1"/>
-        <v>3303.7107811072092</v>
+        <f t="shared" si="0"/>
+        <v>3196.632058955634</v>
       </c>
       <c r="AU3" s="1">
-        <f t="shared" si="1"/>
-        <v>3336.7478889182812</v>
+        <f t="shared" si="0"/>
+        <v>3228.5983795451903</v>
       </c>
       <c r="AV3" s="1">
-        <f t="shared" si="1"/>
-        <v>3370.1153678074638</v>
+        <f t="shared" si="0"/>
+        <v>3260.8843633406423</v>
       </c>
       <c r="AW3" s="1">
-        <f t="shared" si="1"/>
-        <v>3403.8165214855385</v>
+        <f t="shared" si="0"/>
+        <v>3293.4932069740489</v>
       </c>
       <c r="AX3" s="1">
-        <f t="shared" si="1"/>
-        <v>3437.8546867003938</v>
+        <f t="shared" si="0"/>
+        <v>3326.4281390437895</v>
       </c>
     </row>
     <row r="4" spans="2:50" x14ac:dyDescent="0.3">
@@ -1403,19 +1406,18 @@
         <v>471.3</v>
       </c>
       <c r="AA4" s="1">
-        <f>W4*1.01</f>
-        <v>461.267</v>
+        <v>493.2</v>
       </c>
       <c r="AB4" s="1">
         <f>X4*1.03</f>
         <v>466.899</v>
       </c>
       <c r="AC4" s="1">
-        <f t="shared" ref="AC4:AD4" si="2">Y4*1.02</f>
+        <f t="shared" ref="AC4:AD4" si="1">Y4*1.02</f>
         <v>474.91200000000003</v>
       </c>
       <c r="AD4" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>480.726</v>
       </c>
       <c r="AH4" s="1">
@@ -1440,48 +1442,48 @@
         <v>1846.8999999999999</v>
       </c>
       <c r="AN4" s="1">
-        <f t="shared" ref="AN4:AN17" si="3">SUM(AA4:AD4)</f>
-        <v>1883.8040000000001</v>
+        <f t="shared" ref="AN4:AN17" si="2">SUM(AA4:AD4)</f>
+        <v>1915.7370000000001</v>
       </c>
       <c r="AO4" s="1">
         <f>AN4*1.02</f>
-        <v>1921.48008</v>
+        <v>1954.0517400000001</v>
       </c>
       <c r="AP4" s="1">
-        <f t="shared" ref="AP4:AS4" si="4">AO4*1.02</f>
-        <v>1959.9096816000001</v>
+        <f t="shared" ref="AP4:AS4" si="3">AO4*1.02</f>
+        <v>1993.1327748000001</v>
       </c>
       <c r="AQ4" s="1">
-        <f t="shared" si="4"/>
-        <v>1999.1078752320002</v>
+        <f t="shared" si="3"/>
+        <v>2032.9954302960002</v>
       </c>
       <c r="AR4" s="1">
-        <f t="shared" si="4"/>
-        <v>2039.0900327366403</v>
+        <f t="shared" si="3"/>
+        <v>2073.6553389019205</v>
       </c>
       <c r="AS4" s="1">
-        <f t="shared" si="4"/>
-        <v>2079.871833391373</v>
+        <f t="shared" si="3"/>
+        <v>2115.128445679959</v>
       </c>
       <c r="AT4" s="1">
         <f>AS4*1.01</f>
-        <v>2100.6705517252867</v>
+        <v>2136.2797301367586</v>
       </c>
       <c r="AU4" s="1">
-        <f t="shared" si="1"/>
-        <v>2121.6772572425398</v>
+        <f t="shared" si="0"/>
+        <v>2157.6425274381263</v>
       </c>
       <c r="AV4" s="1">
-        <f t="shared" si="1"/>
-        <v>2142.8940298149651</v>
+        <f t="shared" si="0"/>
+        <v>2179.2189527125074</v>
       </c>
       <c r="AW4" s="1">
-        <f t="shared" si="1"/>
-        <v>2164.3229701131149</v>
+        <f t="shared" si="0"/>
+        <v>2201.0111422396326</v>
       </c>
       <c r="AX4" s="1">
-        <f t="shared" si="1"/>
-        <v>2185.966199814246</v>
+        <f t="shared" si="0"/>
+        <v>2223.0212536620288</v>
       </c>
     </row>
     <row r="5" spans="2:50" x14ac:dyDescent="0.3">
@@ -1528,20 +1530,19 @@
         <v>2189.6</v>
       </c>
       <c r="AA5" s="1">
-        <f>W5*1.19</f>
-        <v>2071.9089999999997</v>
+        <v>2303.1</v>
       </c>
       <c r="AB5" s="1">
-        <f>X5*1.17</f>
-        <v>2137.239</v>
+        <f>X5*1.27</f>
+        <v>2319.9090000000001</v>
       </c>
       <c r="AC5" s="1">
-        <f>Y5*1.15</f>
-        <v>2206.7350000000001</v>
+        <f>Y5*1.22</f>
+        <v>2341.058</v>
       </c>
       <c r="AD5" s="1">
-        <f>Z5*1.08</f>
-        <v>2364.768</v>
+        <f>Z5*1.1</f>
+        <v>2408.56</v>
       </c>
       <c r="AH5" s="1">
         <v>1287.8</v>
@@ -1565,48 +1566,48 @@
         <v>7676.3000000000011</v>
       </c>
       <c r="AN5" s="1">
-        <f t="shared" si="3"/>
-        <v>8780.6509999999998</v>
+        <f t="shared" si="2"/>
+        <v>9372.6270000000004</v>
       </c>
       <c r="AO5" s="1">
-        <f>AN5*1.1</f>
-        <v>9658.7161000000015</v>
+        <f>AN5*1.14</f>
+        <v>10684.79478</v>
       </c>
       <c r="AP5" s="1">
         <f>AO5*1.08</f>
-        <v>10431.413388000003</v>
+        <v>11539.578362400001</v>
       </c>
       <c r="AQ5" s="1">
         <f>AP5*1.06</f>
-        <v>11057.298191280004</v>
+        <v>12231.953064144001</v>
       </c>
       <c r="AR5" s="1">
         <f>AQ5*1.04</f>
-        <v>11499.590118931204</v>
+        <v>12721.231186709761</v>
       </c>
       <c r="AS5" s="1">
         <f>AR5*1.03</f>
-        <v>11844.577822499141</v>
+        <v>13102.868122311054</v>
       </c>
       <c r="AT5" s="1">
         <f>AS5*1.02</f>
-        <v>12081.469378949125</v>
+        <v>13364.925484757276</v>
       </c>
       <c r="AU5" s="1">
         <f>AT5*1.01</f>
-        <v>12202.284072738616</v>
+        <v>13498.574739604848</v>
       </c>
       <c r="AV5" s="1">
-        <f t="shared" ref="AV5:AX5" si="5">AU5*1.01</f>
-        <v>12324.306913466002</v>
+        <f t="shared" ref="AV5:AX5" si="4">AU5*1.01</f>
+        <v>13633.560487000897</v>
       </c>
       <c r="AW5" s="1">
-        <f t="shared" si="5"/>
-        <v>12447.549982600662</v>
+        <f t="shared" si="4"/>
+        <v>13769.896091870907</v>
       </c>
       <c r="AX5" s="1">
-        <f t="shared" si="5"/>
-        <v>12572.025482426669</v>
+        <f t="shared" si="4"/>
+        <v>13907.595052789617</v>
       </c>
     </row>
     <row r="6" spans="2:50" x14ac:dyDescent="0.3">
@@ -1629,136 +1630,136 @@
       <c r="M6" s="7"/>
       <c r="N6" s="7"/>
       <c r="O6" s="9">
-        <f t="shared" ref="O6:W6" si="6">SUM(O3:O5)</f>
+        <f t="shared" ref="O6:W6" si="5">SUM(O3:O5)</f>
         <v>1936.8999999999999</v>
       </c>
       <c r="P6" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>2149.6999999999998</v>
       </c>
       <c r="Q6" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>2355.7999999999997</v>
       </c>
       <c r="R6" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>2574</v>
       </c>
       <c r="S6" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>2553.1999999999998</v>
       </c>
       <c r="T6" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>2760</v>
       </c>
       <c r="U6" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>2952.8</v>
       </c>
       <c r="V6" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>3098</v>
       </c>
       <c r="W6" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>2947.6</v>
       </c>
       <c r="X6" s="9">
-        <f t="shared" ref="X6" si="7">SUM(X3:X5)</f>
+        <f t="shared" ref="X6" si="6">SUM(X3:X5)</f>
         <v>3087.5</v>
       </c>
       <c r="Y6" s="9">
-        <f t="shared" ref="Y6" si="8">SUM(Y3:Y5)</f>
+        <f t="shared" ref="Y6" si="7">SUM(Y3:Y5)</f>
         <v>3213.4</v>
       </c>
       <c r="Z6" s="9">
-        <f t="shared" ref="Z6:AD6" si="9">SUM(Z3:Z5)</f>
+        <f t="shared" ref="Z6:AD6" si="8">SUM(Z3:Z5)</f>
         <v>3490.7</v>
       </c>
       <c r="AA6" s="9">
+        <f t="shared" si="8"/>
+        <v>3480.7</v>
+      </c>
+      <c r="AB6" s="9">
+        <f t="shared" si="8"/>
+        <v>3529.7080000000001</v>
+      </c>
+      <c r="AC6" s="9">
+        <f t="shared" si="8"/>
+        <v>3595.136</v>
+      </c>
+      <c r="AD6" s="9">
+        <f t="shared" si="8"/>
+        <v>3694.192</v>
+      </c>
+      <c r="AH6" s="9">
+        <f t="shared" ref="AH6:AM6" si="9">SUM(AH3:AH5)</f>
+        <v>2389.6999999999998</v>
+      </c>
+      <c r="AI6" s="9">
         <f t="shared" si="9"/>
-        <v>3252.9839999999995</v>
-      </c>
-      <c r="AB6" s="9">
+        <v>3179.1</v>
+      </c>
+      <c r="AJ6" s="9">
         <f t="shared" si="9"/>
-        <v>3379.3379999999997</v>
-      </c>
-      <c r="AC6" s="9">
+        <v>4576.5</v>
+      </c>
+      <c r="AK6" s="9">
         <f t="shared" si="9"/>
-        <v>3485.6800000000003</v>
-      </c>
-      <c r="AD6" s="9">
+        <v>9016.4</v>
+      </c>
+      <c r="AL6" s="9">
         <f t="shared" si="9"/>
-        <v>3658.6979999999999</v>
-      </c>
-      <c r="AH6" s="9">
-        <f t="shared" ref="AH6:AM6" si="10">SUM(AH3:AH5)</f>
-        <v>2389.6999999999998</v>
-      </c>
-      <c r="AI6" s="9">
-        <f t="shared" si="10"/>
-        <v>3179.1</v>
-      </c>
-      <c r="AJ6" s="9">
-        <f t="shared" si="10"/>
-        <v>4576.5</v>
-      </c>
-      <c r="AK6" s="9">
-        <f t="shared" si="10"/>
-        <v>9016.4</v>
-      </c>
-      <c r="AL6" s="9">
-        <f t="shared" si="10"/>
         <v>11364</v>
       </c>
       <c r="AM6" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>12739.2</v>
       </c>
       <c r="AN6" s="9">
-        <f t="shared" ref="AN6" si="11">SUM(AN3:AN5)</f>
-        <v>13776.7</v>
+        <f t="shared" ref="AN6" si="10">SUM(AN3:AN5)</f>
+        <v>14299.736000000001</v>
       </c>
       <c r="AO6" s="9">
-        <f t="shared" ref="AO6" si="12">SUM(AO3:AO5)</f>
-        <v>14723.563630000001</v>
+        <f t="shared" ref="AO6" si="11">SUM(AO3:AO5)</f>
+        <v>15680.33224</v>
       </c>
       <c r="AP6" s="9">
-        <f t="shared" ref="AP6" si="13">SUM(AP3:AP5)</f>
-        <v>15566.124194100003</v>
+        <f t="shared" ref="AP6" si="12">SUM(AP3:AP5)</f>
+        <v>16604.611714400002</v>
       </c>
       <c r="AQ6" s="9">
-        <f t="shared" ref="AQ6" si="14">SUM(AQ3:AQ5)</f>
-        <v>16262.955202257004</v>
+        <f t="shared" ref="AQ6" si="13">SUM(AQ3:AQ5)</f>
+        <v>17367.568077412001</v>
       </c>
       <c r="AR6" s="9">
-        <f t="shared" ref="AR6" si="15">SUM(AR3:AR5)</f>
-        <v>16777.294778770294</v>
+        <f t="shared" ref="AR6" si="14">SUM(AR3:AR5)</f>
+        <v>17928.532304413402</v>
       </c>
       <c r="AS6" s="9">
-        <f t="shared" ref="AS6" si="16">SUM(AS3:AS5)</f>
-        <v>17195.45042926399</v>
+        <f t="shared" ref="AS6" si="15">SUM(AS3:AS5)</f>
+        <v>18382.978804580751</v>
       </c>
       <c r="AT6" s="9">
-        <f t="shared" ref="AT6" si="17">SUM(AT3:AT5)</f>
-        <v>17485.850711781619</v>
+        <f t="shared" ref="AT6" si="16">SUM(AT3:AT5)</f>
+        <v>18697.837273849669</v>
       </c>
       <c r="AU6" s="9">
-        <f t="shared" ref="AU6" si="18">SUM(AU3:AU5)</f>
-        <v>17660.709218899436</v>
+        <f t="shared" ref="AU6" si="17">SUM(AU3:AU5)</f>
+        <v>18884.815646588166</v>
       </c>
       <c r="AV6" s="9">
-        <f t="shared" ref="AV6" si="19">SUM(AV3:AV5)</f>
-        <v>17837.316311088431</v>
+        <f t="shared" ref="AV6" si="18">SUM(AV3:AV5)</f>
+        <v>19073.663803054049</v>
       </c>
       <c r="AW6" s="9">
-        <f t="shared" ref="AW6" si="20">SUM(AW3:AW5)</f>
-        <v>18015.689474199316</v>
+        <f t="shared" ref="AW6" si="19">SUM(AW3:AW5)</f>
+        <v>19264.400441084588</v>
       </c>
       <c r="AX6" s="9">
-        <f t="shared" ref="AX6" si="21">SUM(AX3:AX5)</f>
-        <v>18195.846368941307</v>
+        <f t="shared" ref="AX6" si="20">SUM(AX3:AX5)</f>
+        <v>19457.044445495434</v>
       </c>
     </row>
     <row r="7" spans="2:50" x14ac:dyDescent="0.3">
@@ -1806,20 +1807,19 @@
         <v>878.8</v>
       </c>
       <c r="AA7" s="1">
-        <f>AA6-AA8</f>
-        <v>878.30567999999994</v>
+        <v>933.9</v>
       </c>
       <c r="AB7" s="1">
-        <f t="shared" ref="AB7:AD7" si="22">AB6-AB8</f>
-        <v>912.42126000000007</v>
+        <f t="shared" ref="AB7:AD7" si="21">AB6-AB8</f>
+        <v>953.02116000000024</v>
       </c>
       <c r="AC7" s="1">
-        <f t="shared" si="22"/>
-        <v>906.27680000000009</v>
+        <f t="shared" si="21"/>
+        <v>934.73536000000013</v>
       </c>
       <c r="AD7" s="1">
-        <f t="shared" si="22"/>
-        <v>914.67450000000008</v>
+        <f t="shared" si="21"/>
+        <v>923.54799999999977</v>
       </c>
       <c r="AH7" s="1">
         <v>426.9</v>
@@ -1843,48 +1843,48 @@
         <v>3389.1000000000004</v>
       </c>
       <c r="AN7" s="1">
-        <f t="shared" si="3"/>
-        <v>3611.6782400000002</v>
+        <f t="shared" si="2"/>
+        <v>3745.2045200000002</v>
       </c>
       <c r="AO7" s="1">
-        <f t="shared" ref="AO7:AX7" si="23">AO6-AO8</f>
-        <v>3828.1265438000009</v>
+        <f t="shared" ref="AO7:AX7" si="22">AO6-AO8</f>
+        <v>4076.8863824</v>
       </c>
       <c r="AP7" s="1">
-        <f t="shared" si="23"/>
-        <v>4047.1922904660005</v>
+        <f t="shared" si="22"/>
+        <v>4317.1990457440006</v>
       </c>
       <c r="AQ7" s="1">
-        <f t="shared" si="23"/>
-        <v>4228.3683525868219</v>
+        <f t="shared" si="22"/>
+        <v>4515.5677001271197</v>
       </c>
       <c r="AR7" s="1">
-        <f t="shared" si="23"/>
-        <v>4362.0966424802773</v>
+        <f t="shared" si="22"/>
+        <v>4661.4183991474838</v>
       </c>
       <c r="AS7" s="1">
-        <f t="shared" si="23"/>
-        <v>4470.8171116086378</v>
+        <f t="shared" si="22"/>
+        <v>4779.5744891909962</v>
       </c>
       <c r="AT7" s="1">
-        <f t="shared" si="23"/>
-        <v>4546.3211850632215</v>
+        <f t="shared" si="22"/>
+        <v>4861.4376912009138</v>
       </c>
       <c r="AU7" s="1">
-        <f t="shared" si="23"/>
-        <v>4591.7843969138539</v>
+        <f t="shared" si="22"/>
+        <v>4910.0520681129237</v>
       </c>
       <c r="AV7" s="1">
-        <f t="shared" si="23"/>
-        <v>4637.7022408829926</v>
+        <f t="shared" si="22"/>
+        <v>4959.1525887940534</v>
       </c>
       <c r="AW7" s="1">
-        <f t="shared" si="23"/>
-        <v>4684.0792632918219</v>
+        <f t="shared" si="22"/>
+        <v>5008.7441146819929</v>
       </c>
       <c r="AX7" s="1">
-        <f t="shared" si="23"/>
-        <v>4730.9200559247402</v>
+        <f t="shared" si="22"/>
+        <v>5058.8315558288123</v>
       </c>
     </row>
     <row r="8" spans="2:50" x14ac:dyDescent="0.3">
@@ -1907,136 +1907,136 @@
       <c r="M8" s="7"/>
       <c r="N8" s="7"/>
       <c r="O8" s="9">
-        <f t="shared" ref="O8:Z8" si="24">O6-O7</f>
+        <f t="shared" ref="O8:AA8" si="23">O6-O7</f>
         <v>1262.5</v>
       </c>
       <c r="P8" s="9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>1523.4999999999998</v>
       </c>
       <c r="Q8" s="9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>1684.4999999999998</v>
       </c>
       <c r="R8" s="9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>1876</v>
       </c>
       <c r="S8" s="9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>1831.8999999999999</v>
       </c>
       <c r="T8" s="9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>2074.6999999999998</v>
       </c>
       <c r="U8" s="9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>2179.3000000000002</v>
       </c>
       <c r="V8" s="9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>2295.3000000000002</v>
       </c>
       <c r="W8" s="9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>2137.6999999999998</v>
       </c>
       <c r="X8" s="9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>2246.1</v>
       </c>
       <c r="Y8" s="9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>2354.4</v>
       </c>
       <c r="Z8" s="9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>2611.8999999999996</v>
       </c>
       <c r="AA8" s="9">
-        <f>AA6*0.73</f>
-        <v>2374.6783199999995</v>
+        <f t="shared" si="23"/>
+        <v>2546.7999999999997</v>
       </c>
       <c r="AB8" s="9">
-        <f t="shared" ref="AB8" si="25">AB6*0.73</f>
-        <v>2466.9167399999997</v>
+        <f t="shared" ref="AB8" si="24">AB6*0.73</f>
+        <v>2576.6868399999998</v>
       </c>
       <c r="AC8" s="9">
         <f>AC6*0.74</f>
-        <v>2579.4032000000002</v>
+        <v>2660.4006399999998</v>
       </c>
       <c r="AD8" s="9">
         <f>AD6*0.75</f>
-        <v>2744.0234999999998</v>
+        <v>2770.6440000000002</v>
       </c>
       <c r="AH8" s="9">
-        <f t="shared" ref="AH8:AN8" si="26">AH6-AH7</f>
+        <f t="shared" ref="AH8:AN8" si="25">AH6-AH7</f>
         <v>1962.7999999999997</v>
       </c>
       <c r="AI8" s="9">
+        <f t="shared" si="25"/>
+        <v>2409.1999999999998</v>
+      </c>
+      <c r="AJ8" s="9">
+        <f t="shared" si="25"/>
+        <v>2862.7</v>
+      </c>
+      <c r="AK8" s="9">
+        <f t="shared" si="25"/>
+        <v>6346.5</v>
+      </c>
+      <c r="AL8" s="9">
+        <f t="shared" si="25"/>
+        <v>8381.2000000000007</v>
+      </c>
+      <c r="AM8" s="9">
+        <f t="shared" si="25"/>
+        <v>9350.1</v>
+      </c>
+      <c r="AN8" s="9">
+        <f t="shared" si="25"/>
+        <v>10554.531480000001</v>
+      </c>
+      <c r="AO8" s="9">
+        <f t="shared" ref="AO8:AX8" si="26">AO6*0.74</f>
+        <v>11603.4458576</v>
+      </c>
+      <c r="AP8" s="9">
         <f t="shared" si="26"/>
-        <v>2409.1999999999998</v>
-      </c>
-      <c r="AJ8" s="9">
+        <v>12287.412668656001</v>
+      </c>
+      <c r="AQ8" s="9">
         <f t="shared" si="26"/>
-        <v>2862.7</v>
-      </c>
-      <c r="AK8" s="9">
+        <v>12852.000377284881</v>
+      </c>
+      <c r="AR8" s="9">
         <f t="shared" si="26"/>
-        <v>6346.5</v>
-      </c>
-      <c r="AL8" s="9">
+        <v>13267.113905265918</v>
+      </c>
+      <c r="AS8" s="9">
         <f t="shared" si="26"/>
-        <v>8381.2000000000007</v>
-      </c>
-      <c r="AM8" s="9">
+        <v>13603.404315389755</v>
+      </c>
+      <c r="AT8" s="9">
         <f t="shared" si="26"/>
-        <v>9350.1</v>
-      </c>
-      <c r="AN8" s="9">
+        <v>13836.399582648755</v>
+      </c>
+      <c r="AU8" s="9">
         <f t="shared" si="26"/>
-        <v>10165.02176</v>
-      </c>
-      <c r="AO8" s="9">
-        <f t="shared" ref="AO8:AX8" si="27">AO6*0.74</f>
-        <v>10895.4370862</v>
-      </c>
-      <c r="AP8" s="9">
-        <f t="shared" si="27"/>
-        <v>11518.931903634002</v>
-      </c>
-      <c r="AQ8" s="9">
-        <f t="shared" si="27"/>
-        <v>12034.586849670182</v>
-      </c>
-      <c r="AR8" s="9">
-        <f t="shared" si="27"/>
-        <v>12415.198136290017</v>
-      </c>
-      <c r="AS8" s="9">
-        <f t="shared" si="27"/>
-        <v>12724.633317655353</v>
-      </c>
-      <c r="AT8" s="9">
-        <f t="shared" si="27"/>
-        <v>12939.529526718397</v>
-      </c>
-      <c r="AU8" s="9">
-        <f t="shared" si="27"/>
-        <v>13068.924821985582</v>
+        <v>13974.763578475242</v>
       </c>
       <c r="AV8" s="9">
-        <f t="shared" si="27"/>
-        <v>13199.614070205438</v>
+        <f t="shared" si="26"/>
+        <v>14114.511214259996</v>
       </c>
       <c r="AW8" s="9">
-        <f t="shared" si="27"/>
-        <v>13331.610210907495</v>
+        <f t="shared" si="26"/>
+        <v>14255.656326402595</v>
       </c>
       <c r="AX8" s="9">
-        <f t="shared" si="27"/>
-        <v>13464.926313016567</v>
+        <f t="shared" si="26"/>
+        <v>14398.212889666622</v>
       </c>
     </row>
     <row r="9" spans="2:50" x14ac:dyDescent="0.3">
@@ -2083,20 +2083,19 @@
         <v>303.3</v>
       </c>
       <c r="AA9" s="1">
-        <f>AA6*0.09</f>
-        <v>292.76855999999992</v>
+        <v>277.89999999999998</v>
       </c>
       <c r="AB9" s="1">
-        <f t="shared" ref="AB9:AD9" si="28">AB6*0.09</f>
-        <v>304.14041999999995</v>
+        <f t="shared" ref="AB9:AD9" si="27">AB6*0.09</f>
+        <v>317.67372</v>
       </c>
       <c r="AC9" s="1">
-        <f t="shared" si="28"/>
-        <v>313.71120000000002</v>
+        <f t="shared" si="27"/>
+        <v>323.56223999999997</v>
       </c>
       <c r="AD9" s="1">
-        <f t="shared" si="28"/>
-        <v>329.28281999999996</v>
+        <f t="shared" si="27"/>
+        <v>332.47728000000001</v>
       </c>
       <c r="AH9" s="1">
         <v>285.8</v>
@@ -2120,48 +2119,48 @@
         <v>1130.5</v>
       </c>
       <c r="AN9" s="1">
-        <f t="shared" si="3"/>
-        <v>1239.9029999999998</v>
+        <f t="shared" si="2"/>
+        <v>1251.6132399999999</v>
       </c>
       <c r="AO9" s="1">
-        <f t="shared" ref="AO9:AX9" si="29">AO6*0.09</f>
-        <v>1325.1207267</v>
+        <f t="shared" ref="AO9:AX9" si="28">AO6*0.09</f>
+        <v>1411.2299015999999</v>
       </c>
       <c r="AP9" s="1">
-        <f t="shared" si="29"/>
-        <v>1400.9511774690002</v>
+        <f t="shared" si="28"/>
+        <v>1494.4150542960001</v>
       </c>
       <c r="AQ9" s="1">
-        <f t="shared" si="29"/>
-        <v>1463.6659682031304</v>
+        <f t="shared" si="28"/>
+        <v>1563.0811269670801</v>
       </c>
       <c r="AR9" s="1">
-        <f t="shared" si="29"/>
-        <v>1509.9565300893264</v>
+        <f t="shared" si="28"/>
+        <v>1613.5679073972062</v>
       </c>
       <c r="AS9" s="1">
-        <f t="shared" si="29"/>
-        <v>1547.590538633759</v>
+        <f t="shared" si="28"/>
+        <v>1654.4680924122674</v>
       </c>
       <c r="AT9" s="1">
-        <f t="shared" si="29"/>
-        <v>1573.7265640603457</v>
+        <f t="shared" si="28"/>
+        <v>1682.8053546464701</v>
       </c>
       <c r="AU9" s="1">
-        <f t="shared" si="29"/>
-        <v>1589.4638297009492</v>
+        <f t="shared" si="28"/>
+        <v>1699.6334081929349</v>
       </c>
       <c r="AV9" s="1">
-        <f t="shared" si="29"/>
-        <v>1605.3584679979588</v>
+        <f t="shared" si="28"/>
+        <v>1716.6297422748644</v>
       </c>
       <c r="AW9" s="1">
-        <f t="shared" si="29"/>
-        <v>1621.4120526779384</v>
+        <f t="shared" si="28"/>
+        <v>1733.796039697613</v>
       </c>
       <c r="AX9" s="1">
-        <f t="shared" si="29"/>
-        <v>1637.6261732047176</v>
+        <f t="shared" si="28"/>
+        <v>1751.1340000945891</v>
       </c>
     </row>
     <row r="10" spans="2:50" x14ac:dyDescent="0.3">
@@ -2208,20 +2207,19 @@
         <v>549.1</v>
       </c>
       <c r="AA10" s="1">
-        <f>AA6*0.17</f>
-        <v>553.00727999999992</v>
+        <v>593.1</v>
       </c>
       <c r="AB10" s="1">
-        <f t="shared" ref="AB10" si="30">AB6*0.17</f>
-        <v>574.48745999999994</v>
+        <f t="shared" ref="AB10" si="29">AB6*0.17</f>
+        <v>600.05036000000007</v>
       </c>
       <c r="AC10" s="1">
         <f>AC6*0.16</f>
-        <v>557.70880000000011</v>
+        <v>575.22176000000002</v>
       </c>
       <c r="AD10" s="1">
         <f>AD6*0.15</f>
-        <v>548.80469999999991</v>
+        <v>554.12879999999996</v>
       </c>
       <c r="AH10" s="1">
         <v>360.6</v>
@@ -2245,48 +2243,48 @@
         <v>2105.5</v>
       </c>
       <c r="AN10" s="1">
-        <f t="shared" si="3"/>
-        <v>2234.0082400000001</v>
+        <f t="shared" si="2"/>
+        <v>2322.50092</v>
       </c>
       <c r="AO10" s="1">
         <f>AO6*0.15</f>
-        <v>2208.5345444999998</v>
+        <v>2352.0498359999997</v>
       </c>
       <c r="AP10" s="1">
-        <f t="shared" ref="AP10:AX10" si="31">AP6*0.15</f>
-        <v>2334.9186291150004</v>
+        <f t="shared" ref="AP10:AX10" si="30">AP6*0.15</f>
+        <v>2490.6917571600002</v>
       </c>
       <c r="AQ10" s="1">
-        <f t="shared" si="31"/>
-        <v>2439.4432803385507</v>
+        <f t="shared" si="30"/>
+        <v>2605.1352116118001</v>
       </c>
       <c r="AR10" s="1">
-        <f t="shared" si="31"/>
-        <v>2516.5942168155439</v>
+        <f t="shared" si="30"/>
+        <v>2689.2798456620103</v>
       </c>
       <c r="AS10" s="1">
-        <f t="shared" si="31"/>
-        <v>2579.3175643895984</v>
+        <f t="shared" si="30"/>
+        <v>2757.4468206871124</v>
       </c>
       <c r="AT10" s="1">
-        <f t="shared" si="31"/>
-        <v>2622.8776067672429</v>
+        <f t="shared" si="30"/>
+        <v>2804.6755910774505</v>
       </c>
       <c r="AU10" s="1">
-        <f t="shared" si="31"/>
-        <v>2649.1063828349152</v>
+        <f t="shared" si="30"/>
+        <v>2832.7223469882247</v>
       </c>
       <c r="AV10" s="1">
-        <f t="shared" si="31"/>
-        <v>2675.5974466632647</v>
+        <f t="shared" si="30"/>
+        <v>2861.0495704581072</v>
       </c>
       <c r="AW10" s="1">
-        <f t="shared" si="31"/>
-        <v>2702.3534211298975</v>
+        <f t="shared" si="30"/>
+        <v>2889.6600661626881</v>
       </c>
       <c r="AX10" s="1">
-        <f t="shared" si="31"/>
-        <v>2729.3769553411962</v>
+        <f t="shared" si="30"/>
+        <v>2918.556666824315</v>
       </c>
     </row>
     <row r="11" spans="2:50" x14ac:dyDescent="0.3">
@@ -2333,19 +2331,18 @@
         <v>1035.5</v>
       </c>
       <c r="AA11" s="1">
-        <f>W11*1.05</f>
-        <v>941.43000000000006</v>
+        <v>1096.7</v>
       </c>
       <c r="AB11" s="1">
-        <f t="shared" ref="AB11:AD11" si="32">X11*1.05</f>
+        <f t="shared" ref="AB11:AD11" si="31">X11*1.05</f>
         <v>893.65500000000009</v>
       </c>
       <c r="AC11" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>956.02500000000009</v>
       </c>
       <c r="AD11" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>1087.2750000000001</v>
       </c>
       <c r="AH11" s="1">
@@ -2370,48 +2367,48 @@
         <v>3693.7</v>
       </c>
       <c r="AN11" s="1">
-        <f t="shared" si="3"/>
-        <v>3878.3850000000002</v>
+        <f t="shared" si="2"/>
+        <v>4033.6550000000002</v>
       </c>
       <c r="AO11" s="1">
-        <f t="shared" ref="AO11:AR11" si="33">AN11*1.03</f>
-        <v>3994.7365500000005</v>
+        <f t="shared" ref="AO11:AR11" si="32">AN11*1.03</f>
+        <v>4154.6646500000006</v>
       </c>
       <c r="AP11" s="1">
-        <f t="shared" si="33"/>
-        <v>4114.578646500001</v>
+        <f t="shared" si="32"/>
+        <v>4279.3045895000005</v>
       </c>
       <c r="AQ11" s="1">
-        <f t="shared" si="33"/>
-        <v>4238.0160058950014</v>
+        <f t="shared" si="32"/>
+        <v>4407.6837271850009</v>
       </c>
       <c r="AR11" s="1">
-        <f t="shared" si="33"/>
-        <v>4365.1564860718518</v>
+        <f t="shared" si="32"/>
+        <v>4539.9142390005509</v>
       </c>
       <c r="AS11" s="1">
         <f>AR11*1.02</f>
-        <v>4452.4596157932892</v>
+        <v>4630.7125237805622</v>
       </c>
       <c r="AT11" s="1">
-        <f t="shared" ref="AT11:AX11" si="34">AS11*1.02</f>
-        <v>4541.5088081091553</v>
+        <f t="shared" ref="AT11:AX11" si="33">AS11*1.02</f>
+        <v>4723.3267742561738</v>
       </c>
       <c r="AU11" s="1">
-        <f t="shared" si="34"/>
-        <v>4632.3389842713386</v>
+        <f t="shared" si="33"/>
+        <v>4817.793309741297</v>
       </c>
       <c r="AV11" s="1">
-        <f t="shared" si="34"/>
-        <v>4724.9857639567654</v>
+        <f t="shared" si="33"/>
+        <v>4914.1491759361234</v>
       </c>
       <c r="AW11" s="1">
-        <f t="shared" si="34"/>
-        <v>4819.485479235901</v>
+        <f t="shared" si="33"/>
+        <v>5012.4321594548455</v>
       </c>
       <c r="AX11" s="1">
-        <f t="shared" si="34"/>
-        <v>4915.8751888206189</v>
+        <f t="shared" si="33"/>
+        <v>5112.6808026439421</v>
       </c>
     </row>
     <row r="12" spans="2:50" x14ac:dyDescent="0.3">
@@ -2471,19 +2468,19 @@
         <v>-10.600000000000009</v>
       </c>
       <c r="AA12" s="1">
-        <f>W12*1.02</f>
-        <v>-29.784000000000017</v>
+        <f>131.1-189.3</f>
+        <v>-58.200000000000017</v>
       </c>
       <c r="AB12" s="1">
-        <f t="shared" ref="AB12:AD12" si="35">X12*1.02</f>
+        <f t="shared" ref="AB12:AD12" si="34">X12*1.02</f>
         <v>-38.25</v>
       </c>
       <c r="AC12" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="34"/>
         <v>-43.146000000000015</v>
       </c>
       <c r="AD12" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="34"/>
         <v>-10.812000000000008</v>
       </c>
       <c r="AH12" s="1">
@@ -2511,48 +2508,48 @@
         <v>-119.60000000000004</v>
       </c>
       <c r="AN12" s="1">
-        <f t="shared" si="3"/>
-        <v>-121.99200000000005</v>
+        <f t="shared" si="2"/>
+        <v>-150.40800000000004</v>
       </c>
       <c r="AO12" s="1">
-        <f t="shared" ref="AO12:AX12" si="36">AN12*1.03</f>
-        <v>-125.65176000000005</v>
+        <f t="shared" ref="AO12:AX12" si="35">AN12*1.03</f>
+        <v>-154.92024000000004</v>
       </c>
       <c r="AP12" s="1">
-        <f t="shared" si="36"/>
-        <v>-129.42131280000007</v>
+        <f t="shared" si="35"/>
+        <v>-159.56784720000005</v>
       </c>
       <c r="AQ12" s="1">
-        <f t="shared" si="36"/>
-        <v>-133.30395218400008</v>
+        <f t="shared" si="35"/>
+        <v>-164.35488261600005</v>
       </c>
       <c r="AR12" s="1">
-        <f t="shared" si="36"/>
-        <v>-137.30307074952009</v>
+        <f t="shared" si="35"/>
+        <v>-169.28552909448007</v>
       </c>
       <c r="AS12" s="1">
-        <f t="shared" si="36"/>
-        <v>-141.42216287200569</v>
+        <f t="shared" si="35"/>
+        <v>-174.36409496731449</v>
       </c>
       <c r="AT12" s="1">
-        <f t="shared" si="36"/>
-        <v>-145.66482775816587</v>
+        <f t="shared" si="35"/>
+        <v>-179.59501781633392</v>
       </c>
       <c r="AU12" s="1">
-        <f t="shared" si="36"/>
-        <v>-150.03477259091085</v>
+        <f t="shared" si="35"/>
+        <v>-184.98286835082394</v>
       </c>
       <c r="AV12" s="1">
-        <f t="shared" si="36"/>
-        <v>-154.53581576863817</v>
+        <f t="shared" si="35"/>
+        <v>-190.53235440134867</v>
       </c>
       <c r="AW12" s="1">
-        <f t="shared" si="36"/>
-        <v>-159.17189024169733</v>
+        <f t="shared" si="35"/>
+        <v>-196.24832503338914</v>
       </c>
       <c r="AX12" s="1">
-        <f t="shared" si="36"/>
-        <v>-163.94704694894824</v>
+        <f t="shared" si="35"/>
+        <v>-202.1357747843908</v>
       </c>
     </row>
     <row r="13" spans="2:50" x14ac:dyDescent="0.3">
@@ -2575,136 +2572,136 @@
       <c r="M13" s="7"/>
       <c r="N13" s="7"/>
       <c r="O13" s="9">
-        <f t="shared" ref="O13:W13" si="37">O8-SUM(O9:O12)</f>
+        <f t="shared" ref="O13:W13" si="36">O8-SUM(O9:O12)</f>
         <v>-289</v>
       </c>
       <c r="P13" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>-482.10000000000014</v>
       </c>
       <c r="Q13" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>247.79999999999995</v>
       </c>
       <c r="R13" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>139.79999999999995</v>
       </c>
       <c r="S13" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>307.79999999999995</v>
       </c>
       <c r="T13" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>423.19999999999982</v>
       </c>
       <c r="U13" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>504.10000000000014</v>
       </c>
       <c r="V13" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>740</v>
       </c>
       <c r="W13" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>483.59999999999968</v>
       </c>
       <c r="X13" s="9">
-        <f t="shared" ref="X13" si="38">X8-SUM(X9:X12)</f>
+        <f t="shared" ref="X13" si="37">X8-SUM(X9:X12)</f>
         <v>652.09999999999991</v>
       </c>
       <c r="Y13" s="9">
-        <f t="shared" ref="Y13" si="39">Y8-SUM(Y9:Y12)</f>
+        <f t="shared" ref="Y13" si="38">Y8-SUM(Y9:Y12)</f>
         <v>669.7</v>
       </c>
       <c r="Z13" s="9">
-        <f t="shared" ref="Z13:AD13" si="40">Z8-SUM(Z9:Z12)</f>
+        <f t="shared" ref="Z13:AD13" si="39">Z8-SUM(Z9:Z12)</f>
         <v>734.59999999999945</v>
       </c>
       <c r="AA13" s="9">
+        <f t="shared" si="39"/>
+        <v>637.29999999999973</v>
+      </c>
+      <c r="AB13" s="9">
+        <f t="shared" si="39"/>
+        <v>803.55775999999969</v>
+      </c>
+      <c r="AC13" s="9">
+        <f t="shared" si="39"/>
+        <v>848.7376399999996</v>
+      </c>
+      <c r="AD13" s="9">
+        <f t="shared" si="39"/>
+        <v>807.57492000000002</v>
+      </c>
+      <c r="AH13" s="9">
+        <f t="shared" ref="AH13:AM13" si="40">AH8-SUM(AH9:AH12)</f>
+        <v>1091.5999999999997</v>
+      </c>
+      <c r="AI13" s="9">
         <f t="shared" si="40"/>
-        <v>617.25647999999978</v>
-      </c>
-      <c r="AB13" s="9">
+        <v>1134.5999999999997</v>
+      </c>
+      <c r="AJ13" s="9">
         <f t="shared" si="40"/>
-        <v>732.88385999999969</v>
-      </c>
-      <c r="AC13" s="9">
+        <v>-1435</v>
+      </c>
+      <c r="AK13" s="9">
         <f t="shared" si="40"/>
-        <v>795.10419999999999</v>
-      </c>
-      <c r="AD13" s="9">
+        <v>-383.49999999999909</v>
+      </c>
+      <c r="AL13" s="9">
         <f t="shared" si="40"/>
-        <v>789.47297999999978</v>
-      </c>
-      <c r="AH13" s="9">
-        <f t="shared" ref="AH13:AM13" si="41">AH8-SUM(AH9:AH12)</f>
-        <v>1091.5999999999997</v>
-      </c>
-      <c r="AI13" s="9">
-        <f t="shared" si="41"/>
-        <v>1134.5999999999997</v>
-      </c>
-      <c r="AJ13" s="9">
-        <f t="shared" si="41"/>
-        <v>-1435</v>
-      </c>
-      <c r="AK13" s="9">
-        <f t="shared" si="41"/>
-        <v>-383.49999999999909</v>
-      </c>
-      <c r="AL13" s="9">
-        <f t="shared" si="41"/>
         <v>1975.1000000000013</v>
       </c>
       <c r="AM13" s="9">
-        <f t="shared" si="41"/>
+        <f t="shared" si="40"/>
         <v>2540.0000000000009</v>
       </c>
       <c r="AN13" s="9">
-        <f t="shared" ref="AN13" si="42">AN8-SUM(AN9:AN12)</f>
-        <v>2934.7175200000001</v>
+        <f t="shared" ref="AN13" si="41">AN8-SUM(AN9:AN12)</f>
+        <v>3097.170320000002</v>
       </c>
       <c r="AO13" s="9">
-        <f t="shared" ref="AO13" si="43">AO8-SUM(AO9:AO12)</f>
-        <v>3492.6970249999986</v>
+        <f t="shared" ref="AO13" si="42">AO8-SUM(AO9:AO12)</f>
+        <v>3840.4217099999996</v>
       </c>
       <c r="AP13" s="9">
-        <f t="shared" ref="AP13" si="44">AP8-SUM(AP9:AP12)</f>
-        <v>3797.9047633500004</v>
+        <f t="shared" ref="AP13" si="43">AP8-SUM(AP9:AP12)</f>
+        <v>4182.5691149000013</v>
       </c>
       <c r="AQ13" s="9">
-        <f t="shared" ref="AQ13" si="45">AQ8-SUM(AQ9:AQ12)</f>
-        <v>4026.7655474174999</v>
+        <f t="shared" ref="AQ13" si="44">AQ8-SUM(AQ9:AQ12)</f>
+        <v>4440.4551941370009</v>
       </c>
       <c r="AR13" s="9">
-        <f t="shared" ref="AR13" si="46">AR8-SUM(AR9:AR12)</f>
-        <v>4160.7939740628153</v>
+        <f t="shared" ref="AR13" si="45">AR8-SUM(AR9:AR12)</f>
+        <v>4593.6374423006309</v>
       </c>
       <c r="AS13" s="9">
-        <f t="shared" ref="AS13" si="47">AS8-SUM(AS9:AS12)</f>
-        <v>4286.6877617107111</v>
+        <f t="shared" ref="AS13" si="46">AS8-SUM(AS9:AS12)</f>
+        <v>4735.140973477126</v>
       </c>
       <c r="AT13" s="9">
-        <f t="shared" ref="AT13" si="48">AT8-SUM(AT9:AT12)</f>
-        <v>4347.0813755398194</v>
+        <f t="shared" ref="AT13" si="47">AT8-SUM(AT9:AT12)</f>
+        <v>4805.1868804849964</v>
       </c>
       <c r="AU13" s="9">
-        <f t="shared" ref="AU13" si="49">AU8-SUM(AU9:AU12)</f>
-        <v>4348.0503977692897</v>
+        <f t="shared" ref="AU13" si="48">AU8-SUM(AU9:AU12)</f>
+        <v>4809.5973819036099</v>
       </c>
       <c r="AV13" s="9">
-        <f t="shared" ref="AV13" si="50">AV8-SUM(AV9:AV12)</f>
-        <v>4348.2082073560869</v>
+        <f t="shared" ref="AV13" si="49">AV8-SUM(AV9:AV12)</f>
+        <v>4813.2150799922492</v>
       </c>
       <c r="AW13" s="9">
-        <f t="shared" ref="AW13" si="51">AW8-SUM(AW9:AW12)</f>
-        <v>4347.5311481054541</v>
+        <f t="shared" ref="AW13" si="50">AW8-SUM(AW9:AW12)</f>
+        <v>4816.0163861208384</v>
       </c>
       <c r="AX13" s="9">
-        <f t="shared" ref="AX13" si="52">AX8-SUM(AX9:AX12)</f>
-        <v>4345.9950425989828</v>
+        <f t="shared" ref="AX13" si="51">AX8-SUM(AX9:AX12)</f>
+        <v>4817.9771948881662</v>
       </c>
     </row>
     <row r="14" spans="2:50" x14ac:dyDescent="0.3">
@@ -2752,7 +2749,7 @@
         <v>3557.9</v>
       </c>
       <c r="AA14" s="1">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="AB14" s="1">
         <v>0</v>
@@ -2785,8 +2782,8 @@
         <v>3557.6</v>
       </c>
       <c r="AN14" s="1">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>-0.4</v>
       </c>
       <c r="AO14" s="1">
         <v>0</v>
@@ -2839,136 +2836,136 @@
       <c r="M15" s="7"/>
       <c r="N15" s="7"/>
       <c r="O15" s="9">
-        <f t="shared" ref="O15:W15" si="53">O13-O14</f>
+        <f t="shared" ref="O15:W15" si="52">O13-O14</f>
         <v>-289.7</v>
       </c>
       <c r="P15" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="52"/>
         <v>-483.40000000000015</v>
       </c>
       <c r="Q15" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="52"/>
         <v>246.59999999999997</v>
       </c>
       <c r="R15" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="52"/>
         <v>139.49999999999994</v>
       </c>
       <c r="S15" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="52"/>
         <v>306.79999999999995</v>
       </c>
       <c r="T15" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="52"/>
         <v>422.39999999999981</v>
       </c>
       <c r="U15" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="52"/>
         <v>503.50000000000011</v>
       </c>
       <c r="V15" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="52"/>
         <v>738.3</v>
       </c>
       <c r="W15" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="52"/>
         <v>483.89999999999969</v>
       </c>
       <c r="X15" s="9">
-        <f t="shared" ref="X15" si="54">X13-X14</f>
+        <f t="shared" ref="X15" si="53">X13-X14</f>
         <v>651.69999999999993</v>
       </c>
       <c r="Y15" s="9">
-        <f t="shared" ref="Y15" si="55">Y13-Y14</f>
+        <f t="shared" ref="Y15" si="54">Y13-Y14</f>
         <v>670.1</v>
       </c>
       <c r="Z15" s="9">
-        <f t="shared" ref="Z15:AD15" si="56">Z13-Z14</f>
+        <f t="shared" ref="Z15:AD15" si="55">Z13-Z14</f>
         <v>-2823.3000000000006</v>
       </c>
       <c r="AA15" s="9">
+        <f t="shared" si="55"/>
+        <v>637.6999999999997</v>
+      </c>
+      <c r="AB15" s="9">
+        <f t="shared" si="55"/>
+        <v>803.55775999999969</v>
+      </c>
+      <c r="AC15" s="9">
+        <f t="shared" si="55"/>
+        <v>848.7376399999996</v>
+      </c>
+      <c r="AD15" s="9">
+        <f t="shared" si="55"/>
+        <v>807.57492000000002</v>
+      </c>
+      <c r="AH15" s="9">
+        <f t="shared" ref="AH15:AN15" si="56">AH13-AH14</f>
+        <v>1090.7999999999997</v>
+      </c>
+      <c r="AI15" s="9">
         <f t="shared" si="56"/>
-        <v>617.25647999999978</v>
-      </c>
-      <c r="AB15" s="9">
+        <v>1127.6999999999996</v>
+      </c>
+      <c r="AJ15" s="9">
         <f t="shared" si="56"/>
-        <v>732.88385999999969</v>
-      </c>
-      <c r="AC15" s="9">
+        <v>-1445.4</v>
+      </c>
+      <c r="AK15" s="9">
         <f t="shared" si="56"/>
-        <v>795.10419999999999</v>
-      </c>
-      <c r="AD15" s="9">
+        <v>-386.99999999999909</v>
+      </c>
+      <c r="AL15" s="9">
         <f t="shared" si="56"/>
-        <v>789.47297999999978</v>
-      </c>
-      <c r="AH15" s="9">
-        <f t="shared" ref="AH15:AN15" si="57">AH13-AH14</f>
-        <v>1090.7999999999997</v>
-      </c>
-      <c r="AI15" s="9">
-        <f t="shared" si="57"/>
-        <v>1127.6999999999996</v>
-      </c>
-      <c r="AJ15" s="9">
-        <f t="shared" si="57"/>
-        <v>-1445.4</v>
-      </c>
-      <c r="AK15" s="9">
-        <f t="shared" si="57"/>
-        <v>-386.99999999999909</v>
-      </c>
-      <c r="AL15" s="9">
-        <f t="shared" si="57"/>
         <v>1971.0000000000014</v>
       </c>
       <c r="AM15" s="9">
-        <f t="shared" si="57"/>
+        <f t="shared" si="56"/>
         <v>-1017.599999999999</v>
       </c>
       <c r="AN15" s="9">
-        <f t="shared" si="57"/>
-        <v>2934.7175200000001</v>
+        <f t="shared" si="56"/>
+        <v>3097.5703200000021</v>
       </c>
       <c r="AO15" s="9">
-        <f t="shared" ref="AO15" si="58">AO13-AO14</f>
-        <v>3492.6970249999986</v>
+        <f t="shared" ref="AO15" si="57">AO13-AO14</f>
+        <v>3840.4217099999996</v>
       </c>
       <c r="AP15" s="9">
-        <f t="shared" ref="AP15" si="59">AP13-AP14</f>
-        <v>3797.9047633500004</v>
+        <f t="shared" ref="AP15" si="58">AP13-AP14</f>
+        <v>4182.5691149000013</v>
       </c>
       <c r="AQ15" s="9">
-        <f t="shared" ref="AQ15" si="60">AQ13-AQ14</f>
-        <v>4026.7655474174999</v>
+        <f t="shared" ref="AQ15" si="59">AQ13-AQ14</f>
+        <v>4440.4551941370009</v>
       </c>
       <c r="AR15" s="9">
-        <f t="shared" ref="AR15" si="61">AR13-AR14</f>
-        <v>4160.7939740628153</v>
+        <f t="shared" ref="AR15" si="60">AR13-AR14</f>
+        <v>4593.6374423006309</v>
       </c>
       <c r="AS15" s="9">
-        <f t="shared" ref="AS15" si="62">AS13-AS14</f>
-        <v>4286.6877617107111</v>
+        <f t="shared" ref="AS15" si="61">AS13-AS14</f>
+        <v>4735.140973477126</v>
       </c>
       <c r="AT15" s="9">
-        <f t="shared" ref="AT15" si="63">AT13-AT14</f>
-        <v>4347.0813755398194</v>
+        <f t="shared" ref="AT15" si="62">AT13-AT14</f>
+        <v>4805.1868804849964</v>
       </c>
       <c r="AU15" s="9">
-        <f t="shared" ref="AU15" si="64">AU13-AU14</f>
-        <v>4348.0503977692897</v>
+        <f t="shared" ref="AU15" si="63">AU13-AU14</f>
+        <v>4809.5973819036099</v>
       </c>
       <c r="AV15" s="9">
-        <f t="shared" ref="AV15" si="65">AV13-AV14</f>
-        <v>4348.2082073560869</v>
+        <f t="shared" ref="AV15" si="64">AV13-AV14</f>
+        <v>4813.2150799922492</v>
       </c>
       <c r="AW15" s="9">
-        <f t="shared" ref="AW15" si="66">AW13-AW14</f>
-        <v>4347.5311481054541</v>
+        <f t="shared" ref="AW15" si="65">AW13-AW14</f>
+        <v>4816.0163861208384</v>
       </c>
       <c r="AX15" s="9">
-        <f t="shared" ref="AX15" si="67">AX13-AX14</f>
-        <v>4345.9950425989828</v>
+        <f t="shared" ref="AX15" si="66">AX13-AX14</f>
+        <v>4817.9771948881662</v>
       </c>
     </row>
     <row r="16" spans="2:50" x14ac:dyDescent="0.3">
@@ -3019,20 +3016,20 @@
         <v>98.6</v>
       </c>
       <c r="AA16" s="1">
-        <f>AA15*0.2</f>
-        <v>123.45129599999996</v>
+        <f>133-12.2</f>
+        <v>120.8</v>
       </c>
       <c r="AB16" s="1">
-        <f t="shared" ref="AB16:AD16" si="68">AB15*0.2</f>
-        <v>146.57677199999995</v>
+        <f t="shared" ref="AB16:AD16" si="67">AB15*0.2</f>
+        <v>160.71155199999995</v>
       </c>
       <c r="AC16" s="1">
-        <f t="shared" si="68"/>
-        <v>159.02084000000002</v>
+        <f t="shared" si="67"/>
+        <v>169.74752799999993</v>
       </c>
       <c r="AD16" s="1">
-        <f t="shared" si="68"/>
-        <v>157.89459599999998</v>
+        <f t="shared" si="67"/>
+        <v>161.51498400000003</v>
       </c>
       <c r="AH16" s="1">
         <f>217.2+69.2</f>
@@ -3059,48 +3056,48 @@
         <v>489.6</v>
       </c>
       <c r="AN16" s="1">
-        <f t="shared" si="3"/>
-        <v>586.94350399999985</v>
+        <f t="shared" si="2"/>
+        <v>612.77406399999995</v>
       </c>
       <c r="AO16" s="1">
         <f>AO15*0.2</f>
-        <v>698.53940499999976</v>
+        <v>768.08434199999999</v>
       </c>
       <c r="AP16" s="1">
-        <f t="shared" ref="AP16:AX16" si="69">AP15*0.2</f>
-        <v>759.5809526700001</v>
+        <f t="shared" ref="AP16:AX16" si="68">AP15*0.2</f>
+        <v>836.51382298000033</v>
       </c>
       <c r="AQ16" s="1">
-        <f t="shared" si="69"/>
-        <v>805.35310948350002</v>
+        <f t="shared" si="68"/>
+        <v>888.09103882740021</v>
       </c>
       <c r="AR16" s="1">
-        <f t="shared" si="69"/>
-        <v>832.15879481256309</v>
+        <f t="shared" si="68"/>
+        <v>918.72748846012621</v>
       </c>
       <c r="AS16" s="1">
-        <f t="shared" si="69"/>
-        <v>857.33755234214232</v>
+        <f t="shared" si="68"/>
+        <v>947.02819469542521</v>
       </c>
       <c r="AT16" s="1">
-        <f t="shared" si="69"/>
-        <v>869.41627510796388</v>
+        <f t="shared" si="68"/>
+        <v>961.03737609699931</v>
       </c>
       <c r="AU16" s="1">
-        <f t="shared" si="69"/>
-        <v>869.61007955385799</v>
+        <f t="shared" si="68"/>
+        <v>961.91947638072202</v>
       </c>
       <c r="AV16" s="1">
-        <f t="shared" si="69"/>
-        <v>869.64164147121744</v>
+        <f t="shared" si="68"/>
+        <v>962.64301599844987</v>
       </c>
       <c r="AW16" s="1">
-        <f t="shared" si="69"/>
-        <v>869.50622962109082</v>
+        <f t="shared" si="68"/>
+        <v>963.20327722416778</v>
       </c>
       <c r="AX16" s="1">
-        <f t="shared" si="69"/>
-        <v>869.19900851979662</v>
+        <f t="shared" si="68"/>
+        <v>963.59543897763331</v>
       </c>
     </row>
     <row r="17" spans="2:148" x14ac:dyDescent="0.3">
@@ -3147,7 +3144,7 @@
         <v>0</v>
       </c>
       <c r="AA17" s="1">
-        <v>0</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="AB17" s="1">
         <v>0</v>
@@ -3180,48 +3177,48 @@
         <v>6</v>
       </c>
       <c r="AN17" s="1">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>2.2999999999999998</v>
       </c>
       <c r="AO17" s="1">
-        <f t="shared" ref="AO17:AX17" si="70">AO15*0.002</f>
-        <v>6.9853940499999974</v>
+        <f t="shared" ref="AO17:AX17" si="69">AO15*0.002</f>
+        <v>7.6808434199999995</v>
       </c>
       <c r="AP17" s="1">
-        <f t="shared" si="70"/>
-        <v>7.595809526700001</v>
+        <f t="shared" si="69"/>
+        <v>8.365138229800003</v>
       </c>
       <c r="AQ17" s="1">
-        <f t="shared" si="70"/>
-        <v>8.0535310948349998</v>
+        <f t="shared" si="69"/>
+        <v>8.8809103882740015</v>
       </c>
       <c r="AR17" s="1">
-        <f t="shared" si="70"/>
-        <v>8.3215879481256305</v>
+        <f t="shared" si="69"/>
+        <v>9.187274884601262</v>
       </c>
       <c r="AS17" s="1">
-        <f t="shared" si="70"/>
-        <v>8.5733755234214222</v>
+        <f t="shared" si="69"/>
+        <v>9.4702819469542519</v>
       </c>
       <c r="AT17" s="1">
-        <f t="shared" si="70"/>
-        <v>8.6941627510796398</v>
+        <f t="shared" si="69"/>
+        <v>9.6103737609699937</v>
       </c>
       <c r="AU17" s="1">
-        <f t="shared" si="70"/>
-        <v>8.6961007955385803</v>
+        <f t="shared" si="69"/>
+        <v>9.6191947638072204</v>
       </c>
       <c r="AV17" s="1">
-        <f t="shared" si="70"/>
-        <v>8.6964164147121732</v>
+        <f t="shared" si="69"/>
+        <v>9.6264301599844995</v>
       </c>
       <c r="AW17" s="1">
-        <f t="shared" si="70"/>
-        <v>8.6950622962109083</v>
+        <f t="shared" si="69"/>
+        <v>9.6320327722416774</v>
       </c>
       <c r="AX17" s="1">
-        <f t="shared" si="70"/>
-        <v>8.6919900851979666</v>
+        <f t="shared" si="69"/>
+        <v>9.635954389776332</v>
       </c>
     </row>
     <row r="18" spans="2:148" x14ac:dyDescent="0.3">
@@ -3244,528 +3241,528 @@
       <c r="M18" s="7"/>
       <c r="N18" s="7"/>
       <c r="O18" s="9">
-        <f t="shared" ref="O18:W18" si="71">O15-O16-O17</f>
+        <f t="shared" ref="O18:W18" si="70">O15-O16-O17</f>
         <v>-313.09999999999997</v>
       </c>
       <c r="P18" s="9">
-        <f t="shared" si="71"/>
+        <f t="shared" si="70"/>
         <v>-487.40000000000015</v>
       </c>
       <c r="Q18" s="9">
-        <f t="shared" si="71"/>
+        <f t="shared" si="70"/>
         <v>202.49999999999997</v>
       </c>
       <c r="R18" s="9">
-        <f t="shared" si="71"/>
+        <f t="shared" si="70"/>
         <v>78.899999999999949</v>
       </c>
       <c r="S18" s="9">
-        <f t="shared" si="71"/>
+        <f t="shared" si="70"/>
         <v>225.69999999999996</v>
       </c>
       <c r="T18" s="9">
-        <f t="shared" si="71"/>
+        <f t="shared" si="70"/>
         <v>305.49999999999983</v>
       </c>
       <c r="U18" s="9">
-        <f t="shared" si="71"/>
+        <f t="shared" si="70"/>
         <v>408.7000000000001</v>
       </c>
       <c r="V18" s="9">
-        <f t="shared" si="71"/>
+        <f t="shared" si="70"/>
         <v>656.3</v>
       </c>
       <c r="W18" s="9">
-        <f t="shared" si="71"/>
+        <f t="shared" si="70"/>
         <v>372.79999999999967</v>
       </c>
       <c r="X18" s="9">
-        <f t="shared" ref="X18" si="72">X15-X16-X17</f>
+        <f t="shared" ref="X18" si="71">X15-X16-X17</f>
         <v>496.09999999999997</v>
       </c>
       <c r="Y18" s="9">
-        <f t="shared" ref="Y18" si="73">Y15-Y16-Y17</f>
+        <f t="shared" ref="Y18" si="72">Y15-Y16-Y17</f>
         <v>539.79999999999995</v>
       </c>
       <c r="Z18" s="9">
-        <f t="shared" ref="Z18:AD18" si="74">Z15-Z16-Z17</f>
+        <f t="shared" ref="Z18:AD18" si="73">Z15-Z16-Z17</f>
         <v>-2921.9000000000005</v>
       </c>
       <c r="AA18" s="9">
+        <f t="shared" si="73"/>
+        <v>514.5999999999998</v>
+      </c>
+      <c r="AB18" s="9">
+        <f t="shared" si="73"/>
+        <v>642.84620799999971</v>
+      </c>
+      <c r="AC18" s="9">
+        <f t="shared" si="73"/>
+        <v>678.99011199999973</v>
+      </c>
+      <c r="AD18" s="9">
+        <f t="shared" si="73"/>
+        <v>646.05993599999999</v>
+      </c>
+      <c r="AH18" s="9">
+        <f t="shared" ref="AH18:AN18" si="74">AH15-AH16-AH17</f>
+        <v>803.39999999999975</v>
+      </c>
+      <c r="AI18" s="9">
         <f t="shared" si="74"/>
-        <v>493.80518399999983</v>
-      </c>
-      <c r="AB18" s="9">
+        <v>854.09999999999957</v>
+      </c>
+      <c r="AJ18" s="9">
         <f t="shared" si="74"/>
-        <v>586.30708799999979</v>
-      </c>
-      <c r="AC18" s="9">
+        <v>-1358.7</v>
+      </c>
+      <c r="AK18" s="9">
         <f t="shared" si="74"/>
-        <v>636.08335999999997</v>
-      </c>
-      <c r="AD18" s="9">
+        <v>-519.09999999999911</v>
+      </c>
+      <c r="AL18" s="9">
         <f t="shared" si="74"/>
-        <v>631.5783839999998</v>
-      </c>
-      <c r="AH18" s="9">
-        <f t="shared" ref="AH18:AN18" si="75">AH15-AH16-AH17</f>
-        <v>803.39999999999975</v>
-      </c>
-      <c r="AI18" s="9">
-        <f t="shared" si="75"/>
-        <v>854.09999999999957</v>
-      </c>
-      <c r="AJ18" s="9">
-        <f t="shared" si="75"/>
-        <v>-1358.7</v>
-      </c>
-      <c r="AK18" s="9">
-        <f t="shared" si="75"/>
-        <v>-519.09999999999911</v>
-      </c>
-      <c r="AL18" s="9">
-        <f t="shared" si="75"/>
         <v>1596.2000000000014</v>
       </c>
       <c r="AM18" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="74"/>
         <v>-1513.1999999999989</v>
       </c>
       <c r="AN18" s="9">
-        <f t="shared" si="75"/>
-        <v>2347.7740160000003</v>
+        <f t="shared" si="74"/>
+        <v>2482.4962560000022</v>
       </c>
       <c r="AO18" s="9">
-        <f t="shared" ref="AO18" si="76">AO15-AO16-AO17</f>
-        <v>2787.1722259499988</v>
+        <f t="shared" ref="AO18" si="75">AO15-AO16-AO17</f>
+        <v>3064.6565245799993</v>
       </c>
       <c r="AP18" s="9">
-        <f t="shared" ref="AP18" si="77">AP15-AP16-AP17</f>
-        <v>3030.7280011533003</v>
+        <f t="shared" ref="AP18" si="76">AP15-AP16-AP17</f>
+        <v>3337.690153690201</v>
       </c>
       <c r="AQ18" s="9">
-        <f t="shared" ref="AQ18" si="78">AQ15-AQ16-AQ17</f>
-        <v>3213.3589068391652</v>
+        <f t="shared" ref="AQ18" si="77">AQ15-AQ16-AQ17</f>
+        <v>3543.4832449213268</v>
       </c>
       <c r="AR18" s="9">
-        <f t="shared" ref="AR18" si="79">AR15-AR16-AR17</f>
-        <v>3320.3135913021265</v>
+        <f t="shared" ref="AR18" si="78">AR15-AR16-AR17</f>
+        <v>3665.7226789559036</v>
       </c>
       <c r="AS18" s="9">
-        <f t="shared" ref="AS18" si="80">AS15-AS16-AS17</f>
-        <v>3420.7768338451474</v>
+        <f t="shared" ref="AS18" si="79">AS15-AS16-AS17</f>
+        <v>3778.6424968347465</v>
       </c>
       <c r="AT18" s="9">
-        <f t="shared" ref="AT18" si="81">AT15-AT16-AT17</f>
-        <v>3468.9709376807759</v>
+        <f t="shared" ref="AT18" si="80">AT15-AT16-AT17</f>
+        <v>3834.5391306270271</v>
       </c>
       <c r="AU18" s="9">
-        <f t="shared" ref="AU18" si="82">AU15-AU16-AU17</f>
-        <v>3469.7442174198932</v>
+        <f t="shared" ref="AU18" si="81">AU15-AU16-AU17</f>
+        <v>3838.0587107590809</v>
       </c>
       <c r="AV18" s="9">
-        <f t="shared" ref="AV18" si="83">AV15-AV16-AV17</f>
-        <v>3469.8701494701572</v>
+        <f t="shared" ref="AV18" si="82">AV15-AV16-AV17</f>
+        <v>3840.945633833815</v>
       </c>
       <c r="AW18" s="9">
-        <f t="shared" ref="AW18" si="84">AW15-AW16-AW17</f>
-        <v>3469.3298561881525</v>
+        <f t="shared" ref="AW18" si="83">AW15-AW16-AW17</f>
+        <v>3843.1810761244292</v>
       </c>
       <c r="AX18" s="9">
-        <f t="shared" ref="AX18" si="85">AX15-AX16-AX17</f>
-        <v>3468.1040439939879</v>
+        <f t="shared" ref="AX18" si="84">AX15-AX16-AX17</f>
+        <v>3844.7458015207562</v>
       </c>
       <c r="AY18" s="9">
         <f>AX18*(1+$BC$23)</f>
-        <v>3433.4230035540481</v>
+        <v>3806.2983435055485</v>
       </c>
       <c r="AZ18" s="9">
-        <f t="shared" ref="AZ18:DK18" si="86">AY18*(1+$BC$23)</f>
-        <v>3399.0887735185074</v>
+        <f t="shared" ref="AZ18:DK18" si="85">AY18*(1+$BC$23)</f>
+        <v>3768.2353600704928</v>
       </c>
       <c r="BA18" s="9">
+        <f t="shared" si="85"/>
+        <v>3730.5530064697878</v>
+      </c>
+      <c r="BB18" s="9">
+        <f t="shared" si="85"/>
+        <v>3693.2474764050899</v>
+      </c>
+      <c r="BC18" s="9">
+        <f t="shared" si="85"/>
+        <v>3656.3150016410391</v>
+      </c>
+      <c r="BD18" s="9">
+        <f t="shared" si="85"/>
+        <v>3619.7518516246287</v>
+      </c>
+      <c r="BE18" s="9">
+        <f t="shared" si="85"/>
+        <v>3583.5543331083823</v>
+      </c>
+      <c r="BF18" s="9">
+        <f t="shared" si="85"/>
+        <v>3547.7187897772983</v>
+      </c>
+      <c r="BG18" s="9">
+        <f t="shared" si="85"/>
+        <v>3512.2416018795252</v>
+      </c>
+      <c r="BH18" s="9">
+        <f t="shared" si="85"/>
+        <v>3477.1191858607299</v>
+      </c>
+      <c r="BI18" s="9">
+        <f t="shared" si="85"/>
+        <v>3442.3479940021225</v>
+      </c>
+      <c r="BJ18" s="9">
+        <f t="shared" si="85"/>
+        <v>3407.924514062101</v>
+      </c>
+      <c r="BK18" s="9">
+        <f t="shared" si="85"/>
+        <v>3373.8452689214801</v>
+      </c>
+      <c r="BL18" s="9">
+        <f t="shared" si="85"/>
+        <v>3340.1068162322654</v>
+      </c>
+      <c r="BM18" s="9">
+        <f t="shared" si="85"/>
+        <v>3306.7057480699427</v>
+      </c>
+      <c r="BN18" s="9">
+        <f t="shared" si="85"/>
+        <v>3273.6386905892432</v>
+      </c>
+      <c r="BO18" s="9">
+        <f t="shared" si="85"/>
+        <v>3240.9023036833505</v>
+      </c>
+      <c r="BP18" s="9">
+        <f t="shared" si="85"/>
+        <v>3208.4932806465172</v>
+      </c>
+      <c r="BQ18" s="9">
+        <f t="shared" si="85"/>
+        <v>3176.4083478400521</v>
+      </c>
+      <c r="BR18" s="9">
+        <f t="shared" si="85"/>
+        <v>3144.6442643616515</v>
+      </c>
+      <c r="BS18" s="9">
+        <f t="shared" si="85"/>
+        <v>3113.1978217180349</v>
+      </c>
+      <c r="BT18" s="9">
+        <f t="shared" si="85"/>
+        <v>3082.0658435008545</v>
+      </c>
+      <c r="BU18" s="9">
+        <f t="shared" si="85"/>
+        <v>3051.2451850658458</v>
+      </c>
+      <c r="BV18" s="9">
+        <f t="shared" si="85"/>
+        <v>3020.7327332151872</v>
+      </c>
+      <c r="BW18" s="9">
+        <f t="shared" si="85"/>
+        <v>2990.5254058830351</v>
+      </c>
+      <c r="BX18" s="9">
+        <f t="shared" si="85"/>
+        <v>2960.6201518242046</v>
+      </c>
+      <c r="BY18" s="9">
+        <f t="shared" si="85"/>
+        <v>2931.0139503059627</v>
+      </c>
+      <c r="BZ18" s="9">
+        <f t="shared" si="85"/>
+        <v>2901.7038108029028</v>
+      </c>
+      <c r="CA18" s="9">
+        <f t="shared" si="85"/>
+        <v>2872.686772694874</v>
+      </c>
+      <c r="CB18" s="9">
+        <f t="shared" si="85"/>
+        <v>2843.959904967925</v>
+      </c>
+      <c r="CC18" s="9">
+        <f t="shared" si="85"/>
+        <v>2815.5203059182459</v>
+      </c>
+      <c r="CD18" s="9">
+        <f t="shared" si="85"/>
+        <v>2787.3651028590634</v>
+      </c>
+      <c r="CE18" s="9">
+        <f t="shared" si="85"/>
+        <v>2759.4914518304727</v>
+      </c>
+      <c r="CF18" s="9">
+        <f t="shared" si="85"/>
+        <v>2731.8965373121678</v>
+      </c>
+      <c r="CG18" s="9">
+        <f t="shared" si="85"/>
+        <v>2704.5775719390463</v>
+      </c>
+      <c r="CH18" s="9">
+        <f t="shared" si="85"/>
+        <v>2677.5317962196559</v>
+      </c>
+      <c r="CI18" s="9">
+        <f t="shared" si="85"/>
+        <v>2650.7564782574595</v>
+      </c>
+      <c r="CJ18" s="9">
+        <f t="shared" si="85"/>
+        <v>2624.2489134748848</v>
+      </c>
+      <c r="CK18" s="9">
+        <f t="shared" si="85"/>
+        <v>2598.0064243401362</v>
+      </c>
+      <c r="CL18" s="9">
+        <f t="shared" si="85"/>
+        <v>2572.0263600967346</v>
+      </c>
+      <c r="CM18" s="9">
+        <f t="shared" si="85"/>
+        <v>2546.3060964957672</v>
+      </c>
+      <c r="CN18" s="9">
+        <f t="shared" si="85"/>
+        <v>2520.8430355308096</v>
+      </c>
+      <c r="CO18" s="9">
+        <f t="shared" si="85"/>
+        <v>2495.6346051755013</v>
+      </c>
+      <c r="CP18" s="9">
+        <f t="shared" si="85"/>
+        <v>2470.6782591237461</v>
+      </c>
+      <c r="CQ18" s="9">
+        <f t="shared" si="85"/>
+        <v>2445.9714765325084</v>
+      </c>
+      <c r="CR18" s="9">
+        <f t="shared" si="85"/>
+        <v>2421.5117617671831</v>
+      </c>
+      <c r="CS18" s="9">
+        <f t="shared" si="85"/>
+        <v>2397.2966441495114</v>
+      </c>
+      <c r="CT18" s="9">
+        <f t="shared" si="85"/>
+        <v>2373.3236777080165</v>
+      </c>
+      <c r="CU18" s="9">
+        <f t="shared" si="85"/>
+        <v>2349.5904409309364</v>
+      </c>
+      <c r="CV18" s="9">
+        <f t="shared" si="85"/>
+        <v>2326.0945365216271</v>
+      </c>
+      <c r="CW18" s="9">
+        <f t="shared" si="85"/>
+        <v>2302.8335911564109</v>
+      </c>
+      <c r="CX18" s="9">
+        <f t="shared" si="85"/>
+        <v>2279.8052552448466</v>
+      </c>
+      <c r="CY18" s="9">
+        <f t="shared" si="85"/>
+        <v>2257.0072026923981</v>
+      </c>
+      <c r="CZ18" s="9">
+        <f t="shared" si="85"/>
+        <v>2234.4371306654739</v>
+      </c>
+      <c r="DA18" s="9">
+        <f t="shared" si="85"/>
+        <v>2212.092759358819</v>
+      </c>
+      <c r="DB18" s="9">
+        <f t="shared" si="85"/>
+        <v>2189.9718317652309</v>
+      </c>
+      <c r="DC18" s="9">
+        <f t="shared" si="85"/>
+        <v>2168.0721134475784</v>
+      </c>
+      <c r="DD18" s="9">
+        <f t="shared" si="85"/>
+        <v>2146.3913923131026</v>
+      </c>
+      <c r="DE18" s="9">
+        <f t="shared" si="85"/>
+        <v>2124.9274783899714</v>
+      </c>
+      <c r="DF18" s="9">
+        <f t="shared" si="85"/>
+        <v>2103.6782036060717</v>
+      </c>
+      <c r="DG18" s="9">
+        <f t="shared" si="85"/>
+        <v>2082.6414215700111</v>
+      </c>
+      <c r="DH18" s="9">
+        <f t="shared" si="85"/>
+        <v>2061.8150073543111</v>
+      </c>
+      <c r="DI18" s="9">
+        <f t="shared" si="85"/>
+        <v>2041.196857280768</v>
+      </c>
+      <c r="DJ18" s="9">
+        <f t="shared" si="85"/>
+        <v>2020.7848887079604</v>
+      </c>
+      <c r="DK18" s="9">
+        <f t="shared" si="85"/>
+        <v>2000.5770398208808</v>
+      </c>
+      <c r="DL18" s="9">
+        <f t="shared" ref="DL18:ER18" si="86">DK18*(1+$BC$23)</f>
+        <v>1980.571269422672</v>
+      </c>
+      <c r="DM18" s="9">
         <f t="shared" si="86"/>
-        <v>3365.0978857833225</v>
-      </c>
-      <c r="BB18" s="9">
+        <v>1960.7655567284453</v>
+      </c>
+      <c r="DN18" s="9">
         <f t="shared" si="86"/>
-        <v>3331.4469069254892</v>
-      </c>
-      <c r="BC18" s="9">
+        <v>1941.1579011611609</v>
+      </c>
+      <c r="DO18" s="9">
         <f t="shared" si="86"/>
-        <v>3298.1324378562344</v>
-      </c>
-      <c r="BD18" s="9">
+        <v>1921.7463221495493</v>
+      </c>
+      <c r="DP18" s="9">
         <f t="shared" si="86"/>
-        <v>3265.151113477672</v>
-      </c>
-      <c r="BE18" s="9">
+        <v>1902.5288589280538</v>
+      </c>
+      <c r="DQ18" s="9">
         <f t="shared" si="86"/>
-        <v>3232.4996023428953</v>
-      </c>
-      <c r="BF18" s="9">
+        <v>1883.5035703387732</v>
+      </c>
+      <c r="DR18" s="9">
         <f t="shared" si="86"/>
-        <v>3200.1746063194664</v>
-      </c>
-      <c r="BG18" s="9">
+        <v>1864.6685346353854</v>
+      </c>
+      <c r="DS18" s="9">
         <f t="shared" si="86"/>
-        <v>3168.1728602562716</v>
-      </c>
-      <c r="BH18" s="9">
+        <v>1846.0218492890315</v>
+      </c>
+      <c r="DT18" s="9">
         <f t="shared" si="86"/>
-        <v>3136.4911316537091</v>
-      </c>
-      <c r="BI18" s="9">
+        <v>1827.5616307961411</v>
+      </c>
+      <c r="DU18" s="9">
         <f t="shared" si="86"/>
-        <v>3105.1262203371721</v>
-      </c>
-      <c r="BJ18" s="9">
+        <v>1809.2860144881797</v>
+      </c>
+      <c r="DV18" s="9">
         <f t="shared" si="86"/>
-        <v>3074.0749581338005</v>
-      </c>
-      <c r="BK18" s="9">
+        <v>1791.1931543432979</v>
+      </c>
+      <c r="DW18" s="9">
         <f t="shared" si="86"/>
-        <v>3043.3342085524623</v>
-      </c>
-      <c r="BL18" s="9">
+        <v>1773.281222799865</v>
+      </c>
+      <c r="DX18" s="9">
         <f t="shared" si="86"/>
-        <v>3012.9008664669377</v>
-      </c>
-      <c r="BM18" s="9">
+        <v>1755.5484105718663</v>
+      </c>
+      <c r="DY18" s="9">
         <f t="shared" si="86"/>
-        <v>2982.7718578022682</v>
-      </c>
-      <c r="BN18" s="9">
+        <v>1737.9929264661475</v>
+      </c>
+      <c r="DZ18" s="9">
         <f t="shared" si="86"/>
-        <v>2952.9441392242456</v>
-      </c>
-      <c r="BO18" s="9">
+        <v>1720.612997201486</v>
+      </c>
+      <c r="EA18" s="9">
         <f t="shared" si="86"/>
-        <v>2923.4146978320032</v>
-      </c>
-      <c r="BP18" s="9">
+        <v>1703.4068672294711</v>
+      </c>
+      <c r="EB18" s="9">
         <f t="shared" si="86"/>
-        <v>2894.1805508536831</v>
-      </c>
-      <c r="BQ18" s="9">
+        <v>1686.3727985571763</v>
+      </c>
+      <c r="EC18" s="9">
         <f t="shared" si="86"/>
-        <v>2865.2387453451461</v>
-      </c>
-      <c r="BR18" s="9">
+        <v>1669.5090705716045</v>
+      </c>
+      <c r="ED18" s="9">
         <f t="shared" si="86"/>
-        <v>2836.5863578916947</v>
-      </c>
-      <c r="BS18" s="9">
+        <v>1652.8139798658885</v>
+      </c>
+      <c r="EE18" s="9">
         <f t="shared" si="86"/>
-        <v>2808.2204943127776</v>
-      </c>
-      <c r="BT18" s="9">
+        <v>1636.2858400672296</v>
+      </c>
+      <c r="EF18" s="9">
         <f t="shared" si="86"/>
-        <v>2780.13828936965</v>
-      </c>
-      <c r="BU18" s="9">
+        <v>1619.9229816665572</v>
+      </c>
+      <c r="EG18" s="9">
         <f t="shared" si="86"/>
-        <v>2752.3369064759536</v>
-      </c>
-      <c r="BV18" s="9">
+        <v>1603.7237518498916</v>
+      </c>
+      <c r="EH18" s="9">
         <f t="shared" si="86"/>
-        <v>2724.8135374111939</v>
-      </c>
-      <c r="BW18" s="9">
+        <v>1587.6865143313928</v>
+      </c>
+      <c r="EI18" s="9">
         <f t="shared" si="86"/>
-        <v>2697.5654020370821</v>
-      </c>
-      <c r="BX18" s="9">
+        <v>1571.8096491880788</v>
+      </c>
+      <c r="EJ18" s="9">
         <f t="shared" si="86"/>
-        <v>2670.5897480167114</v>
-      </c>
-      <c r="BY18" s="9">
+        <v>1556.0915526961981</v>
+      </c>
+      <c r="EK18" s="9">
         <f t="shared" si="86"/>
-        <v>2643.8838505365443</v>
-      </c>
-      <c r="BZ18" s="9">
+        <v>1540.5306371692361</v>
+      </c>
+      <c r="EL18" s="9">
         <f t="shared" si="86"/>
-        <v>2617.445012031179</v>
-      </c>
-      <c r="CA18" s="9">
+        <v>1525.1253307975437</v>
+      </c>
+      <c r="EM18" s="9">
         <f t="shared" si="86"/>
-        <v>2591.2705619108669</v>
-      </c>
-      <c r="CB18" s="9">
+        <v>1509.8740774895682</v>
+      </c>
+      <c r="EN18" s="9">
         <f t="shared" si="86"/>
-        <v>2565.3578562917583</v>
-      </c>
-      <c r="CC18" s="9">
+        <v>1494.7753367146724</v>
+      </c>
+      <c r="EO18" s="9">
         <f t="shared" si="86"/>
-        <v>2539.7042777288407</v>
-      </c>
-      <c r="CD18" s="9">
+        <v>1479.8275833475257</v>
+      </c>
+      <c r="EP18" s="9">
         <f t="shared" si="86"/>
-        <v>2514.3072349515523</v>
-      </c>
-      <c r="CE18" s="9">
+        <v>1465.0293075140503</v>
+      </c>
+      <c r="EQ18" s="9">
         <f t="shared" si="86"/>
-        <v>2489.1641626020369</v>
-      </c>
-      <c r="CF18" s="9">
+        <v>1450.3790144389097</v>
+      </c>
+      <c r="ER18" s="9">
         <f t="shared" si="86"/>
-        <v>2464.2725209760165</v>
-      </c>
-      <c r="CG18" s="9">
-        <f t="shared" si="86"/>
-        <v>2439.6297957662564</v>
-      </c>
-      <c r="CH18" s="9">
-        <f t="shared" si="86"/>
-        <v>2415.2334978085937</v>
-      </c>
-      <c r="CI18" s="9">
-        <f t="shared" si="86"/>
-        <v>2391.0811628305078</v>
-      </c>
-      <c r="CJ18" s="9">
-        <f t="shared" si="86"/>
-        <v>2367.1703512022027</v>
-      </c>
-      <c r="CK18" s="9">
-        <f t="shared" si="86"/>
-        <v>2343.4986476901809</v>
-      </c>
-      <c r="CL18" s="9">
-        <f t="shared" si="86"/>
-        <v>2320.0636612132789</v>
-      </c>
-      <c r="CM18" s="9">
-        <f t="shared" si="86"/>
-        <v>2296.8630246011462</v>
-      </c>
-      <c r="CN18" s="9">
-        <f t="shared" si="86"/>
-        <v>2273.8943943551349</v>
-      </c>
-      <c r="CO18" s="9">
-        <f t="shared" si="86"/>
-        <v>2251.1554504115834</v>
-      </c>
-      <c r="CP18" s="9">
-        <f t="shared" si="86"/>
-        <v>2228.6438959074676</v>
-      </c>
-      <c r="CQ18" s="9">
-        <f t="shared" si="86"/>
-        <v>2206.3574569483931</v>
-      </c>
-      <c r="CR18" s="9">
-        <f t="shared" si="86"/>
-        <v>2184.2938823789091</v>
-      </c>
-      <c r="CS18" s="9">
-        <f t="shared" si="86"/>
-        <v>2162.4509435551199</v>
-      </c>
-      <c r="CT18" s="9">
-        <f t="shared" si="86"/>
-        <v>2140.8264341195686</v>
-      </c>
-      <c r="CU18" s="9">
-        <f t="shared" si="86"/>
-        <v>2119.4181697783729</v>
-      </c>
-      <c r="CV18" s="9">
-        <f t="shared" si="86"/>
-        <v>2098.2239880805892</v>
-      </c>
-      <c r="CW18" s="9">
-        <f t="shared" si="86"/>
-        <v>2077.2417481997832</v>
-      </c>
-      <c r="CX18" s="9">
-        <f t="shared" si="86"/>
-        <v>2056.4693307177854</v>
-      </c>
-      <c r="CY18" s="9">
-        <f t="shared" si="86"/>
-        <v>2035.9046374106076</v>
-      </c>
-      <c r="CZ18" s="9">
-        <f t="shared" si="86"/>
-        <v>2015.5455910365015</v>
-      </c>
-      <c r="DA18" s="9">
-        <f t="shared" si="86"/>
-        <v>1995.3901351261366</v>
-      </c>
-      <c r="DB18" s="9">
-        <f t="shared" si="86"/>
-        <v>1975.4362337748751</v>
-      </c>
-      <c r="DC18" s="9">
-        <f t="shared" si="86"/>
-        <v>1955.6818714371263</v>
-      </c>
-      <c r="DD18" s="9">
-        <f t="shared" si="86"/>
-        <v>1936.1250527227551</v>
-      </c>
-      <c r="DE18" s="9">
-        <f t="shared" si="86"/>
-        <v>1916.7638021955274</v>
-      </c>
-      <c r="DF18" s="9">
-        <f t="shared" si="86"/>
-        <v>1897.5961641735721</v>
-      </c>
-      <c r="DG18" s="9">
-        <f t="shared" si="86"/>
-        <v>1878.6202025318364</v>
-      </c>
-      <c r="DH18" s="9">
-        <f t="shared" si="86"/>
-        <v>1859.8340005065181</v>
-      </c>
-      <c r="DI18" s="9">
-        <f t="shared" si="86"/>
-        <v>1841.2356605014529</v>
-      </c>
-      <c r="DJ18" s="9">
-        <f t="shared" si="86"/>
-        <v>1822.8233038964383</v>
-      </c>
-      <c r="DK18" s="9">
-        <f t="shared" si="86"/>
-        <v>1804.595070857474</v>
-      </c>
-      <c r="DL18" s="9">
-        <f t="shared" ref="DL18:ER18" si="87">DK18*(1+$BC$23)</f>
-        <v>1786.5491201488992</v>
-      </c>
-      <c r="DM18" s="9">
-        <f t="shared" si="87"/>
-        <v>1768.6836289474102</v>
-      </c>
-      <c r="DN18" s="9">
-        <f t="shared" si="87"/>
-        <v>1750.9967926579361</v>
-      </c>
-      <c r="DO18" s="9">
-        <f t="shared" si="87"/>
-        <v>1733.4868247313568</v>
-      </c>
-      <c r="DP18" s="9">
-        <f t="shared" si="87"/>
-        <v>1716.1519564840432</v>
-      </c>
-      <c r="DQ18" s="9">
-        <f t="shared" si="87"/>
-        <v>1698.9904369192027</v>
-      </c>
-      <c r="DR18" s="9">
-        <f t="shared" si="87"/>
-        <v>1682.0005325500106</v>
-      </c>
-      <c r="DS18" s="9">
-        <f t="shared" si="87"/>
-        <v>1665.1805272245103</v>
-      </c>
-      <c r="DT18" s="9">
-        <f t="shared" si="87"/>
-        <v>1648.5287219522652</v>
-      </c>
-      <c r="DU18" s="9">
-        <f t="shared" si="87"/>
-        <v>1632.0434347327425</v>
-      </c>
-      <c r="DV18" s="9">
-        <f t="shared" si="87"/>
-        <v>1615.7230003854152</v>
-      </c>
-      <c r="DW18" s="9">
-        <f t="shared" si="87"/>
-        <v>1599.5657703815609</v>
-      </c>
-      <c r="DX18" s="9">
-        <f t="shared" si="87"/>
-        <v>1583.5701126777453</v>
-      </c>
-      <c r="DY18" s="9">
-        <f t="shared" si="87"/>
-        <v>1567.7344115509679</v>
-      </c>
-      <c r="DZ18" s="9">
-        <f t="shared" si="87"/>
-        <v>1552.0570674354583</v>
-      </c>
-      <c r="EA18" s="9">
-        <f t="shared" si="87"/>
-        <v>1536.5364967611038</v>
-      </c>
-      <c r="EB18" s="9">
-        <f t="shared" si="87"/>
-        <v>1521.1711317934928</v>
-      </c>
-      <c r="EC18" s="9">
-        <f t="shared" si="87"/>
-        <v>1505.9594204755579</v>
-      </c>
-      <c r="ED18" s="9">
-        <f t="shared" si="87"/>
-        <v>1490.8998262708024</v>
-      </c>
-      <c r="EE18" s="9">
-        <f t="shared" si="87"/>
-        <v>1475.9908280080942</v>
-      </c>
-      <c r="EF18" s="9">
-        <f t="shared" si="87"/>
-        <v>1461.2309197280133</v>
-      </c>
-      <c r="EG18" s="9">
-        <f t="shared" si="87"/>
-        <v>1446.6186105307331</v>
-      </c>
-      <c r="EH18" s="9">
-        <f t="shared" si="87"/>
-        <v>1432.1524244254258</v>
-      </c>
-      <c r="EI18" s="9">
-        <f t="shared" si="87"/>
-        <v>1417.8309001811715</v>
-      </c>
-      <c r="EJ18" s="9">
-        <f t="shared" si="87"/>
-        <v>1403.6525911793597</v>
-      </c>
-      <c r="EK18" s="9">
-        <f t="shared" si="87"/>
-        <v>1389.616065267566</v>
-      </c>
-      <c r="EL18" s="9">
-        <f t="shared" si="87"/>
-        <v>1375.7199046148903</v>
-      </c>
-      <c r="EM18" s="9">
-        <f t="shared" si="87"/>
-        <v>1361.9627055687413</v>
-      </c>
-      <c r="EN18" s="9">
-        <f t="shared" si="87"/>
-        <v>1348.3430785130538</v>
-      </c>
-      <c r="EO18" s="9">
-        <f t="shared" si="87"/>
-        <v>1334.8596477279232</v>
-      </c>
-      <c r="EP18" s="9">
-        <f t="shared" si="87"/>
-        <v>1321.511051250644</v>
-      </c>
-      <c r="EQ18" s="9">
-        <f t="shared" si="87"/>
-        <v>1308.2959407381375</v>
-      </c>
-      <c r="ER18" s="9">
-        <f t="shared" si="87"/>
-        <v>1295.2129813307561</v>
+        <v>1435.8752242945206</v>
       </c>
     </row>
     <row r="19" spans="2:148" x14ac:dyDescent="0.3">
@@ -3812,16 +3809,20 @@
         <v>293.10000000000002</v>
       </c>
       <c r="AA19" s="1">
-        <v>293.10000000000002</v>
+        <f>279.8</f>
+        <v>279.8</v>
       </c>
       <c r="AB19" s="1">
-        <v>293.10000000000002</v>
+        <f>279.8</f>
+        <v>279.8</v>
       </c>
       <c r="AC19" s="1">
-        <v>293.10000000000002</v>
+        <f>279.8</f>
+        <v>279.8</v>
       </c>
       <c r="AD19" s="1">
-        <v>293.10000000000002</v>
+        <f>279.8</f>
+        <v>279.8</v>
       </c>
       <c r="AH19" s="1">
         <v>309</v>
@@ -3842,37 +3843,48 @@
         <v>293.10000000000002</v>
       </c>
       <c r="AN19" s="1">
-        <v>293.10000000000002</v>
+        <f t="shared" ref="AN19:AX19" si="87">279.8</f>
+        <v>279.8</v>
       </c>
       <c r="AO19" s="1">
-        <v>293.10000000000002</v>
+        <f t="shared" si="87"/>
+        <v>279.8</v>
       </c>
       <c r="AP19" s="1">
-        <v>293.10000000000002</v>
+        <f t="shared" si="87"/>
+        <v>279.8</v>
       </c>
       <c r="AQ19" s="1">
-        <v>293.10000000000002</v>
+        <f t="shared" si="87"/>
+        <v>279.8</v>
       </c>
       <c r="AR19" s="1">
-        <v>293.10000000000002</v>
+        <f t="shared" si="87"/>
+        <v>279.8</v>
       </c>
       <c r="AS19" s="1">
-        <v>293.10000000000002</v>
+        <f t="shared" si="87"/>
+        <v>279.8</v>
       </c>
       <c r="AT19" s="1">
-        <v>293.10000000000002</v>
+        <f t="shared" si="87"/>
+        <v>279.8</v>
       </c>
       <c r="AU19" s="1">
-        <v>293.10000000000002</v>
+        <f t="shared" si="87"/>
+        <v>279.8</v>
       </c>
       <c r="AV19" s="1">
-        <v>293.10000000000002</v>
+        <f t="shared" si="87"/>
+        <v>279.8</v>
       </c>
       <c r="AW19" s="1">
-        <v>293.10000000000002</v>
+        <f t="shared" si="87"/>
+        <v>279.8</v>
       </c>
       <c r="AX19" s="1">
-        <v>293.10000000000002</v>
+        <f t="shared" si="87"/>
+        <v>279.8</v>
       </c>
     </row>
     <row r="20" spans="2:148" x14ac:dyDescent="0.3">
@@ -3933,19 +3945,19 @@
       </c>
       <c r="AA20" s="8">
         <f t="shared" si="91"/>
-        <v>1.6847669191402244</v>
+        <v>1.8391708363116503</v>
       </c>
       <c r="AB20" s="8">
         <f t="shared" si="91"/>
-        <v>2.0003653633572149</v>
+        <v>2.2975204002859173</v>
       </c>
       <c r="AC20" s="8">
         <f t="shared" si="91"/>
-        <v>2.1701922893210503</v>
+        <v>2.4266980414581831</v>
       </c>
       <c r="AD20" s="8">
         <f t="shared" si="91"/>
-        <v>2.1548221903787095</v>
+        <v>2.309006204431737</v>
       </c>
       <c r="AH20" s="8">
         <f t="shared" ref="AH20:AN20" si="92">AH18/AH19</f>
@@ -3973,47 +3985,47 @@
       </c>
       <c r="AN20" s="8">
         <f t="shared" si="92"/>
-        <v>8.010146762197202</v>
+        <v>8.872395482487498</v>
       </c>
       <c r="AO20" s="8">
         <f t="shared" ref="AO20" si="93">AO18/AO19</f>
-        <v>9.5092877036847447</v>
+        <v>10.953025463116509</v>
       </c>
       <c r="AP20" s="8">
         <f t="shared" ref="AP20" si="94">AP18/AP19</f>
-        <v>10.340252477493348</v>
+        <v>11.928842579307366</v>
       </c>
       <c r="AQ20" s="8">
         <f t="shared" ref="AQ20" si="95">AQ18/AQ19</f>
-        <v>10.963353486315814</v>
+        <v>12.664343262763856</v>
       </c>
       <c r="AR20" s="8">
         <f t="shared" ref="AR20" si="96">AR18/AR19</f>
-        <v>11.32826199693663</v>
+        <v>13.101224728219812</v>
       </c>
       <c r="AS20" s="8">
         <f t="shared" ref="AS20" si="97">AS18/AS19</f>
-        <v>11.671022974565497</v>
+        <v>13.504798058737478</v>
       </c>
       <c r="AT20" s="8">
         <f t="shared" ref="AT20" si="98">AT18/AT19</f>
-        <v>11.835451851520899</v>
+        <v>13.704571589088731</v>
       </c>
       <c r="AU20" s="8">
         <f t="shared" ref="AU20" si="99">AU18/AU19</f>
-        <v>11.838090131081177</v>
+        <v>13.717150503070339</v>
       </c>
       <c r="AV20" s="8">
         <f t="shared" ref="AV20" si="100">AV18/AV19</f>
-        <v>11.838519786660379</v>
+        <v>13.727468312486829</v>
       </c>
       <c r="AW20" s="8">
         <f t="shared" ref="AW20" si="101">AW18/AW19</f>
-        <v>11.836676411423241</v>
+        <v>13.735457741688453</v>
       </c>
       <c r="AX20" s="8">
         <f t="shared" ref="AX20" si="102">AX18/AX19</f>
-        <v>11.832494179440422</v>
+        <v>13.741050041174969</v>
       </c>
     </row>
     <row r="22" spans="2:148" x14ac:dyDescent="0.3">
@@ -4061,19 +4073,19 @@
       </c>
       <c r="AA22" s="10">
         <f t="shared" ref="AA22:AA25" si="104">AA3/W3-1</f>
-        <v>-4.0000000000000147E-2</v>
+        <v>-8.7223259535876174E-2</v>
       </c>
       <c r="AB22" s="10">
         <f t="shared" ref="AB22:AB25" si="105">AB3/X3-1</f>
-        <v>-4.0000000000000036E-2</v>
+        <v>-8.0000000000000071E-2</v>
       </c>
       <c r="AC22" s="10">
         <f t="shared" ref="AC22:AC25" si="106">AC3/Y3-1</f>
-        <v>-3.0000000000000138E-2</v>
+        <v>-6.0000000000000053E-2</v>
       </c>
       <c r="AD22" s="10">
         <f t="shared" ref="AD22:AD25" si="107">AD3/Z3-1</f>
-        <v>-2.0000000000000018E-2</v>
+        <v>-3.0000000000000027E-2</v>
       </c>
       <c r="AH22" s="10"/>
       <c r="AI22" s="10">
@@ -4098,7 +4110,7 @@
       </c>
       <c r="AN22" s="10">
         <f t="shared" ref="AN22:AX22" si="109">AN3/AM3-1</f>
-        <v>-3.2262126865671648E-2</v>
+        <v>-6.3628109452736337E-2</v>
       </c>
       <c r="AO22" s="10">
         <f t="shared" si="109"/>
@@ -4186,7 +4198,7 @@
       </c>
       <c r="AA23" s="10">
         <f t="shared" si="104"/>
-        <v>1.0000000000000009E-2</v>
+        <v>7.9921173636960718E-2</v>
       </c>
       <c r="AB23" s="10">
         <f t="shared" si="105"/>
@@ -4223,7 +4235,7 @@
       </c>
       <c r="AN23" s="10">
         <f t="shared" si="111"/>
-        <v>1.9981590773729074E-2</v>
+        <v>3.7271644377064428E-2</v>
       </c>
       <c r="AO23" s="10">
         <f t="shared" si="111"/>
@@ -4317,19 +4329,19 @@
       </c>
       <c r="AA24" s="10">
         <f t="shared" si="104"/>
-        <v>0.18999999999999995</v>
+        <v>0.32278444661420935</v>
       </c>
       <c r="AB24" s="10">
         <f t="shared" si="105"/>
-        <v>0.16999999999999993</v>
+        <v>0.27</v>
       </c>
       <c r="AC24" s="10">
         <f t="shared" si="106"/>
-        <v>0.14999999999999991</v>
+        <v>0.21999999999999997</v>
       </c>
       <c r="AD24" s="10">
         <f t="shared" si="107"/>
-        <v>8.0000000000000071E-2</v>
+        <v>0.10000000000000009</v>
       </c>
       <c r="AH24" s="10"/>
       <c r="AI24" s="10">
@@ -4354,11 +4366,11 @@
       </c>
       <c r="AN24" s="10">
         <f t="shared" si="111"/>
-        <v>0.14386501309224475</v>
+        <v>0.22098237432096179</v>
       </c>
       <c r="AO24" s="10">
         <f t="shared" si="111"/>
-        <v>0.10000000000000009</v>
+        <v>0.1399999999999999</v>
       </c>
       <c r="AP24" s="10">
         <f t="shared" si="111"/>
@@ -4460,19 +4472,19 @@
       </c>
       <c r="AA25" s="11">
         <f t="shared" si="104"/>
-        <v>0.10360428823449563</v>
+        <v>0.18085900393540499</v>
       </c>
       <c r="AB25" s="11">
         <f t="shared" si="105"/>
-        <v>9.4522429149797471E-2</v>
+        <v>0.14322526315789474</v>
       </c>
       <c r="AC25" s="11">
         <f t="shared" si="106"/>
-        <v>8.4732681894566619E-2</v>
+        <v>0.1187950457459388</v>
       </c>
       <c r="AD25" s="11">
         <f t="shared" si="107"/>
-        <v>4.8127309708654531E-2</v>
+        <v>5.8295470822471218E-2</v>
       </c>
       <c r="AH25" s="10"/>
       <c r="AI25" s="11">
@@ -4497,31 +4509,31 @@
       </c>
       <c r="AN25" s="11">
         <f t="shared" si="111"/>
-        <v>8.1441534790253733E-2</v>
+        <v>0.12249874403416228</v>
       </c>
       <c r="AO25" s="11">
         <f t="shared" si="111"/>
-        <v>6.8729349553956931E-2</v>
+        <v>9.6546974014065645E-2</v>
       </c>
       <c r="AP25" s="11">
         <f t="shared" si="111"/>
-        <v>5.7225314826856444E-2</v>
+        <v>5.8945146075553012E-2</v>
       </c>
       <c r="AQ25" s="11">
         <f t="shared" si="111"/>
-        <v>4.4765864608810046E-2</v>
+        <v>4.5948461556035047E-2</v>
       </c>
       <c r="AR25" s="11">
         <f t="shared" si="111"/>
-        <v>3.1626452272457195E-2</v>
+        <v>3.2299526594686823E-2</v>
       </c>
       <c r="AS25" s="11">
         <f t="shared" si="111"/>
-        <v>2.4923901976308116E-2</v>
+        <v>2.5347668869441176E-2</v>
       </c>
       <c r="AT25" s="11">
         <f t="shared" si="111"/>
-        <v>1.6888204453394895E-2</v>
+        <v>1.7127717581356228E-2</v>
       </c>
       <c r="AU25" s="11">
         <f t="shared" si="111"/>
@@ -4537,14 +4549,14 @@
       </c>
       <c r="AX25" s="11">
         <f t="shared" si="111"/>
-        <v>9.9999999999997868E-3</v>
+        <v>1.0000000000000009E-2</v>
       </c>
       <c r="BB25" t="s">
         <v>64</v>
       </c>
       <c r="BC25" s="12">
         <f>NPV(BC24,AN18:ER18)</f>
-        <v>20748.911835943079</v>
+        <v>22830.50813356306</v>
       </c>
     </row>
     <row r="26" spans="2:148" x14ac:dyDescent="0.3">
@@ -4605,7 +4617,7 @@
       </c>
       <c r="AA26" s="10">
         <f t="shared" ref="AA26:AD26" si="116">AA8/AA6</f>
-        <v>0.73</v>
+        <v>0.73169190105438553</v>
       </c>
       <c r="AB26" s="10">
         <f t="shared" si="116"/>
@@ -4617,7 +4629,7 @@
       </c>
       <c r="AD26" s="10">
         <f t="shared" si="116"/>
-        <v>0.75</v>
+        <v>0.75000000000000011</v>
       </c>
       <c r="AH26" s="10">
         <f t="shared" ref="AH26:AL26" si="117">AH8/AH6</f>
@@ -4645,7 +4657,7 @@
       </c>
       <c r="AN26" s="10">
         <f t="shared" si="118"/>
-        <v>0.73784155567008058</v>
+        <v>0.73809275080323167</v>
       </c>
       <c r="AO26" s="10">
         <f t="shared" si="118"/>
@@ -4692,7 +4704,7 @@
       </c>
       <c r="BC26" s="12">
         <f>BC25/Main!D13</f>
-        <v>3665.8854833821692</v>
+        <v>4033.65868084153</v>
       </c>
     </row>
     <row r="27" spans="2:148" x14ac:dyDescent="0.3">
@@ -4753,7 +4765,7 @@
       </c>
       <c r="AA27" s="10">
         <f t="shared" ref="AA27:AD27" si="121">AA9/AA6</f>
-        <v>0.09</v>
+        <v>7.9840262016261099E-2</v>
       </c>
       <c r="AB27" s="10">
         <f t="shared" si="121"/>
@@ -4793,7 +4805,7 @@
       </c>
       <c r="AN27" s="10">
         <f t="shared" si="123"/>
-        <v>8.9999999999999983E-2</v>
+        <v>8.7527017281997369E-2</v>
       </c>
       <c r="AO27" s="10">
         <f t="shared" si="123"/>
@@ -4840,7 +4852,7 @@
       </c>
       <c r="BC27" s="1">
         <f>Main!D10</f>
-        <v>-1257.5441696113076</v>
+        <v>-1344.0106007067136</v>
       </c>
     </row>
     <row r="28" spans="2:148" x14ac:dyDescent="0.3">
@@ -4901,15 +4913,15 @@
       </c>
       <c r="AA28" s="10">
         <f t="shared" ref="AA28:AD28" si="126">AA10/AA6</f>
-        <v>0.17</v>
+        <v>0.17039675927256012</v>
       </c>
       <c r="AB28" s="10">
         <f t="shared" si="126"/>
-        <v>0.16999999999999998</v>
+        <v>0.17</v>
       </c>
       <c r="AC28" s="10">
         <f t="shared" si="126"/>
-        <v>0.16000000000000003</v>
+        <v>0.16</v>
       </c>
       <c r="AD28" s="10">
         <f t="shared" si="126"/>
@@ -4941,7 +4953,7 @@
       </c>
       <c r="AN28" s="10">
         <f t="shared" si="128"/>
-        <v>0.16215844432991935</v>
+        <v>0.1624156501910245</v>
       </c>
       <c r="AO28" s="10">
         <f t="shared" si="128"/>
@@ -4988,7 +5000,7 @@
       </c>
       <c r="BC28" s="12">
         <f>BC26-BC27</f>
-        <v>4923.4296529934763</v>
+        <v>5377.6692815482438</v>
       </c>
     </row>
     <row r="29" spans="2:148" x14ac:dyDescent="0.3">
@@ -5037,7 +5049,7 @@
       </c>
       <c r="AA29" s="10">
         <f t="shared" ref="AA29" si="130">AA11/W11-1</f>
-        <v>5.0000000000000044E-2</v>
+        <v>0.22317644434530459</v>
       </c>
       <c r="AB29" s="10">
         <f t="shared" ref="AB29" si="131">AB11/X11-1</f>
@@ -5074,7 +5086,7 @@
       </c>
       <c r="AN29" s="10">
         <f t="shared" si="134"/>
-        <v>5.0000000000000044E-2</v>
+        <v>9.2036440425589561E-2</v>
       </c>
       <c r="AO29" s="10">
         <f t="shared" si="134"/>
@@ -5121,7 +5133,7 @@
       </c>
       <c r="BC29" s="2">
         <f>BC28/AX19</f>
-        <v>16.797781142932365</v>
+        <v>19.219690069865059</v>
       </c>
     </row>
     <row r="30" spans="2:148" x14ac:dyDescent="0.3">
@@ -5185,19 +5197,19 @@
       </c>
       <c r="AA30" s="10">
         <f t="shared" ref="AA30:AD30" si="136">AA13/AA6</f>
-        <v>0.1897508502962203</v>
+        <v>0.18309535438273902</v>
       </c>
       <c r="AB30" s="10">
         <f t="shared" si="136"/>
-        <v>0.21687202049632198</v>
+        <v>0.22765559077408093</v>
       </c>
       <c r="AC30" s="10">
         <f t="shared" si="136"/>
-        <v>0.22810590759909111</v>
+        <v>0.23607942508989913</v>
       </c>
       <c r="AD30" s="10">
         <f t="shared" si="136"/>
-        <v>0.21577976099694476</v>
+        <v>0.21860664524204482</v>
       </c>
       <c r="AH30" s="10">
         <f t="shared" ref="AH30:AL30" si="137">AH13/AH6</f>
@@ -5225,54 +5237,54 @@
       </c>
       <c r="AN30" s="10">
         <f t="shared" si="138"/>
-        <v>0.21302035465677557</v>
+        <v>0.21658933563528737</v>
       </c>
       <c r="AO30" s="10">
         <f t="shared" si="138"/>
-        <v>0.23721818391054819</v>
+        <v>0.24491966440629448</v>
       </c>
       <c r="AP30" s="10">
         <f t="shared" si="138"/>
-        <v>0.24398525387517547</v>
+        <v>0.25189201571469183</v>
       </c>
       <c r="AQ30" s="10">
         <f t="shared" si="138"/>
-        <v>0.24760355650851559</v>
+        <v>0.25567512816674609</v>
       </c>
       <c r="AR30" s="10">
         <f t="shared" si="138"/>
-        <v>0.24800148229664618</v>
+        <v>0.25621938061097349</v>
       </c>
       <c r="AS30" s="10">
         <f t="shared" si="138"/>
-        <v>0.24929197285902049</v>
+        <v>0.25758289904012743</v>
       </c>
       <c r="AT30" s="10">
         <f t="shared" si="138"/>
-        <v>0.24860565534914708</v>
+        <v>0.25699158732146049</v>
       </c>
       <c r="AU30" s="10">
         <f t="shared" si="138"/>
-        <v>0.24619908203438773</v>
+        <v>0.25468066365649367</v>
       </c>
       <c r="AV30" s="10">
         <f t="shared" si="138"/>
-        <v>0.24377031452052328</v>
+        <v>0.25234874273193197</v>
       </c>
       <c r="AW30" s="10">
         <f t="shared" si="138"/>
-        <v>0.24131916540477974</v>
+        <v>0.24999565394466519</v>
       </c>
       <c r="AX30" s="10">
         <f t="shared" si="138"/>
-        <v>0.23884544606934086</v>
+        <v>0.24762122574087003</v>
       </c>
       <c r="BB30" t="s">
         <v>68</v>
       </c>
       <c r="BC30" s="2">
         <f>Main!D3</f>
-        <v>13.77</v>
+        <v>13.28</v>
       </c>
     </row>
     <row r="31" spans="2:148" x14ac:dyDescent="0.3">
@@ -5336,7 +5348,7 @@
       </c>
       <c r="AA31" s="10">
         <f t="shared" ref="AA31:AD31" si="140">AA16/AA15</f>
-        <v>0.2</v>
+        <v>0.18943076681825319</v>
       </c>
       <c r="AB31" s="10">
         <f t="shared" si="140"/>
@@ -5344,7 +5356,7 @@
       </c>
       <c r="AC31" s="10">
         <f t="shared" si="140"/>
-        <v>0.20000000000000004</v>
+        <v>0.2</v>
       </c>
       <c r="AD31" s="10">
         <f t="shared" si="140"/>
@@ -5376,7 +5388,7 @@
       </c>
       <c r="AN31" s="10">
         <f t="shared" si="142"/>
-        <v>0.19999999999999993</v>
+        <v>0.19782410105220777</v>
       </c>
       <c r="AO31" s="10">
         <f t="shared" si="142"/>
@@ -5423,7 +5435,7 @@
       </c>
       <c r="BC31" s="11">
         <f>BC29/BC30-1</f>
-        <v>0.21988243594280066</v>
+        <v>0.44726581851393532</v>
       </c>
     </row>
     <row r="32" spans="2:148" x14ac:dyDescent="0.3">
@@ -5487,19 +5499,19 @@
       </c>
       <c r="AA32" s="10">
         <f t="shared" ref="AA32:AD32" si="144">AA18/AA6</f>
-        <v>0.15180068023697624</v>
+        <v>0.14784382451805667</v>
       </c>
       <c r="AB32" s="10">
         <f t="shared" si="144"/>
-        <v>0.1734976163970576</v>
+        <v>0.18212447261926473</v>
       </c>
       <c r="AC32" s="10">
         <f t="shared" si="144"/>
-        <v>0.18248472607927288</v>
+        <v>0.18886354007191933</v>
       </c>
       <c r="AD32" s="10">
         <f t="shared" si="144"/>
-        <v>0.17262380879755582</v>
+        <v>0.17488531619363584</v>
       </c>
       <c r="AH32" s="10">
         <f t="shared" ref="AH32:AX32" si="145">AH18/AH6</f>
@@ -5527,53 +5539,53 @@
       </c>
       <c r="AN32" s="10">
         <f t="shared" si="145"/>
-        <v>0.17041628372542048</v>
+        <v>0.1736043417864499</v>
       </c>
       <c r="AO32" s="10">
         <f t="shared" si="145"/>
-        <v>0.18930011076061745</v>
+        <v>0.19544589219622296</v>
       </c>
       <c r="AP32" s="10">
         <f t="shared" si="145"/>
-        <v>0.19470023259239003</v>
+        <v>0.20100982854032406</v>
       </c>
       <c r="AQ32" s="10">
         <f t="shared" si="145"/>
-        <v>0.19758763809379548</v>
+        <v>0.20402875227706335</v>
       </c>
       <c r="AR32" s="10">
         <f t="shared" si="145"/>
-        <v>0.19790518287272363</v>
+        <v>0.20446306572755685</v>
       </c>
       <c r="AS32" s="10">
         <f t="shared" si="145"/>
-        <v>0.19893499434149836</v>
+        <v>0.20555115343402169</v>
       </c>
       <c r="AT32" s="10">
         <f t="shared" si="145"/>
-        <v>0.19838731296861939</v>
+        <v>0.20507928668252548</v>
       </c>
       <c r="AU32" s="10">
         <f t="shared" si="145"/>
-        <v>0.19646686746344141</v>
+        <v>0.20323516959788196</v>
       </c>
       <c r="AV32" s="10">
         <f t="shared" si="145"/>
-        <v>0.19452871098737756</v>
+        <v>0.20137429670008172</v>
       </c>
       <c r="AW32" s="10">
         <f t="shared" si="145"/>
-        <v>0.19257269399301424</v>
+        <v>0.19949653184784283</v>
       </c>
       <c r="AX32" s="10">
         <f t="shared" si="145"/>
-        <v>0.190598665963334</v>
+        <v>0.19760173814121426</v>
       </c>
       <c r="BB32" t="s">
         <v>71</v>
       </c>
       <c r="BC32" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="34" spans="2:39" s="7" customFormat="1" x14ac:dyDescent="0.3">
@@ -7118,7 +7130,10 @@
         <f>Z18</f>
         <v>-2921.9000000000005</v>
       </c>
-      <c r="AA80" s="9"/>
+      <c r="AA80" s="9">
+        <f>AA18</f>
+        <v>514.5999999999998</v>
+      </c>
       <c r="AB80" s="9"/>
       <c r="AC80" s="9"/>
       <c r="AD80" s="9"/>
@@ -7144,47 +7159,47 @@
       </c>
       <c r="AN80" s="9">
         <f t="shared" ref="AN80:AX80" si="149">AN18</f>
-        <v>2347.7740160000003</v>
+        <v>2482.4962560000022</v>
       </c>
       <c r="AO80" s="9">
         <f t="shared" si="149"/>
-        <v>2787.1722259499988</v>
+        <v>3064.6565245799993</v>
       </c>
       <c r="AP80" s="9">
         <f t="shared" si="149"/>
-        <v>3030.7280011533003</v>
+        <v>3337.690153690201</v>
       </c>
       <c r="AQ80" s="9">
         <f t="shared" si="149"/>
-        <v>3213.3589068391652</v>
+        <v>3543.4832449213268</v>
       </c>
       <c r="AR80" s="9">
         <f t="shared" si="149"/>
-        <v>3320.3135913021265</v>
+        <v>3665.7226789559036</v>
       </c>
       <c r="AS80" s="9">
         <f t="shared" si="149"/>
-        <v>3420.7768338451474</v>
+        <v>3778.6424968347465</v>
       </c>
       <c r="AT80" s="9">
         <f t="shared" si="149"/>
-        <v>3468.9709376807759</v>
+        <v>3834.5391306270271</v>
       </c>
       <c r="AU80" s="9">
         <f t="shared" si="149"/>
-        <v>3469.7442174198932</v>
+        <v>3838.0587107590809</v>
       </c>
       <c r="AV80" s="9">
         <f t="shared" si="149"/>
-        <v>3469.8701494701572</v>
+        <v>3840.945633833815</v>
       </c>
       <c r="AW80" s="9">
         <f t="shared" si="149"/>
-        <v>3469.3298561881525</v>
+        <v>3843.1810761244292</v>
       </c>
       <c r="AX80" s="9">
         <f t="shared" si="149"/>
-        <v>3468.1040439939879</v>
+        <v>3844.7458015207562</v>
       </c>
     </row>
     <row r="81" spans="2:50" x14ac:dyDescent="0.3">
@@ -7220,6 +7235,9 @@
       <c r="Z81" s="1">
         <v>244</v>
       </c>
+      <c r="AA81" s="1">
+        <v>258.39999999999998</v>
+      </c>
       <c r="AI81" s="1">
         <v>256.3</v>
       </c>
@@ -7315,6 +7333,9 @@
       <c r="Z82" s="1">
         <v>-59.5</v>
       </c>
+      <c r="AA82" s="1">
+        <v>-12.2</v>
+      </c>
       <c r="AI82" s="1">
         <v>73.3</v>
       </c>
@@ -7410,6 +7431,9 @@
       <c r="Z83" s="1">
         <v>-0.1</v>
       </c>
+      <c r="AA83" s="1">
+        <v>-0.4</v>
+      </c>
       <c r="AI83" s="1">
         <v>6.9</v>
       </c>
@@ -7494,6 +7518,9 @@
       <c r="Z84" s="1">
         <v>76.900000000000006</v>
       </c>
+      <c r="AA84" s="1">
+        <v>174.3</v>
+      </c>
       <c r="AI84" s="1">
         <v>-283.89999999999998</v>
       </c>
@@ -7578,6 +7605,9 @@
       <c r="Z85" s="1">
         <v>-3.3</v>
       </c>
+      <c r="AA85" s="1">
+        <v>24.4</v>
+      </c>
       <c r="AI85" s="1">
         <v>2.2999999999999998</v>
       </c>
@@ -7673,6 +7703,9 @@
       <c r="Z86" s="1">
         <v>74.3</v>
       </c>
+      <c r="AA86" s="1">
+        <v>87.1</v>
+      </c>
       <c r="AI86" s="1">
         <v>31.5</v>
       </c>
@@ -7768,6 +7801,9 @@
       <c r="Z87" s="1">
         <v>24.5</v>
       </c>
+      <c r="AA87" s="1">
+        <v>45.4</v>
+      </c>
       <c r="AI87" s="1">
         <v>35.6</v>
       </c>
@@ -7862,6 +7898,9 @@
       </c>
       <c r="Z88" s="1">
         <v>23.6</v>
+      </c>
+      <c r="AA88" s="1">
+        <v>-4.2</v>
       </c>
       <c r="AI88" s="1">
         <v>52.7</v>
@@ -7928,6 +7967,9 @@
       <c r="Z89" s="1">
         <v>3558</v>
       </c>
+      <c r="AA89" s="1">
+        <v>0</v>
+      </c>
       <c r="AI89" s="1"/>
       <c r="AJ89" s="1"/>
       <c r="AK89" s="1"/>
@@ -8003,6 +8045,9 @@
       <c r="Z90" s="1">
         <v>-4</v>
       </c>
+      <c r="AA90" s="1">
+        <v>7</v>
+      </c>
       <c r="AI90" s="1">
         <v>0</v>
       </c>
@@ -8087,6 +8132,9 @@
       <c r="Z91" s="1">
         <v>5.3</v>
       </c>
+      <c r="AA91" s="1">
+        <v>0</v>
+      </c>
       <c r="AI91" s="1">
         <v>0</v>
       </c>
@@ -8171,6 +8219,9 @@
       <c r="Z92" s="1">
         <v>-230.6</v>
       </c>
+      <c r="AA92" s="1">
+        <v>69.7</v>
+      </c>
       <c r="AI92" s="1">
         <v>-12.5</v>
       </c>
@@ -8254,6 +8305,9 @@
       </c>
       <c r="Z93" s="1">
         <v>233.4</v>
+      </c>
+      <c r="AA93" s="1">
+        <v>-73.2</v>
       </c>
       <c r="AI93" s="1">
         <v>-5.8</v>
@@ -8335,6 +8389,9 @@
       <c r="Z94" s="1">
         <v>0.1</v>
       </c>
+      <c r="AA94" s="1">
+        <v>0</v>
+      </c>
       <c r="AI94" s="1">
         <v>-3</v>
       </c>
@@ -8413,6 +8470,9 @@
         <v>0</v>
       </c>
       <c r="Z95" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA95" s="1">
         <v>0</v>
       </c>
       <c r="AI95" s="1"/>
@@ -8493,6 +8553,9 @@
       <c r="Z96" s="1">
         <v>-2476.4</v>
       </c>
+      <c r="AA96" s="1">
+        <v>-4851.3</v>
+      </c>
       <c r="AE96" s="1"/>
       <c r="AI96" s="1">
         <v>-2081.9</v>
@@ -8578,6 +8641,9 @@
       <c r="Z97" s="1">
         <v>4.5</v>
       </c>
+      <c r="AA97" s="1">
+        <v>0.2</v>
+      </c>
       <c r="AI97" s="1">
         <v>8.6999999999999993</v>
       </c>
@@ -8662,6 +8728,9 @@
       <c r="Z98" s="1">
         <v>27.8</v>
       </c>
+      <c r="AA98" s="1">
+        <v>-44.4</v>
+      </c>
       <c r="AI98" s="1">
         <v>-18.600000000000001</v>
       </c>
@@ -8746,6 +8815,9 @@
       <c r="Z99" s="1">
         <v>-33.4</v>
       </c>
+      <c r="AA99" s="1">
+        <v>-99.7</v>
+      </c>
       <c r="AI99" s="1">
         <v>-106.4</v>
       </c>
@@ -8830,6 +8902,9 @@
       <c r="Z100" s="1">
         <v>839.6</v>
       </c>
+      <c r="AA100" s="1">
+        <v>6343.2</v>
+      </c>
       <c r="AI100" s="1">
         <v>-1362.4</v>
       </c>
@@ -8913,6 +8988,9 @@
       </c>
       <c r="Z101" s="1">
         <v>-207.2</v>
+      </c>
+      <c r="AA101" s="1">
+        <v>-147.4</v>
       </c>
       <c r="AI101" s="1"/>
       <c r="AJ101" s="1"/>
@@ -8992,6 +9070,9 @@
       <c r="Z102" s="1">
         <v>-808.6</v>
       </c>
+      <c r="AA102" s="1">
+        <v>-2956</v>
+      </c>
       <c r="AI102" s="1">
         <v>1379.1</v>
       </c>
@@ -9011,47 +9092,47 @@
         <v>-8507.2999999999993</v>
       </c>
       <c r="AN102" s="1">
-        <v>-3000</v>
+        <v>0</v>
       </c>
       <c r="AO102" s="1">
         <f>AN102*0.9</f>
-        <v>-2700</v>
+        <v>0</v>
       </c>
       <c r="AP102" s="1">
         <f t="shared" ref="AP102:AX102" si="168">AO102*0.9</f>
-        <v>-2430</v>
+        <v>0</v>
       </c>
       <c r="AQ102" s="1">
         <f t="shared" si="168"/>
-        <v>-2187</v>
+        <v>0</v>
       </c>
       <c r="AR102" s="1">
         <f t="shared" si="168"/>
-        <v>-1968.3</v>
+        <v>0</v>
       </c>
       <c r="AS102" s="1">
         <f t="shared" si="168"/>
-        <v>-1771.47</v>
+        <v>0</v>
       </c>
       <c r="AT102" s="1">
         <f t="shared" si="168"/>
-        <v>-1594.3230000000001</v>
+        <v>0</v>
       </c>
       <c r="AU102" s="1">
         <f t="shared" si="168"/>
-        <v>-1434.8907000000002</v>
+        <v>0</v>
       </c>
       <c r="AV102" s="1">
         <f t="shared" si="168"/>
-        <v>-1291.4016300000001</v>
+        <v>0</v>
       </c>
       <c r="AW102" s="1">
         <f t="shared" si="168"/>
-        <v>-1162.261467</v>
+        <v>0</v>
       </c>
       <c r="AX102" s="1">
         <f t="shared" si="168"/>
-        <v>-1046.0353203</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103" spans="2:50" x14ac:dyDescent="0.3">
@@ -9087,6 +9168,9 @@
       <c r="Z103" s="1">
         <v>158.19999999999999</v>
       </c>
+      <c r="AA103" s="1">
+        <v>162.30000000000001</v>
+      </c>
       <c r="AI103" s="1">
         <v>270</v>
       </c>
@@ -9171,6 +9255,9 @@
       <c r="Z104" s="1">
         <v>-27.2</v>
       </c>
+      <c r="AA104" s="1">
+        <v>-162.6</v>
+      </c>
       <c r="AI104" s="1">
         <v>110</v>
       </c>
@@ -9255,6 +9342,9 @@
       <c r="Z105" s="1">
         <v>-14</v>
       </c>
+      <c r="AA105" s="1">
+        <v>-13.7</v>
+      </c>
       <c r="AI105" s="1">
         <v>-2.2000000000000002</v>
       </c>
@@ -9339,6 +9429,9 @@
       <c r="Z106" s="1">
         <v>136.80000000000001</v>
       </c>
+      <c r="AA106" s="1">
+        <v>23.6</v>
+      </c>
       <c r="AI106" s="1">
         <v>31.8</v>
       </c>
@@ -9423,6 +9516,9 @@
       <c r="Z107" s="1">
         <v>-202.6</v>
       </c>
+      <c r="AA107" s="1">
+        <v>-143.9</v>
+      </c>
       <c r="AI107" s="1">
         <v>-177.6</v>
       </c>
@@ -9441,48 +9537,37 @@
         <v>-782.4</v>
       </c>
       <c r="AN107" s="1">
-        <f>AM107*1.02</f>
-        <v>-798.048</v>
+        <v>0</v>
       </c>
       <c r="AO107" s="1">
-        <f t="shared" ref="AO107:AX107" si="169">AN107*1.02</f>
-        <v>-814.00896</v>
+        <v>0</v>
       </c>
       <c r="AP107" s="1">
-        <f t="shared" si="169"/>
-        <v>-830.28913920000002</v>
+        <v>0</v>
       </c>
       <c r="AQ107" s="1">
-        <f t="shared" si="169"/>
-        <v>-846.89492198400001</v>
+        <v>0</v>
       </c>
       <c r="AR107" s="1">
-        <f t="shared" si="169"/>
-        <v>-863.83282042368</v>
+        <v>0</v>
       </c>
       <c r="AS107" s="1">
-        <f t="shared" si="169"/>
-        <v>-881.10947683215363</v>
+        <v>0</v>
       </c>
       <c r="AT107" s="1">
-        <f t="shared" si="169"/>
-        <v>-898.73166636879671</v>
+        <v>0</v>
       </c>
       <c r="AU107" s="1">
-        <f t="shared" si="169"/>
-        <v>-916.70629969617266</v>
+        <v>0</v>
       </c>
       <c r="AV107" s="1">
-        <f t="shared" si="169"/>
-        <v>-935.04042569009619</v>
+        <v>0</v>
       </c>
       <c r="AW107" s="1">
-        <f t="shared" si="169"/>
-        <v>-953.7412342038981</v>
+        <v>0</v>
       </c>
       <c r="AX107" s="1">
-        <f t="shared" si="169"/>
-        <v>-972.81605888797606</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108" spans="2:50" x14ac:dyDescent="0.3">
@@ -9518,6 +9603,9 @@
       <c r="Z108" s="1">
         <v>1335.5</v>
       </c>
+      <c r="AA108" s="1">
+        <v>1528.9</v>
+      </c>
       <c r="AI108" s="1">
         <v>1172.8</v>
       </c>
@@ -9536,48 +9624,37 @@
         <v>4578.2</v>
       </c>
       <c r="AN108" s="1">
-        <f>AM108*1.01</f>
-        <v>4623.982</v>
+        <v>0</v>
       </c>
       <c r="AO108" s="1">
-        <f t="shared" ref="AO108:AX108" si="170">AN108*1.01</f>
-        <v>4670.2218199999998</v>
+        <v>0</v>
       </c>
       <c r="AP108" s="1">
-        <f t="shared" si="170"/>
-        <v>4716.9240381999998</v>
+        <v>0</v>
       </c>
       <c r="AQ108" s="1">
-        <f t="shared" si="170"/>
-        <v>4764.0932785819996</v>
+        <v>0</v>
       </c>
       <c r="AR108" s="1">
-        <f t="shared" si="170"/>
-        <v>4811.7342113678196</v>
+        <v>0</v>
       </c>
       <c r="AS108" s="1">
-        <f t="shared" si="170"/>
-        <v>4859.8515534814978</v>
+        <v>0</v>
       </c>
       <c r="AT108" s="1">
-        <f t="shared" si="170"/>
-        <v>4908.4500690163131</v>
+        <v>0</v>
       </c>
       <c r="AU108" s="1">
-        <f t="shared" si="170"/>
-        <v>4957.5345697064768</v>
+        <v>0</v>
       </c>
       <c r="AV108" s="1">
-        <f t="shared" si="170"/>
-        <v>5007.1099154035419</v>
+        <v>0</v>
       </c>
       <c r="AW108" s="1">
-        <f t="shared" si="170"/>
-        <v>5057.1810145575773</v>
+        <v>0</v>
       </c>
       <c r="AX108" s="1">
-        <f t="shared" si="170"/>
-        <v>5107.7528247031532</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109" spans="2:50" x14ac:dyDescent="0.3">
@@ -9613,6 +9690,9 @@
       <c r="Z109" s="1">
         <v>-54.4</v>
       </c>
+      <c r="AA109" s="1">
+        <v>-108</v>
+      </c>
       <c r="AI109" s="1">
         <v>-157.69999999999999</v>
       </c>
@@ -9631,48 +9711,37 @@
         <v>-174</v>
       </c>
       <c r="AN109" s="1">
-        <f>AM109*1.02</f>
-        <v>-177.48</v>
+        <v>0</v>
       </c>
       <c r="AO109" s="1">
-        <f t="shared" ref="AO109:AX109" si="171">AN109*1.02</f>
-        <v>-181.02959999999999</v>
+        <v>0</v>
       </c>
       <c r="AP109" s="1">
-        <f t="shared" si="171"/>
-        <v>-184.650192</v>
+        <v>0</v>
       </c>
       <c r="AQ109" s="1">
-        <f t="shared" si="171"/>
-        <v>-188.34319584000002</v>
+        <v>0</v>
       </c>
       <c r="AR109" s="1">
-        <f t="shared" si="171"/>
-        <v>-192.11005975680001</v>
+        <v>0</v>
       </c>
       <c r="AS109" s="1">
-        <f t="shared" si="171"/>
-        <v>-195.95226095193601</v>
+        <v>0</v>
       </c>
       <c r="AT109" s="1">
-        <f t="shared" si="171"/>
-        <v>-199.87130617097475</v>
+        <v>0</v>
       </c>
       <c r="AU109" s="1">
-        <f t="shared" si="171"/>
-        <v>-203.86873229439425</v>
+        <v>0</v>
       </c>
       <c r="AV109" s="1">
-        <f t="shared" si="171"/>
-        <v>-207.94610694028214</v>
+        <v>0</v>
       </c>
       <c r="AW109" s="1">
-        <f t="shared" si="171"/>
-        <v>-212.10502907908779</v>
+        <v>0</v>
       </c>
       <c r="AX109" s="1">
-        <f t="shared" si="171"/>
-        <v>-216.34712966066954</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110" spans="2:50" s="7" customFormat="1" x14ac:dyDescent="0.3">
@@ -9680,43 +9749,43 @@
         <v>118</v>
       </c>
       <c r="O110" s="9">
-        <f t="shared" ref="O110:X110" si="172">O80+SUM(O81:O109)</f>
+        <f t="shared" ref="O110:X110" si="169">O80+SUM(O81:O109)</f>
         <v>-313.09999999999997</v>
       </c>
       <c r="P110" s="9">
-        <f t="shared" si="172"/>
+        <f t="shared" si="169"/>
         <v>-487.40000000000015</v>
       </c>
       <c r="Q110" s="9">
-        <f t="shared" si="172"/>
+        <f t="shared" si="169"/>
         <v>202.49999999999997</v>
       </c>
       <c r="R110" s="9">
-        <f t="shared" si="172"/>
+        <f t="shared" si="169"/>
         <v>78.899999999999949</v>
       </c>
       <c r="S110" s="9">
-        <f t="shared" si="172"/>
+        <f t="shared" si="169"/>
         <v>1168.4000000000001</v>
       </c>
       <c r="T110" s="9">
-        <f t="shared" si="172"/>
+        <f t="shared" si="169"/>
         <v>830.80000000000018</v>
       </c>
       <c r="U110" s="9">
-        <f t="shared" si="172"/>
+        <f t="shared" si="169"/>
         <v>60.399999999999352</v>
       </c>
       <c r="V110" s="9">
-        <f t="shared" si="172"/>
+        <f t="shared" si="169"/>
         <v>-416.09999999999991</v>
       </c>
       <c r="W110" s="9">
-        <f t="shared" si="172"/>
+        <f t="shared" si="169"/>
         <v>-2473.9999999999995</v>
       </c>
       <c r="X110" s="9">
-        <f t="shared" si="172"/>
+        <f t="shared" si="169"/>
         <v>-718.10000000000014</v>
       </c>
       <c r="Y110" s="9">
@@ -9727,73 +9796,76 @@
         <f>Z80+SUM(Z81:Z109)</f>
         <v>-300.70000000000027</v>
       </c>
-      <c r="AA110" s="9"/>
+      <c r="AA110" s="9">
+        <f>AA80+SUM(AA81:AA109)</f>
+        <v>622.0999999999998</v>
+      </c>
       <c r="AB110" s="9"/>
       <c r="AC110" s="9"/>
       <c r="AD110" s="9"/>
       <c r="AI110" s="9">
-        <f t="shared" ref="AI110" si="173">AI80+SUM(AI81:AI109)</f>
+        <f t="shared" ref="AI110" si="170">AI80+SUM(AI81:AI109)</f>
         <v>73.099999999999568</v>
       </c>
       <c r="AJ110" s="9">
-        <f t="shared" ref="AJ110:AK110" si="174">AJ80+SUM(AJ81:AJ109)</f>
+        <f t="shared" ref="AJ110:AK110" si="171">AJ80+SUM(AJ81:AJ109)</f>
         <v>3625.7000000000007</v>
       </c>
       <c r="AK110" s="9">
-        <f t="shared" si="174"/>
+        <f t="shared" si="171"/>
         <v>1690.8000000000011</v>
       </c>
       <c r="AL110" s="9">
-        <f t="shared" ref="AL110:AN110" si="175">AL80+SUM(AL81:AL109)</f>
+        <f t="shared" ref="AL110:AN110" si="172">AL80+SUM(AL81:AL109)</f>
         <v>1643.500000000002</v>
       </c>
       <c r="AM110" s="9">
-        <f t="shared" si="175"/>
+        <f t="shared" si="172"/>
         <v>-3627.199999999998</v>
       </c>
       <c r="AN110" s="9">
-        <f t="shared" si="175"/>
-        <v>4335.4190159999998</v>
+        <f t="shared" si="172"/>
+        <v>3821.687256000002</v>
       </c>
       <c r="AO110" s="9">
-        <f t="shared" ref="AO110:AX110" si="176">AO80+SUM(AO81:AO109)</f>
-        <v>5092.6038159499985</v>
+        <f t="shared" ref="AO110:AX110" si="173">AO80+SUM(AO81:AO109)</f>
+        <v>4394.9048545799997</v>
       </c>
       <c r="AP110" s="9">
-        <f t="shared" si="176"/>
-        <v>5624.1844172533001</v>
+        <f t="shared" si="173"/>
+        <v>4659.1618627902008</v>
       </c>
       <c r="AQ110" s="9">
-        <f t="shared" si="176"/>
-        <v>6068.0749532301652</v>
+        <f t="shared" si="173"/>
+        <v>4856.3441305543265</v>
       </c>
       <c r="AR110" s="9">
-        <f t="shared" si="176"/>
-        <v>6403.2793322172965</v>
+        <f t="shared" si="173"/>
+        <v>4961.1970886837335</v>
       </c>
       <c r="AS110" s="9">
-        <f t="shared" si="176"/>
-        <v>6710.8864397264842</v>
+        <f t="shared" si="173"/>
+        <v>5057.4322870186743</v>
       </c>
       <c r="AT110" s="9">
-        <f t="shared" si="176"/>
-        <v>6947.2741807602997</v>
+        <f t="shared" si="173"/>
+        <v>5097.3182772300088</v>
       </c>
       <c r="AU110" s="9">
-        <f t="shared" si="176"/>
-        <v>7119.2290787309103</v>
+        <f t="shared" si="173"/>
+        <v>5085.4747343541885</v>
       </c>
       <c r="AV110" s="9">
-        <f t="shared" si="176"/>
-        <v>7275.2672234476995</v>
+        <f t="shared" si="173"/>
+        <v>5073.6209550381946</v>
       </c>
       <c r="AW110" s="9">
-        <f t="shared" si="176"/>
-        <v>7416.9363692980141</v>
+        <f t="shared" si="173"/>
+        <v>5061.7143049596998</v>
       </c>
       <c r="AX110" s="9">
-        <f t="shared" si="176"/>
-        <v>7545.6255223540084</v>
+        <f t="shared" si="173"/>
+        <v>5049.7129640262683</v>
       </c>
     </row>
     <row r="111" spans="2:50" x14ac:dyDescent="0.3">
@@ -9829,7 +9901,9 @@
       <c r="Z111" s="1">
         <v>203.4</v>
       </c>
-      <c r="AA111" s="1"/>
+      <c r="AA111" s="1">
+        <v>180.2</v>
+      </c>
       <c r="AB111" s="1"/>
       <c r="AC111" s="1"/>
       <c r="AD111" s="1"/>
@@ -9843,11 +9917,11 @@
         <v>417.7</v>
       </c>
       <c r="AL111" s="1">
-        <f t="shared" ref="AL111:AL112" si="177">SUM(S111:V111)</f>
+        <f t="shared" ref="AL111:AL112" si="174">SUM(S111:V111)</f>
         <v>736.2</v>
       </c>
       <c r="AM111" s="1">
-        <f t="shared" ref="AM111:AM112" si="178">SUM(W111:Z111)</f>
+        <f t="shared" ref="AM111:AM112" si="175">SUM(W111:Z111)</f>
         <v>764.5</v>
       </c>
       <c r="AN111" s="1">
@@ -9855,44 +9929,44 @@
         <v>779.79</v>
       </c>
       <c r="AO111" s="1">
-        <f t="shared" ref="AO111:AX111" si="179">AN111*1.02</f>
+        <f t="shared" ref="AO111:AR112" si="176">AN111*1.02</f>
         <v>795.38580000000002</v>
       </c>
       <c r="AP111" s="1">
-        <f t="shared" si="179"/>
-        <v>811.29351600000007</v>
+        <f>AO111*1.01</f>
+        <v>803.33965799999999</v>
       </c>
       <c r="AQ111" s="1">
-        <f t="shared" si="179"/>
-        <v>827.51938632000008</v>
+        <f t="shared" ref="AQ111:AX111" si="177">AP111*1.01</f>
+        <v>811.37305458000003</v>
       </c>
       <c r="AR111" s="1">
-        <f t="shared" si="179"/>
-        <v>844.06977404640008</v>
+        <f t="shared" si="177"/>
+        <v>819.4867851258</v>
       </c>
       <c r="AS111" s="1">
-        <f t="shared" si="179"/>
-        <v>860.95116952732815</v>
+        <f t="shared" si="177"/>
+        <v>827.68165297705798</v>
       </c>
       <c r="AT111" s="1">
-        <f t="shared" si="179"/>
-        <v>878.17019291787472</v>
+        <f t="shared" si="177"/>
+        <v>835.95846950682858</v>
       </c>
       <c r="AU111" s="1">
-        <f t="shared" si="179"/>
-        <v>895.73359677623228</v>
+        <f t="shared" si="177"/>
+        <v>844.31805420189687</v>
       </c>
       <c r="AV111" s="1">
-        <f t="shared" si="179"/>
-        <v>913.64826871175694</v>
+        <f t="shared" si="177"/>
+        <v>852.76123474391579</v>
       </c>
       <c r="AW111" s="1">
-        <f t="shared" si="179"/>
-        <v>931.92123408599207</v>
+        <f t="shared" si="177"/>
+        <v>861.28884709135491</v>
       </c>
       <c r="AX111" s="1">
-        <f t="shared" si="179"/>
-        <v>950.55965876771188</v>
+        <f t="shared" si="177"/>
+        <v>869.90173556226841</v>
       </c>
     </row>
     <row r="112" spans="2:50" x14ac:dyDescent="0.3">
@@ -9928,7 +10002,9 @@
       <c r="Z112" s="1">
         <v>119</v>
       </c>
-      <c r="AA112" s="1"/>
+      <c r="AA112" s="1">
+        <v>107.3</v>
+      </c>
       <c r="AB112" s="1"/>
       <c r="AC112" s="1"/>
       <c r="AD112" s="1"/>
@@ -9942,56 +10018,56 @@
         <v>305.5</v>
       </c>
       <c r="AL112" s="1">
-        <f t="shared" si="177"/>
+        <f t="shared" si="174"/>
         <v>474.1</v>
       </c>
       <c r="AM112" s="1">
+        <f t="shared" si="175"/>
+        <v>507.2</v>
+      </c>
+      <c r="AN112" s="1">
+        <f>AM112*0.88</f>
+        <v>446.33600000000001</v>
+      </c>
+      <c r="AO112" s="1">
+        <f>AN112*1.02</f>
+        <v>455.26272</v>
+      </c>
+      <c r="AP112" s="1">
+        <f t="shared" si="176"/>
+        <v>464.36797440000004</v>
+      </c>
+      <c r="AQ112" s="1">
+        <f t="shared" si="176"/>
+        <v>473.65533388800003</v>
+      </c>
+      <c r="AR112" s="1">
+        <f t="shared" si="176"/>
+        <v>483.12844056576006</v>
+      </c>
+      <c r="AS112" s="1">
+        <f>AR112*1.01</f>
+        <v>487.95972497141764</v>
+      </c>
+      <c r="AT112" s="1">
+        <f t="shared" ref="AT112:AX112" si="178">AS112*1.01</f>
+        <v>492.83932222113185</v>
+      </c>
+      <c r="AU112" s="1">
         <f t="shared" si="178"/>
-        <v>507.2</v>
-      </c>
-      <c r="AN112" s="1">
-        <f>AM112*1.03</f>
-        <v>522.41600000000005</v>
-      </c>
-      <c r="AO112" s="1">
-        <f t="shared" ref="AO112:AQ112" si="180">AN112*1.03</f>
-        <v>538.08848000000012</v>
-      </c>
-      <c r="AP112" s="1">
-        <f t="shared" si="180"/>
-        <v>554.23113440000009</v>
-      </c>
-      <c r="AQ112" s="1">
-        <f t="shared" si="180"/>
-        <v>570.8580684320001</v>
-      </c>
-      <c r="AR112" s="1">
-        <f>AQ112*1.02</f>
-        <v>582.27522980064009</v>
-      </c>
-      <c r="AS112" s="1">
-        <f t="shared" ref="AS112:AX112" si="181">AR112*1.02</f>
-        <v>593.92073439665285</v>
-      </c>
-      <c r="AT112" s="1">
-        <f t="shared" si="181"/>
-        <v>605.79914908458591</v>
-      </c>
-      <c r="AU112" s="1">
-        <f t="shared" si="181"/>
-        <v>617.91513206627758</v>
+        <v>497.76771544334315</v>
       </c>
       <c r="AV112" s="1">
-        <f t="shared" si="181"/>
-        <v>630.27343470760309</v>
+        <f t="shared" si="178"/>
+        <v>502.74539259777657</v>
       </c>
       <c r="AW112" s="1">
-        <f t="shared" si="181"/>
-        <v>642.87890340175511</v>
+        <f t="shared" si="178"/>
+        <v>507.77284652375437</v>
       </c>
       <c r="AX112" s="1">
-        <f t="shared" si="181"/>
-        <v>655.73648146979019</v>
+        <f t="shared" si="178"/>
+        <v>512.85057498899187</v>
       </c>
     </row>
     <row r="113" spans="2:148" x14ac:dyDescent="0.3">
@@ -10003,100 +10079,103 @@
         <v>416.4</v>
       </c>
       <c r="T113" s="1">
-        <f t="shared" ref="T113:Z113" si="182">T111+T112</f>
+        <f t="shared" ref="T113:Z113" si="179">T111+T112</f>
         <v>332.2</v>
       </c>
       <c r="U113" s="1">
-        <f t="shared" si="182"/>
+        <f t="shared" si="179"/>
         <v>176.39999999999995</v>
       </c>
       <c r="V113" s="1">
-        <f t="shared" si="182"/>
+        <f t="shared" si="179"/>
         <v>285.30000000000007</v>
       </c>
       <c r="W113" s="1">
-        <f t="shared" si="182"/>
+        <f t="shared" si="179"/>
         <v>306.60000000000002</v>
       </c>
       <c r="X113" s="1">
-        <f t="shared" si="182"/>
+        <f t="shared" si="179"/>
         <v>344.6</v>
       </c>
       <c r="Y113" s="1">
-        <f t="shared" si="182"/>
+        <f t="shared" si="179"/>
         <v>298.10000000000002</v>
       </c>
       <c r="Z113" s="1">
-        <f t="shared" si="182"/>
+        <f t="shared" si="179"/>
         <v>322.39999999999998</v>
       </c>
-      <c r="AA113" s="1"/>
+      <c r="AA113" s="1">
+        <f t="shared" ref="AA113" si="180">AA111+AA112</f>
+        <v>287.5</v>
+      </c>
       <c r="AB113" s="1"/>
       <c r="AC113" s="1"/>
       <c r="AD113" s="1"/>
       <c r="AI113" s="1">
-        <f t="shared" ref="AI113:AK113" si="183">AI111+AI112</f>
+        <f t="shared" ref="AI113:AK113" si="181">AI111+AI112</f>
         <v>455.1</v>
       </c>
       <c r="AJ113" s="1">
-        <f t="shared" si="183"/>
+        <f t="shared" si="181"/>
         <v>1298.7</v>
       </c>
       <c r="AK113" s="1">
-        <f t="shared" si="183"/>
+        <f t="shared" si="181"/>
         <v>723.2</v>
       </c>
       <c r="AL113" s="1">
-        <f t="shared" ref="AL113" si="184">AL111+AL112</f>
+        <f t="shared" ref="AL113" si="182">AL111+AL112</f>
         <v>1210.3000000000002</v>
       </c>
       <c r="AM113" s="1">
-        <f t="shared" ref="AM113" si="185">AM111+AM112</f>
+        <f t="shared" ref="AM113" si="183">AM111+AM112</f>
         <v>1271.7</v>
       </c>
       <c r="AN113" s="1">
-        <f t="shared" ref="AN113" si="186">AN111+AN112</f>
-        <v>1302.2060000000001</v>
+        <f t="shared" ref="AN113" si="184">AN111+AN112</f>
+        <v>1226.126</v>
       </c>
       <c r="AO113" s="1">
-        <f t="shared" ref="AO113" si="187">AO111+AO112</f>
-        <v>1333.4742800000001</v>
+        <f t="shared" ref="AO113" si="185">AO111+AO112</f>
+        <v>1250.64852</v>
       </c>
       <c r="AP113" s="1">
-        <f t="shared" ref="AP113" si="188">AP111+AP112</f>
-        <v>1365.5246504000002</v>
+        <f t="shared" ref="AP113" si="186">AP111+AP112</f>
+        <v>1267.7076324</v>
       </c>
       <c r="AQ113" s="1">
-        <f t="shared" ref="AQ113" si="189">AQ111+AQ112</f>
-        <v>1398.3774547520002</v>
+        <f t="shared" ref="AQ113" si="187">AQ111+AQ112</f>
+        <v>1285.028388468</v>
       </c>
       <c r="AR113" s="1">
-        <f t="shared" ref="AR113" si="190">AR111+AR112</f>
-        <v>1426.3450038470401</v>
+        <f t="shared" ref="AR113" si="188">AR111+AR112</f>
+        <v>1302.61522569156</v>
       </c>
       <c r="AS113" s="1">
-        <f t="shared" ref="AS113" si="191">AS111+AS112</f>
-        <v>1454.8719039239809</v>
+        <f t="shared" ref="AS113" si="189">AS111+AS112</f>
+        <v>1315.6413779484756</v>
       </c>
       <c r="AT113" s="1">
-        <f t="shared" ref="AT113" si="192">AT111+AT112</f>
-        <v>1483.9693420024605</v>
+        <f t="shared" ref="AT113" si="190">AT111+AT112</f>
+        <v>1328.7977917279604</v>
       </c>
       <c r="AU113" s="1">
-        <f t="shared" ref="AU113" si="193">AU111+AU112</f>
-        <v>1513.6487288425099</v>
+        <f t="shared" ref="AU113" si="191">AU111+AU112</f>
+        <v>1342.0857696452399</v>
       </c>
       <c r="AV113" s="1">
-        <f t="shared" ref="AV113" si="194">AV111+AV112</f>
-        <v>1543.92170341936</v>
+        <f t="shared" ref="AV113" si="192">AV111+AV112</f>
+        <v>1355.5066273416924</v>
       </c>
       <c r="AW113" s="1">
-        <f t="shared" ref="AW113" si="195">AW111+AW112</f>
-        <v>1574.8001374877472</v>
+        <f t="shared" ref="AW113" si="193">AW111+AW112</f>
+        <v>1369.0616936151093</v>
       </c>
       <c r="AX113" s="1">
-        <f t="shared" ref="AX113" si="196">AX111+AX112</f>
-        <v>1606.2961402375022</v>
+        <f t="shared" ref="AX113" si="194">AX111+AX112</f>
+        <v>1382.7523105512603</v>
       </c>
     </row>
     <row r="114" spans="2:148" s="7" customFormat="1" x14ac:dyDescent="0.3">
@@ -10104,19 +10183,19 @@
         <v>119</v>
       </c>
       <c r="O114" s="9">
-        <f t="shared" ref="O114:R114" si="197">O110+O111+O112</f>
+        <f t="shared" ref="O114:R114" si="195">O110+O111+O112</f>
         <v>-313.09999999999997</v>
       </c>
       <c r="P114" s="9">
-        <f t="shared" si="197"/>
+        <f t="shared" si="195"/>
         <v>-487.40000000000015</v>
       </c>
       <c r="Q114" s="9">
-        <f t="shared" si="197"/>
+        <f t="shared" si="195"/>
         <v>202.49999999999997</v>
       </c>
       <c r="R114" s="9">
-        <f t="shared" si="197"/>
+        <f t="shared" si="195"/>
         <v>78.899999999999949</v>
       </c>
       <c r="S114" s="9">
@@ -10124,492 +10203,495 @@
         <v>752.00000000000011</v>
       </c>
       <c r="T114" s="9">
-        <f t="shared" ref="T114:Z114" si="198">T110-T113</f>
+        <f t="shared" ref="T114:Z114" si="196">T110-T113</f>
         <v>498.60000000000019</v>
       </c>
       <c r="U114" s="9">
-        <f t="shared" si="198"/>
+        <f t="shared" si="196"/>
         <v>-116.0000000000006</v>
       </c>
       <c r="V114" s="9">
-        <f t="shared" si="198"/>
+        <f t="shared" si="196"/>
         <v>-701.4</v>
       </c>
       <c r="W114" s="9">
-        <f t="shared" si="198"/>
+        <f t="shared" si="196"/>
         <v>-2780.5999999999995</v>
       </c>
       <c r="X114" s="9">
-        <f t="shared" si="198"/>
+        <f t="shared" si="196"/>
         <v>-1062.7000000000003</v>
       </c>
       <c r="Y114" s="9">
-        <f t="shared" si="198"/>
+        <f t="shared" si="196"/>
         <v>-432.50000000000011</v>
       </c>
       <c r="Z114" s="9">
-        <f t="shared" si="198"/>
+        <f t="shared" si="196"/>
         <v>-623.10000000000025</v>
       </c>
-      <c r="AA114" s="9"/>
+      <c r="AA114" s="9">
+        <f t="shared" ref="AA114" si="197">AA110-AA113</f>
+        <v>334.5999999999998</v>
+      </c>
       <c r="AB114" s="9"/>
       <c r="AC114" s="9"/>
       <c r="AD114" s="9"/>
       <c r="AI114" s="9">
-        <f t="shared" ref="AI114:AK114" si="199">AI110-AI113</f>
+        <f t="shared" ref="AI114:AK114" si="198">AI110-AI113</f>
         <v>-382.00000000000045</v>
       </c>
       <c r="AJ114" s="9">
-        <f t="shared" si="199"/>
+        <f t="shared" si="198"/>
         <v>2327.0000000000009</v>
       </c>
       <c r="AK114" s="9">
-        <f t="shared" si="199"/>
+        <f t="shared" si="198"/>
         <v>967.60000000000105</v>
       </c>
       <c r="AL114" s="9">
-        <f t="shared" ref="AL114" si="200">AL110-AL113</f>
+        <f t="shared" ref="AL114" si="199">AL110-AL113</f>
         <v>433.20000000000186</v>
       </c>
       <c r="AM114" s="9">
-        <f t="shared" ref="AM114" si="201">AM110-AM113</f>
+        <f t="shared" ref="AM114" si="200">AM110-AM113</f>
         <v>-4898.8999999999978</v>
       </c>
       <c r="AN114" s="9">
-        <f t="shared" ref="AN114" si="202">AN110-AN113</f>
-        <v>3033.2130159999997</v>
+        <f t="shared" ref="AN114" si="201">AN110-AN113</f>
+        <v>2595.5612560000018</v>
       </c>
       <c r="AO114" s="9">
-        <f t="shared" ref="AO114" si="203">AO110-AO113</f>
-        <v>3759.1295359499982</v>
+        <f t="shared" ref="AO114" si="202">AO110-AO113</f>
+        <v>3144.2563345799999</v>
       </c>
       <c r="AP114" s="9">
-        <f t="shared" ref="AP114" si="204">AP110-AP113</f>
-        <v>4258.6597668532995</v>
+        <f t="shared" ref="AP114" si="203">AP110-AP113</f>
+        <v>3391.4542303902008</v>
       </c>
       <c r="AQ114" s="9">
-        <f t="shared" ref="AQ114" si="205">AQ110-AQ113</f>
-        <v>4669.6974984781646</v>
+        <f t="shared" ref="AQ114" si="204">AQ110-AQ113</f>
+        <v>3571.3157420863263</v>
       </c>
       <c r="AR114" s="9">
-        <f t="shared" ref="AR114" si="206">AR110-AR113</f>
-        <v>4976.9343283702565</v>
+        <f t="shared" ref="AR114" si="205">AR110-AR113</f>
+        <v>3658.5818629921732</v>
       </c>
       <c r="AS114" s="9">
-        <f t="shared" ref="AS114" si="207">AS110-AS113</f>
-        <v>5256.0145358025038</v>
+        <f t="shared" ref="AS114" si="206">AS110-AS113</f>
+        <v>3741.7909090701987</v>
       </c>
       <c r="AT114" s="9">
-        <f t="shared" ref="AT114" si="208">AT110-AT113</f>
-        <v>5463.3048387578392</v>
+        <f t="shared" ref="AT114" si="207">AT110-AT113</f>
+        <v>3768.5204855020484</v>
       </c>
       <c r="AU114" s="9">
-        <f t="shared" ref="AU114" si="209">AU110-AU113</f>
-        <v>5605.5803498884006</v>
+        <f t="shared" ref="AU114" si="208">AU110-AU113</f>
+        <v>3743.3889647089486</v>
       </c>
       <c r="AV114" s="9">
-        <f t="shared" ref="AV114" si="210">AV110-AV113</f>
-        <v>5731.3455200283397</v>
+        <f t="shared" ref="AV114" si="209">AV110-AV113</f>
+        <v>3718.1143276965022</v>
       </c>
       <c r="AW114" s="9">
-        <f t="shared" ref="AW114" si="211">AW110-AW113</f>
-        <v>5842.1362318102674</v>
+        <f t="shared" ref="AW114" si="210">AW110-AW113</f>
+        <v>3692.6526113445907</v>
       </c>
       <c r="AX114" s="9">
-        <f t="shared" ref="AX114" si="212">AX110-AX113</f>
-        <v>5939.3293821165062</v>
+        <f t="shared" ref="AX114" si="211">AX110-AX113</f>
+        <v>3666.9606534750083</v>
       </c>
       <c r="AY114" s="7">
         <f>AX114*(1+$BC$23)</f>
-        <v>5879.9360882953415</v>
+        <v>3630.2910469402582</v>
       </c>
       <c r="AZ114" s="7">
-        <f t="shared" ref="AZ114:DK114" si="213">AY114*(1+$BC$23)</f>
-        <v>5821.1367274123877</v>
+        <f t="shared" ref="AZ114:DK114" si="212">AY114*(1+$BC$23)</f>
+        <v>3593.9881364708554</v>
       </c>
       <c r="BA114" s="7">
+        <f t="shared" si="212"/>
+        <v>3558.0482551061468</v>
+      </c>
+      <c r="BB114" s="7">
+        <f t="shared" si="212"/>
+        <v>3522.4677725550855</v>
+      </c>
+      <c r="BC114" s="7">
+        <f t="shared" si="212"/>
+        <v>3487.2430948295346</v>
+      </c>
+      <c r="BD114" s="7">
+        <f t="shared" si="212"/>
+        <v>3452.3706638812391</v>
+      </c>
+      <c r="BE114" s="7">
+        <f t="shared" si="212"/>
+        <v>3417.8469572424269</v>
+      </c>
+      <c r="BF114" s="7">
+        <f t="shared" si="212"/>
+        <v>3383.6684876700028</v>
+      </c>
+      <c r="BG114" s="7">
+        <f t="shared" si="212"/>
+        <v>3349.8318027933028</v>
+      </c>
+      <c r="BH114" s="7">
+        <f t="shared" si="212"/>
+        <v>3316.3334847653696</v>
+      </c>
+      <c r="BI114" s="7">
+        <f t="shared" si="212"/>
+        <v>3283.1701499177157</v>
+      </c>
+      <c r="BJ114" s="7">
+        <f t="shared" si="212"/>
+        <v>3250.3384484185385</v>
+      </c>
+      <c r="BK114" s="7">
+        <f t="shared" si="212"/>
+        <v>3217.835063934353</v>
+      </c>
+      <c r="BL114" s="7">
+        <f t="shared" si="212"/>
+        <v>3185.6567132950095</v>
+      </c>
+      <c r="BM114" s="7">
+        <f t="shared" si="212"/>
+        <v>3153.8001461620593</v>
+      </c>
+      <c r="BN114" s="7">
+        <f t="shared" si="212"/>
+        <v>3122.2621447004385</v>
+      </c>
+      <c r="BO114" s="7">
+        <f t="shared" si="212"/>
+        <v>3091.0395232534343</v>
+      </c>
+      <c r="BP114" s="7">
+        <f t="shared" si="212"/>
+        <v>3060.1291280208998</v>
+      </c>
+      <c r="BQ114" s="7">
+        <f t="shared" si="212"/>
+        <v>3029.5278367406909</v>
+      </c>
+      <c r="BR114" s="7">
+        <f t="shared" si="212"/>
+        <v>2999.2325583732841</v>
+      </c>
+      <c r="BS114" s="7">
+        <f t="shared" si="212"/>
+        <v>2969.2402327895511</v>
+      </c>
+      <c r="BT114" s="7">
+        <f t="shared" si="212"/>
+        <v>2939.5478304616554</v>
+      </c>
+      <c r="BU114" s="7">
+        <f t="shared" si="212"/>
+        <v>2910.1523521570389</v>
+      </c>
+      <c r="BV114" s="7">
+        <f t="shared" si="212"/>
+        <v>2881.0508286354684</v>
+      </c>
+      <c r="BW114" s="7">
+        <f t="shared" si="212"/>
+        <v>2852.2403203491135</v>
+      </c>
+      <c r="BX114" s="7">
+        <f t="shared" si="212"/>
+        <v>2823.7179171456223</v>
+      </c>
+      <c r="BY114" s="7">
+        <f t="shared" si="212"/>
+        <v>2795.480737974166</v>
+      </c>
+      <c r="BZ114" s="7">
+        <f t="shared" si="212"/>
+        <v>2767.5259305944242</v>
+      </c>
+      <c r="CA114" s="7">
+        <f t="shared" si="212"/>
+        <v>2739.85067128848</v>
+      </c>
+      <c r="CB114" s="7">
+        <f t="shared" si="212"/>
+        <v>2712.4521645755954</v>
+      </c>
+      <c r="CC114" s="7">
+        <f t="shared" si="212"/>
+        <v>2685.3276429298394</v>
+      </c>
+      <c r="CD114" s="7">
+        <f t="shared" si="212"/>
+        <v>2658.4743665005408</v>
+      </c>
+      <c r="CE114" s="7">
+        <f t="shared" si="212"/>
+        <v>2631.8896228355352</v>
+      </c>
+      <c r="CF114" s="7">
+        <f t="shared" si="212"/>
+        <v>2605.5707266071799</v>
+      </c>
+      <c r="CG114" s="7">
+        <f t="shared" si="212"/>
+        <v>2579.5150193411082</v>
+      </c>
+      <c r="CH114" s="7">
+        <f t="shared" si="212"/>
+        <v>2553.719869147697</v>
+      </c>
+      <c r="CI114" s="7">
+        <f t="shared" si="212"/>
+        <v>2528.18267045622</v>
+      </c>
+      <c r="CJ114" s="7">
+        <f t="shared" si="212"/>
+        <v>2502.9008437516577</v>
+      </c>
+      <c r="CK114" s="7">
+        <f t="shared" si="212"/>
+        <v>2477.8718353141412</v>
+      </c>
+      <c r="CL114" s="7">
+        <f t="shared" si="212"/>
+        <v>2453.0931169609999</v>
+      </c>
+      <c r="CM114" s="7">
+        <f t="shared" si="212"/>
+        <v>2428.5621857913898</v>
+      </c>
+      <c r="CN114" s="7">
+        <f t="shared" si="212"/>
+        <v>2404.2765639334757</v>
+      </c>
+      <c r="CO114" s="7">
+        <f t="shared" si="212"/>
+        <v>2380.2337982941408</v>
+      </c>
+      <c r="CP114" s="7">
+        <f t="shared" si="212"/>
+        <v>2356.4314603111993</v>
+      </c>
+      <c r="CQ114" s="7">
+        <f t="shared" si="212"/>
+        <v>2332.8671457080873</v>
+      </c>
+      <c r="CR114" s="7">
+        <f t="shared" si="212"/>
+        <v>2309.5384742510064</v>
+      </c>
+      <c r="CS114" s="7">
+        <f t="shared" si="212"/>
+        <v>2286.4430895084961</v>
+      </c>
+      <c r="CT114" s="7">
+        <f t="shared" si="212"/>
+        <v>2263.5786586134109</v>
+      </c>
+      <c r="CU114" s="7">
+        <f t="shared" si="212"/>
+        <v>2240.9428720272767</v>
+      </c>
+      <c r="CV114" s="7">
+        <f t="shared" si="212"/>
+        <v>2218.5334433070038</v>
+      </c>
+      <c r="CW114" s="7">
+        <f t="shared" si="212"/>
+        <v>2196.3481088739336</v>
+      </c>
+      <c r="CX114" s="7">
+        <f t="shared" si="212"/>
+        <v>2174.3846277851944</v>
+      </c>
+      <c r="CY114" s="7">
+        <f t="shared" si="212"/>
+        <v>2152.6407815073426</v>
+      </c>
+      <c r="CZ114" s="7">
+        <f t="shared" si="212"/>
+        <v>2131.1143736922691</v>
+      </c>
+      <c r="DA114" s="7">
+        <f t="shared" si="212"/>
+        <v>2109.8032299553465</v>
+      </c>
+      <c r="DB114" s="7">
+        <f t="shared" si="212"/>
+        <v>2088.7051976557932</v>
+      </c>
+      <c r="DC114" s="7">
+        <f t="shared" si="212"/>
+        <v>2067.8181456792354</v>
+      </c>
+      <c r="DD114" s="7">
+        <f t="shared" si="212"/>
+        <v>2047.139964222443</v>
+      </c>
+      <c r="DE114" s="7">
+        <f t="shared" si="212"/>
+        <v>2026.6685645802186</v>
+      </c>
+      <c r="DF114" s="7">
+        <f t="shared" si="212"/>
+        <v>2006.4018789344163</v>
+      </c>
+      <c r="DG114" s="7">
+        <f t="shared" si="212"/>
+        <v>1986.3378601450722</v>
+      </c>
+      <c r="DH114" s="7">
+        <f t="shared" si="212"/>
+        <v>1966.4744815436216</v>
+      </c>
+      <c r="DI114" s="7">
+        <f t="shared" si="212"/>
+        <v>1946.8097367281853</v>
+      </c>
+      <c r="DJ114" s="7">
+        <f t="shared" si="212"/>
+        <v>1927.3416393609034</v>
+      </c>
+      <c r="DK114" s="7">
+        <f t="shared" si="212"/>
+        <v>1908.0682229672943</v>
+      </c>
+      <c r="DL114" s="7">
+        <f t="shared" ref="DL114:ER114" si="213">DK114*(1+$BC$23)</f>
+        <v>1888.9875407376214</v>
+      </c>
+      <c r="DM114" s="7">
         <f t="shared" si="213"/>
-        <v>5762.9253601382634</v>
-      </c>
-      <c r="BB114" s="7">
+        <v>1870.0976653302453</v>
+      </c>
+      <c r="DN114" s="7">
         <f t="shared" si="213"/>
-        <v>5705.2961065368809</v>
-      </c>
-      <c r="BC114" s="7">
+        <v>1851.3966886769429</v>
+      </c>
+      <c r="DO114" s="7">
         <f t="shared" si="213"/>
-        <v>5648.2431454715124</v>
-      </c>
-      <c r="BD114" s="7">
+        <v>1832.8827217901735</v>
+      </c>
+      <c r="DP114" s="7">
         <f t="shared" si="213"/>
-        <v>5591.7607140167975</v>
-      </c>
-      <c r="BE114" s="7">
+        <v>1814.5538945722717</v>
+      </c>
+      <c r="DQ114" s="7">
         <f t="shared" si="213"/>
-        <v>5535.8431068766295</v>
-      </c>
-      <c r="BF114" s="7">
+        <v>1796.4083556265489</v>
+      </c>
+      <c r="DR114" s="7">
         <f t="shared" si="213"/>
-        <v>5480.4846758078629</v>
-      </c>
-      <c r="BG114" s="7">
+        <v>1778.4442720702834</v>
+      </c>
+      <c r="DS114" s="7">
         <f t="shared" si="213"/>
-        <v>5425.6798290497845</v>
-      </c>
-      <c r="BH114" s="7">
+        <v>1760.6598293495806</v>
+      </c>
+      <c r="DT114" s="7">
         <f t="shared" si="213"/>
-        <v>5371.423030759287</v>
-      </c>
-      <c r="BI114" s="7">
+        <v>1743.0532310560848</v>
+      </c>
+      <c r="DU114" s="7">
         <f t="shared" si="213"/>
-        <v>5317.7088004516945</v>
-      </c>
-      <c r="BJ114" s="7">
+        <v>1725.6226987455238</v>
+      </c>
+      <c r="DV114" s="7">
         <f t="shared" si="213"/>
-        <v>5264.5317124471776</v>
-      </c>
-      <c r="BK114" s="7">
+        <v>1708.3664717580687</v>
+      </c>
+      <c r="DW114" s="7">
         <f t="shared" si="213"/>
-        <v>5211.8863953227055</v>
-      </c>
-      <c r="BL114" s="7">
+        <v>1691.282807040488</v>
+      </c>
+      <c r="DX114" s="7">
         <f t="shared" si="213"/>
-        <v>5159.7675313694781</v>
-      </c>
-      <c r="BM114" s="7">
+        <v>1674.3699789700831</v>
+      </c>
+      <c r="DY114" s="7">
         <f t="shared" si="213"/>
-        <v>5108.1698560557834</v>
-      </c>
-      <c r="BN114" s="7">
+        <v>1657.6262791803822</v>
+      </c>
+      <c r="DZ114" s="7">
         <f t="shared" si="213"/>
-        <v>5057.0881574952255</v>
-      </c>
-      <c r="BO114" s="7">
+        <v>1641.0500163885783</v>
+      </c>
+      <c r="EA114" s="7">
         <f t="shared" si="213"/>
-        <v>5006.5172759202733</v>
-      </c>
-      <c r="BP114" s="7">
+        <v>1624.6395162246924</v>
+      </c>
+      <c r="EB114" s="7">
         <f t="shared" si="213"/>
-        <v>4956.4521031610702</v>
-      </c>
-      <c r="BQ114" s="7">
+        <v>1608.3931210624455</v>
+      </c>
+      <c r="EC114" s="7">
         <f t="shared" si="213"/>
-        <v>4906.8875821294596</v>
-      </c>
-      <c r="BR114" s="7">
+        <v>1592.309189851821</v>
+      </c>
+      <c r="ED114" s="7">
         <f t="shared" si="213"/>
-        <v>4857.818706308165</v>
-      </c>
-      <c r="BS114" s="7">
+        <v>1576.3860979533029</v>
+      </c>
+      <c r="EE114" s="7">
         <f t="shared" si="213"/>
-        <v>4809.2405192450833</v>
-      </c>
-      <c r="BT114" s="7">
+        <v>1560.6222369737698</v>
+      </c>
+      <c r="EF114" s="7">
         <f t="shared" si="213"/>
-        <v>4761.1481140526321</v>
-      </c>
-      <c r="BU114" s="7">
+        <v>1545.0160146040321</v>
+      </c>
+      <c r="EG114" s="7">
         <f t="shared" si="213"/>
-        <v>4713.5366329121061</v>
-      </c>
-      <c r="BV114" s="7">
+        <v>1529.5658544579917</v>
+      </c>
+      <c r="EH114" s="7">
         <f t="shared" si="213"/>
-        <v>4666.401266582985</v>
-      </c>
-      <c r="BW114" s="7">
+        <v>1514.2701959134117</v>
+      </c>
+      <c r="EI114" s="7">
         <f t="shared" si="213"/>
-        <v>4619.7372539171547</v>
-      </c>
-      <c r="BX114" s="7">
+        <v>1499.1274939542775</v>
+      </c>
+      <c r="EJ114" s="7">
         <f t="shared" si="213"/>
-        <v>4573.539881377983</v>
-      </c>
-      <c r="BY114" s="7">
+        <v>1484.1362190147347</v>
+      </c>
+      <c r="EK114" s="7">
         <f t="shared" si="213"/>
-        <v>4527.8044825642028</v>
-      </c>
-      <c r="BZ114" s="7">
+        <v>1469.2948568245874</v>
+      </c>
+      <c r="EL114" s="7">
         <f t="shared" si="213"/>
-        <v>4482.5264377385611</v>
-      </c>
-      <c r="CA114" s="7">
+        <v>1454.6019082563416</v>
+      </c>
+      <c r="EM114" s="7">
         <f t="shared" si="213"/>
-        <v>4437.7011733611753</v>
-      </c>
-      <c r="CB114" s="7">
+        <v>1440.0558891737783</v>
+      </c>
+      <c r="EN114" s="7">
         <f t="shared" si="213"/>
-        <v>4393.3241616275636</v>
-      </c>
-      <c r="CC114" s="7">
+        <v>1425.6553302820405</v>
+      </c>
+      <c r="EO114" s="7">
         <f t="shared" si="213"/>
-        <v>4349.3909200112876</v>
-      </c>
-      <c r="CD114" s="7">
+        <v>1411.39877697922</v>
+      </c>
+      <c r="EP114" s="7">
         <f t="shared" si="213"/>
-        <v>4305.8970108111744</v>
-      </c>
-      <c r="CE114" s="7">
+        <v>1397.2847892094278</v>
+      </c>
+      <c r="EQ114" s="7">
         <f t="shared" si="213"/>
-        <v>4262.8380407030627</v>
-      </c>
-      <c r="CF114" s="7">
+        <v>1383.3119413173335</v>
+      </c>
+      <c r="ER114" s="7">
         <f t="shared" si="213"/>
-        <v>4220.2096602960319</v>
-      </c>
-      <c r="CG114" s="7">
-        <f t="shared" si="213"/>
-        <v>4178.0075636930715</v>
-      </c>
-      <c r="CH114" s="7">
-        <f t="shared" si="213"/>
-        <v>4136.2274880561408</v>
-      </c>
-      <c r="CI114" s="7">
-        <f t="shared" si="213"/>
-        <v>4094.8652131755794</v>
-      </c>
-      <c r="CJ114" s="7">
-        <f t="shared" si="213"/>
-        <v>4053.9165610438235</v>
-      </c>
-      <c r="CK114" s="7">
-        <f t="shared" si="213"/>
-        <v>4013.3773954333851</v>
-      </c>
-      <c r="CL114" s="7">
-        <f t="shared" si="213"/>
-        <v>3973.2436214790514</v>
-      </c>
-      <c r="CM114" s="7">
-        <f t="shared" si="213"/>
-        <v>3933.5111852642608</v>
-      </c>
-      <c r="CN114" s="7">
-        <f t="shared" si="213"/>
-        <v>3894.1760734116183</v>
-      </c>
-      <c r="CO114" s="7">
-        <f t="shared" si="213"/>
-        <v>3855.2343126775022</v>
-      </c>
-      <c r="CP114" s="7">
-        <f t="shared" si="213"/>
-        <v>3816.681969550727</v>
-      </c>
-      <c r="CQ114" s="7">
-        <f t="shared" si="213"/>
-        <v>3778.5151498552195</v>
-      </c>
-      <c r="CR114" s="7">
-        <f t="shared" si="213"/>
-        <v>3740.7299983566672</v>
-      </c>
-      <c r="CS114" s="7">
-        <f t="shared" si="213"/>
-        <v>3703.3226983731006</v>
-      </c>
-      <c r="CT114" s="7">
-        <f t="shared" si="213"/>
-        <v>3666.2894713893697</v>
-      </c>
-      <c r="CU114" s="7">
-        <f t="shared" si="213"/>
-        <v>3629.6265766754759</v>
-      </c>
-      <c r="CV114" s="7">
-        <f t="shared" si="213"/>
-        <v>3593.330310908721</v>
-      </c>
-      <c r="CW114" s="7">
-        <f t="shared" si="213"/>
-        <v>3557.3970077996337</v>
-      </c>
-      <c r="CX114" s="7">
-        <f t="shared" si="213"/>
-        <v>3521.8230377216373</v>
-      </c>
-      <c r="CY114" s="7">
-        <f t="shared" si="213"/>
-        <v>3486.6048073444208</v>
-      </c>
-      <c r="CZ114" s="7">
-        <f t="shared" si="213"/>
-        <v>3451.7387592709765</v>
-      </c>
-      <c r="DA114" s="7">
-        <f t="shared" si="213"/>
-        <v>3417.2213716782667</v>
-      </c>
-      <c r="DB114" s="7">
-        <f t="shared" si="213"/>
-        <v>3383.0491579614841</v>
-      </c>
-      <c r="DC114" s="7">
-        <f t="shared" si="213"/>
-        <v>3349.2186663818693</v>
-      </c>
-      <c r="DD114" s="7">
-        <f t="shared" si="213"/>
-        <v>3315.7264797180505</v>
-      </c>
-      <c r="DE114" s="7">
-        <f t="shared" si="213"/>
-        <v>3282.5692149208699</v>
-      </c>
-      <c r="DF114" s="7">
-        <f t="shared" si="213"/>
-        <v>3249.743522771661</v>
-      </c>
-      <c r="DG114" s="7">
-        <f t="shared" si="213"/>
-        <v>3217.2460875439442</v>
-      </c>
-      <c r="DH114" s="7">
-        <f t="shared" si="213"/>
-        <v>3185.0736266685049</v>
-      </c>
-      <c r="DI114" s="7">
-        <f t="shared" si="213"/>
-        <v>3153.2228904018198</v>
-      </c>
-      <c r="DJ114" s="7">
-        <f t="shared" si="213"/>
-        <v>3121.6906614978016</v>
-      </c>
-      <c r="DK114" s="7">
-        <f t="shared" si="213"/>
-        <v>3090.4737548828234</v>
-      </c>
-      <c r="DL114" s="7">
-        <f t="shared" ref="DL114:ER114" si="214">DK114*(1+$BC$23)</f>
-        <v>3059.5690173339954</v>
-      </c>
-      <c r="DM114" s="7">
-        <f t="shared" si="214"/>
-        <v>3028.9733271606556</v>
-      </c>
-      <c r="DN114" s="7">
-        <f t="shared" si="214"/>
-        <v>2998.683593889049</v>
-      </c>
-      <c r="DO114" s="7">
-        <f t="shared" si="214"/>
-        <v>2968.6967579501584</v>
-      </c>
-      <c r="DP114" s="7">
-        <f t="shared" si="214"/>
-        <v>2939.0097903706569</v>
-      </c>
-      <c r="DQ114" s="7">
-        <f t="shared" si="214"/>
-        <v>2909.6196924669503</v>
-      </c>
-      <c r="DR114" s="7">
-        <f t="shared" si="214"/>
-        <v>2880.5234955422807</v>
-      </c>
-      <c r="DS114" s="7">
-        <f t="shared" si="214"/>
-        <v>2851.7182605868579</v>
-      </c>
-      <c r="DT114" s="7">
-        <f t="shared" si="214"/>
-        <v>2823.2010779809893</v>
-      </c>
-      <c r="DU114" s="7">
-        <f t="shared" si="214"/>
-        <v>2794.9690672011793</v>
-      </c>
-      <c r="DV114" s="7">
-        <f t="shared" si="214"/>
-        <v>2767.0193765291674</v>
-      </c>
-      <c r="DW114" s="7">
-        <f t="shared" si="214"/>
-        <v>2739.3491827638759</v>
-      </c>
-      <c r="DX114" s="7">
-        <f t="shared" si="214"/>
-        <v>2711.9556909362373</v>
-      </c>
-      <c r="DY114" s="7">
-        <f t="shared" si="214"/>
-        <v>2684.8361340268748</v>
-      </c>
-      <c r="DZ114" s="7">
-        <f t="shared" si="214"/>
-        <v>2657.9877726866061</v>
-      </c>
-      <c r="EA114" s="7">
-        <f t="shared" si="214"/>
-        <v>2631.4078949597401</v>
-      </c>
-      <c r="EB114" s="7">
-        <f t="shared" si="214"/>
-        <v>2605.0938160101427</v>
-      </c>
-      <c r="EC114" s="7">
-        <f t="shared" si="214"/>
-        <v>2579.0428778500414</v>
-      </c>
-      <c r="ED114" s="7">
-        <f t="shared" si="214"/>
-        <v>2553.2524490715409</v>
-      </c>
-      <c r="EE114" s="7">
-        <f t="shared" si="214"/>
-        <v>2527.7199245808256</v>
-      </c>
-      <c r="EF114" s="7">
-        <f t="shared" si="214"/>
-        <v>2502.4427253350173</v>
-      </c>
-      <c r="EG114" s="7">
-        <f t="shared" si="214"/>
-        <v>2477.4182980816672</v>
-      </c>
-      <c r="EH114" s="7">
-        <f t="shared" si="214"/>
-        <v>2452.6441151008507</v>
-      </c>
-      <c r="EI114" s="7">
-        <f t="shared" si="214"/>
-        <v>2428.1176739498424</v>
-      </c>
-      <c r="EJ114" s="7">
-        <f t="shared" si="214"/>
-        <v>2403.8364972103441</v>
-      </c>
-      <c r="EK114" s="7">
-        <f t="shared" si="214"/>
-        <v>2379.7981322382407</v>
-      </c>
-      <c r="EL114" s="7">
-        <f t="shared" si="214"/>
-        <v>2356.0001509158583</v>
-      </c>
-      <c r="EM114" s="7">
-        <f t="shared" si="214"/>
-        <v>2332.4401494066997</v>
-      </c>
-      <c r="EN114" s="7">
-        <f t="shared" si="214"/>
-        <v>2309.1157479126327</v>
-      </c>
-      <c r="EO114" s="7">
-        <f t="shared" si="214"/>
-        <v>2286.0245904335065</v>
-      </c>
-      <c r="EP114" s="7">
-        <f t="shared" si="214"/>
-        <v>2263.1643445291716</v>
-      </c>
-      <c r="EQ114" s="7">
-        <f t="shared" si="214"/>
-        <v>2240.5327010838796</v>
-      </c>
-      <c r="ER114" s="7">
-        <f t="shared" si="214"/>
-        <v>2218.1273740730408</v>
+        <v>1369.4788219041602</v>
       </c>
     </row>
     <row r="115" spans="2:148" x14ac:dyDescent="0.3">
@@ -10617,39 +10699,47 @@
     </row>
     <row r="116" spans="2:148" x14ac:dyDescent="0.3">
       <c r="W116" s="10">
-        <f t="shared" ref="W116:Y116" si="215">W111/S111-1</f>
+        <f t="shared" ref="W116:Y116" si="214">W111/S111-1</f>
         <v>-0.46929180135174853</v>
       </c>
       <c r="X116" s="10">
-        <f t="shared" si="215"/>
+        <f t="shared" si="214"/>
         <v>7.1865443425076503E-2</v>
       </c>
       <c r="Y116" s="10">
-        <f t="shared" si="215"/>
+        <f t="shared" si="214"/>
         <v>2.0777576853526258</v>
       </c>
       <c r="Z116" s="10">
         <f>Z111/V111-1</f>
         <v>0.40858725761772763</v>
       </c>
+      <c r="AA116" s="10">
+        <f>AA111/W111-1</f>
+        <v>-2.2148394241418012E-3</v>
+      </c>
       <c r="BA116" s="10"/>
     </row>
     <row r="117" spans="2:148" x14ac:dyDescent="0.3">
       <c r="W117" s="10">
-        <f t="shared" ref="W117:Z117" si="216">W112/S112-1</f>
+        <f t="shared" ref="W117:AA117" si="215">W112/S112-1</f>
         <v>0.65571616294349555</v>
       </c>
       <c r="X117" s="10">
-        <f t="shared" si="216"/>
+        <f t="shared" si="215"/>
         <v>-1.2499999999999956E-2</v>
       </c>
       <c r="Y117" s="10">
-        <f t="shared" si="216"/>
+        <f t="shared" si="215"/>
         <v>5.6151940545003942E-2</v>
       </c>
       <c r="Z117" s="10">
-        <f t="shared" si="216"/>
+        <f t="shared" si="215"/>
         <v>-0.15542938254080907</v>
+      </c>
+      <c r="AA117" s="10">
+        <f t="shared" si="215"/>
+        <v>-0.14841269841269844</v>
       </c>
       <c r="BA117" s="10"/>
     </row>
@@ -10659,7 +10749,7 @@
       </c>
       <c r="BA118" s="14">
         <f>NPV(BC24,AN114:ER114)</f>
-        <v>31832.125734523866</v>
+        <v>22618.244104935922</v>
       </c>
     </row>
     <row r="119" spans="2:148" x14ac:dyDescent="0.3">
@@ -10668,7 +10758,7 @@
       </c>
       <c r="BA119" s="1">
         <f>BA118/Main!D13</f>
-        <v>5624.0504831314247</v>
+        <v>3996.1562022854987</v>
       </c>
     </row>
     <row r="120" spans="2:148" x14ac:dyDescent="0.3">
@@ -10732,7 +10822,7 @@
       </c>
       <c r="BA120" s="1">
         <f>Main!D10</f>
-        <v>-1257.5441696113076</v>
+        <v>-1344.0106007067136</v>
       </c>
     </row>
     <row r="121" spans="2:148" x14ac:dyDescent="0.3">
@@ -10762,7 +10852,7 @@
       </c>
       <c r="BA121" s="1">
         <f>BA119+BA120</f>
-        <v>4366.5063135201171</v>
+        <v>2652.1456015787853</v>
       </c>
     </row>
     <row r="122" spans="2:148" x14ac:dyDescent="0.3">
@@ -10792,7 +10882,7 @@
       </c>
       <c r="BA122" s="2">
         <f>BA121/AX19</f>
-        <v>14.897667395155636</v>
+        <v>9.4787190907033061</v>
       </c>
     </row>
     <row r="123" spans="2:148" x14ac:dyDescent="0.3">
@@ -10822,7 +10912,7 @@
       </c>
       <c r="BA123" s="2">
         <f>Main!D3</f>
-        <v>13.77</v>
+        <v>13.28</v>
       </c>
     </row>
     <row r="124" spans="2:148" x14ac:dyDescent="0.3">
@@ -10852,7 +10942,7 @@
       </c>
       <c r="BA124" s="11">
         <f>BA122/BA123-1</f>
-        <v>8.189305701929106E-2</v>
+        <v>-0.28624103232655829</v>
       </c>
     </row>
     <row r="125" spans="2:148" x14ac:dyDescent="0.3">
@@ -11413,28 +11503,28 @@
       </c>
       <c r="O149" s="1"/>
       <c r="P149" s="1">
-        <f t="shared" ref="P149:V149" si="217">P120+SUM(P121:P148)</f>
+        <f t="shared" ref="P149:V149" si="216">P120+SUM(P121:P148)</f>
         <v>-800.50000000000011</v>
       </c>
       <c r="Q149" s="1">
-        <f t="shared" si="217"/>
+        <f t="shared" si="216"/>
         <v>-598.00000000000023</v>
       </c>
       <c r="R149" s="1">
-        <f t="shared" si="217"/>
+        <f t="shared" si="216"/>
         <v>1690.9999999999998</v>
       </c>
       <c r="S149" s="1"/>
       <c r="T149" s="1">
-        <f t="shared" si="217"/>
+        <f t="shared" si="216"/>
         <v>1999.2000000000005</v>
       </c>
       <c r="U149" s="1">
-        <f t="shared" si="217"/>
+        <f t="shared" si="216"/>
         <v>2059.5999999999995</v>
       </c>
       <c r="V149" s="1">
-        <f t="shared" si="217"/>
+        <f t="shared" si="216"/>
         <v>1643.5</v>
       </c>
       <c r="W149" s="1"/>

--- a/Financial Analysis/STNE.xlsx
+++ b/Financial Analysis/STNE.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EF69E5E-475C-4982-825E-7BA0B0E09635}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35F0F8F3-5586-47C4-A8BA-245EBF92EEC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{739ADCDA-92AA-4302-8B1F-47F1B6FD860D}"/>
   </bookViews>
@@ -25,8 +25,42 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Anton Mniszek</author>
+  </authors>
+  <commentList>
+    <comment ref="AB2" authorId="0" shapeId="0" xr:uid="{DFA0DBB1-5BB8-4E27-A794-D1E3AEE68554}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Anton Mniszek:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+sold Linx</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="130">
   <si>
     <t>Price</t>
   </si>
@@ -413,9 +447,6 @@
   </si>
   <si>
     <t>Impairment</t>
-  </si>
-  <si>
-    <t>Q125 6K</t>
   </si>
   <si>
     <t>Undervalued</t>
@@ -431,7 +462,7 @@
     <numFmt numFmtId="166" formatCode="#,##0;[Red]#,##0"/>
     <numFmt numFmtId="167" formatCode="#,##0_ ;[Red]\-#,##0\ "/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -478,6 +509,19 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -549,14 +593,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>27</xdr:col>
-      <xdr:colOff>15240</xdr:colOff>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>30480</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>27</xdr:col>
-      <xdr:colOff>15240</xdr:colOff>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>30480</xdr:colOff>
       <xdr:row>122</xdr:row>
       <xdr:rowOff>106680</xdr:rowOff>
     </xdr:to>
@@ -573,7 +617,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="17312640" y="7620"/>
+          <a:off x="17937480" y="7620"/>
           <a:ext cx="0" cy="22410420"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -970,17 +1014,17 @@
         <v>0</v>
       </c>
       <c r="D3" s="2">
-        <v>13.28</v>
+        <v>15.35</v>
       </c>
       <c r="E3" s="6">
-        <v>45804</v>
+        <v>45892</v>
       </c>
       <c r="F3" s="6">
         <f ca="1">TODAY()</f>
-        <v>45804</v>
+        <v>45892</v>
       </c>
       <c r="G3" s="6">
-        <v>45882</v>
+        <v>45979</v>
       </c>
     </row>
     <row r="4" spans="3:9" x14ac:dyDescent="0.3">
@@ -988,11 +1032,11 @@
         <v>1</v>
       </c>
       <c r="D4" s="1">
-        <f>279.8</f>
-        <v>279.8</v>
+        <f>274.2</f>
+        <v>274.2</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="5" spans="3:9" x14ac:dyDescent="0.3">
@@ -1001,7 +1045,7 @@
       </c>
       <c r="D5" s="1">
         <f>D3*D4</f>
-        <v>3715.7440000000001</v>
+        <v>4208.9699999999993</v>
       </c>
     </row>
     <row r="6" spans="3:9" x14ac:dyDescent="0.3">
@@ -1009,11 +1053,11 @@
         <v>5</v>
       </c>
       <c r="D6" s="1">
-        <f>5650.4+146.2+32.1</f>
-        <v>5828.7</v>
+        <f>5185.6+234.8+20.8</f>
+        <v>5441.2000000000007</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="7" spans="3:9" x14ac:dyDescent="0.3">
@@ -1021,11 +1065,11 @@
         <v>6</v>
       </c>
       <c r="D7" s="1">
-        <f>2853+2086.1+6025+2471.7</f>
-        <v>13435.8</v>
+        <f>3116.6+1999.4+6221.6+2618.8</f>
+        <v>13956.400000000001</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="8" spans="3:9" x14ac:dyDescent="0.3">
@@ -1034,10 +1078,10 @@
       </c>
       <c r="D8" s="1">
         <f>D6/D13</f>
-        <v>1029.8056537102473</v>
+        <v>1003.9114391143913</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I8" t="s">
         <v>78</v>
@@ -1049,10 +1093,10 @@
       </c>
       <c r="D9" s="1">
         <f>D7/D13</f>
-        <v>2373.8162544169609</v>
+        <v>2574.9815498154985</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="10" spans="3:9" x14ac:dyDescent="0.3">
@@ -1061,7 +1105,7 @@
       </c>
       <c r="D10" s="1">
         <f>D8-D9</f>
-        <v>-1344.0106007067136</v>
+        <v>-1571.0701107011073</v>
       </c>
       <c r="E10" s="5"/>
     </row>
@@ -1071,7 +1115,7 @@
       </c>
       <c r="D11" s="1">
         <f>D5-D10</f>
-        <v>5059.754600706714</v>
+        <v>5780.0401107011066</v>
       </c>
     </row>
     <row r="13" spans="3:9" x14ac:dyDescent="0.3">
@@ -1079,7 +1123,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="3">
-        <v>5.66</v>
+        <v>5.42</v>
       </c>
     </row>
   </sheetData>
@@ -1088,7 +1132,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28E5E6C2-86A3-4082-9B40-CDF31EC12934}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28E5E6C2-86A3-4082-9B40-CDF31EC12934}">
   <dimension ref="B2:ER151"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1098,7 +1142,7 @@
     <col min="55" max="55" width="17.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:50" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:51" x14ac:dyDescent="0.3">
       <c r="C2" s="4" t="s">
         <v>14</v>
       </c>
@@ -1238,7 +1282,7 @@
         <v>2035</v>
       </c>
     </row>
-    <row r="3" spans="2:50" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:51" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>38</v>
       </c>
@@ -1285,16 +1329,15 @@
         <v>684.4</v>
       </c>
       <c r="AB3" s="1">
-        <f>X3*0.92</f>
-        <v>742.9</v>
+        <v>658.1</v>
       </c>
       <c r="AC3" s="1">
-        <f>Y3*0.94</f>
-        <v>779.16599999999994</v>
+        <f>Y3*0.91</f>
+        <v>754.29899999999998</v>
       </c>
       <c r="AD3" s="1">
-        <f>Z3*0.97</f>
-        <v>804.90599999999995</v>
+        <f>Z3*0.95</f>
+        <v>788.31</v>
       </c>
       <c r="AH3" s="1">
         <v>770.3</v>
@@ -1319,50 +1362,50 @@
       </c>
       <c r="AN3" s="1">
         <f>SUM(AA3:AD3)</f>
-        <v>3011.3719999999998</v>
+        <v>2885.1089999999999</v>
       </c>
       <c r="AO3" s="1">
-        <f t="shared" ref="AO3:AX4" si="0">AN3*1.01</f>
-        <v>3041.4857199999997</v>
+        <f>AN3*1.02</f>
+        <v>2942.8111800000001</v>
       </c>
       <c r="AP3" s="1">
-        <f t="shared" si="0"/>
-        <v>3071.9005771999996</v>
+        <f t="shared" ref="AP3:AX3" si="0">AO3*1.01</f>
+        <v>2972.2392918</v>
       </c>
       <c r="AQ3" s="1">
         <f t="shared" si="0"/>
-        <v>3102.6195829719995</v>
+        <v>3001.961684718</v>
       </c>
       <c r="AR3" s="1">
         <f t="shared" si="0"/>
-        <v>3133.6457788017196</v>
+        <v>3031.9813015651798</v>
       </c>
       <c r="AS3" s="1">
         <f t="shared" si="0"/>
-        <v>3164.9822365897367</v>
+        <v>3062.3011145808318</v>
       </c>
       <c r="AT3" s="1">
         <f t="shared" si="0"/>
-        <v>3196.632058955634</v>
+        <v>3092.9241257266403</v>
       </c>
       <c r="AU3" s="1">
         <f t="shared" si="0"/>
-        <v>3228.5983795451903</v>
+        <v>3123.8533669839067</v>
       </c>
       <c r="AV3" s="1">
         <f t="shared" si="0"/>
-        <v>3260.8843633406423</v>
+        <v>3155.0919006537456</v>
       </c>
       <c r="AW3" s="1">
         <f t="shared" si="0"/>
-        <v>3293.4932069740489</v>
+        <v>3186.6428196602833</v>
       </c>
       <c r="AX3" s="1">
         <f t="shared" si="0"/>
-        <v>3326.4281390437895</v>
-      </c>
-    </row>
-    <row r="4" spans="2:50" x14ac:dyDescent="0.3">
+        <v>3218.5092478568863</v>
+      </c>
+    </row>
+    <row r="4" spans="2:51" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>39</v>
       </c>
@@ -1409,16 +1452,13 @@
         <v>493.2</v>
       </c>
       <c r="AB4" s="1">
-        <f>X4*1.03</f>
-        <v>466.899</v>
+        <v>218.9</v>
       </c>
       <c r="AC4" s="1">
-        <f t="shared" ref="AC4:AD4" si="1">Y4*1.02</f>
-        <v>474.91200000000003</v>
+        <v>225</v>
       </c>
       <c r="AD4" s="1">
-        <f t="shared" si="1"/>
-        <v>480.726</v>
+        <v>240</v>
       </c>
       <c r="AH4" s="1">
         <v>331.6</v>
@@ -1442,51 +1482,51 @@
         <v>1846.8999999999999</v>
       </c>
       <c r="AN4" s="1">
-        <f t="shared" ref="AN4:AN17" si="2">SUM(AA4:AD4)</f>
-        <v>1915.7370000000001</v>
+        <f t="shared" ref="AN4:AN17" si="1">SUM(AA4:AD4)</f>
+        <v>1177.0999999999999</v>
       </c>
       <c r="AO4" s="1">
         <f>AN4*1.02</f>
-        <v>1954.0517400000001</v>
+        <v>1200.6419999999998</v>
       </c>
       <c r="AP4" s="1">
-        <f t="shared" ref="AP4:AS4" si="3">AO4*1.02</f>
-        <v>1993.1327748000001</v>
+        <f>AO4*1.1</f>
+        <v>1320.7061999999999</v>
       </c>
       <c r="AQ4" s="1">
-        <f t="shared" si="3"/>
-        <v>2032.9954302960002</v>
+        <f>AP4*1.08</f>
+        <v>1426.3626959999999</v>
       </c>
       <c r="AR4" s="1">
-        <f t="shared" si="3"/>
-        <v>2073.6553389019205</v>
+        <f>AQ4*1.06</f>
+        <v>1511.94445776</v>
       </c>
       <c r="AS4" s="1">
-        <f t="shared" si="3"/>
-        <v>2115.128445679959</v>
+        <f>AR4*1.05</f>
+        <v>1587.541680648</v>
       </c>
       <c r="AT4" s="1">
-        <f>AS4*1.01</f>
-        <v>2136.2797301367586</v>
+        <f>AS4*1.04</f>
+        <v>1651.0433478739201</v>
       </c>
       <c r="AU4" s="1">
-        <f t="shared" si="0"/>
-        <v>2157.6425274381263</v>
+        <f>AT4*1.03</f>
+        <v>1700.5746483101377</v>
       </c>
       <c r="AV4" s="1">
-        <f t="shared" si="0"/>
-        <v>2179.2189527125074</v>
+        <f t="shared" ref="AV4:AX4" si="2">AU4*1.03</f>
+        <v>1751.591887759442</v>
       </c>
       <c r="AW4" s="1">
-        <f t="shared" si="0"/>
-        <v>2201.0111422396326</v>
+        <f t="shared" si="2"/>
+        <v>1804.1396443922254</v>
       </c>
       <c r="AX4" s="1">
-        <f t="shared" si="0"/>
-        <v>2223.0212536620288</v>
-      </c>
-    </row>
-    <row r="5" spans="2:50" x14ac:dyDescent="0.3">
+        <f t="shared" si="2"/>
+        <v>1858.2638337239921</v>
+      </c>
+    </row>
+    <row r="5" spans="2:51" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>40</v>
       </c>
@@ -1533,16 +1573,15 @@
         <v>2303.1</v>
       </c>
       <c r="AB5" s="1">
-        <f>X5*1.27</f>
-        <v>2319.9090000000001</v>
+        <v>2409.1999999999998</v>
       </c>
       <c r="AC5" s="1">
-        <f>Y5*1.22</f>
-        <v>2341.058</v>
+        <f>Y5*1.28</f>
+        <v>2456.192</v>
       </c>
       <c r="AD5" s="1">
-        <f>Z5*1.1</f>
-        <v>2408.56</v>
+        <f>Z5*1.14</f>
+        <v>2496.1439999999998</v>
       </c>
       <c r="AH5" s="1">
         <v>1287.8</v>
@@ -1566,51 +1605,51 @@
         <v>7676.3000000000011</v>
       </c>
       <c r="AN5" s="1">
-        <f t="shared" si="2"/>
-        <v>9372.6270000000004</v>
+        <f t="shared" si="1"/>
+        <v>9664.6359999999986</v>
       </c>
       <c r="AO5" s="1">
-        <f>AN5*1.14</f>
-        <v>10684.79478</v>
+        <f>AN5*1.16</f>
+        <v>11210.977759999998</v>
       </c>
       <c r="AP5" s="1">
         <f>AO5*1.08</f>
-        <v>11539.578362400001</v>
+        <v>12107.855980799999</v>
       </c>
       <c r="AQ5" s="1">
         <f>AP5*1.06</f>
-        <v>12231.953064144001</v>
+        <v>12834.327339648</v>
       </c>
       <c r="AR5" s="1">
         <f>AQ5*1.04</f>
-        <v>12721.231186709761</v>
+        <v>13347.70043323392</v>
       </c>
       <c r="AS5" s="1">
         <f>AR5*1.03</f>
-        <v>13102.868122311054</v>
+        <v>13748.131446230938</v>
       </c>
       <c r="AT5" s="1">
         <f>AS5*1.02</f>
-        <v>13364.925484757276</v>
+        <v>14023.094075155557</v>
       </c>
       <c r="AU5" s="1">
         <f>AT5*1.01</f>
-        <v>13498.574739604848</v>
+        <v>14163.325015907112</v>
       </c>
       <c r="AV5" s="1">
-        <f t="shared" ref="AV5:AX5" si="4">AU5*1.01</f>
-        <v>13633.560487000897</v>
+        <f t="shared" ref="AV5:AX5" si="3">AU5*1.01</f>
+        <v>14304.958266066184</v>
       </c>
       <c r="AW5" s="1">
-        <f t="shared" si="4"/>
-        <v>13769.896091870907</v>
+        <f t="shared" si="3"/>
+        <v>14448.007848726846</v>
       </c>
       <c r="AX5" s="1">
-        <f t="shared" si="4"/>
-        <v>13907.595052789617</v>
-      </c>
-    </row>
-    <row r="6" spans="2:50" x14ac:dyDescent="0.3">
+        <f t="shared" si="3"/>
+        <v>14592.487927214113</v>
+      </c>
+    </row>
+    <row r="6" spans="2:51" x14ac:dyDescent="0.3">
       <c r="B6" s="7" t="s">
         <v>41</v>
       </c>
@@ -1630,139 +1669,140 @@
       <c r="M6" s="7"/>
       <c r="N6" s="7"/>
       <c r="O6" s="9">
-        <f t="shared" ref="O6:W6" si="5">SUM(O3:O5)</f>
+        <f t="shared" ref="O6:W6" si="4">SUM(O3:O5)</f>
         <v>1936.8999999999999</v>
       </c>
       <c r="P6" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>2149.6999999999998</v>
       </c>
       <c r="Q6" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>2355.7999999999997</v>
       </c>
       <c r="R6" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>2574</v>
       </c>
       <c r="S6" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>2553.1999999999998</v>
       </c>
       <c r="T6" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>2760</v>
       </c>
       <c r="U6" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>2952.8</v>
       </c>
       <c r="V6" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>3098</v>
       </c>
       <c r="W6" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>2947.6</v>
       </c>
       <c r="X6" s="9">
-        <f t="shared" ref="X6" si="6">SUM(X3:X5)</f>
+        <f t="shared" ref="X6" si="5">SUM(X3:X5)</f>
         <v>3087.5</v>
       </c>
       <c r="Y6" s="9">
-        <f t="shared" ref="Y6" si="7">SUM(Y3:Y5)</f>
+        <f t="shared" ref="Y6" si="6">SUM(Y3:Y5)</f>
         <v>3213.4</v>
       </c>
       <c r="Z6" s="9">
-        <f t="shared" ref="Z6:AD6" si="8">SUM(Z3:Z5)</f>
+        <f t="shared" ref="Z6:AD6" si="7">SUM(Z3:Z5)</f>
         <v>3490.7</v>
       </c>
       <c r="AA6" s="9">
+        <f t="shared" si="7"/>
+        <v>3480.7</v>
+      </c>
+      <c r="AB6" s="9">
+        <f t="shared" si="7"/>
+        <v>3286.2</v>
+      </c>
+      <c r="AC6" s="9">
+        <f t="shared" si="7"/>
+        <v>3435.491</v>
+      </c>
+      <c r="AD6" s="9">
+        <f t="shared" si="7"/>
+        <v>3524.4539999999997</v>
+      </c>
+      <c r="AH6" s="9">
+        <f t="shared" ref="AH6:AM6" si="8">SUM(AH3:AH5)</f>
+        <v>2389.6999999999998</v>
+      </c>
+      <c r="AI6" s="9">
         <f t="shared" si="8"/>
-        <v>3480.7</v>
-      </c>
-      <c r="AB6" s="9">
+        <v>3179.1</v>
+      </c>
+      <c r="AJ6" s="9">
         <f t="shared" si="8"/>
-        <v>3529.7080000000001</v>
-      </c>
-      <c r="AC6" s="9">
+        <v>4576.5</v>
+      </c>
+      <c r="AK6" s="9">
         <f t="shared" si="8"/>
-        <v>3595.136</v>
-      </c>
-      <c r="AD6" s="9">
+        <v>9016.4</v>
+      </c>
+      <c r="AL6" s="9">
         <f t="shared" si="8"/>
-        <v>3694.192</v>
-      </c>
-      <c r="AH6" s="9">
-        <f t="shared" ref="AH6:AM6" si="9">SUM(AH3:AH5)</f>
-        <v>2389.6999999999998</v>
-      </c>
-      <c r="AI6" s="9">
-        <f t="shared" si="9"/>
-        <v>3179.1</v>
-      </c>
-      <c r="AJ6" s="9">
-        <f t="shared" si="9"/>
-        <v>4576.5</v>
-      </c>
-      <c r="AK6" s="9">
-        <f t="shared" si="9"/>
-        <v>9016.4</v>
-      </c>
-      <c r="AL6" s="9">
-        <f t="shared" si="9"/>
         <v>11364</v>
       </c>
       <c r="AM6" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>12739.2</v>
       </c>
       <c r="AN6" s="9">
-        <f t="shared" ref="AN6" si="10">SUM(AN3:AN5)</f>
-        <v>14299.736000000001</v>
+        <f t="shared" ref="AN6" si="9">SUM(AN3:AN5)</f>
+        <v>13726.844999999998</v>
       </c>
       <c r="AO6" s="9">
-        <f t="shared" ref="AO6" si="11">SUM(AO3:AO5)</f>
-        <v>15680.33224</v>
+        <f t="shared" ref="AO6" si="10">SUM(AO3:AO5)</f>
+        <v>15354.430939999998</v>
       </c>
       <c r="AP6" s="9">
-        <f t="shared" ref="AP6" si="12">SUM(AP3:AP5)</f>
-        <v>16604.611714400002</v>
+        <f t="shared" ref="AP6" si="11">SUM(AP3:AP5)</f>
+        <v>16400.8014726</v>
       </c>
       <c r="AQ6" s="9">
-        <f t="shared" ref="AQ6" si="13">SUM(AQ3:AQ5)</f>
-        <v>17367.568077412001</v>
+        <f t="shared" ref="AQ6" si="12">SUM(AQ3:AQ5)</f>
+        <v>17262.651720366001</v>
       </c>
       <c r="AR6" s="9">
-        <f t="shared" ref="AR6" si="14">SUM(AR3:AR5)</f>
-        <v>17928.532304413402</v>
+        <f t="shared" ref="AR6" si="13">SUM(AR3:AR5)</f>
+        <v>17891.626192559099</v>
       </c>
       <c r="AS6" s="9">
-        <f t="shared" ref="AS6" si="15">SUM(AS3:AS5)</f>
-        <v>18382.978804580751</v>
+        <f t="shared" ref="AS6" si="14">SUM(AS3:AS5)</f>
+        <v>18397.974241459771</v>
       </c>
       <c r="AT6" s="9">
-        <f t="shared" ref="AT6" si="16">SUM(AT3:AT5)</f>
-        <v>18697.837273849669</v>
+        <f t="shared" ref="AT6" si="15">SUM(AT3:AT5)</f>
+        <v>18767.061548756115</v>
       </c>
       <c r="AU6" s="9">
-        <f t="shared" ref="AU6" si="17">SUM(AU3:AU5)</f>
-        <v>18884.815646588166</v>
+        <f t="shared" ref="AU6" si="16">SUM(AU3:AU5)</f>
+        <v>18987.753031201159</v>
       </c>
       <c r="AV6" s="9">
-        <f t="shared" ref="AV6" si="18">SUM(AV3:AV5)</f>
-        <v>19073.663803054049</v>
+        <f t="shared" ref="AV6" si="17">SUM(AV3:AV5)</f>
+        <v>19211.642054479373</v>
       </c>
       <c r="AW6" s="9">
-        <f t="shared" ref="AW6" si="19">SUM(AW3:AW5)</f>
-        <v>19264.400441084588</v>
+        <f t="shared" ref="AW6" si="18">SUM(AW3:AW5)</f>
+        <v>19438.790312779354</v>
       </c>
       <c r="AX6" s="9">
-        <f t="shared" ref="AX6" si="20">SUM(AX3:AX5)</f>
-        <v>19457.044445495434</v>
-      </c>
-    </row>
-    <row r="7" spans="2:50" x14ac:dyDescent="0.3">
+        <f t="shared" ref="AX6" si="19">SUM(AX3:AX5)</f>
+        <v>19669.261008794991</v>
+      </c>
+      <c r="AY6" s="9"/>
+    </row>
+    <row r="7" spans="2:51" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>37</v>
       </c>
@@ -1810,16 +1850,15 @@
         <v>933.9</v>
       </c>
       <c r="AB7" s="1">
-        <f t="shared" ref="AB7:AD7" si="21">AB6-AB8</f>
-        <v>953.02116000000024</v>
+        <v>850.4</v>
       </c>
       <c r="AC7" s="1">
-        <f t="shared" si="21"/>
-        <v>934.73536000000013</v>
+        <f t="shared" ref="AC7:AD7" si="20">AC6-AC8</f>
+        <v>893.22766000000001</v>
       </c>
       <c r="AD7" s="1">
-        <f t="shared" si="21"/>
-        <v>923.54799999999977</v>
+        <f t="shared" si="20"/>
+        <v>881.11349999999993</v>
       </c>
       <c r="AH7" s="1">
         <v>426.9</v>
@@ -1843,51 +1882,51 @@
         <v>3389.1000000000004</v>
       </c>
       <c r="AN7" s="1">
-        <f t="shared" si="2"/>
-        <v>3745.2045200000002</v>
+        <f t="shared" si="1"/>
+        <v>3558.6411599999997</v>
       </c>
       <c r="AO7" s="1">
-        <f t="shared" ref="AO7:AX7" si="22">AO6-AO8</f>
-        <v>4076.8863824</v>
+        <f t="shared" ref="AO7:AX7" si="21">AO6-AO8</f>
+        <v>3992.1520443999998</v>
       </c>
       <c r="AP7" s="1">
-        <f t="shared" si="22"/>
-        <v>4317.1990457440006</v>
+        <f t="shared" si="21"/>
+        <v>4264.2083828760005</v>
       </c>
       <c r="AQ7" s="1">
-        <f t="shared" si="22"/>
-        <v>4515.5677001271197</v>
+        <f t="shared" si="21"/>
+        <v>4488.2894472951612</v>
       </c>
       <c r="AR7" s="1">
-        <f t="shared" si="22"/>
-        <v>4661.4183991474838</v>
+        <f t="shared" si="21"/>
+        <v>4651.822810065365</v>
       </c>
       <c r="AS7" s="1">
-        <f t="shared" si="22"/>
-        <v>4779.5744891909962</v>
+        <f t="shared" si="21"/>
+        <v>4783.473302779541</v>
       </c>
       <c r="AT7" s="1">
-        <f t="shared" si="22"/>
-        <v>4861.4376912009138</v>
+        <f t="shared" si="21"/>
+        <v>4879.4360026765899</v>
       </c>
       <c r="AU7" s="1">
-        <f t="shared" si="22"/>
-        <v>4910.0520681129237</v>
+        <f t="shared" si="21"/>
+        <v>4936.8157881123007</v>
       </c>
       <c r="AV7" s="1">
-        <f t="shared" si="22"/>
-        <v>4959.1525887940534</v>
+        <f t="shared" si="21"/>
+        <v>4995.0269341646363</v>
       </c>
       <c r="AW7" s="1">
-        <f t="shared" si="22"/>
-        <v>5008.7441146819929</v>
+        <f t="shared" si="21"/>
+        <v>5054.0854813226324</v>
       </c>
       <c r="AX7" s="1">
-        <f t="shared" si="22"/>
-        <v>5058.8315558288123</v>
-      </c>
-    </row>
-    <row r="8" spans="2:50" x14ac:dyDescent="0.3">
+        <f t="shared" si="21"/>
+        <v>5114.0078622866986</v>
+      </c>
+    </row>
+    <row r="8" spans="2:51" x14ac:dyDescent="0.3">
       <c r="B8" s="7" t="s">
         <v>46</v>
       </c>
@@ -1907,139 +1946,140 @@
       <c r="M8" s="7"/>
       <c r="N8" s="7"/>
       <c r="O8" s="9">
-        <f t="shared" ref="O8:AA8" si="23">O6-O7</f>
+        <f t="shared" ref="O8:AB8" si="22">O6-O7</f>
         <v>1262.5</v>
       </c>
       <c r="P8" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>1523.4999999999998</v>
       </c>
       <c r="Q8" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>1684.4999999999998</v>
       </c>
       <c r="R8" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>1876</v>
       </c>
       <c r="S8" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>1831.8999999999999</v>
       </c>
       <c r="T8" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>2074.6999999999998</v>
       </c>
       <c r="U8" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>2179.3000000000002</v>
       </c>
       <c r="V8" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>2295.3000000000002</v>
       </c>
       <c r="W8" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>2137.6999999999998</v>
       </c>
       <c r="X8" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>2246.1</v>
       </c>
       <c r="Y8" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>2354.4</v>
       </c>
       <c r="Z8" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>2611.8999999999996</v>
       </c>
       <c r="AA8" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>2546.7999999999997</v>
       </c>
       <c r="AB8" s="9">
-        <f t="shared" ref="AB8" si="24">AB6*0.73</f>
-        <v>2576.6868399999998</v>
+        <f t="shared" si="22"/>
+        <v>2435.7999999999997</v>
       </c>
       <c r="AC8" s="9">
         <f>AC6*0.74</f>
-        <v>2660.4006399999998</v>
+        <v>2542.26334</v>
       </c>
       <c r="AD8" s="9">
         <f>AD6*0.75</f>
-        <v>2770.6440000000002</v>
+        <v>2643.3404999999998</v>
       </c>
       <c r="AH8" s="9">
-        <f t="shared" ref="AH8:AN8" si="25">AH6-AH7</f>
+        <f t="shared" ref="AH8:AN8" si="23">AH6-AH7</f>
         <v>1962.7999999999997</v>
       </c>
       <c r="AI8" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>2409.1999999999998</v>
       </c>
       <c r="AJ8" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>2862.7</v>
       </c>
       <c r="AK8" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>6346.5</v>
       </c>
       <c r="AL8" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>8381.2000000000007</v>
       </c>
       <c r="AM8" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>9350.1</v>
       </c>
       <c r="AN8" s="9">
-        <f t="shared" si="25"/>
-        <v>10554.531480000001</v>
+        <f t="shared" si="23"/>
+        <v>10168.203839999998</v>
       </c>
       <c r="AO8" s="9">
-        <f t="shared" ref="AO8:AX8" si="26">AO6*0.74</f>
-        <v>11603.4458576</v>
+        <f t="shared" ref="AO8:AX8" si="24">AO6*0.74</f>
+        <v>11362.278895599999</v>
       </c>
       <c r="AP8" s="9">
-        <f t="shared" si="26"/>
-        <v>12287.412668656001</v>
+        <f t="shared" si="24"/>
+        <v>12136.593089724</v>
       </c>
       <c r="AQ8" s="9">
-        <f t="shared" si="26"/>
-        <v>12852.000377284881</v>
+        <f t="shared" si="24"/>
+        <v>12774.362273070839</v>
       </c>
       <c r="AR8" s="9">
-        <f t="shared" si="26"/>
-        <v>13267.113905265918</v>
+        <f t="shared" si="24"/>
+        <v>13239.803382493734</v>
       </c>
       <c r="AS8" s="9">
-        <f t="shared" si="26"/>
-        <v>13603.404315389755</v>
+        <f t="shared" si="24"/>
+        <v>13614.50093868023</v>
       </c>
       <c r="AT8" s="9">
-        <f t="shared" si="26"/>
-        <v>13836.399582648755</v>
+        <f t="shared" si="24"/>
+        <v>13887.625546079526</v>
       </c>
       <c r="AU8" s="9">
-        <f t="shared" si="26"/>
-        <v>13974.763578475242</v>
+        <f t="shared" si="24"/>
+        <v>14050.937243088858</v>
       </c>
       <c r="AV8" s="9">
-        <f t="shared" si="26"/>
-        <v>14114.511214259996</v>
+        <f t="shared" si="24"/>
+        <v>14216.615120314736</v>
       </c>
       <c r="AW8" s="9">
-        <f t="shared" si="26"/>
-        <v>14255.656326402595</v>
+        <f t="shared" si="24"/>
+        <v>14384.704831456722</v>
       </c>
       <c r="AX8" s="9">
-        <f t="shared" si="26"/>
-        <v>14398.212889666622</v>
-      </c>
-    </row>
-    <row r="9" spans="2:50" x14ac:dyDescent="0.3">
+        <f t="shared" si="24"/>
+        <v>14555.253146508292</v>
+      </c>
+      <c r="AY8" s="9"/>
+    </row>
+    <row r="9" spans="2:51" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>42</v>
       </c>
@@ -2086,16 +2126,15 @@
         <v>277.89999999999998</v>
       </c>
       <c r="AB9" s="1">
-        <f t="shared" ref="AB9:AD9" si="27">AB6*0.09</f>
-        <v>317.67372</v>
+        <v>225.1</v>
       </c>
       <c r="AC9" s="1">
-        <f t="shared" si="27"/>
-        <v>323.56223999999997</v>
+        <f>AC6*0.08</f>
+        <v>274.83928000000003</v>
       </c>
       <c r="AD9" s="1">
-        <f t="shared" si="27"/>
-        <v>332.47728000000001</v>
+        <f>AD6*0.08</f>
+        <v>281.95632000000001</v>
       </c>
       <c r="AH9" s="1">
         <v>285.8</v>
@@ -2119,51 +2158,51 @@
         <v>1130.5</v>
       </c>
       <c r="AN9" s="1">
-        <f t="shared" si="2"/>
-        <v>1251.6132399999999</v>
+        <f t="shared" si="1"/>
+        <v>1059.7955999999999</v>
       </c>
       <c r="AO9" s="1">
-        <f t="shared" ref="AO9:AX9" si="28">AO6*0.09</f>
-        <v>1411.2299015999999</v>
+        <f>AO6*0.08</f>
+        <v>1228.3544751999998</v>
       </c>
       <c r="AP9" s="1">
-        <f t="shared" si="28"/>
-        <v>1494.4150542960001</v>
+        <f t="shared" ref="AP9:AX9" si="25">AP6*0.08</f>
+        <v>1312.064117808</v>
       </c>
       <c r="AQ9" s="1">
-        <f t="shared" si="28"/>
-        <v>1563.0811269670801</v>
+        <f t="shared" si="25"/>
+        <v>1381.01213762928</v>
       </c>
       <c r="AR9" s="1">
-        <f t="shared" si="28"/>
-        <v>1613.5679073972062</v>
+        <f t="shared" si="25"/>
+        <v>1431.3300954047279</v>
       </c>
       <c r="AS9" s="1">
-        <f t="shared" si="28"/>
-        <v>1654.4680924122674</v>
+        <f t="shared" si="25"/>
+        <v>1471.8379393167818</v>
       </c>
       <c r="AT9" s="1">
-        <f t="shared" si="28"/>
-        <v>1682.8053546464701</v>
+        <f t="shared" si="25"/>
+        <v>1501.3649239004892</v>
       </c>
       <c r="AU9" s="1">
-        <f t="shared" si="28"/>
-        <v>1699.6334081929349</v>
+        <f t="shared" si="25"/>
+        <v>1519.0202424960928</v>
       </c>
       <c r="AV9" s="1">
-        <f t="shared" si="28"/>
-        <v>1716.6297422748644</v>
+        <f t="shared" si="25"/>
+        <v>1536.9313643583498</v>
       </c>
       <c r="AW9" s="1">
-        <f t="shared" si="28"/>
-        <v>1733.796039697613</v>
+        <f t="shared" si="25"/>
+        <v>1555.1032250223484</v>
       </c>
       <c r="AX9" s="1">
-        <f t="shared" si="28"/>
-        <v>1751.1340000945891</v>
-      </c>
-    </row>
-    <row r="10" spans="2:50" x14ac:dyDescent="0.3">
+        <f t="shared" si="25"/>
+        <v>1573.5408807035992</v>
+      </c>
+    </row>
+    <row r="10" spans="2:51" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>43</v>
       </c>
@@ -2210,16 +2249,15 @@
         <v>593.1</v>
       </c>
       <c r="AB10" s="1">
-        <f t="shared" ref="AB10" si="29">AB6*0.17</f>
-        <v>600.05036000000007</v>
+        <v>531</v>
       </c>
       <c r="AC10" s="1">
         <f>AC6*0.16</f>
-        <v>575.22176000000002</v>
+        <v>549.67856000000006</v>
       </c>
       <c r="AD10" s="1">
         <f>AD6*0.15</f>
-        <v>554.12879999999996</v>
+        <v>528.66809999999998</v>
       </c>
       <c r="AH10" s="1">
         <v>360.6</v>
@@ -2243,51 +2281,51 @@
         <v>2105.5</v>
       </c>
       <c r="AN10" s="1">
-        <f t="shared" si="2"/>
-        <v>2322.50092</v>
+        <f t="shared" si="1"/>
+        <v>2202.4466600000001</v>
       </c>
       <c r="AO10" s="1">
         <f>AO6*0.15</f>
-        <v>2352.0498359999997</v>
+        <v>2303.1646409999998</v>
       </c>
       <c r="AP10" s="1">
-        <f t="shared" ref="AP10:AX10" si="30">AP6*0.15</f>
-        <v>2490.6917571600002</v>
+        <f t="shared" ref="AP10:AX10" si="26">AP6*0.15</f>
+        <v>2460.1202208899999</v>
       </c>
       <c r="AQ10" s="1">
-        <f t="shared" si="30"/>
-        <v>2605.1352116118001</v>
+        <f t="shared" si="26"/>
+        <v>2589.3977580548999</v>
       </c>
       <c r="AR10" s="1">
-        <f t="shared" si="30"/>
-        <v>2689.2798456620103</v>
+        <f t="shared" si="26"/>
+        <v>2683.7439288838646</v>
       </c>
       <c r="AS10" s="1">
-        <f t="shared" si="30"/>
-        <v>2757.4468206871124</v>
+        <f t="shared" si="26"/>
+        <v>2759.6961362189654</v>
       </c>
       <c r="AT10" s="1">
-        <f t="shared" si="30"/>
-        <v>2804.6755910774505</v>
+        <f t="shared" si="26"/>
+        <v>2815.0592323134174</v>
       </c>
       <c r="AU10" s="1">
-        <f t="shared" si="30"/>
-        <v>2832.7223469882247</v>
+        <f t="shared" si="26"/>
+        <v>2848.1629546801737</v>
       </c>
       <c r="AV10" s="1">
-        <f t="shared" si="30"/>
-        <v>2861.0495704581072</v>
+        <f t="shared" si="26"/>
+        <v>2881.7463081719056</v>
       </c>
       <c r="AW10" s="1">
-        <f t="shared" si="30"/>
-        <v>2889.6600661626881</v>
+        <f t="shared" si="26"/>
+        <v>2915.818546916903</v>
       </c>
       <c r="AX10" s="1">
-        <f t="shared" si="30"/>
-        <v>2918.556666824315</v>
-      </c>
-    </row>
-    <row r="11" spans="2:50" x14ac:dyDescent="0.3">
+        <f t="shared" si="26"/>
+        <v>2950.3891513192484</v>
+      </c>
+    </row>
+    <row r="11" spans="2:51" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>44</v>
       </c>
@@ -2334,16 +2372,15 @@
         <v>1096.7</v>
       </c>
       <c r="AB11" s="1">
-        <f t="shared" ref="AB11:AD11" si="31">X11*1.05</f>
-        <v>893.65500000000009</v>
+        <v>1091.8</v>
       </c>
       <c r="AC11" s="1">
-        <f t="shared" si="31"/>
-        <v>956.02500000000009</v>
+        <f>Y11*1.2</f>
+        <v>1092.5999999999999</v>
       </c>
       <c r="AD11" s="1">
-        <f t="shared" si="31"/>
-        <v>1087.2750000000001</v>
+        <f>Z11*1.07</f>
+        <v>1107.9850000000001</v>
       </c>
       <c r="AH11" s="1">
         <v>353.5</v>
@@ -2367,51 +2404,51 @@
         <v>3693.7</v>
       </c>
       <c r="AN11" s="1">
-        <f t="shared" si="2"/>
-        <v>4033.6550000000002</v>
+        <f t="shared" si="1"/>
+        <v>4389.085</v>
       </c>
       <c r="AO11" s="1">
-        <f t="shared" ref="AO11:AR11" si="32">AN11*1.03</f>
-        <v>4154.6646500000006</v>
+        <f t="shared" ref="AO11:AQ11" si="27">AN11*1.03</f>
+        <v>4520.7575500000003</v>
       </c>
       <c r="AP11" s="1">
-        <f t="shared" si="32"/>
-        <v>4279.3045895000005</v>
+        <f t="shared" si="27"/>
+        <v>4656.3802765</v>
       </c>
       <c r="AQ11" s="1">
-        <f t="shared" si="32"/>
-        <v>4407.6837271850009</v>
+        <f t="shared" si="27"/>
+        <v>4796.0716847949998</v>
       </c>
       <c r="AR11" s="1">
-        <f t="shared" si="32"/>
-        <v>4539.9142390005509</v>
+        <f>AQ11*1.02</f>
+        <v>4891.9931184909001</v>
       </c>
       <c r="AS11" s="1">
         <f>AR11*1.02</f>
-        <v>4630.7125237805622</v>
+        <v>4989.8329808607177</v>
       </c>
       <c r="AT11" s="1">
-        <f t="shared" ref="AT11:AX11" si="33">AS11*1.02</f>
-        <v>4723.3267742561738</v>
+        <f>AS11*1.01</f>
+        <v>5039.7313106693246</v>
       </c>
       <c r="AU11" s="1">
-        <f t="shared" si="33"/>
-        <v>4817.793309741297</v>
+        <f t="shared" ref="AU11:AX11" si="28">AT11*1.01</f>
+        <v>5090.1286237760178</v>
       </c>
       <c r="AV11" s="1">
-        <f t="shared" si="33"/>
-        <v>4914.1491759361234</v>
+        <f t="shared" si="28"/>
+        <v>5141.0299100137781</v>
       </c>
       <c r="AW11" s="1">
-        <f t="shared" si="33"/>
-        <v>5012.4321594548455</v>
+        <f t="shared" si="28"/>
+        <v>5192.4402091139164</v>
       </c>
       <c r="AX11" s="1">
-        <f t="shared" si="33"/>
-        <v>5112.6808026439421</v>
-      </c>
-    </row>
-    <row r="12" spans="2:50" x14ac:dyDescent="0.3">
+        <f t="shared" si="28"/>
+        <v>5244.3646112050556</v>
+      </c>
+    </row>
+    <row r="12" spans="2:51" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>45</v>
       </c>
@@ -2472,16 +2509,16 @@
         <v>-58.200000000000017</v>
       </c>
       <c r="AB12" s="1">
-        <f t="shared" ref="AB12:AD12" si="34">X12*1.02</f>
-        <v>-38.25</v>
+        <f>-214.7+110.8</f>
+        <v>-103.89999999999999</v>
       </c>
       <c r="AC12" s="1">
-        <f t="shared" si="34"/>
-        <v>-43.146000000000015</v>
+        <f>Y12*2.5</f>
+        <v>-105.75000000000003</v>
       </c>
       <c r="AD12" s="1">
-        <f t="shared" si="34"/>
-        <v>-10.812000000000008</v>
+        <f>Z12*10</f>
+        <v>-106.00000000000009</v>
       </c>
       <c r="AH12" s="1">
         <f>57.7-186.4</f>
@@ -2508,51 +2545,51 @@
         <v>-119.60000000000004</v>
       </c>
       <c r="AN12" s="1">
-        <f t="shared" si="2"/>
-        <v>-150.40800000000004</v>
+        <f t="shared" si="1"/>
+        <v>-373.85000000000014</v>
       </c>
       <c r="AO12" s="1">
-        <f t="shared" ref="AO12:AX12" si="35">AN12*1.03</f>
-        <v>-154.92024000000004</v>
+        <f t="shared" ref="AO12:AX12" si="29">AN12*1.03</f>
+        <v>-385.06550000000016</v>
       </c>
       <c r="AP12" s="1">
-        <f t="shared" si="35"/>
-        <v>-159.56784720000005</v>
+        <f t="shared" si="29"/>
+        <v>-396.61746500000015</v>
       </c>
       <c r="AQ12" s="1">
-        <f t="shared" si="35"/>
-        <v>-164.35488261600005</v>
+        <f t="shared" si="29"/>
+        <v>-408.51598895000018</v>
       </c>
       <c r="AR12" s="1">
-        <f t="shared" si="35"/>
-        <v>-169.28552909448007</v>
+        <f t="shared" si="29"/>
+        <v>-420.77146861850019</v>
       </c>
       <c r="AS12" s="1">
-        <f t="shared" si="35"/>
-        <v>-174.36409496731449</v>
+        <f t="shared" si="29"/>
+        <v>-433.39461267705519</v>
       </c>
       <c r="AT12" s="1">
-        <f t="shared" si="35"/>
-        <v>-179.59501781633392</v>
+        <f t="shared" si="29"/>
+        <v>-446.39645105736685</v>
       </c>
       <c r="AU12" s="1">
-        <f t="shared" si="35"/>
-        <v>-184.98286835082394</v>
+        <f t="shared" si="29"/>
+        <v>-459.78834458908784</v>
       </c>
       <c r="AV12" s="1">
-        <f t="shared" si="35"/>
-        <v>-190.53235440134867</v>
+        <f t="shared" si="29"/>
+        <v>-473.5819949267605</v>
       </c>
       <c r="AW12" s="1">
-        <f t="shared" si="35"/>
-        <v>-196.24832503338914</v>
+        <f t="shared" si="29"/>
+        <v>-487.78945477456335</v>
       </c>
       <c r="AX12" s="1">
-        <f t="shared" si="35"/>
-        <v>-202.1357747843908</v>
-      </c>
-    </row>
-    <row r="13" spans="2:50" x14ac:dyDescent="0.3">
+        <f t="shared" si="29"/>
+        <v>-502.42313841780026</v>
+      </c>
+    </row>
+    <row r="13" spans="2:51" x14ac:dyDescent="0.3">
       <c r="B13" s="7" t="s">
         <v>47</v>
       </c>
@@ -2572,139 +2609,139 @@
       <c r="M13" s="7"/>
       <c r="N13" s="7"/>
       <c r="O13" s="9">
-        <f t="shared" ref="O13:W13" si="36">O8-SUM(O9:O12)</f>
+        <f t="shared" ref="O13:W13" si="30">O8-SUM(O9:O12)</f>
         <v>-289</v>
       </c>
       <c r="P13" s="9">
-        <f t="shared" si="36"/>
+        <f t="shared" si="30"/>
         <v>-482.10000000000014</v>
       </c>
       <c r="Q13" s="9">
-        <f t="shared" si="36"/>
+        <f t="shared" si="30"/>
         <v>247.79999999999995</v>
       </c>
       <c r="R13" s="9">
-        <f t="shared" si="36"/>
+        <f t="shared" si="30"/>
         <v>139.79999999999995</v>
       </c>
       <c r="S13" s="9">
-        <f t="shared" si="36"/>
+        <f t="shared" si="30"/>
         <v>307.79999999999995</v>
       </c>
       <c r="T13" s="9">
-        <f t="shared" si="36"/>
+        <f t="shared" si="30"/>
         <v>423.19999999999982</v>
       </c>
       <c r="U13" s="9">
-        <f t="shared" si="36"/>
+        <f t="shared" si="30"/>
         <v>504.10000000000014</v>
       </c>
       <c r="V13" s="9">
-        <f t="shared" si="36"/>
+        <f t="shared" si="30"/>
         <v>740</v>
       </c>
       <c r="W13" s="9">
-        <f t="shared" si="36"/>
+        <f t="shared" si="30"/>
         <v>483.59999999999968</v>
       </c>
       <c r="X13" s="9">
-        <f t="shared" ref="X13" si="37">X8-SUM(X9:X12)</f>
+        <f t="shared" ref="X13" si="31">X8-SUM(X9:X12)</f>
         <v>652.09999999999991</v>
       </c>
       <c r="Y13" s="9">
-        <f t="shared" ref="Y13" si="38">Y8-SUM(Y9:Y12)</f>
+        <f t="shared" ref="Y13" si="32">Y8-SUM(Y9:Y12)</f>
         <v>669.7</v>
       </c>
       <c r="Z13" s="9">
-        <f t="shared" ref="Z13:AD13" si="39">Z8-SUM(Z9:Z12)</f>
+        <f t="shared" ref="Z13:AD13" si="33">Z8-SUM(Z9:Z12)</f>
         <v>734.59999999999945</v>
       </c>
       <c r="AA13" s="9">
-        <f t="shared" si="39"/>
+        <f t="shared" si="33"/>
         <v>637.29999999999973</v>
       </c>
       <c r="AB13" s="9">
-        <f t="shared" si="39"/>
-        <v>803.55775999999969</v>
+        <f t="shared" si="33"/>
+        <v>691.79999999999973</v>
       </c>
       <c r="AC13" s="9">
-        <f t="shared" si="39"/>
-        <v>848.7376399999996</v>
+        <f t="shared" si="33"/>
+        <v>730.89550000000008</v>
       </c>
       <c r="AD13" s="9">
-        <f t="shared" si="39"/>
-        <v>807.57492000000002</v>
+        <f t="shared" si="33"/>
+        <v>830.73107999999957</v>
       </c>
       <c r="AH13" s="9">
-        <f t="shared" ref="AH13:AM13" si="40">AH8-SUM(AH9:AH12)</f>
+        <f t="shared" ref="AH13:AM13" si="34">AH8-SUM(AH9:AH12)</f>
         <v>1091.5999999999997</v>
       </c>
       <c r="AI13" s="9">
-        <f t="shared" si="40"/>
+        <f t="shared" si="34"/>
         <v>1134.5999999999997</v>
       </c>
       <c r="AJ13" s="9">
-        <f t="shared" si="40"/>
+        <f t="shared" si="34"/>
         <v>-1435</v>
       </c>
       <c r="AK13" s="9">
-        <f t="shared" si="40"/>
+        <f t="shared" si="34"/>
         <v>-383.49999999999909</v>
       </c>
       <c r="AL13" s="9">
-        <f t="shared" si="40"/>
+        <f t="shared" si="34"/>
         <v>1975.1000000000013</v>
       </c>
       <c r="AM13" s="9">
-        <f t="shared" si="40"/>
+        <f t="shared" si="34"/>
         <v>2540.0000000000009</v>
       </c>
       <c r="AN13" s="9">
-        <f t="shared" ref="AN13" si="41">AN8-SUM(AN9:AN12)</f>
-        <v>3097.170320000002</v>
+        <f t="shared" ref="AN13" si="35">AN8-SUM(AN9:AN12)</f>
+        <v>2890.7265799999986</v>
       </c>
       <c r="AO13" s="9">
-        <f t="shared" ref="AO13" si="42">AO8-SUM(AO9:AO12)</f>
-        <v>3840.4217099999996</v>
+        <f t="shared" ref="AO13" si="36">AO8-SUM(AO9:AO12)</f>
+        <v>3695.0677293999997</v>
       </c>
       <c r="AP13" s="9">
-        <f t="shared" ref="AP13" si="43">AP8-SUM(AP9:AP12)</f>
-        <v>4182.5691149000013</v>
+        <f t="shared" ref="AP13" si="37">AP8-SUM(AP9:AP12)</f>
+        <v>4104.6459395259999</v>
       </c>
       <c r="AQ13" s="9">
-        <f t="shared" ref="AQ13" si="44">AQ8-SUM(AQ9:AQ12)</f>
-        <v>4440.4551941370009</v>
+        <f t="shared" ref="AQ13" si="38">AQ8-SUM(AQ9:AQ12)</f>
+        <v>4416.3966815416607</v>
       </c>
       <c r="AR13" s="9">
-        <f t="shared" ref="AR13" si="45">AR8-SUM(AR9:AR12)</f>
-        <v>4593.6374423006309</v>
+        <f t="shared" ref="AR13" si="39">AR8-SUM(AR9:AR12)</f>
+        <v>4653.5077083327433</v>
       </c>
       <c r="AS13" s="9">
-        <f t="shared" ref="AS13" si="46">AS8-SUM(AS9:AS12)</f>
-        <v>4735.140973477126</v>
+        <f t="shared" ref="AS13" si="40">AS8-SUM(AS9:AS12)</f>
+        <v>4826.5284949608194</v>
       </c>
       <c r="AT13" s="9">
-        <f t="shared" ref="AT13" si="47">AT8-SUM(AT9:AT12)</f>
-        <v>4805.1868804849964</v>
+        <f t="shared" ref="AT13" si="41">AT8-SUM(AT9:AT12)</f>
+        <v>4977.8665302536592</v>
       </c>
       <c r="AU13" s="9">
-        <f t="shared" ref="AU13" si="48">AU8-SUM(AU9:AU12)</f>
-        <v>4809.5973819036099</v>
+        <f t="shared" ref="AU13" si="42">AU8-SUM(AU9:AU12)</f>
+        <v>5053.4137667256618</v>
       </c>
       <c r="AV13" s="9">
-        <f t="shared" ref="AV13" si="49">AV8-SUM(AV9:AV12)</f>
-        <v>4813.2150799922492</v>
+        <f t="shared" ref="AV13" si="43">AV8-SUM(AV9:AV12)</f>
+        <v>5130.4895326974638</v>
       </c>
       <c r="AW13" s="9">
-        <f t="shared" ref="AW13" si="50">AW8-SUM(AW9:AW12)</f>
-        <v>4816.0163861208384</v>
+        <f t="shared" ref="AW13" si="44">AW8-SUM(AW9:AW12)</f>
+        <v>5209.1323051781183</v>
       </c>
       <c r="AX13" s="9">
-        <f t="shared" ref="AX13" si="51">AX8-SUM(AX9:AX12)</f>
-        <v>4817.9771948881662</v>
-      </c>
-    </row>
-    <row r="14" spans="2:50" x14ac:dyDescent="0.3">
+        <f t="shared" ref="AX13" si="45">AX8-SUM(AX9:AX12)</f>
+        <v>5289.3816416981899</v>
+      </c>
+    </row>
+    <row r="14" spans="2:51" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>48</v>
       </c>
@@ -2752,7 +2789,7 @@
         <v>-0.4</v>
       </c>
       <c r="AB14" s="1">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AC14" s="1">
         <v>0</v>
@@ -2782,8 +2819,8 @@
         <v>3557.6</v>
       </c>
       <c r="AN14" s="1">
-        <f t="shared" si="2"/>
-        <v>-0.4</v>
+        <f t="shared" si="1"/>
+        <v>9.9999999999999978E-2</v>
       </c>
       <c r="AO14" s="1">
         <v>0</v>
@@ -2816,7 +2853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:50" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:51" x14ac:dyDescent="0.3">
       <c r="B15" s="7" t="s">
         <v>49</v>
       </c>
@@ -2836,139 +2873,139 @@
       <c r="M15" s="7"/>
       <c r="N15" s="7"/>
       <c r="O15" s="9">
-        <f t="shared" ref="O15:W15" si="52">O13-O14</f>
+        <f t="shared" ref="O15:W15" si="46">O13-O14</f>
         <v>-289.7</v>
       </c>
       <c r="P15" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="46"/>
         <v>-483.40000000000015</v>
       </c>
       <c r="Q15" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="46"/>
         <v>246.59999999999997</v>
       </c>
       <c r="R15" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="46"/>
         <v>139.49999999999994</v>
       </c>
       <c r="S15" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="46"/>
         <v>306.79999999999995</v>
       </c>
       <c r="T15" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="46"/>
         <v>422.39999999999981</v>
       </c>
       <c r="U15" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="46"/>
         <v>503.50000000000011</v>
       </c>
       <c r="V15" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="46"/>
         <v>738.3</v>
       </c>
       <c r="W15" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="46"/>
         <v>483.89999999999969</v>
       </c>
       <c r="X15" s="9">
-        <f t="shared" ref="X15" si="53">X13-X14</f>
+        <f t="shared" ref="X15" si="47">X13-X14</f>
         <v>651.69999999999993</v>
       </c>
       <c r="Y15" s="9">
-        <f t="shared" ref="Y15" si="54">Y13-Y14</f>
+        <f t="shared" ref="Y15" si="48">Y13-Y14</f>
         <v>670.1</v>
       </c>
       <c r="Z15" s="9">
-        <f t="shared" ref="Z15:AD15" si="55">Z13-Z14</f>
+        <f t="shared" ref="Z15:AD15" si="49">Z13-Z14</f>
         <v>-2823.3000000000006</v>
       </c>
       <c r="AA15" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="49"/>
         <v>637.6999999999997</v>
       </c>
       <c r="AB15" s="9">
-        <f t="shared" si="55"/>
-        <v>803.55775999999969</v>
+        <f t="shared" si="49"/>
+        <v>691.29999999999973</v>
       </c>
       <c r="AC15" s="9">
-        <f t="shared" si="55"/>
-        <v>848.7376399999996</v>
+        <f t="shared" si="49"/>
+        <v>730.89550000000008</v>
       </c>
       <c r="AD15" s="9">
-        <f t="shared" si="55"/>
-        <v>807.57492000000002</v>
+        <f t="shared" si="49"/>
+        <v>830.73107999999957</v>
       </c>
       <c r="AH15" s="9">
-        <f t="shared" ref="AH15:AN15" si="56">AH13-AH14</f>
+        <f t="shared" ref="AH15:AN15" si="50">AH13-AH14</f>
         <v>1090.7999999999997</v>
       </c>
       <c r="AI15" s="9">
-        <f t="shared" si="56"/>
+        <f t="shared" si="50"/>
         <v>1127.6999999999996</v>
       </c>
       <c r="AJ15" s="9">
-        <f t="shared" si="56"/>
+        <f t="shared" si="50"/>
         <v>-1445.4</v>
       </c>
       <c r="AK15" s="9">
-        <f t="shared" si="56"/>
+        <f t="shared" si="50"/>
         <v>-386.99999999999909</v>
       </c>
       <c r="AL15" s="9">
-        <f t="shared" si="56"/>
+        <f t="shared" si="50"/>
         <v>1971.0000000000014</v>
       </c>
       <c r="AM15" s="9">
-        <f t="shared" si="56"/>
+        <f t="shared" si="50"/>
         <v>-1017.599999999999</v>
       </c>
       <c r="AN15" s="9">
-        <f t="shared" si="56"/>
-        <v>3097.5703200000021</v>
+        <f t="shared" si="50"/>
+        <v>2890.6265799999987</v>
       </c>
       <c r="AO15" s="9">
-        <f t="shared" ref="AO15" si="57">AO13-AO14</f>
-        <v>3840.4217099999996</v>
+        <f t="shared" ref="AO15" si="51">AO13-AO14</f>
+        <v>3695.0677293999997</v>
       </c>
       <c r="AP15" s="9">
-        <f t="shared" ref="AP15" si="58">AP13-AP14</f>
-        <v>4182.5691149000013</v>
+        <f t="shared" ref="AP15" si="52">AP13-AP14</f>
+        <v>4104.6459395259999</v>
       </c>
       <c r="AQ15" s="9">
-        <f t="shared" ref="AQ15" si="59">AQ13-AQ14</f>
-        <v>4440.4551941370009</v>
+        <f t="shared" ref="AQ15" si="53">AQ13-AQ14</f>
+        <v>4416.3966815416607</v>
       </c>
       <c r="AR15" s="9">
-        <f t="shared" ref="AR15" si="60">AR13-AR14</f>
-        <v>4593.6374423006309</v>
+        <f t="shared" ref="AR15" si="54">AR13-AR14</f>
+        <v>4653.5077083327433</v>
       </c>
       <c r="AS15" s="9">
-        <f t="shared" ref="AS15" si="61">AS13-AS14</f>
-        <v>4735.140973477126</v>
+        <f t="shared" ref="AS15" si="55">AS13-AS14</f>
+        <v>4826.5284949608194</v>
       </c>
       <c r="AT15" s="9">
-        <f t="shared" ref="AT15" si="62">AT13-AT14</f>
-        <v>4805.1868804849964</v>
+        <f t="shared" ref="AT15" si="56">AT13-AT14</f>
+        <v>4977.8665302536592</v>
       </c>
       <c r="AU15" s="9">
-        <f t="shared" ref="AU15" si="63">AU13-AU14</f>
-        <v>4809.5973819036099</v>
+        <f t="shared" ref="AU15" si="57">AU13-AU14</f>
+        <v>5053.4137667256618</v>
       </c>
       <c r="AV15" s="9">
-        <f t="shared" ref="AV15" si="64">AV13-AV14</f>
-        <v>4813.2150799922492</v>
+        <f t="shared" ref="AV15" si="58">AV13-AV14</f>
+        <v>5130.4895326974638</v>
       </c>
       <c r="AW15" s="9">
-        <f t="shared" ref="AW15" si="65">AW13-AW14</f>
-        <v>4816.0163861208384</v>
+        <f t="shared" ref="AW15" si="59">AW13-AW14</f>
+        <v>5209.1323051781183</v>
       </c>
       <c r="AX15" s="9">
-        <f t="shared" ref="AX15" si="66">AX13-AX14</f>
-        <v>4817.9771948881662</v>
-      </c>
-    </row>
-    <row r="16" spans="2:50" x14ac:dyDescent="0.3">
+        <f t="shared" ref="AX15" si="60">AX13-AX14</f>
+        <v>5289.3816416981899</v>
+      </c>
+    </row>
+    <row r="16" spans="2:51" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>50</v>
       </c>
@@ -3020,16 +3057,16 @@
         <v>120.8</v>
       </c>
       <c r="AB16" s="1">
-        <f t="shared" ref="AB16:AD16" si="67">AB15*0.2</f>
-        <v>160.71155199999995</v>
+        <f>175.3-71.2</f>
+        <v>104.10000000000001</v>
       </c>
       <c r="AC16" s="1">
-        <f t="shared" si="67"/>
-        <v>169.74752799999993</v>
+        <f t="shared" ref="AC16:AD16" si="61">AC15*0.2</f>
+        <v>146.17910000000003</v>
       </c>
       <c r="AD16" s="1">
-        <f t="shared" si="67"/>
-        <v>161.51498400000003</v>
+        <f t="shared" si="61"/>
+        <v>166.14621599999992</v>
       </c>
       <c r="AH16" s="1">
         <f>217.2+69.2</f>
@@ -3056,48 +3093,48 @@
         <v>489.6</v>
       </c>
       <c r="AN16" s="1">
-        <f t="shared" si="2"/>
-        <v>612.77406399999995</v>
+        <f t="shared" si="1"/>
+        <v>537.22531600000002</v>
       </c>
       <c r="AO16" s="1">
         <f>AO15*0.2</f>
-        <v>768.08434199999999</v>
+        <v>739.01354588000004</v>
       </c>
       <c r="AP16" s="1">
-        <f t="shared" ref="AP16:AX16" si="68">AP15*0.2</f>
-        <v>836.51382298000033</v>
+        <f t="shared" ref="AP16:AX16" si="62">AP15*0.2</f>
+        <v>820.92918790520002</v>
       </c>
       <c r="AQ16" s="1">
-        <f t="shared" si="68"/>
-        <v>888.09103882740021</v>
+        <f t="shared" si="62"/>
+        <v>883.27933630833218</v>
       </c>
       <c r="AR16" s="1">
-        <f t="shared" si="68"/>
-        <v>918.72748846012621</v>
+        <f t="shared" si="62"/>
+        <v>930.70154166654868</v>
       </c>
       <c r="AS16" s="1">
-        <f t="shared" si="68"/>
-        <v>947.02819469542521</v>
+        <f t="shared" si="62"/>
+        <v>965.30569899216391</v>
       </c>
       <c r="AT16" s="1">
-        <f t="shared" si="68"/>
-        <v>961.03737609699931</v>
+        <f t="shared" si="62"/>
+        <v>995.57330605073184</v>
       </c>
       <c r="AU16" s="1">
-        <f t="shared" si="68"/>
-        <v>961.91947638072202</v>
+        <f t="shared" si="62"/>
+        <v>1010.6827533451324</v>
       </c>
       <c r="AV16" s="1">
-        <f t="shared" si="68"/>
-        <v>962.64301599844987</v>
+        <f t="shared" si="62"/>
+        <v>1026.0979065394929</v>
       </c>
       <c r="AW16" s="1">
-        <f t="shared" si="68"/>
-        <v>963.20327722416778</v>
+        <f t="shared" si="62"/>
+        <v>1041.8264610356237</v>
       </c>
       <c r="AX16" s="1">
-        <f t="shared" si="68"/>
-        <v>963.59543897763331</v>
+        <f t="shared" si="62"/>
+        <v>1057.8763283396381</v>
       </c>
     </row>
     <row r="17" spans="2:148" x14ac:dyDescent="0.3">
@@ -3147,7 +3184,8 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="AB17" s="1">
-        <v>0</v>
+        <f>-15.8+3.2</f>
+        <v>-12.600000000000001</v>
       </c>
       <c r="AC17" s="1">
         <v>0</v>
@@ -3177,48 +3215,48 @@
         <v>6</v>
       </c>
       <c r="AN17" s="1">
-        <f t="shared" si="2"/>
-        <v>2.2999999999999998</v>
+        <f t="shared" si="1"/>
+        <v>-10.3</v>
       </c>
       <c r="AO17" s="1">
-        <f t="shared" ref="AO17:AX17" si="69">AO15*0.002</f>
-        <v>7.6808434199999995</v>
+        <f t="shared" ref="AO17:AX17" si="63">AO15*0.002</f>
+        <v>7.3901354587999997</v>
       </c>
       <c r="AP17" s="1">
-        <f t="shared" si="69"/>
-        <v>8.365138229800003</v>
+        <f t="shared" si="63"/>
+        <v>8.2092918790519995</v>
       </c>
       <c r="AQ17" s="1">
-        <f t="shared" si="69"/>
-        <v>8.8809103882740015</v>
+        <f t="shared" si="63"/>
+        <v>8.8327933630833222</v>
       </c>
       <c r="AR17" s="1">
-        <f t="shared" si="69"/>
-        <v>9.187274884601262</v>
+        <f t="shared" si="63"/>
+        <v>9.3070154166654859</v>
       </c>
       <c r="AS17" s="1">
-        <f t="shared" si="69"/>
-        <v>9.4702819469542519</v>
+        <f t="shared" si="63"/>
+        <v>9.6530569899216392</v>
       </c>
       <c r="AT17" s="1">
-        <f t="shared" si="69"/>
-        <v>9.6103737609699937</v>
+        <f t="shared" si="63"/>
+        <v>9.9557330605073187</v>
       </c>
       <c r="AU17" s="1">
-        <f t="shared" si="69"/>
-        <v>9.6191947638072204</v>
+        <f t="shared" si="63"/>
+        <v>10.106827533451323</v>
       </c>
       <c r="AV17" s="1">
-        <f t="shared" si="69"/>
-        <v>9.6264301599844995</v>
+        <f t="shared" si="63"/>
+        <v>10.260979065394928</v>
       </c>
       <c r="AW17" s="1">
-        <f t="shared" si="69"/>
-        <v>9.6320327722416774</v>
+        <f t="shared" si="63"/>
+        <v>10.418264610356237</v>
       </c>
       <c r="AX17" s="1">
-        <f t="shared" si="69"/>
-        <v>9.635954389776332</v>
+        <f t="shared" si="63"/>
+        <v>10.578763283396381</v>
       </c>
     </row>
     <row r="18" spans="2:148" x14ac:dyDescent="0.3">
@@ -3241,528 +3279,528 @@
       <c r="M18" s="7"/>
       <c r="N18" s="7"/>
       <c r="O18" s="9">
-        <f t="shared" ref="O18:W18" si="70">O15-O16-O17</f>
+        <f t="shared" ref="O18:W18" si="64">O15-O16-O17</f>
         <v>-313.09999999999997</v>
       </c>
       <c r="P18" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="64"/>
         <v>-487.40000000000015</v>
       </c>
       <c r="Q18" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="64"/>
         <v>202.49999999999997</v>
       </c>
       <c r="R18" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="64"/>
         <v>78.899999999999949</v>
       </c>
       <c r="S18" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="64"/>
         <v>225.69999999999996</v>
       </c>
       <c r="T18" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="64"/>
         <v>305.49999999999983</v>
       </c>
       <c r="U18" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="64"/>
         <v>408.7000000000001</v>
       </c>
       <c r="V18" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="64"/>
         <v>656.3</v>
       </c>
       <c r="W18" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="64"/>
         <v>372.79999999999967</v>
       </c>
       <c r="X18" s="9">
-        <f t="shared" ref="X18" si="71">X15-X16-X17</f>
+        <f t="shared" ref="X18" si="65">X15-X16-X17</f>
         <v>496.09999999999997</v>
       </c>
       <c r="Y18" s="9">
-        <f t="shared" ref="Y18" si="72">Y15-Y16-Y17</f>
+        <f t="shared" ref="Y18" si="66">Y15-Y16-Y17</f>
         <v>539.79999999999995</v>
       </c>
       <c r="Z18" s="9">
-        <f t="shared" ref="Z18:AD18" si="73">Z15-Z16-Z17</f>
+        <f t="shared" ref="Z18:AD18" si="67">Z15-Z16-Z17</f>
         <v>-2921.9000000000005</v>
       </c>
       <c r="AA18" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="67"/>
         <v>514.5999999999998</v>
       </c>
       <c r="AB18" s="9">
-        <f t="shared" si="73"/>
-        <v>642.84620799999971</v>
+        <f t="shared" si="67"/>
+        <v>599.79999999999973</v>
       </c>
       <c r="AC18" s="9">
-        <f t="shared" si="73"/>
-        <v>678.99011199999973</v>
+        <f t="shared" si="67"/>
+        <v>584.71640000000002</v>
       </c>
       <c r="AD18" s="9">
-        <f t="shared" si="73"/>
-        <v>646.05993599999999</v>
+        <f t="shared" si="67"/>
+        <v>664.5848639999997</v>
       </c>
       <c r="AH18" s="9">
-        <f t="shared" ref="AH18:AN18" si="74">AH15-AH16-AH17</f>
+        <f t="shared" ref="AH18:AN18" si="68">AH15-AH16-AH17</f>
         <v>803.39999999999975</v>
       </c>
       <c r="AI18" s="9">
-        <f t="shared" si="74"/>
+        <f t="shared" si="68"/>
         <v>854.09999999999957</v>
       </c>
       <c r="AJ18" s="9">
-        <f t="shared" si="74"/>
+        <f t="shared" si="68"/>
         <v>-1358.7</v>
       </c>
       <c r="AK18" s="9">
-        <f t="shared" si="74"/>
+        <f t="shared" si="68"/>
         <v>-519.09999999999911</v>
       </c>
       <c r="AL18" s="9">
-        <f t="shared" si="74"/>
+        <f t="shared" si="68"/>
         <v>1596.2000000000014</v>
       </c>
       <c r="AM18" s="9">
-        <f t="shared" si="74"/>
+        <f t="shared" si="68"/>
         <v>-1513.1999999999989</v>
       </c>
       <c r="AN18" s="9">
-        <f t="shared" si="74"/>
-        <v>2482.4962560000022</v>
+        <f t="shared" si="68"/>
+        <v>2363.7012639999989</v>
       </c>
       <c r="AO18" s="9">
-        <f t="shared" ref="AO18" si="75">AO15-AO16-AO17</f>
-        <v>3064.6565245799993</v>
+        <f t="shared" ref="AO18" si="69">AO15-AO16-AO17</f>
+        <v>2948.6640480611995</v>
       </c>
       <c r="AP18" s="9">
-        <f t="shared" ref="AP18" si="76">AP15-AP16-AP17</f>
-        <v>3337.690153690201</v>
+        <f t="shared" ref="AP18" si="70">AP15-AP16-AP17</f>
+        <v>3275.5074597417479</v>
       </c>
       <c r="AQ18" s="9">
-        <f t="shared" ref="AQ18" si="77">AQ15-AQ16-AQ17</f>
-        <v>3543.4832449213268</v>
+        <f t="shared" ref="AQ18" si="71">AQ15-AQ16-AQ17</f>
+        <v>3524.2845518702452</v>
       </c>
       <c r="AR18" s="9">
-        <f t="shared" ref="AR18" si="78">AR15-AR16-AR17</f>
-        <v>3665.7226789559036</v>
+        <f t="shared" ref="AR18" si="72">AR15-AR16-AR17</f>
+        <v>3713.4991512495294</v>
       </c>
       <c r="AS18" s="9">
-        <f t="shared" ref="AS18" si="79">AS15-AS16-AS17</f>
-        <v>3778.6424968347465</v>
+        <f t="shared" ref="AS18" si="73">AS15-AS16-AS17</f>
+        <v>3851.5697389787342</v>
       </c>
       <c r="AT18" s="9">
-        <f t="shared" ref="AT18" si="80">AT15-AT16-AT17</f>
-        <v>3834.5391306270271</v>
+        <f t="shared" ref="AT18" si="74">AT15-AT16-AT17</f>
+        <v>3972.3374911424203</v>
       </c>
       <c r="AU18" s="9">
-        <f t="shared" ref="AU18" si="81">AU15-AU16-AU17</f>
-        <v>3838.0587107590809</v>
+        <f t="shared" ref="AU18" si="75">AU15-AU16-AU17</f>
+        <v>4032.624185847078</v>
       </c>
       <c r="AV18" s="9">
-        <f t="shared" ref="AV18" si="82">AV15-AV16-AV17</f>
-        <v>3840.945633833815</v>
+        <f t="shared" ref="AV18" si="76">AV15-AV16-AV17</f>
+        <v>4094.1306470925756</v>
       </c>
       <c r="AW18" s="9">
-        <f t="shared" ref="AW18" si="83">AW15-AW16-AW17</f>
-        <v>3843.1810761244292</v>
+        <f t="shared" ref="AW18" si="77">AW15-AW16-AW17</f>
+        <v>4156.8875795321383</v>
       </c>
       <c r="AX18" s="9">
-        <f t="shared" ref="AX18" si="84">AX15-AX16-AX17</f>
-        <v>3844.7458015207562</v>
+        <f t="shared" ref="AX18" si="78">AX15-AX16-AX17</f>
+        <v>4220.9265500751553</v>
       </c>
       <c r="AY18" s="9">
         <f>AX18*(1+$BC$23)</f>
-        <v>3806.2983435055485</v>
+        <v>4178.7172845744035</v>
       </c>
       <c r="AZ18" s="9">
-        <f t="shared" ref="AZ18:DK18" si="85">AY18*(1+$BC$23)</f>
-        <v>3768.2353600704928</v>
+        <f t="shared" ref="AZ18:DK18" si="79">AY18*(1+$BC$23)</f>
+        <v>4136.9301117286595</v>
       </c>
       <c r="BA18" s="9">
-        <f t="shared" si="85"/>
-        <v>3730.5530064697878</v>
+        <f t="shared" si="79"/>
+        <v>4095.5608106113727</v>
       </c>
       <c r="BB18" s="9">
-        <f t="shared" si="85"/>
-        <v>3693.2474764050899</v>
+        <f t="shared" si="79"/>
+        <v>4054.6052025052591</v>
       </c>
       <c r="BC18" s="9">
-        <f t="shared" si="85"/>
-        <v>3656.3150016410391</v>
+        <f t="shared" si="79"/>
+        <v>4014.0591504802064</v>
       </c>
       <c r="BD18" s="9">
-        <f t="shared" si="85"/>
-        <v>3619.7518516246287</v>
+        <f t="shared" si="79"/>
+        <v>3973.9185589754043</v>
       </c>
       <c r="BE18" s="9">
-        <f t="shared" si="85"/>
-        <v>3583.5543331083823</v>
+        <f t="shared" si="79"/>
+        <v>3934.1793733856503</v>
       </c>
       <c r="BF18" s="9">
-        <f t="shared" si="85"/>
-        <v>3547.7187897772983</v>
+        <f t="shared" si="79"/>
+        <v>3894.8375796517939</v>
       </c>
       <c r="BG18" s="9">
-        <f t="shared" si="85"/>
-        <v>3512.2416018795252</v>
+        <f t="shared" si="79"/>
+        <v>3855.8892038552758</v>
       </c>
       <c r="BH18" s="9">
-        <f t="shared" si="85"/>
-        <v>3477.1191858607299</v>
+        <f t="shared" si="79"/>
+        <v>3817.3303118167232</v>
       </c>
       <c r="BI18" s="9">
-        <f t="shared" si="85"/>
-        <v>3442.3479940021225</v>
+        <f t="shared" si="79"/>
+        <v>3779.1570086985562</v>
       </c>
       <c r="BJ18" s="9">
-        <f t="shared" si="85"/>
-        <v>3407.924514062101</v>
+        <f t="shared" si="79"/>
+        <v>3741.3654386115704</v>
       </c>
       <c r="BK18" s="9">
-        <f t="shared" si="85"/>
-        <v>3373.8452689214801</v>
+        <f t="shared" si="79"/>
+        <v>3703.9517842254545</v>
       </c>
       <c r="BL18" s="9">
-        <f t="shared" si="85"/>
-        <v>3340.1068162322654</v>
+        <f t="shared" si="79"/>
+        <v>3666.9122663831999</v>
       </c>
       <c r="BM18" s="9">
-        <f t="shared" si="85"/>
-        <v>3306.7057480699427</v>
+        <f t="shared" si="79"/>
+        <v>3630.2431437193677</v>
       </c>
       <c r="BN18" s="9">
-        <f t="shared" si="85"/>
-        <v>3273.6386905892432</v>
+        <f t="shared" si="79"/>
+        <v>3593.940712282174</v>
       </c>
       <c r="BO18" s="9">
-        <f t="shared" si="85"/>
-        <v>3240.9023036833505</v>
+        <f t="shared" si="79"/>
+        <v>3558.0013051593523</v>
       </c>
       <c r="BP18" s="9">
-        <f t="shared" si="85"/>
-        <v>3208.4932806465172</v>
+        <f t="shared" si="79"/>
+        <v>3522.4212921077587</v>
       </c>
       <c r="BQ18" s="9">
-        <f t="shared" si="85"/>
-        <v>3176.4083478400521</v>
+        <f t="shared" si="79"/>
+        <v>3487.1970791866811</v>
       </c>
       <c r="BR18" s="9">
-        <f t="shared" si="85"/>
-        <v>3144.6442643616515</v>
+        <f t="shared" si="79"/>
+        <v>3452.3251083948144</v>
       </c>
       <c r="BS18" s="9">
-        <f t="shared" si="85"/>
-        <v>3113.1978217180349</v>
+        <f t="shared" si="79"/>
+        <v>3417.8018573108661</v>
       </c>
       <c r="BT18" s="9">
-        <f t="shared" si="85"/>
-        <v>3082.0658435008545</v>
+        <f t="shared" si="79"/>
+        <v>3383.6238387377575</v>
       </c>
       <c r="BU18" s="9">
-        <f t="shared" si="85"/>
-        <v>3051.2451850658458</v>
+        <f t="shared" si="79"/>
+        <v>3349.7876003503798</v>
       </c>
       <c r="BV18" s="9">
-        <f t="shared" si="85"/>
-        <v>3020.7327332151872</v>
+        <f t="shared" si="79"/>
+        <v>3316.289724346876</v>
       </c>
       <c r="BW18" s="9">
-        <f t="shared" si="85"/>
-        <v>2990.5254058830351</v>
+        <f t="shared" si="79"/>
+        <v>3283.1268271034073</v>
       </c>
       <c r="BX18" s="9">
-        <f t="shared" si="85"/>
-        <v>2960.6201518242046</v>
+        <f t="shared" si="79"/>
+        <v>3250.2955588323734</v>
       </c>
       <c r="BY18" s="9">
-        <f t="shared" si="85"/>
-        <v>2931.0139503059627</v>
+        <f t="shared" si="79"/>
+        <v>3217.7926032440496</v>
       </c>
       <c r="BZ18" s="9">
-        <f t="shared" si="85"/>
-        <v>2901.7038108029028</v>
+        <f t="shared" si="79"/>
+        <v>3185.614677211609</v>
       </c>
       <c r="CA18" s="9">
-        <f t="shared" si="85"/>
-        <v>2872.686772694874</v>
+        <f t="shared" si="79"/>
+        <v>3153.7585304394929</v>
       </c>
       <c r="CB18" s="9">
-        <f t="shared" si="85"/>
-        <v>2843.959904967925</v>
+        <f t="shared" si="79"/>
+        <v>3122.2209451350977</v>
       </c>
       <c r="CC18" s="9">
-        <f t="shared" si="85"/>
-        <v>2815.5203059182459</v>
+        <f t="shared" si="79"/>
+        <v>3090.9987356837469</v>
       </c>
       <c r="CD18" s="9">
-        <f t="shared" si="85"/>
-        <v>2787.3651028590634</v>
+        <f t="shared" si="79"/>
+        <v>3060.0887483269094</v>
       </c>
       <c r="CE18" s="9">
-        <f t="shared" si="85"/>
-        <v>2759.4914518304727</v>
+        <f t="shared" si="79"/>
+        <v>3029.4878608436402</v>
       </c>
       <c r="CF18" s="9">
-        <f t="shared" si="85"/>
-        <v>2731.8965373121678</v>
+        <f t="shared" si="79"/>
+        <v>2999.1929822352035</v>
       </c>
       <c r="CG18" s="9">
-        <f t="shared" si="85"/>
-        <v>2704.5775719390463</v>
+        <f t="shared" si="79"/>
+        <v>2969.2010524128514</v>
       </c>
       <c r="CH18" s="9">
-        <f t="shared" si="85"/>
-        <v>2677.5317962196559</v>
+        <f t="shared" si="79"/>
+        <v>2939.509041888723</v>
       </c>
       <c r="CI18" s="9">
-        <f t="shared" si="85"/>
-        <v>2650.7564782574595</v>
+        <f t="shared" si="79"/>
+        <v>2910.1139514698357</v>
       </c>
       <c r="CJ18" s="9">
-        <f t="shared" si="85"/>
-        <v>2624.2489134748848</v>
+        <f t="shared" si="79"/>
+        <v>2881.0128119551373</v>
       </c>
       <c r="CK18" s="9">
-        <f t="shared" si="85"/>
-        <v>2598.0064243401362</v>
+        <f t="shared" si="79"/>
+        <v>2852.202683835586</v>
       </c>
       <c r="CL18" s="9">
-        <f t="shared" si="85"/>
-        <v>2572.0263600967346</v>
+        <f t="shared" si="79"/>
+        <v>2823.68065699723</v>
       </c>
       <c r="CM18" s="9">
-        <f t="shared" si="85"/>
-        <v>2546.3060964957672</v>
+        <f t="shared" si="79"/>
+        <v>2795.4438504272575</v>
       </c>
       <c r="CN18" s="9">
-        <f t="shared" si="85"/>
-        <v>2520.8430355308096</v>
+        <f t="shared" si="79"/>
+        <v>2767.4894119229848</v>
       </c>
       <c r="CO18" s="9">
-        <f t="shared" si="85"/>
-        <v>2495.6346051755013</v>
+        <f t="shared" si="79"/>
+        <v>2739.8145178037548</v>
       </c>
       <c r="CP18" s="9">
-        <f t="shared" si="85"/>
-        <v>2470.6782591237461</v>
+        <f t="shared" si="79"/>
+        <v>2712.416372625717</v>
       </c>
       <c r="CQ18" s="9">
-        <f t="shared" si="85"/>
-        <v>2445.9714765325084</v>
+        <f t="shared" si="79"/>
+        <v>2685.2922088994596</v>
       </c>
       <c r="CR18" s="9">
-        <f t="shared" si="85"/>
-        <v>2421.5117617671831</v>
+        <f t="shared" si="79"/>
+        <v>2658.4392868104651</v>
       </c>
       <c r="CS18" s="9">
-        <f t="shared" si="85"/>
-        <v>2397.2966441495114</v>
+        <f t="shared" si="79"/>
+        <v>2631.8548939423604</v>
       </c>
       <c r="CT18" s="9">
-        <f t="shared" si="85"/>
-        <v>2373.3236777080165</v>
+        <f t="shared" si="79"/>
+        <v>2605.5363450029367</v>
       </c>
       <c r="CU18" s="9">
-        <f t="shared" si="85"/>
-        <v>2349.5904409309364</v>
+        <f t="shared" si="79"/>
+        <v>2579.4809815529075</v>
       </c>
       <c r="CV18" s="9">
-        <f t="shared" si="85"/>
-        <v>2326.0945365216271</v>
+        <f t="shared" si="79"/>
+        <v>2553.6861717373786</v>
       </c>
       <c r="CW18" s="9">
-        <f t="shared" si="85"/>
-        <v>2302.8335911564109</v>
+        <f t="shared" si="79"/>
+        <v>2528.1493100200046</v>
       </c>
       <c r="CX18" s="9">
-        <f t="shared" si="85"/>
-        <v>2279.8052552448466</v>
+        <f t="shared" si="79"/>
+        <v>2502.8678169198047</v>
       </c>
       <c r="CY18" s="9">
-        <f t="shared" si="85"/>
-        <v>2257.0072026923981</v>
+        <f t="shared" si="79"/>
+        <v>2477.8391387506067</v>
       </c>
       <c r="CZ18" s="9">
-        <f t="shared" si="85"/>
-        <v>2234.4371306654739</v>
+        <f t="shared" si="79"/>
+        <v>2453.0607473631007</v>
       </c>
       <c r="DA18" s="9">
-        <f t="shared" si="85"/>
-        <v>2212.092759358819</v>
+        <f t="shared" si="79"/>
+        <v>2428.5301398894699</v>
       </c>
       <c r="DB18" s="9">
-        <f t="shared" si="85"/>
-        <v>2189.9718317652309</v>
+        <f t="shared" si="79"/>
+        <v>2404.2448384905751</v>
       </c>
       <c r="DC18" s="9">
-        <f t="shared" si="85"/>
-        <v>2168.0721134475784</v>
+        <f t="shared" si="79"/>
+        <v>2380.2023901056696</v>
       </c>
       <c r="DD18" s="9">
-        <f t="shared" si="85"/>
-        <v>2146.3913923131026</v>
+        <f t="shared" si="79"/>
+        <v>2356.400366204613</v>
       </c>
       <c r="DE18" s="9">
-        <f t="shared" si="85"/>
-        <v>2124.9274783899714</v>
+        <f t="shared" si="79"/>
+        <v>2332.8363625425668</v>
       </c>
       <c r="DF18" s="9">
-        <f t="shared" si="85"/>
-        <v>2103.6782036060717</v>
+        <f t="shared" si="79"/>
+        <v>2309.5079989171413</v>
       </c>
       <c r="DG18" s="9">
-        <f t="shared" si="85"/>
-        <v>2082.6414215700111</v>
+        <f t="shared" si="79"/>
+        <v>2286.4129189279697</v>
       </c>
       <c r="DH18" s="9">
-        <f t="shared" si="85"/>
-        <v>2061.8150073543111</v>
+        <f t="shared" si="79"/>
+        <v>2263.5487897386902</v>
       </c>
       <c r="DI18" s="9">
-        <f t="shared" si="85"/>
-        <v>2041.196857280768</v>
+        <f t="shared" si="79"/>
+        <v>2240.9133018413031</v>
       </c>
       <c r="DJ18" s="9">
-        <f t="shared" si="85"/>
-        <v>2020.7848887079604</v>
+        <f t="shared" si="79"/>
+        <v>2218.5041688228903</v>
       </c>
       <c r="DK18" s="9">
-        <f t="shared" si="85"/>
-        <v>2000.5770398208808</v>
+        <f t="shared" si="79"/>
+        <v>2196.3191271346614</v>
       </c>
       <c r="DL18" s="9">
-        <f t="shared" ref="DL18:ER18" si="86">DK18*(1+$BC$23)</f>
-        <v>1980.571269422672</v>
+        <f t="shared" ref="DL18:ER18" si="80">DK18*(1+$BC$23)</f>
+        <v>2174.3559358633147</v>
       </c>
       <c r="DM18" s="9">
-        <f t="shared" si="86"/>
-        <v>1960.7655567284453</v>
+        <f t="shared" si="80"/>
+        <v>2152.6123765046814</v>
       </c>
       <c r="DN18" s="9">
-        <f t="shared" si="86"/>
-        <v>1941.1579011611609</v>
+        <f t="shared" si="80"/>
+        <v>2131.0862527396343</v>
       </c>
       <c r="DO18" s="9">
-        <f t="shared" si="86"/>
-        <v>1921.7463221495493</v>
+        <f t="shared" si="80"/>
+        <v>2109.7753902122381</v>
       </c>
       <c r="DP18" s="9">
-        <f t="shared" si="86"/>
-        <v>1902.5288589280538</v>
+        <f t="shared" si="80"/>
+        <v>2088.6776363101158</v>
       </c>
       <c r="DQ18" s="9">
-        <f t="shared" si="86"/>
-        <v>1883.5035703387732</v>
+        <f t="shared" si="80"/>
+        <v>2067.7908599470147</v>
       </c>
       <c r="DR18" s="9">
-        <f t="shared" si="86"/>
-        <v>1864.6685346353854</v>
+        <f t="shared" si="80"/>
+        <v>2047.1129513475446</v>
       </c>
       <c r="DS18" s="9">
-        <f t="shared" si="86"/>
-        <v>1846.0218492890315</v>
+        <f t="shared" si="80"/>
+        <v>2026.6418218340691</v>
       </c>
       <c r="DT18" s="9">
-        <f t="shared" si="86"/>
-        <v>1827.5616307961411</v>
+        <f t="shared" si="80"/>
+        <v>2006.3754036157284</v>
       </c>
       <c r="DU18" s="9">
-        <f t="shared" si="86"/>
-        <v>1809.2860144881797</v>
+        <f t="shared" si="80"/>
+        <v>1986.3116495795712</v>
       </c>
       <c r="DV18" s="9">
-        <f t="shared" si="86"/>
-        <v>1791.1931543432979</v>
+        <f t="shared" si="80"/>
+        <v>1966.4485330837754</v>
       </c>
       <c r="DW18" s="9">
-        <f t="shared" si="86"/>
-        <v>1773.281222799865</v>
+        <f t="shared" si="80"/>
+        <v>1946.7840477529376</v>
       </c>
       <c r="DX18" s="9">
-        <f t="shared" si="86"/>
-        <v>1755.5484105718663</v>
+        <f t="shared" si="80"/>
+        <v>1927.3162072754083</v>
       </c>
       <c r="DY18" s="9">
-        <f t="shared" si="86"/>
-        <v>1737.9929264661475</v>
+        <f t="shared" si="80"/>
+        <v>1908.0430452026542</v>
       </c>
       <c r="DZ18" s="9">
-        <f t="shared" si="86"/>
-        <v>1720.612997201486</v>
+        <f t="shared" si="80"/>
+        <v>1888.9626147506276</v>
       </c>
       <c r="EA18" s="9">
-        <f t="shared" si="86"/>
-        <v>1703.4068672294711</v>
+        <f t="shared" si="80"/>
+        <v>1870.0729886031213</v>
       </c>
       <c r="EB18" s="9">
-        <f t="shared" si="86"/>
-        <v>1686.3727985571763</v>
+        <f t="shared" si="80"/>
+        <v>1851.3722587170901</v>
       </c>
       <c r="EC18" s="9">
-        <f t="shared" si="86"/>
-        <v>1669.5090705716045</v>
+        <f t="shared" si="80"/>
+        <v>1832.8585361299192</v>
       </c>
       <c r="ED18" s="9">
-        <f t="shared" si="86"/>
-        <v>1652.8139798658885</v>
+        <f t="shared" si="80"/>
+        <v>1814.52995076862</v>
       </c>
       <c r="EE18" s="9">
-        <f t="shared" si="86"/>
-        <v>1636.2858400672296</v>
+        <f t="shared" si="80"/>
+        <v>1796.3846512609339</v>
       </c>
       <c r="EF18" s="9">
-        <f t="shared" si="86"/>
-        <v>1619.9229816665572</v>
+        <f t="shared" si="80"/>
+        <v>1778.4208047483246</v>
       </c>
       <c r="EG18" s="9">
-        <f t="shared" si="86"/>
-        <v>1603.7237518498916</v>
+        <f t="shared" si="80"/>
+        <v>1760.6365967008414</v>
       </c>
       <c r="EH18" s="9">
-        <f t="shared" si="86"/>
-        <v>1587.6865143313928</v>
+        <f t="shared" si="80"/>
+        <v>1743.0302307338329</v>
       </c>
       <c r="EI18" s="9">
-        <f t="shared" si="86"/>
-        <v>1571.8096491880788</v>
+        <f t="shared" si="80"/>
+        <v>1725.5999284264947</v>
       </c>
       <c r="EJ18" s="9">
-        <f t="shared" si="86"/>
-        <v>1556.0915526961981</v>
+        <f t="shared" si="80"/>
+        <v>1708.3439291422296</v>
       </c>
       <c r="EK18" s="9">
-        <f t="shared" si="86"/>
-        <v>1540.5306371692361</v>
+        <f t="shared" si="80"/>
+        <v>1691.2604898508073</v>
       </c>
       <c r="EL18" s="9">
-        <f t="shared" si="86"/>
-        <v>1525.1253307975437</v>
+        <f t="shared" si="80"/>
+        <v>1674.3478849522992</v>
       </c>
       <c r="EM18" s="9">
-        <f t="shared" si="86"/>
-        <v>1509.8740774895682</v>
+        <f t="shared" si="80"/>
+        <v>1657.6044061027762</v>
       </c>
       <c r="EN18" s="9">
-        <f t="shared" si="86"/>
-        <v>1494.7753367146724</v>
+        <f t="shared" si="80"/>
+        <v>1641.0283620417486</v>
       </c>
       <c r="EO18" s="9">
-        <f t="shared" si="86"/>
-        <v>1479.8275833475257</v>
+        <f t="shared" si="80"/>
+        <v>1624.6180784213311</v>
       </c>
       <c r="EP18" s="9">
-        <f t="shared" si="86"/>
-        <v>1465.0293075140503</v>
+        <f t="shared" si="80"/>
+        <v>1608.3718976371179</v>
       </c>
       <c r="EQ18" s="9">
-        <f t="shared" si="86"/>
-        <v>1450.3790144389097</v>
+        <f t="shared" si="80"/>
+        <v>1592.2881786607466</v>
       </c>
       <c r="ER18" s="9">
-        <f t="shared" si="86"/>
-        <v>1435.8752242945206</v>
+        <f t="shared" si="80"/>
+        <v>1576.3652968741392</v>
       </c>
     </row>
     <row r="19" spans="2:148" x14ac:dyDescent="0.3">
@@ -3813,16 +3851,16 @@
         <v>279.8</v>
       </c>
       <c r="AB19" s="1">
-        <f>279.8</f>
-        <v>279.8</v>
+        <f>274.2</f>
+        <v>274.2</v>
       </c>
       <c r="AC19" s="1">
-        <f>279.8</f>
-        <v>279.8</v>
+        <f>274.2</f>
+        <v>274.2</v>
       </c>
       <c r="AD19" s="1">
-        <f>279.8</f>
-        <v>279.8</v>
+        <f>274.2</f>
+        <v>274.2</v>
       </c>
       <c r="AH19" s="1">
         <v>309</v>
@@ -3843,48 +3881,48 @@
         <v>293.10000000000002</v>
       </c>
       <c r="AN19" s="1">
-        <f t="shared" ref="AN19:AX19" si="87">279.8</f>
-        <v>279.8</v>
+        <f t="shared" ref="AN19:AX19" si="81">274.2</f>
+        <v>274.2</v>
       </c>
       <c r="AO19" s="1">
-        <f t="shared" si="87"/>
-        <v>279.8</v>
+        <f t="shared" si="81"/>
+        <v>274.2</v>
       </c>
       <c r="AP19" s="1">
-        <f t="shared" si="87"/>
-        <v>279.8</v>
+        <f t="shared" si="81"/>
+        <v>274.2</v>
       </c>
       <c r="AQ19" s="1">
-        <f t="shared" si="87"/>
-        <v>279.8</v>
+        <f t="shared" si="81"/>
+        <v>274.2</v>
       </c>
       <c r="AR19" s="1">
-        <f t="shared" si="87"/>
-        <v>279.8</v>
+        <f t="shared" si="81"/>
+        <v>274.2</v>
       </c>
       <c r="AS19" s="1">
-        <f t="shared" si="87"/>
-        <v>279.8</v>
+        <f t="shared" si="81"/>
+        <v>274.2</v>
       </c>
       <c r="AT19" s="1">
-        <f t="shared" si="87"/>
-        <v>279.8</v>
+        <f t="shared" si="81"/>
+        <v>274.2</v>
       </c>
       <c r="AU19" s="1">
-        <f t="shared" si="87"/>
-        <v>279.8</v>
+        <f t="shared" si="81"/>
+        <v>274.2</v>
       </c>
       <c r="AV19" s="1">
-        <f t="shared" si="87"/>
-        <v>279.8</v>
+        <f t="shared" si="81"/>
+        <v>274.2</v>
       </c>
       <c r="AW19" s="1">
-        <f t="shared" si="87"/>
-        <v>279.8</v>
+        <f t="shared" si="81"/>
+        <v>274.2</v>
       </c>
       <c r="AX19" s="1">
-        <f t="shared" si="87"/>
-        <v>279.8</v>
+        <f t="shared" si="81"/>
+        <v>274.2</v>
       </c>
     </row>
     <row r="20" spans="2:148" x14ac:dyDescent="0.3">
@@ -3896,136 +3934,136 @@
         <v>0.51197411003236237</v>
       </c>
       <c r="O20" s="8">
-        <f t="shared" ref="O20:W20" si="88">O18/O19</f>
+        <f t="shared" ref="O20:W20" si="82">O18/O19</f>
         <v>-1.0132686084142393</v>
       </c>
       <c r="P20" s="8">
-        <f t="shared" si="88"/>
+        <f t="shared" si="82"/>
         <v>-1.5773462783171526</v>
       </c>
       <c r="Q20" s="8">
-        <f t="shared" si="88"/>
+        <f t="shared" si="82"/>
         <v>0.65533980582524265</v>
       </c>
       <c r="R20" s="8">
-        <f t="shared" si="88"/>
+        <f t="shared" si="82"/>
         <v>0.25533980582524257</v>
       </c>
       <c r="S20" s="8">
-        <f t="shared" si="88"/>
+        <f t="shared" si="82"/>
         <v>0.73042071197410985</v>
       </c>
       <c r="T20" s="8">
-        <f t="shared" si="88"/>
+        <f t="shared" si="82"/>
         <v>0.98867313915857546</v>
       </c>
       <c r="U20" s="8">
-        <f t="shared" si="88"/>
+        <f t="shared" si="82"/>
         <v>1.3226537216828482</v>
       </c>
       <c r="V20" s="8">
-        <f t="shared" si="88"/>
+        <f t="shared" si="82"/>
         <v>2.1239482200647246</v>
       </c>
       <c r="W20" s="8">
-        <f t="shared" si="88"/>
+        <f t="shared" si="82"/>
         <v>1.2064724919093841</v>
       </c>
       <c r="X20" s="8">
-        <f t="shared" ref="X20" si="89">X18/X19</f>
+        <f t="shared" ref="X20" si="83">X18/X19</f>
         <v>1.6133333333333333</v>
       </c>
       <c r="Y20" s="8">
-        <f t="shared" ref="Y20" si="90">Y18/Y19</f>
+        <f t="shared" ref="Y20" si="84">Y18/Y19</f>
         <v>1.8175084175084173</v>
       </c>
       <c r="Z20" s="8">
-        <f t="shared" ref="Z20:AD20" si="91">Z18/Z19</f>
+        <f t="shared" ref="Z20:AD20" si="85">Z18/Z19</f>
         <v>-9.9689525759126596</v>
       </c>
       <c r="AA20" s="8">
-        <f t="shared" si="91"/>
+        <f t="shared" si="85"/>
         <v>1.8391708363116503</v>
       </c>
       <c r="AB20" s="8">
-        <f t="shared" si="91"/>
-        <v>2.2975204002859173</v>
+        <f t="shared" si="85"/>
+        <v>2.1874544128373441</v>
       </c>
       <c r="AC20" s="8">
-        <f t="shared" si="91"/>
-        <v>2.4266980414581831</v>
+        <f t="shared" si="85"/>
+        <v>2.1324449307075128</v>
       </c>
       <c r="AD20" s="8">
-        <f t="shared" si="91"/>
-        <v>2.309006204431737</v>
+        <f t="shared" si="85"/>
+        <v>2.4237230634573295</v>
       </c>
       <c r="AH20" s="8">
-        <f t="shared" ref="AH20:AN20" si="92">AH18/AH19</f>
+        <f t="shared" ref="AH20:AN20" si="86">AH18/AH19</f>
         <v>2.5999999999999992</v>
       </c>
       <c r="AI20" s="8">
-        <f t="shared" si="92"/>
+        <f t="shared" si="86"/>
         <v>2.7640776699029113</v>
       </c>
       <c r="AJ20" s="8">
-        <f t="shared" si="92"/>
+        <f t="shared" si="86"/>
         <v>-4.3970873786407765</v>
       </c>
       <c r="AK20" s="8">
-        <f t="shared" si="92"/>
+        <f t="shared" si="86"/>
         <v>-1.6799352750809033</v>
       </c>
       <c r="AL20" s="8">
-        <f t="shared" si="92"/>
+        <f t="shared" si="86"/>
         <v>5.1656957928802631</v>
       </c>
       <c r="AM20" s="8">
-        <f t="shared" si="92"/>
+        <f t="shared" si="86"/>
         <v>-5.1627430910951855</v>
       </c>
       <c r="AN20" s="8">
-        <f t="shared" si="92"/>
-        <v>8.872395482487498</v>
+        <f t="shared" si="86"/>
+        <v>8.6203547191830747</v>
       </c>
       <c r="AO20" s="8">
-        <f t="shared" ref="AO20" si="93">AO18/AO19</f>
-        <v>10.953025463116509</v>
+        <f t="shared" ref="AO20" si="87">AO18/AO19</f>
+        <v>10.753698205912471</v>
       </c>
       <c r="AP20" s="8">
-        <f t="shared" ref="AP20" si="94">AP18/AP19</f>
-        <v>11.928842579307366</v>
+        <f t="shared" ref="AP20" si="88">AP18/AP19</f>
+        <v>11.945687307592079</v>
       </c>
       <c r="AQ20" s="8">
-        <f t="shared" ref="AQ20" si="95">AQ18/AQ19</f>
-        <v>12.664343262763856</v>
+        <f t="shared" ref="AQ20" si="89">AQ18/AQ19</f>
+        <v>12.852970648687984</v>
       </c>
       <c r="AR20" s="8">
-        <f t="shared" ref="AR20" si="96">AR18/AR19</f>
-        <v>13.101224728219812</v>
+        <f t="shared" ref="AR20" si="90">AR18/AR19</f>
+        <v>13.543031186176256</v>
       </c>
       <c r="AS20" s="8">
-        <f t="shared" ref="AS20" si="97">AS18/AS19</f>
-        <v>13.504798058737478</v>
+        <f t="shared" ref="AS20" si="91">AS18/AS19</f>
+        <v>14.046570893430832</v>
       </c>
       <c r="AT20" s="8">
-        <f t="shared" ref="AT20" si="98">AT18/AT19</f>
-        <v>13.704571589088731</v>
+        <f t="shared" ref="AT20" si="92">AT18/AT19</f>
+        <v>14.487007626339972</v>
       </c>
       <c r="AU20" s="8">
-        <f t="shared" ref="AU20" si="99">AU18/AU19</f>
-        <v>13.717150503070339</v>
+        <f t="shared" ref="AU20" si="93">AU18/AU19</f>
+        <v>14.70687157493464</v>
       </c>
       <c r="AV20" s="8">
-        <f t="shared" ref="AV20" si="100">AV18/AV19</f>
-        <v>13.727468312486829</v>
+        <f t="shared" ref="AV20" si="94">AV18/AV19</f>
+        <v>14.931183979185178</v>
       </c>
       <c r="AW20" s="8">
-        <f t="shared" ref="AW20" si="101">AW18/AW19</f>
-        <v>13.735457741688453</v>
+        <f t="shared" ref="AW20" si="95">AW18/AW19</f>
+        <v>15.160056818133254</v>
       </c>
       <c r="AX20" s="8">
-        <f t="shared" ref="AX20" si="102">AX18/AX19</f>
-        <v>13.741050041174969</v>
+        <f t="shared" ref="AX20" si="96">AX18/AX19</f>
+        <v>15.393605215445497</v>
       </c>
     </row>
     <row r="22" spans="2:148" x14ac:dyDescent="0.3">
@@ -4040,68 +4078,68 @@
       <c r="Q22" s="10"/>
       <c r="R22" s="10"/>
       <c r="S22" s="10">
-        <f t="shared" ref="S22:Z22" si="103">S3/O3-1</f>
+        <f t="shared" ref="S22:Z22" si="97">S3/O3-1</f>
         <v>0.32113894395386566</v>
       </c>
       <c r="T22" s="10">
-        <f t="shared" si="103"/>
+        <f t="shared" si="97"/>
         <v>0.3842478167737684</v>
       </c>
       <c r="U22" s="10">
-        <f t="shared" si="103"/>
+        <f t="shared" si="97"/>
         <v>0.28135143110061978</v>
       </c>
       <c r="V22" s="10">
-        <f t="shared" si="103"/>
+        <f t="shared" si="97"/>
         <v>0.11609668295191566</v>
       </c>
       <c r="W22" s="10">
-        <f t="shared" si="103"/>
+        <f t="shared" si="97"/>
         <v>2.2779975446733047E-2</v>
       </c>
       <c r="X22" s="10">
-        <f t="shared" si="103"/>
+        <f t="shared" si="97"/>
         <v>-3.8804904178074029E-2</v>
       </c>
       <c r="Y22" s="10">
-        <f t="shared" si="103"/>
+        <f t="shared" si="97"/>
         <v>-4.5595854922279799E-2</v>
       </c>
       <c r="Z22" s="10">
-        <f t="shared" si="103"/>
+        <f t="shared" si="97"/>
         <v>-4.4119341089736253E-2</v>
       </c>
       <c r="AA22" s="10">
-        <f t="shared" ref="AA22:AA25" si="104">AA3/W3-1</f>
+        <f t="shared" ref="AA22:AA25" si="98">AA3/W3-1</f>
         <v>-8.7223259535876174E-2</v>
       </c>
       <c r="AB22" s="10">
-        <f t="shared" ref="AB22:AB25" si="105">AB3/X3-1</f>
-        <v>-8.0000000000000071E-2</v>
+        <f t="shared" ref="AB22:AB25" si="99">AB3/X3-1</f>
+        <v>-0.18501547987616096</v>
       </c>
       <c r="AC22" s="10">
-        <f t="shared" ref="AC22:AC25" si="106">AC3/Y3-1</f>
-        <v>-6.0000000000000053E-2</v>
+        <f t="shared" ref="AC22:AC25" si="100">AC3/Y3-1</f>
+        <v>-8.9999999999999969E-2</v>
       </c>
       <c r="AD22" s="10">
-        <f t="shared" ref="AD22:AD25" si="107">AD3/Z3-1</f>
-        <v>-3.0000000000000027E-2</v>
+        <f t="shared" ref="AD22:AD25" si="101">AD3/Z3-1</f>
+        <v>-5.0000000000000044E-2</v>
       </c>
       <c r="AH22" s="10"/>
       <c r="AI22" s="10">
-        <f t="shared" ref="AI22:AL25" si="108">AI3/AH3-1</f>
+        <f t="shared" ref="AI22:AL25" si="102">AI3/AH3-1</f>
         <v>0.48526548098143585</v>
       </c>
       <c r="AJ22" s="10">
-        <f t="shared" si="108"/>
+        <f t="shared" si="102"/>
         <v>0.42199108469539404</v>
       </c>
       <c r="AK22" s="10">
-        <f t="shared" si="108"/>
+        <f t="shared" si="102"/>
         <v>0.60882660274140976</v>
       </c>
       <c r="AL22" s="10">
-        <f t="shared" si="108"/>
+        <f t="shared" si="102"/>
         <v>0.26453732711851452</v>
       </c>
       <c r="AM22" s="10">
@@ -4109,47 +4147,47 @@
         <v>-2.8340080971659853E-2</v>
       </c>
       <c r="AN22" s="10">
-        <f t="shared" ref="AN22:AX22" si="109">AN3/AM3-1</f>
-        <v>-6.3628109452736337E-2</v>
+        <f t="shared" ref="AN22:AX22" si="103">AN3/AM3-1</f>
+        <v>-0.10288899253731343</v>
       </c>
       <c r="AO22" s="10">
-        <f t="shared" si="109"/>
+        <f t="shared" si="103"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AP22" s="10">
+        <f t="shared" si="103"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AP22" s="10">
-        <f t="shared" si="109"/>
+      <c r="AQ22" s="10">
+        <f t="shared" si="103"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AQ22" s="10">
-        <f t="shared" si="109"/>
+      <c r="AR22" s="10">
+        <f t="shared" si="103"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AR22" s="10">
-        <f t="shared" si="109"/>
+      <c r="AS22" s="10">
+        <f t="shared" si="103"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AS22" s="10">
-        <f t="shared" si="109"/>
+      <c r="AT22" s="10">
+        <f t="shared" si="103"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AT22" s="10">
-        <f t="shared" si="109"/>
+      <c r="AU22" s="10">
+        <f t="shared" si="103"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AU22" s="10">
-        <f t="shared" si="109"/>
+      <c r="AV22" s="10">
+        <f t="shared" si="103"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AV22" s="10">
-        <f t="shared" si="109"/>
+      <c r="AW22" s="10">
+        <f t="shared" si="103"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AW22" s="10">
-        <f t="shared" si="109"/>
-        <v>1.0000000000000009E-2</v>
-      </c>
       <c r="AX22" s="10">
-        <f t="shared" si="109"/>
+        <f t="shared" si="103"/>
         <v>1.0000000000000009E-2</v>
       </c>
     </row>
@@ -4158,124 +4196,124 @@
         <v>58</v>
       </c>
       <c r="O23" s="10">
-        <f t="shared" ref="O23:Z23" si="110">O4/K4-1</f>
+        <f t="shared" ref="O23:Z23" si="104">O4/K4-1</f>
         <v>2.0893495353824156</v>
       </c>
       <c r="P23" s="10"/>
       <c r="Q23" s="10"/>
       <c r="R23" s="10"/>
       <c r="S23" s="10">
-        <f t="shared" si="110"/>
+        <f t="shared" si="104"/>
         <v>2.9847292919944479E-2</v>
       </c>
       <c r="T23" s="10">
-        <f t="shared" si="110"/>
+        <f t="shared" si="104"/>
         <v>4.4540886249428979E-2</v>
       </c>
       <c r="U23" s="10">
-        <f t="shared" si="110"/>
+        <f t="shared" si="104"/>
         <v>8.6772983114446589E-2</v>
       </c>
       <c r="V23" s="10">
-        <f t="shared" si="110"/>
+        <f t="shared" si="104"/>
         <v>-1.1838140335772684E-2</v>
       </c>
       <c r="W23" s="10">
-        <f t="shared" si="110"/>
+        <f t="shared" si="104"/>
         <v>2.6061559200179607E-2</v>
       </c>
       <c r="X23" s="10">
-        <f t="shared" si="110"/>
+        <f t="shared" si="104"/>
         <v>-8.7469932210803014E-3</v>
       </c>
       <c r="Y23" s="10">
-        <f t="shared" si="110"/>
+        <f t="shared" si="104"/>
         <v>4.747518342684609E-3</v>
       </c>
       <c r="Z23" s="10">
-        <f t="shared" si="110"/>
+        <f t="shared" si="104"/>
         <v>2.6573731213243246E-2</v>
       </c>
       <c r="AA23" s="10">
-        <f t="shared" si="104"/>
+        <f t="shared" si="98"/>
         <v>7.9921173636960718E-2</v>
       </c>
       <c r="AB23" s="10">
+        <f t="shared" si="99"/>
+        <v>-0.5170968453562762</v>
+      </c>
+      <c r="AC23" s="10">
+        <f t="shared" si="100"/>
+        <v>-0.51675257731958757</v>
+      </c>
+      <c r="AD23" s="10">
+        <f t="shared" si="101"/>
+        <v>-0.49077021005728838</v>
+      </c>
+      <c r="AH23" s="10"/>
+      <c r="AI23" s="10">
+        <f t="shared" si="102"/>
+        <v>0.17008443908323279</v>
+      </c>
+      <c r="AJ23" s="10">
+        <f t="shared" si="102"/>
+        <v>1.7626288659793818</v>
+      </c>
+      <c r="AK23" s="10">
+        <f t="shared" si="102"/>
+        <v>0.6428771340610131</v>
+      </c>
+      <c r="AL23" s="10">
+        <f t="shared" si="102"/>
+        <v>3.6286201022146525E-2</v>
+      </c>
+      <c r="AM23" s="10">
+        <f t="shared" ref="AM23:AX25" si="105">AM4/AL4-1</f>
+        <v>1.2055455093429757E-2</v>
+      </c>
+      <c r="AN23" s="10">
+        <f t="shared" si="105"/>
+        <v>-0.36266175753966101</v>
+      </c>
+      <c r="AO23" s="10">
+        <f t="shared" si="105"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AP23" s="10">
+        <f t="shared" si="105"/>
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="AQ23" s="10">
+        <f t="shared" si="105"/>
+        <v>8.0000000000000071E-2</v>
+      </c>
+      <c r="AR23" s="10">
+        <f t="shared" si="105"/>
+        <v>6.0000000000000053E-2</v>
+      </c>
+      <c r="AS23" s="10">
+        <f t="shared" si="105"/>
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="AT23" s="10">
+        <f t="shared" si="105"/>
+        <v>4.0000000000000036E-2</v>
+      </c>
+      <c r="AU23" s="10">
         <f t="shared" si="105"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AC23" s="10">
-        <f t="shared" si="106"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="AD23" s="10">
-        <f t="shared" si="107"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="AH23" s="10"/>
-      <c r="AI23" s="10">
-        <f t="shared" si="108"/>
-        <v>0.17008443908323279</v>
-      </c>
-      <c r="AJ23" s="10">
-        <f t="shared" si="108"/>
-        <v>1.7626288659793818</v>
-      </c>
-      <c r="AK23" s="10">
-        <f t="shared" si="108"/>
-        <v>0.6428771340610131</v>
-      </c>
-      <c r="AL23" s="10">
-        <f t="shared" si="108"/>
-        <v>3.6286201022146525E-2</v>
-      </c>
-      <c r="AM23" s="10">
-        <f t="shared" ref="AM23:AX25" si="111">AM4/AL4-1</f>
-        <v>1.2055455093429757E-2</v>
-      </c>
-      <c r="AN23" s="10">
-        <f t="shared" si="111"/>
-        <v>3.7271644377064428E-2</v>
-      </c>
-      <c r="AO23" s="10">
-        <f t="shared" si="111"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="AP23" s="10">
-        <f t="shared" si="111"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="AQ23" s="10">
-        <f t="shared" si="111"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="AR23" s="10">
-        <f t="shared" si="111"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="AS23" s="10">
-        <f t="shared" si="111"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="AT23" s="10">
-        <f t="shared" si="111"/>
-        <v>1.0000000000000009E-2</v>
-      </c>
-      <c r="AU23" s="10">
-        <f t="shared" si="111"/>
-        <v>1.0000000000000009E-2</v>
-      </c>
       <c r="AV23" s="10">
-        <f t="shared" si="111"/>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" si="105"/>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="AW23" s="10">
-        <f t="shared" si="111"/>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" si="105"/>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="AX23" s="10">
-        <f t="shared" si="111"/>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" si="105"/>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="BB23" t="s">
         <v>62</v>
@@ -4289,123 +4327,123 @@
         <v>59</v>
       </c>
       <c r="O24" s="10">
-        <f t="shared" ref="O24:Z24" si="112">O5/K5-1</f>
+        <f t="shared" ref="O24:Z24" si="106">O5/K5-1</f>
         <v>1.5753796095444685</v>
       </c>
       <c r="P24" s="10"/>
       <c r="Q24" s="10"/>
       <c r="R24" s="10"/>
       <c r="S24" s="10">
-        <f t="shared" si="112"/>
+        <f t="shared" si="106"/>
         <v>0.44767319435670672</v>
       </c>
       <c r="T24" s="10">
-        <f t="shared" si="112"/>
+        <f t="shared" si="106"/>
         <v>0.32361990950226227</v>
       </c>
       <c r="U24" s="10">
-        <f t="shared" si="112"/>
+        <f t="shared" si="106"/>
         <v>0.2950623202301057</v>
       </c>
       <c r="V24" s="10">
-        <f t="shared" si="112"/>
+        <f t="shared" si="106"/>
         <v>0.32982877741063388</v>
       </c>
       <c r="W24" s="10">
-        <f t="shared" si="112"/>
+        <f t="shared" si="106"/>
         <v>0.2662545454545453</v>
       </c>
       <c r="X24" s="10">
-        <f t="shared" si="112"/>
+        <f t="shared" si="106"/>
         <v>0.24894024340216059</v>
       </c>
       <c r="Y24" s="10">
-        <f t="shared" si="112"/>
+        <f t="shared" si="106"/>
         <v>0.18384847923992842</v>
       </c>
       <c r="Z24" s="10">
-        <f t="shared" si="112"/>
+        <f t="shared" si="106"/>
         <v>0.23650327535577143</v>
       </c>
       <c r="AA24" s="10">
-        <f t="shared" si="104"/>
+        <f t="shared" si="98"/>
         <v>0.32278444661420935</v>
       </c>
       <c r="AB24" s="10">
-        <f t="shared" si="105"/>
-        <v>0.27</v>
+        <f t="shared" si="99"/>
+        <v>0.31888104231674586</v>
       </c>
       <c r="AC24" s="10">
-        <f t="shared" si="106"/>
-        <v>0.21999999999999997</v>
+        <f t="shared" si="100"/>
+        <v>0.28000000000000003</v>
       </c>
       <c r="AD24" s="10">
-        <f t="shared" si="107"/>
-        <v>0.10000000000000009</v>
+        <f t="shared" si="101"/>
+        <v>0.1399999999999999</v>
       </c>
       <c r="AH24" s="10"/>
       <c r="AI24" s="10">
-        <f t="shared" si="108"/>
+        <f t="shared" si="102"/>
         <v>0.27892529895946572</v>
       </c>
       <c r="AJ24" s="10">
-        <f t="shared" si="108"/>
+        <f t="shared" si="102"/>
         <v>0.14007285974499095</v>
       </c>
       <c r="AK24" s="10">
-        <f t="shared" si="108"/>
+        <f t="shared" si="102"/>
         <v>1.4700431378814507</v>
       </c>
       <c r="AL24" s="10">
-        <f t="shared" si="108"/>
+        <f t="shared" si="102"/>
         <v>0.34310047434238911</v>
       </c>
       <c r="AM24" s="10">
-        <f t="shared" si="111"/>
+        <f t="shared" si="105"/>
         <v>0.23228934230170339</v>
       </c>
       <c r="AN24" s="10">
-        <f t="shared" si="111"/>
-        <v>0.22098237432096179</v>
+        <f t="shared" si="105"/>
+        <v>0.25902270625170942</v>
       </c>
       <c r="AO24" s="10">
-        <f t="shared" si="111"/>
-        <v>0.1399999999999999</v>
+        <f t="shared" si="105"/>
+        <v>0.15999999999999992</v>
       </c>
       <c r="AP24" s="10">
-        <f t="shared" si="111"/>
+        <f t="shared" si="105"/>
         <v>8.0000000000000071E-2</v>
       </c>
       <c r="AQ24" s="10">
-        <f t="shared" si="111"/>
+        <f t="shared" si="105"/>
         <v>6.0000000000000053E-2</v>
       </c>
       <c r="AR24" s="10">
-        <f t="shared" si="111"/>
+        <f t="shared" si="105"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="AS24" s="10">
-        <f t="shared" si="111"/>
+        <f t="shared" si="105"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AT24" s="10">
-        <f t="shared" si="111"/>
+        <f t="shared" si="105"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AU24" s="10">
-        <f t="shared" si="111"/>
+        <f t="shared" si="105"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AV24" s="10">
-        <f t="shared" si="111"/>
+        <f t="shared" si="105"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AW24" s="10">
-        <f t="shared" si="111"/>
+        <f t="shared" si="105"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AX24" s="10">
-        <f t="shared" si="111"/>
+        <f t="shared" si="105"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BB24" t="s">
@@ -4432,131 +4470,131 @@
       <c r="M25" s="7"/>
       <c r="N25" s="7"/>
       <c r="O25" s="11">
-        <f t="shared" ref="O25:Z25" si="113">O6/K6-1</f>
+        <f t="shared" ref="O25:Z25" si="107">O6/K6-1</f>
         <v>1.3420798065296249</v>
       </c>
       <c r="P25" s="11"/>
       <c r="Q25" s="11"/>
       <c r="R25" s="11"/>
       <c r="S25" s="11">
-        <f t="shared" si="113"/>
+        <f t="shared" si="107"/>
         <v>0.31818885848520839</v>
       </c>
       <c r="T25" s="11">
-        <f t="shared" si="113"/>
+        <f t="shared" si="107"/>
         <v>0.28390007908080217</v>
       </c>
       <c r="U25" s="11">
-        <f t="shared" si="113"/>
+        <f t="shared" si="107"/>
         <v>0.25341709822565606</v>
       </c>
       <c r="V25" s="11">
-        <f t="shared" si="113"/>
+        <f t="shared" si="107"/>
         <v>0.20357420357420364</v>
       </c>
       <c r="W25" s="11">
-        <f t="shared" si="113"/>
+        <f t="shared" si="107"/>
         <v>0.15447281842393856</v>
       </c>
       <c r="X25" s="11">
-        <f t="shared" si="113"/>
+        <f t="shared" si="107"/>
         <v>0.11865942028985499</v>
       </c>
       <c r="Y25" s="11">
-        <f t="shared" si="113"/>
+        <f t="shared" si="107"/>
         <v>8.8255215388783448E-2</v>
       </c>
       <c r="Z25" s="11">
-        <f t="shared" si="113"/>
+        <f t="shared" si="107"/>
         <v>0.12675919948353775</v>
       </c>
       <c r="AA25" s="11">
-        <f t="shared" si="104"/>
+        <f t="shared" si="98"/>
         <v>0.18085900393540499</v>
       </c>
       <c r="AB25" s="11">
-        <f t="shared" si="105"/>
-        <v>0.14322526315789474</v>
+        <f t="shared" si="99"/>
+        <v>6.435627530364374E-2</v>
       </c>
       <c r="AC25" s="11">
-        <f t="shared" si="106"/>
-        <v>0.1187950457459388</v>
+        <f t="shared" si="100"/>
+        <v>6.9114022530652797E-2</v>
       </c>
       <c r="AD25" s="11">
-        <f t="shared" si="107"/>
-        <v>5.8295470822471218E-2</v>
+        <f t="shared" si="101"/>
+        <v>9.6696937576989939E-3</v>
       </c>
       <c r="AH25" s="10"/>
       <c r="AI25" s="11">
-        <f t="shared" si="108"/>
+        <f t="shared" si="102"/>
         <v>0.33033435159225011</v>
       </c>
       <c r="AJ25" s="11">
-        <f t="shared" si="108"/>
+        <f t="shared" si="102"/>
         <v>0.43955836557516292</v>
       </c>
       <c r="AK25" s="11">
-        <f t="shared" si="108"/>
+        <f t="shared" si="102"/>
         <v>0.97015186277723142</v>
       </c>
       <c r="AL25" s="11">
-        <f t="shared" si="108"/>
+        <f t="shared" si="102"/>
         <v>0.26036999245818726</v>
       </c>
       <c r="AM25" s="11">
-        <f t="shared" si="111"/>
+        <f t="shared" si="105"/>
         <v>0.12101372756071815</v>
       </c>
       <c r="AN25" s="11">
-        <f t="shared" si="111"/>
-        <v>0.12249874403416228</v>
+        <f t="shared" si="105"/>
+        <v>7.7528023737754026E-2</v>
       </c>
       <c r="AO25" s="11">
-        <f t="shared" si="111"/>
-        <v>9.6546974014065645E-2</v>
+        <f t="shared" si="105"/>
+        <v>0.11856955768058874</v>
       </c>
       <c r="AP25" s="11">
-        <f t="shared" si="111"/>
-        <v>5.8945146075553012E-2</v>
+        <f t="shared" si="105"/>
+        <v>6.8147789826198624E-2</v>
       </c>
       <c r="AQ25" s="11">
-        <f t="shared" si="111"/>
-        <v>4.5948461556035047E-2</v>
+        <f t="shared" si="105"/>
+        <v>5.2549276278104573E-2</v>
       </c>
       <c r="AR25" s="11">
-        <f t="shared" si="111"/>
-        <v>3.2299526594686823E-2</v>
+        <f t="shared" si="105"/>
+        <v>3.6435565194833375E-2</v>
       </c>
       <c r="AS25" s="11">
-        <f t="shared" si="111"/>
-        <v>2.5347668869441176E-2</v>
+        <f t="shared" si="105"/>
+        <v>2.8300839926515886E-2</v>
       </c>
       <c r="AT25" s="11">
-        <f t="shared" si="111"/>
-        <v>1.7127717581356228E-2</v>
+        <f t="shared" si="105"/>
+        <v>2.0061301448319524E-2</v>
       </c>
       <c r="AU25" s="11">
-        <f t="shared" si="111"/>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" si="105"/>
+        <v>1.1759511837891923E-2</v>
       </c>
       <c r="AV25" s="11">
-        <f t="shared" si="111"/>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" si="105"/>
+        <v>1.1791233165415305E-2</v>
       </c>
       <c r="AW25" s="11">
-        <f t="shared" si="111"/>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" si="105"/>
+        <v>1.1823469209755633E-2</v>
       </c>
       <c r="AX25" s="11">
-        <f t="shared" si="111"/>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" si="105"/>
+        <v>1.1856226252110025E-2</v>
       </c>
       <c r="BB25" t="s">
         <v>64</v>
       </c>
       <c r="BC25" s="12">
         <f>NPV(BC24,AN18:ER18)</f>
-        <v>22830.50813356306</v>
+        <v>23489.004755336726</v>
       </c>
     </row>
     <row r="26" spans="2:148" x14ac:dyDescent="0.3">
@@ -4572,131 +4610,131 @@
         <v>0.6518147555371987</v>
       </c>
       <c r="P26" s="10">
-        <f t="shared" ref="P26:R26" si="114">P8/P6</f>
+        <f t="shared" ref="P26:R26" si="108">P8/P6</f>
         <v>0.70870354002884117</v>
       </c>
       <c r="Q26" s="10">
-        <f t="shared" si="114"/>
+        <f t="shared" si="108"/>
         <v>0.71504372187791831</v>
       </c>
       <c r="R26" s="10">
-        <f t="shared" si="114"/>
+        <f t="shared" si="108"/>
         <v>0.72882672882672883</v>
       </c>
       <c r="S26" s="10">
-        <f t="shared" ref="S26:Z26" si="115">S8/S6</f>
+        <f t="shared" ref="S26:Z26" si="109">S8/S6</f>
         <v>0.71749177502741657</v>
       </c>
       <c r="T26" s="10">
-        <f t="shared" si="115"/>
+        <f t="shared" si="109"/>
         <v>0.75170289855072459</v>
       </c>
       <c r="U26" s="10">
-        <f t="shared" si="115"/>
+        <f t="shared" si="109"/>
         <v>0.73804524519100512</v>
       </c>
       <c r="V26" s="10">
-        <f t="shared" si="115"/>
+        <f t="shared" si="109"/>
         <v>0.74089735313105232</v>
       </c>
       <c r="W26" s="10">
-        <f t="shared" si="115"/>
+        <f t="shared" si="109"/>
         <v>0.72523408875016959</v>
       </c>
       <c r="X26" s="10">
-        <f t="shared" si="115"/>
+        <f t="shared" si="109"/>
         <v>0.7274817813765182</v>
       </c>
       <c r="Y26" s="10">
-        <f t="shared" si="115"/>
+        <f t="shared" si="109"/>
         <v>0.73268189456650279</v>
       </c>
       <c r="Z26" s="10">
-        <f t="shared" si="115"/>
+        <f t="shared" si="109"/>
         <v>0.74824533761136724</v>
       </c>
       <c r="AA26" s="10">
-        <f t="shared" ref="AA26:AD26" si="116">AA8/AA6</f>
+        <f t="shared" ref="AA26:AD26" si="110">AA8/AA6</f>
         <v>0.73169190105438553</v>
       </c>
       <c r="AB26" s="10">
-        <f t="shared" si="116"/>
-        <v>0.73</v>
+        <f t="shared" si="110"/>
+        <v>0.74122086300286039</v>
       </c>
       <c r="AC26" s="10">
-        <f t="shared" si="116"/>
+        <f t="shared" si="110"/>
         <v>0.74</v>
       </c>
       <c r="AD26" s="10">
-        <f t="shared" si="116"/>
-        <v>0.75000000000000011</v>
+        <f t="shared" si="110"/>
+        <v>0.75</v>
       </c>
       <c r="AH26" s="10">
-        <f t="shared" ref="AH26:AL26" si="117">AH8/AH6</f>
+        <f t="shared" ref="AH26:AL26" si="111">AH8/AH6</f>
         <v>0.82135832949742638</v>
       </c>
       <c r="AI26" s="10">
-        <f t="shared" si="117"/>
+        <f t="shared" si="111"/>
         <v>0.75782454153691292</v>
       </c>
       <c r="AJ26" s="10">
-        <f t="shared" si="117"/>
+        <f t="shared" si="111"/>
         <v>0.62552168687861898</v>
       </c>
       <c r="AK26" s="10">
-        <f t="shared" si="117"/>
+        <f t="shared" si="111"/>
         <v>0.70388403353888473</v>
       </c>
       <c r="AL26" s="10">
-        <f t="shared" si="117"/>
+        <f t="shared" si="111"/>
         <v>0.73752199929602258</v>
       </c>
       <c r="AM26" s="10">
-        <f t="shared" ref="AM26:AX26" si="118">AM8/AM6</f>
+        <f t="shared" ref="AM26:AX26" si="112">AM8/AM6</f>
         <v>0.73396288620949512</v>
       </c>
       <c r="AN26" s="10">
-        <f t="shared" si="118"/>
-        <v>0.73809275080323167</v>
+        <f t="shared" si="112"/>
+        <v>0.74075316214323106</v>
       </c>
       <c r="AO26" s="10">
-        <f t="shared" si="118"/>
+        <f t="shared" si="112"/>
         <v>0.74</v>
       </c>
       <c r="AP26" s="10">
-        <f t="shared" si="118"/>
+        <f t="shared" si="112"/>
         <v>0.74</v>
       </c>
       <c r="AQ26" s="10">
-        <f t="shared" si="118"/>
+        <f t="shared" si="112"/>
         <v>0.74</v>
       </c>
       <c r="AR26" s="10">
-        <f t="shared" si="118"/>
+        <f t="shared" si="112"/>
         <v>0.74</v>
       </c>
       <c r="AS26" s="10">
-        <f t="shared" si="118"/>
+        <f t="shared" si="112"/>
         <v>0.74</v>
       </c>
       <c r="AT26" s="10">
-        <f t="shared" si="118"/>
+        <f t="shared" si="112"/>
         <v>0.74</v>
       </c>
       <c r="AU26" s="10">
-        <f t="shared" si="118"/>
+        <f t="shared" si="112"/>
         <v>0.74</v>
       </c>
       <c r="AV26" s="10">
-        <f t="shared" si="118"/>
+        <f t="shared" si="112"/>
         <v>0.74</v>
       </c>
       <c r="AW26" s="10">
-        <f t="shared" si="118"/>
+        <f t="shared" si="112"/>
         <v>0.74</v>
       </c>
       <c r="AX26" s="10">
-        <f t="shared" si="118"/>
+        <f t="shared" si="112"/>
         <v>0.74</v>
       </c>
       <c r="BB26" t="s">
@@ -4704,7 +4742,7 @@
       </c>
       <c r="BC26" s="12">
         <f>BC25/Main!D13</f>
-        <v>4033.65868084153</v>
+        <v>4333.764715006776</v>
       </c>
     </row>
     <row r="27" spans="2:148" x14ac:dyDescent="0.3">
@@ -4720,139 +4758,139 @@
         <v>0.12298001961897878</v>
       </c>
       <c r="P27" s="10">
-        <f t="shared" ref="P27:R27" si="119">P9/P6</f>
+        <f t="shared" ref="P27:R27" si="113">P9/P6</f>
         <v>0.12652928315578918</v>
       </c>
       <c r="Q27" s="10">
-        <f t="shared" si="119"/>
+        <f t="shared" si="113"/>
         <v>0.12051107903896766</v>
       </c>
       <c r="R27" s="10">
-        <f t="shared" si="119"/>
+        <f t="shared" si="113"/>
         <v>0.12711732711732712</v>
       </c>
       <c r="S27" s="10">
-        <f t="shared" ref="S27:Z27" si="120">S9/S6</f>
+        <f t="shared" ref="S27:Z27" si="114">S9/S6</f>
         <v>0.11671627761240796</v>
       </c>
       <c r="T27" s="10">
-        <f t="shared" si="120"/>
+        <f t="shared" si="114"/>
         <v>0.1101086956521739</v>
       </c>
       <c r="U27" s="10">
-        <f t="shared" si="120"/>
+        <f t="shared" si="114"/>
         <v>9.424952587374695E-2</v>
       </c>
       <c r="V27" s="10">
-        <f t="shared" si="120"/>
+        <f t="shared" si="114"/>
         <v>9.9612653324725631E-2</v>
       </c>
       <c r="W27" s="10">
-        <f t="shared" si="120"/>
+        <f t="shared" si="114"/>
         <v>8.7189577961731587E-2</v>
       </c>
       <c r="X27" s="10">
-        <f t="shared" si="120"/>
+        <f t="shared" si="114"/>
         <v>8.2753036437246963E-2</v>
       </c>
       <c r="Y27" s="10">
-        <f t="shared" si="120"/>
+        <f t="shared" si="114"/>
         <v>9.7933652828779486E-2</v>
       </c>
       <c r="Z27" s="10">
-        <f t="shared" si="120"/>
+        <f t="shared" si="114"/>
         <v>8.6888016730168743E-2</v>
       </c>
       <c r="AA27" s="10">
-        <f t="shared" ref="AA27:AD27" si="121">AA9/AA6</f>
+        <f t="shared" ref="AA27:AD27" si="115">AA9/AA6</f>
         <v>7.9840262016261099E-2</v>
       </c>
       <c r="AB27" s="10">
-        <f t="shared" si="121"/>
-        <v>0.09</v>
+        <f t="shared" si="115"/>
+        <v>6.8498569776641718E-2</v>
       </c>
       <c r="AC27" s="10">
-        <f t="shared" si="121"/>
-        <v>0.09</v>
+        <f t="shared" si="115"/>
+        <v>8.0000000000000016E-2</v>
       </c>
       <c r="AD27" s="10">
-        <f t="shared" si="121"/>
-        <v>0.09</v>
+        <f t="shared" si="115"/>
+        <v>0.08</v>
       </c>
       <c r="AH27" s="10">
-        <f t="shared" ref="AH27:AL27" si="122">AH9/AH6</f>
+        <f t="shared" ref="AH27:AL27" si="116">AH9/AH6</f>
         <v>0.1195966020839436</v>
       </c>
       <c r="AI27" s="10">
-        <f t="shared" si="122"/>
+        <f t="shared" si="116"/>
         <v>0.12346261520556133</v>
       </c>
       <c r="AJ27" s="10">
-        <f t="shared" si="122"/>
+        <f t="shared" si="116"/>
         <v>0.17771222549983612</v>
       </c>
       <c r="AK27" s="10">
-        <f t="shared" si="122"/>
+        <f t="shared" si="116"/>
         <v>0.12436227319107404</v>
       </c>
       <c r="AL27" s="10">
-        <f t="shared" si="122"/>
+        <f t="shared" si="116"/>
         <v>0.10461105244632174</v>
       </c>
       <c r="AM27" s="10">
-        <f t="shared" ref="AM27:AX27" si="123">AM9/AM6</f>
+        <f t="shared" ref="AM27:AX27" si="117">AM9/AM6</f>
         <v>8.8741836222054754E-2</v>
       </c>
       <c r="AN27" s="10">
-        <f t="shared" si="123"/>
-        <v>8.7527017281997369E-2</v>
+        <f t="shared" si="117"/>
+        <v>7.720605863911191E-2</v>
       </c>
       <c r="AO27" s="10">
-        <f t="shared" si="123"/>
-        <v>0.09</v>
+        <f t="shared" si="117"/>
+        <v>0.08</v>
       </c>
       <c r="AP27" s="10">
-        <f t="shared" si="123"/>
-        <v>0.09</v>
+        <f t="shared" si="117"/>
+        <v>0.08</v>
       </c>
       <c r="AQ27" s="10">
-        <f t="shared" si="123"/>
-        <v>0.09</v>
+        <f t="shared" si="117"/>
+        <v>0.08</v>
       </c>
       <c r="AR27" s="10">
-        <f t="shared" si="123"/>
-        <v>0.09</v>
+        <f t="shared" si="117"/>
+        <v>0.08</v>
       </c>
       <c r="AS27" s="10">
-        <f t="shared" si="123"/>
-        <v>0.09</v>
+        <f t="shared" si="117"/>
+        <v>0.08</v>
       </c>
       <c r="AT27" s="10">
-        <f t="shared" si="123"/>
-        <v>0.09</v>
+        <f t="shared" si="117"/>
+        <v>0.08</v>
       </c>
       <c r="AU27" s="10">
-        <f t="shared" si="123"/>
-        <v>0.09</v>
+        <f t="shared" si="117"/>
+        <v>0.08</v>
       </c>
       <c r="AV27" s="10">
-        <f t="shared" si="123"/>
-        <v>0.09</v>
+        <f t="shared" si="117"/>
+        <v>0.08</v>
       </c>
       <c r="AW27" s="10">
-        <f t="shared" si="123"/>
-        <v>0.09</v>
+        <f t="shared" si="117"/>
+        <v>0.08</v>
       </c>
       <c r="AX27" s="10">
-        <f t="shared" si="123"/>
-        <v>0.09</v>
+        <f t="shared" si="117"/>
+        <v>0.08</v>
       </c>
       <c r="BB27" t="s">
         <v>65</v>
       </c>
       <c r="BC27" s="1">
         <f>Main!D10</f>
-        <v>-1344.0106007067136</v>
+        <v>-1571.0701107011073</v>
       </c>
     </row>
     <row r="28" spans="2:148" x14ac:dyDescent="0.3">
@@ -4868,139 +4906,139 @@
         <v>0.19810005679178069</v>
       </c>
       <c r="P28" s="10">
-        <f t="shared" ref="P28:R28" si="124">P10/P6</f>
+        <f t="shared" ref="P28:R28" si="118">P10/P6</f>
         <v>0.15625436107363819</v>
       </c>
       <c r="Q28" s="10">
-        <f t="shared" si="124"/>
+        <f t="shared" si="118"/>
         <v>0.16359623057984549</v>
       </c>
       <c r="R28" s="10">
-        <f t="shared" si="124"/>
+        <f t="shared" si="118"/>
         <v>0.15777000777000777</v>
       </c>
       <c r="S28" s="10">
-        <f t="shared" ref="S28:Z28" si="125">S10/S6</f>
+        <f t="shared" ref="S28:Z28" si="119">S10/S6</f>
         <v>0.15271032429891901</v>
       </c>
       <c r="T28" s="10">
-        <f t="shared" si="125"/>
+        <f t="shared" si="119"/>
         <v>0.1492391304347826</v>
       </c>
       <c r="U28" s="10">
-        <f t="shared" si="125"/>
+        <f t="shared" si="119"/>
         <v>0.1498238959631536</v>
       </c>
       <c r="V28" s="10">
-        <f t="shared" si="125"/>
+        <f t="shared" si="119"/>
         <v>0.14654615881213687</v>
       </c>
       <c r="W28" s="10">
-        <f t="shared" si="125"/>
+        <f t="shared" si="119"/>
         <v>0.17970552313746779</v>
       </c>
       <c r="X28" s="10">
-        <f t="shared" si="125"/>
+        <f t="shared" si="119"/>
         <v>0.17000809716599188</v>
       </c>
       <c r="Y28" s="10">
-        <f t="shared" si="125"/>
+        <f t="shared" si="119"/>
         <v>0.1561585859214539</v>
       </c>
       <c r="Z28" s="10">
-        <f t="shared" si="125"/>
+        <f t="shared" si="119"/>
         <v>0.15730369266909217</v>
       </c>
       <c r="AA28" s="10">
-        <f t="shared" ref="AA28:AD28" si="126">AA10/AA6</f>
+        <f t="shared" ref="AA28:AD28" si="120">AA10/AA6</f>
         <v>0.17039675927256012</v>
       </c>
       <c r="AB28" s="10">
-        <f t="shared" si="126"/>
-        <v>0.17</v>
+        <f t="shared" si="120"/>
+        <v>0.16158480920211796</v>
       </c>
       <c r="AC28" s="10">
-        <f t="shared" si="126"/>
-        <v>0.16</v>
+        <f t="shared" si="120"/>
+        <v>0.16000000000000003</v>
       </c>
       <c r="AD28" s="10">
-        <f t="shared" si="126"/>
+        <f t="shared" si="120"/>
         <v>0.15</v>
       </c>
       <c r="AH28" s="10">
-        <f t="shared" ref="AH28:AL28" si="127">AH10/AH6</f>
+        <f t="shared" ref="AH28:AL28" si="121">AH10/AH6</f>
         <v>0.1508976022094824</v>
       </c>
       <c r="AI28" s="10">
-        <f t="shared" si="127"/>
+        <f t="shared" si="121"/>
         <v>0.15913308798087508</v>
       </c>
       <c r="AJ28" s="10">
-        <f t="shared" si="127"/>
+        <f t="shared" si="121"/>
         <v>0.22123893805309736</v>
       </c>
       <c r="AK28" s="10">
-        <f t="shared" si="127"/>
+        <f t="shared" si="121"/>
         <v>0.16759460538574153</v>
       </c>
       <c r="AL28" s="10">
-        <f t="shared" si="127"/>
+        <f t="shared" si="121"/>
         <v>0.14943681802182329</v>
       </c>
       <c r="AM28" s="10">
-        <f t="shared" ref="AM28:AX28" si="128">AM10/AM6</f>
+        <f t="shared" ref="AM28:AX28" si="122">AM10/AM6</f>
         <v>0.16527725445867872</v>
       </c>
       <c r="AN28" s="10">
-        <f t="shared" si="128"/>
-        <v>0.1624156501910245</v>
+        <f t="shared" si="122"/>
+        <v>0.16044813356601612</v>
       </c>
       <c r="AO28" s="10">
-        <f t="shared" si="128"/>
+        <f t="shared" si="122"/>
         <v>0.15</v>
       </c>
       <c r="AP28" s="10">
-        <f t="shared" si="128"/>
+        <f t="shared" si="122"/>
         <v>0.15</v>
       </c>
       <c r="AQ28" s="10">
-        <f t="shared" si="128"/>
+        <f t="shared" si="122"/>
         <v>0.15</v>
       </c>
       <c r="AR28" s="10">
-        <f t="shared" si="128"/>
+        <f t="shared" si="122"/>
         <v>0.15</v>
       </c>
       <c r="AS28" s="10">
-        <f t="shared" si="128"/>
+        <f t="shared" si="122"/>
         <v>0.15</v>
       </c>
       <c r="AT28" s="10">
-        <f t="shared" si="128"/>
+        <f t="shared" si="122"/>
         <v>0.15</v>
       </c>
       <c r="AU28" s="10">
-        <f t="shared" si="128"/>
+        <f t="shared" si="122"/>
         <v>0.15</v>
       </c>
       <c r="AV28" s="10">
-        <f t="shared" si="128"/>
+        <f t="shared" si="122"/>
         <v>0.15</v>
       </c>
       <c r="AW28" s="10">
-        <f t="shared" si="128"/>
+        <f t="shared" si="122"/>
         <v>0.15</v>
       </c>
       <c r="AX28" s="10">
-        <f t="shared" si="128"/>
+        <f t="shared" si="122"/>
         <v>0.15</v>
       </c>
       <c r="BB28" t="s">
         <v>66</v>
       </c>
       <c r="BC28" s="12">
-        <f>BC26-BC27</f>
-        <v>5377.6692815482438</v>
+        <f>BC26+BC27</f>
+        <v>2762.6946043056687</v>
       </c>
     </row>
     <row r="29" spans="2:148" x14ac:dyDescent="0.3">
@@ -5016,52 +5054,52 @@
       <c r="Q29" s="10"/>
       <c r="R29" s="10"/>
       <c r="S29" s="10">
-        <f t="shared" ref="S29:Z29" si="129">S11/O11-1</f>
+        <f t="shared" ref="S29:Z29" si="123">S11/O11-1</f>
         <v>0.30415136966958478</v>
       </c>
       <c r="T29" s="10">
-        <f t="shared" si="129"/>
+        <f t="shared" si="123"/>
         <v>0.124751230753116</v>
       </c>
       <c r="U29" s="10">
-        <f t="shared" si="129"/>
+        <f t="shared" si="123"/>
         <v>0.12612995852387554</v>
       </c>
       <c r="V29" s="10">
-        <f t="shared" si="129"/>
+        <f t="shared" si="123"/>
         <v>3.466812945693909E-2</v>
       </c>
       <c r="W29" s="10">
-        <f t="shared" si="129"/>
+        <f t="shared" si="123"/>
         <v>-2.9233434387180623E-2</v>
       </c>
       <c r="X29" s="10">
-        <f t="shared" si="129"/>
+        <f t="shared" si="123"/>
         <v>-0.20739430061463959</v>
       </c>
       <c r="Y29" s="10">
-        <f t="shared" si="129"/>
+        <f t="shared" si="123"/>
         <v>-0.14014543394088208</v>
       </c>
       <c r="Z29" s="10">
-        <f t="shared" si="129"/>
+        <f t="shared" si="123"/>
         <v>9.7974764075919873E-2</v>
       </c>
       <c r="AA29" s="10">
-        <f t="shared" ref="AA29" si="130">AA11/W11-1</f>
+        <f t="shared" ref="AA29" si="124">AA11/W11-1</f>
         <v>0.22317644434530459</v>
       </c>
       <c r="AB29" s="10">
-        <f t="shared" ref="AB29" si="131">AB11/X11-1</f>
-        <v>5.0000000000000044E-2</v>
+        <f t="shared" ref="AB29" si="125">AB11/X11-1</f>
+        <v>0.28281048055457636</v>
       </c>
       <c r="AC29" s="10">
-        <f t="shared" ref="AC29" si="132">AC11/Y11-1</f>
-        <v>5.0000000000000044E-2</v>
+        <f t="shared" ref="AC29" si="126">AC11/Y11-1</f>
+        <v>0.19999999999999996</v>
       </c>
       <c r="AD29" s="10">
-        <f t="shared" ref="AD29" si="133">AD11/Z11-1</f>
-        <v>5.0000000000000044E-2</v>
+        <f t="shared" ref="AD29" si="127">AD11/Z11-1</f>
+        <v>7.0000000000000062E-2</v>
       </c>
       <c r="AH29" s="10"/>
       <c r="AI29" s="10">
@@ -5069,71 +5107,71 @@
         <v>-3.8755304101838695E-2</v>
       </c>
       <c r="AJ29" s="10">
-        <f t="shared" ref="AJ29:AX29" si="134">AJ11/AI11-1</f>
+        <f t="shared" ref="AJ29:AX29" si="128">AJ11/AI11-1</f>
         <v>2.7348440258975866</v>
       </c>
       <c r="AK29" s="10">
-        <f t="shared" si="134"/>
+        <f t="shared" si="128"/>
         <v>1.7694429123000552</v>
       </c>
       <c r="AL29" s="10">
-        <f t="shared" si="134"/>
+        <f t="shared" si="128"/>
         <v>0.13790650695649709</v>
       </c>
       <c r="AM29" s="10">
-        <f t="shared" si="134"/>
+        <f t="shared" si="128"/>
         <v>-7.6436465469820525E-2</v>
       </c>
       <c r="AN29" s="10">
-        <f t="shared" si="134"/>
-        <v>9.2036440425589561E-2</v>
+        <f t="shared" si="128"/>
+        <v>0.18826244686899329</v>
       </c>
       <c r="AO29" s="10">
-        <f t="shared" si="134"/>
+        <f t="shared" si="128"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AP29" s="10">
-        <f t="shared" si="134"/>
+        <f t="shared" si="128"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AQ29" s="10">
-        <f t="shared" si="134"/>
+        <f t="shared" si="128"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AR29" s="10">
-        <f t="shared" si="134"/>
-        <v>3.0000000000000027E-2</v>
+        <f t="shared" si="128"/>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="AS29" s="10">
-        <f t="shared" si="134"/>
+        <f t="shared" si="128"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AT29" s="10">
-        <f t="shared" si="134"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="128"/>
+        <v>1.0000000000000009E-2</v>
       </c>
       <c r="AU29" s="10">
-        <f t="shared" si="134"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="128"/>
+        <v>1.0000000000000009E-2</v>
       </c>
       <c r="AV29" s="10">
-        <f t="shared" si="134"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="128"/>
+        <v>1.0000000000000009E-2</v>
       </c>
       <c r="AW29" s="10">
-        <f t="shared" si="134"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="128"/>
+        <v>1.0000000000000009E-2</v>
       </c>
       <c r="AX29" s="10">
-        <f t="shared" si="134"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="128"/>
+        <v>1.0000000000000009E-2</v>
       </c>
       <c r="BB29" t="s">
         <v>67</v>
       </c>
       <c r="BC29" s="2">
         <f>BC28/AX19</f>
-        <v>19.219690069865059</v>
+        <v>10.075472663405066</v>
       </c>
     </row>
     <row r="30" spans="2:148" x14ac:dyDescent="0.3">
@@ -5148,143 +5186,143 @@
       <c r="M30" s="10"/>
       <c r="N30" s="10"/>
       <c r="O30" s="10">
-        <f t="shared" ref="O30:Z30" si="135">O13/O6</f>
+        <f t="shared" ref="O30:Z30" si="129">O13/O6</f>
         <v>-0.14920749651504983</v>
       </c>
       <c r="P30" s="10">
-        <f t="shared" si="135"/>
+        <f t="shared" si="129"/>
         <v>-0.22426385076987496</v>
       </c>
       <c r="Q30" s="10">
-        <f t="shared" si="135"/>
+        <f t="shared" si="129"/>
         <v>0.1051871975549707</v>
       </c>
       <c r="R30" s="10">
-        <f t="shared" si="135"/>
+        <f t="shared" si="129"/>
         <v>5.4312354312354295E-2</v>
       </c>
       <c r="S30" s="10">
-        <f t="shared" si="135"/>
+        <f t="shared" si="129"/>
         <v>0.12055459815133948</v>
       </c>
       <c r="T30" s="10">
-        <f t="shared" si="135"/>
+        <f t="shared" si="129"/>
         <v>0.15333333333333327</v>
       </c>
       <c r="U30" s="10">
-        <f t="shared" si="135"/>
+        <f t="shared" si="129"/>
         <v>0.17071931725819564</v>
       </c>
       <c r="V30" s="10">
-        <f t="shared" si="135"/>
+        <f t="shared" si="129"/>
         <v>0.23886378308586184</v>
       </c>
       <c r="W30" s="10">
-        <f t="shared" si="135"/>
+        <f t="shared" si="129"/>
         <v>0.16406568055367068</v>
       </c>
       <c r="X30" s="10">
-        <f t="shared" si="135"/>
+        <f t="shared" si="129"/>
         <v>0.2112064777327935</v>
       </c>
       <c r="Y30" s="10">
-        <f t="shared" si="135"/>
+        <f t="shared" si="129"/>
         <v>0.20840853924192446</v>
       </c>
       <c r="Z30" s="10">
-        <f t="shared" si="135"/>
+        <f t="shared" si="129"/>
         <v>0.21044489643910949</v>
       </c>
       <c r="AA30" s="10">
-        <f t="shared" ref="AA30:AD30" si="136">AA13/AA6</f>
+        <f t="shared" ref="AA30:AD30" si="130">AA13/AA6</f>
         <v>0.18309535438273902</v>
       </c>
       <c r="AB30" s="10">
-        <f t="shared" si="136"/>
-        <v>0.22765559077408093</v>
+        <f t="shared" si="130"/>
+        <v>0.21051670622603608</v>
       </c>
       <c r="AC30" s="10">
-        <f t="shared" si="136"/>
-        <v>0.23607942508989913</v>
+        <f t="shared" si="130"/>
+        <v>0.2127484834045556</v>
       </c>
       <c r="AD30" s="10">
-        <f t="shared" si="136"/>
-        <v>0.21860664524204482</v>
+        <f t="shared" si="130"/>
+        <v>0.23570490067397662</v>
       </c>
       <c r="AH30" s="10">
-        <f t="shared" ref="AH30:AL30" si="137">AH13/AH6</f>
+        <f t="shared" ref="AH30:AL30" si="131">AH13/AH6</f>
         <v>0.45679373979997479</v>
       </c>
       <c r="AI30" s="10">
-        <f t="shared" si="137"/>
+        <f t="shared" si="131"/>
         <v>0.35689346041332443</v>
       </c>
       <c r="AJ30" s="10">
-        <f t="shared" si="137"/>
+        <f t="shared" si="131"/>
         <v>-0.31355839615426634</v>
       </c>
       <c r="AK30" s="10">
-        <f t="shared" si="137"/>
+        <f t="shared" si="131"/>
         <v>-4.2533605430105044E-2</v>
       </c>
       <c r="AL30" s="10">
-        <f t="shared" si="137"/>
+        <f t="shared" si="131"/>
         <v>0.17380323829637462</v>
       </c>
       <c r="AM30" s="10">
-        <f t="shared" ref="AM30:AX30" si="138">AM13/AM6</f>
+        <f t="shared" ref="AM30:AX30" si="132">AM13/AM6</f>
         <v>0.19938457673951274</v>
       </c>
       <c r="AN30" s="10">
-        <f t="shared" si="138"/>
-        <v>0.21658933563528737</v>
+        <f t="shared" si="132"/>
+        <v>0.21058929273259799</v>
       </c>
       <c r="AO30" s="10">
-        <f t="shared" si="138"/>
-        <v>0.24491966440629448</v>
+        <f t="shared" si="132"/>
+        <v>0.24065155809675354</v>
       </c>
       <c r="AP30" s="10">
-        <f t="shared" si="138"/>
-        <v>0.25189201571469183</v>
+        <f t="shared" si="132"/>
+        <v>0.25027105817867662</v>
       </c>
       <c r="AQ30" s="10">
-        <f t="shared" si="138"/>
-        <v>0.25567512816674609</v>
+        <f t="shared" si="132"/>
+        <v>0.25583535792078327</v>
       </c>
       <c r="AR30" s="10">
-        <f t="shared" si="138"/>
-        <v>0.25621938061097349</v>
+        <f t="shared" si="132"/>
+        <v>0.26009417244968364</v>
       </c>
       <c r="AS30" s="10">
-        <f t="shared" si="138"/>
-        <v>0.25758289904012743</v>
+        <f t="shared" si="132"/>
+        <v>0.26234021374398137</v>
       </c>
       <c r="AT30" s="10">
-        <f t="shared" si="138"/>
-        <v>0.25699158732146049</v>
+        <f t="shared" si="132"/>
+        <v>0.2652448555849487</v>
       </c>
       <c r="AU30" s="10">
-        <f t="shared" si="138"/>
-        <v>0.25468066365649367</v>
+        <f t="shared" si="132"/>
+        <v>0.26614069386839845</v>
       </c>
       <c r="AV30" s="10">
-        <f t="shared" si="138"/>
-        <v>0.25234874273193197</v>
+        <f t="shared" si="132"/>
+        <v>0.26705106820898961</v>
       </c>
       <c r="AW30" s="10">
-        <f t="shared" si="138"/>
-        <v>0.24999565394466519</v>
+        <f t="shared" si="132"/>
+        <v>0.26797615599328506</v>
       </c>
       <c r="AX30" s="10">
-        <f t="shared" si="138"/>
-        <v>0.24762122574087003</v>
+        <f t="shared" si="132"/>
+        <v>0.26891613463937841</v>
       </c>
       <c r="BB30" t="s">
         <v>68</v>
       </c>
       <c r="BC30" s="2">
         <f>Main!D3</f>
-        <v>13.28</v>
+        <v>15.35</v>
       </c>
     </row>
     <row r="31" spans="2:148" x14ac:dyDescent="0.3">
@@ -5299,143 +5337,143 @@
       <c r="M31" s="10"/>
       <c r="N31" s="10"/>
       <c r="O31" s="10">
-        <f t="shared" ref="O31:Z31" si="139">O16/O15</f>
+        <f t="shared" ref="O31:Z31" si="133">O16/O15</f>
         <v>-8.0082844321712116E-2</v>
       </c>
       <c r="P31" s="10">
-        <f t="shared" si="139"/>
+        <f t="shared" si="133"/>
         <v>-1.2205213074058748E-2</v>
       </c>
       <c r="Q31" s="10">
-        <f t="shared" si="139"/>
+        <f t="shared" si="133"/>
         <v>0.20032441200324413</v>
       </c>
       <c r="R31" s="10">
-        <f t="shared" si="139"/>
+        <f t="shared" si="133"/>
         <v>0.43440860215053784</v>
       </c>
       <c r="S31" s="10">
-        <f t="shared" si="139"/>
+        <f t="shared" si="133"/>
         <v>0.26466753585397657</v>
       </c>
       <c r="T31" s="10">
-        <f t="shared" si="139"/>
+        <f t="shared" si="133"/>
         <v>0.27249053030303039</v>
       </c>
       <c r="U31" s="10">
-        <f t="shared" si="139"/>
+        <f t="shared" si="133"/>
         <v>0.18311817279046669</v>
       </c>
       <c r="V31" s="10">
-        <f t="shared" si="139"/>
+        <f t="shared" si="133"/>
         <v>0.11106596234592984</v>
       </c>
       <c r="W31" s="10">
-        <f t="shared" si="139"/>
+        <f t="shared" si="133"/>
         <v>0.22835296548873749</v>
       </c>
       <c r="X31" s="10">
-        <f t="shared" si="139"/>
+        <f t="shared" si="133"/>
         <v>0.23538437931563605</v>
       </c>
       <c r="Y31" s="10">
-        <f t="shared" si="139"/>
+        <f t="shared" si="133"/>
         <v>0.18967318310699896</v>
       </c>
       <c r="Z31" s="10">
-        <f t="shared" si="139"/>
+        <f t="shared" si="133"/>
         <v>-3.4923670881592456E-2</v>
       </c>
       <c r="AA31" s="10">
-        <f t="shared" ref="AA31:AD31" si="140">AA16/AA15</f>
+        <f t="shared" ref="AA31:AD31" si="134">AA16/AA15</f>
         <v>0.18943076681825319</v>
       </c>
       <c r="AB31" s="10">
-        <f t="shared" si="140"/>
+        <f t="shared" si="134"/>
+        <v>0.15058585274121228</v>
+      </c>
+      <c r="AC31" s="10">
+        <f t="shared" si="134"/>
         <v>0.2</v>
       </c>
-      <c r="AC31" s="10">
-        <f t="shared" si="140"/>
+      <c r="AD31" s="10">
+        <f t="shared" si="134"/>
         <v>0.2</v>
       </c>
-      <c r="AD31" s="10">
-        <f t="shared" si="140"/>
+      <c r="AH31" s="10">
+        <f t="shared" ref="AH31:AL31" si="135">AH16/AH15</f>
+        <v>0.26255958929226259</v>
+      </c>
+      <c r="AI31" s="10">
+        <f t="shared" si="135"/>
+        <v>0.25733794448878256</v>
+      </c>
+      <c r="AJ31" s="10">
+        <f t="shared" si="135"/>
+        <v>4.7184170471841716E-2</v>
+      </c>
+      <c r="AK31" s="10">
+        <f t="shared" si="135"/>
+        <v>-0.35943152454780447</v>
+      </c>
+      <c r="AL31" s="10">
+        <f t="shared" si="135"/>
+        <v>0.18797564687975635</v>
+      </c>
+      <c r="AM31" s="10">
+        <f t="shared" ref="AM31:AX31" si="136">AM16/AM15</f>
+        <v>-0.48113207547169862</v>
+      </c>
+      <c r="AN31" s="10">
+        <f t="shared" si="136"/>
+        <v>0.185850818544677</v>
+      </c>
+      <c r="AO31" s="10">
+        <f t="shared" si="136"/>
+        <v>0.2</v>
+      </c>
+      <c r="AP31" s="10">
+        <f t="shared" si="136"/>
+        <v>0.2</v>
+      </c>
+      <c r="AQ31" s="10">
+        <f t="shared" si="136"/>
+        <v>0.2</v>
+      </c>
+      <c r="AR31" s="10">
+        <f t="shared" si="136"/>
+        <v>0.2</v>
+      </c>
+      <c r="AS31" s="10">
+        <f t="shared" si="136"/>
+        <v>0.2</v>
+      </c>
+      <c r="AT31" s="10">
+        <f t="shared" si="136"/>
+        <v>0.2</v>
+      </c>
+      <c r="AU31" s="10">
+        <f t="shared" si="136"/>
+        <v>0.2</v>
+      </c>
+      <c r="AV31" s="10">
+        <f t="shared" si="136"/>
         <v>0.20000000000000004</v>
       </c>
-      <c r="AH31" s="10">
-        <f t="shared" ref="AH31:AL31" si="141">AH16/AH15</f>
-        <v>0.26255958929226259</v>
-      </c>
-      <c r="AI31" s="10">
-        <f t="shared" si="141"/>
-        <v>0.25733794448878256</v>
-      </c>
-      <c r="AJ31" s="10">
-        <f t="shared" si="141"/>
-        <v>4.7184170471841716E-2</v>
-      </c>
-      <c r="AK31" s="10">
-        <f t="shared" si="141"/>
-        <v>-0.35943152454780447</v>
-      </c>
-      <c r="AL31" s="10">
-        <f t="shared" si="141"/>
-        <v>0.18797564687975635</v>
-      </c>
-      <c r="AM31" s="10">
-        <f t="shared" ref="AM31:AX31" si="142">AM16/AM15</f>
-        <v>-0.48113207547169862</v>
-      </c>
-      <c r="AN31" s="10">
-        <f t="shared" si="142"/>
-        <v>0.19782410105220777</v>
-      </c>
-      <c r="AO31" s="10">
-        <f t="shared" si="142"/>
+      <c r="AW31" s="10">
+        <f t="shared" si="136"/>
         <v>0.2</v>
       </c>
-      <c r="AP31" s="10">
-        <f t="shared" si="142"/>
-        <v>0.2</v>
-      </c>
-      <c r="AQ31" s="10">
-        <f t="shared" si="142"/>
-        <v>0.2</v>
-      </c>
-      <c r="AR31" s="10">
-        <f t="shared" si="142"/>
-        <v>0.2</v>
-      </c>
-      <c r="AS31" s="10">
-        <f t="shared" si="142"/>
-        <v>0.2</v>
-      </c>
-      <c r="AT31" s="10">
-        <f t="shared" si="142"/>
-        <v>0.2</v>
-      </c>
-      <c r="AU31" s="10">
-        <f t="shared" si="142"/>
-        <v>0.2</v>
-      </c>
-      <c r="AV31" s="10">
-        <f t="shared" si="142"/>
-        <v>0.2</v>
-      </c>
-      <c r="AW31" s="10">
-        <f t="shared" si="142"/>
-        <v>0.2</v>
-      </c>
       <c r="AX31" s="10">
-        <f t="shared" si="142"/>
-        <v>0.2</v>
+        <f t="shared" si="136"/>
+        <v>0.20000000000000004</v>
       </c>
       <c r="BB31" s="7" t="s">
         <v>69</v>
       </c>
       <c r="BC31" s="11">
         <f>BC29/BC30-1</f>
-        <v>0.44726581851393532</v>
+        <v>-0.34361741606481655</v>
       </c>
     </row>
     <row r="32" spans="2:148" x14ac:dyDescent="0.3">
@@ -5450,142 +5488,142 @@
       <c r="M32" s="10"/>
       <c r="N32" s="10"/>
       <c r="O32" s="10">
-        <f t="shared" ref="O32:Z32" si="143">O18/O6</f>
+        <f t="shared" ref="O32:Z32" si="137">O18/O6</f>
         <v>-0.16165005937322524</v>
       </c>
       <c r="P32" s="10">
-        <f t="shared" si="143"/>
+        <f t="shared" si="137"/>
         <v>-0.22672931106666055</v>
       </c>
       <c r="Q32" s="10">
-        <f t="shared" si="143"/>
+        <f t="shared" si="137"/>
         <v>8.5958060955938539E-2</v>
       </c>
       <c r="R32" s="10">
-        <f t="shared" si="143"/>
+        <f t="shared" si="137"/>
         <v>3.0652680652680633E-2</v>
       </c>
       <c r="S32" s="10">
-        <f t="shared" si="143"/>
+        <f t="shared" si="137"/>
         <v>8.8398872003759982E-2</v>
       </c>
       <c r="T32" s="10">
-        <f t="shared" si="143"/>
+        <f t="shared" si="137"/>
         <v>0.11068840579710139</v>
       </c>
       <c r="U32" s="10">
-        <f t="shared" si="143"/>
+        <f t="shared" si="137"/>
         <v>0.13841099972907073</v>
       </c>
       <c r="V32" s="10">
-        <f t="shared" si="143"/>
+        <f t="shared" si="137"/>
         <v>0.21184635248547448</v>
       </c>
       <c r="W32" s="10">
-        <f t="shared" si="143"/>
+        <f t="shared" si="137"/>
         <v>0.12647577690324321</v>
       </c>
       <c r="X32" s="10">
-        <f t="shared" si="143"/>
+        <f t="shared" si="137"/>
         <v>0.16068016194331983</v>
       </c>
       <c r="Y32" s="10">
-        <f t="shared" si="143"/>
+        <f t="shared" si="137"/>
         <v>0.16798406672060745</v>
       </c>
       <c r="Z32" s="10">
-        <f t="shared" si="143"/>
+        <f t="shared" si="137"/>
         <v>-0.8370527401380814</v>
       </c>
       <c r="AA32" s="10">
-        <f t="shared" ref="AA32:AD32" si="144">AA18/AA6</f>
+        <f t="shared" ref="AA32:AD32" si="138">AA18/AA6</f>
         <v>0.14784382451805667</v>
       </c>
       <c r="AB32" s="10">
-        <f t="shared" si="144"/>
-        <v>0.18212447261926473</v>
+        <f t="shared" si="138"/>
+        <v>0.18252084474468985</v>
       </c>
       <c r="AC32" s="10">
-        <f t="shared" si="144"/>
-        <v>0.18886354007191933</v>
+        <f t="shared" si="138"/>
+        <v>0.17019878672364447</v>
       </c>
       <c r="AD32" s="10">
-        <f t="shared" si="144"/>
-        <v>0.17488531619363584</v>
+        <f t="shared" si="138"/>
+        <v>0.18856392053918131</v>
       </c>
       <c r="AH32" s="10">
-        <f t="shared" ref="AH32:AX32" si="145">AH18/AH6</f>
+        <f t="shared" ref="AH32:AX32" si="139">AH18/AH6</f>
         <v>0.33619282755157542</v>
       </c>
       <c r="AI32" s="10">
-        <f t="shared" si="145"/>
+        <f t="shared" si="139"/>
         <v>0.26866094177597422</v>
       </c>
       <c r="AJ32" s="10">
-        <f t="shared" si="145"/>
+        <f t="shared" si="139"/>
         <v>-0.29688626679777125</v>
       </c>
       <c r="AK32" s="10">
-        <f t="shared" si="145"/>
+        <f t="shared" si="139"/>
         <v>-5.7572867219732836E-2</v>
       </c>
       <c r="AL32" s="10">
-        <f t="shared" si="145"/>
+        <f t="shared" si="139"/>
         <v>0.14046110524463229</v>
       </c>
       <c r="AM32" s="10">
-        <f t="shared" si="145"/>
+        <f t="shared" si="139"/>
         <v>-0.11878296910324029</v>
       </c>
       <c r="AN32" s="10">
-        <f t="shared" si="145"/>
-        <v>0.1736043417864499</v>
+        <f t="shared" si="139"/>
+        <v>0.17219552373469646</v>
       </c>
       <c r="AO32" s="10">
-        <f t="shared" si="145"/>
-        <v>0.19544589219622296</v>
+        <f t="shared" si="139"/>
+        <v>0.1920399433612093</v>
       </c>
       <c r="AP32" s="10">
-        <f t="shared" si="145"/>
-        <v>0.20100982854032406</v>
+        <f t="shared" si="139"/>
+        <v>0.19971630442658395</v>
       </c>
       <c r="AQ32" s="10">
-        <f t="shared" si="145"/>
-        <v>0.20402875227706335</v>
+        <f t="shared" si="139"/>
+        <v>0.20415661562078505</v>
       </c>
       <c r="AR32" s="10">
-        <f t="shared" si="145"/>
-        <v>0.20446306572755685</v>
+        <f t="shared" si="139"/>
+        <v>0.20755514961484758</v>
       </c>
       <c r="AS32" s="10">
-        <f t="shared" si="145"/>
-        <v>0.20555115343402169</v>
+        <f t="shared" si="139"/>
+        <v>0.20934749056769714</v>
       </c>
       <c r="AT32" s="10">
-        <f t="shared" si="145"/>
-        <v>0.20507928668252548</v>
+        <f t="shared" si="139"/>
+        <v>0.21166539475678905</v>
       </c>
       <c r="AU32" s="10">
-        <f t="shared" si="145"/>
-        <v>0.20323516959788196</v>
+        <f t="shared" si="139"/>
+        <v>0.21238027370698193</v>
       </c>
       <c r="AV32" s="10">
-        <f t="shared" si="145"/>
-        <v>0.20137429670008172</v>
+        <f t="shared" si="139"/>
+        <v>0.21310675243077365</v>
       </c>
       <c r="AW32" s="10">
-        <f t="shared" si="145"/>
-        <v>0.19949653184784283</v>
+        <f t="shared" si="139"/>
+        <v>0.21384497248264145</v>
       </c>
       <c r="AX32" s="10">
-        <f t="shared" si="145"/>
-        <v>0.19760173814121426</v>
+        <f t="shared" si="139"/>
+        <v>0.21459507544222398</v>
       </c>
       <c r="BB32" t="s">
         <v>71</v>
       </c>
       <c r="BC32" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="34" spans="2:39" s="7" customFormat="1" x14ac:dyDescent="0.3">
@@ -7083,27 +7121,27 @@
         <v>106</v>
       </c>
       <c r="O80" s="9">
-        <f t="shared" ref="O80:R80" si="146">O18</f>
+        <f t="shared" ref="O80:R80" si="140">O18</f>
         <v>-313.09999999999997</v>
       </c>
       <c r="P80" s="9">
-        <f t="shared" si="146"/>
+        <f t="shared" si="140"/>
         <v>-487.40000000000015</v>
       </c>
       <c r="Q80" s="9">
-        <f t="shared" si="146"/>
+        <f t="shared" si="140"/>
         <v>202.49999999999997</v>
       </c>
       <c r="R80" s="9">
-        <f t="shared" si="146"/>
+        <f t="shared" si="140"/>
         <v>78.899999999999949</v>
       </c>
       <c r="S80" s="9">
-        <f t="shared" ref="S80:T80" si="147">S18</f>
+        <f t="shared" ref="S80:T80" si="141">S18</f>
         <v>225.69999999999996</v>
       </c>
       <c r="T80" s="9">
-        <f t="shared" si="147"/>
+        <f t="shared" si="141"/>
         <v>305.49999999999983</v>
       </c>
       <c r="U80" s="9">
@@ -7111,15 +7149,15 @@
         <v>408.7000000000001</v>
       </c>
       <c r="V80" s="9">
-        <f t="shared" ref="V80:X80" si="148">V18</f>
+        <f t="shared" ref="V80:X80" si="142">V18</f>
         <v>656.3</v>
       </c>
       <c r="W80" s="9">
-        <f t="shared" si="148"/>
+        <f t="shared" si="142"/>
         <v>372.79999999999967</v>
       </c>
       <c r="X80" s="9">
-        <f t="shared" si="148"/>
+        <f t="shared" si="142"/>
         <v>496.09999999999997</v>
       </c>
       <c r="Y80" s="9">
@@ -7158,48 +7196,48 @@
         <v>-1513.1999999999989</v>
       </c>
       <c r="AN80" s="9">
-        <f t="shared" ref="AN80:AX80" si="149">AN18</f>
-        <v>2482.4962560000022</v>
+        <f t="shared" ref="AN80:AX80" si="143">AN18</f>
+        <v>2363.7012639999989</v>
       </c>
       <c r="AO80" s="9">
-        <f t="shared" si="149"/>
-        <v>3064.6565245799993</v>
+        <f t="shared" si="143"/>
+        <v>2948.6640480611995</v>
       </c>
       <c r="AP80" s="9">
-        <f t="shared" si="149"/>
-        <v>3337.690153690201</v>
+        <f t="shared" si="143"/>
+        <v>3275.5074597417479</v>
       </c>
       <c r="AQ80" s="9">
-        <f t="shared" si="149"/>
-        <v>3543.4832449213268</v>
+        <f t="shared" si="143"/>
+        <v>3524.2845518702452</v>
       </c>
       <c r="AR80" s="9">
-        <f t="shared" si="149"/>
-        <v>3665.7226789559036</v>
+        <f t="shared" si="143"/>
+        <v>3713.4991512495294</v>
       </c>
       <c r="AS80" s="9">
-        <f t="shared" si="149"/>
-        <v>3778.6424968347465</v>
+        <f t="shared" si="143"/>
+        <v>3851.5697389787342</v>
       </c>
       <c r="AT80" s="9">
-        <f t="shared" si="149"/>
-        <v>3834.5391306270271</v>
+        <f t="shared" si="143"/>
+        <v>3972.3374911424203</v>
       </c>
       <c r="AU80" s="9">
-        <f t="shared" si="149"/>
-        <v>3838.0587107590809</v>
+        <f t="shared" si="143"/>
+        <v>4032.624185847078</v>
       </c>
       <c r="AV80" s="9">
-        <f t="shared" si="149"/>
-        <v>3840.945633833815</v>
+        <f t="shared" si="143"/>
+        <v>4094.1306470925756</v>
       </c>
       <c r="AW80" s="9">
-        <f t="shared" si="149"/>
-        <v>3843.1810761244292</v>
+        <f t="shared" si="143"/>
+        <v>4156.8875795321383</v>
       </c>
       <c r="AX80" s="9">
-        <f t="shared" si="149"/>
-        <v>3844.7458015207562</v>
+        <f t="shared" si="143"/>
+        <v>4220.9265500751553</v>
       </c>
     </row>
     <row r="81" spans="2:50" x14ac:dyDescent="0.3">
@@ -7210,26 +7248,26 @@
         <v>212.5</v>
       </c>
       <c r="T81" s="1">
-        <f t="shared" ref="T81:T88" si="150">T121-S81</f>
+        <f t="shared" ref="T81:T88" si="144">T121-S81</f>
         <v>221.7</v>
       </c>
       <c r="U81" s="1">
-        <f t="shared" ref="U81:U88" si="151">U121-T81-S81</f>
+        <f t="shared" ref="U81:U88" si="145">U121-T81-S81</f>
         <v>222.90000000000003</v>
       </c>
       <c r="V81" s="1">
-        <f t="shared" ref="V81:V88" si="152">V121-U81-T81-S81</f>
+        <f t="shared" ref="V81:V88" si="146">V121-U81-T81-S81</f>
         <v>221.09999999999997</v>
       </c>
       <c r="W81" s="1">
         <v>217.3</v>
       </c>
       <c r="X81" s="1">
-        <f t="shared" ref="X81:X88" si="153">X121-W81</f>
+        <f t="shared" ref="X81:X88" si="147">X121-W81</f>
         <v>224.3</v>
       </c>
       <c r="Y81" s="1">
-        <f t="shared" ref="Y81:Y88" si="154">Y121-X81-W81</f>
+        <f t="shared" ref="Y81:Y88" si="148">Y121-X81-W81</f>
         <v>263.79999999999995</v>
       </c>
       <c r="Z81" s="1">
@@ -7260,44 +7298,44 @@
         <v>939.90599999999995</v>
       </c>
       <c r="AO81" s="1">
-        <f t="shared" ref="AO81:AX81" si="155">AN81*0.99</f>
-        <v>930.50693999999999</v>
+        <f>AN81*1.01</f>
+        <v>949.30505999999991</v>
       </c>
       <c r="AP81" s="1">
-        <f t="shared" si="155"/>
-        <v>921.20187060000001</v>
+        <f t="shared" ref="AP81:AX81" si="149">AO81*1.01</f>
+        <v>958.79811059999997</v>
       </c>
       <c r="AQ81" s="1">
-        <f t="shared" si="155"/>
-        <v>911.98985189400003</v>
+        <f t="shared" si="149"/>
+        <v>968.386091706</v>
       </c>
       <c r="AR81" s="1">
-        <f t="shared" si="155"/>
-        <v>902.86995337506005</v>
+        <f t="shared" si="149"/>
+        <v>978.06995262305998</v>
       </c>
       <c r="AS81" s="1">
-        <f t="shared" si="155"/>
-        <v>893.84125384130948</v>
+        <f t="shared" si="149"/>
+        <v>987.85065214929057</v>
       </c>
       <c r="AT81" s="1">
-        <f t="shared" si="155"/>
-        <v>884.90284130289638</v>
+        <f t="shared" si="149"/>
+        <v>997.72915867078348</v>
       </c>
       <c r="AU81" s="1">
-        <f t="shared" si="155"/>
-        <v>876.05381288986746</v>
+        <f t="shared" si="149"/>
+        <v>1007.7064502574913</v>
       </c>
       <c r="AV81" s="1">
-        <f t="shared" si="155"/>
-        <v>867.29327476096876</v>
+        <f t="shared" si="149"/>
+        <v>1017.7835147600662</v>
       </c>
       <c r="AW81" s="1">
-        <f t="shared" si="155"/>
-        <v>858.62034201335905</v>
+        <f t="shared" si="149"/>
+        <v>1027.9613499076668</v>
       </c>
       <c r="AX81" s="1">
-        <f t="shared" si="155"/>
-        <v>850.03413859322541</v>
+        <f t="shared" si="149"/>
+        <v>1038.2409634067435</v>
       </c>
     </row>
     <row r="82" spans="2:50" x14ac:dyDescent="0.3">
@@ -7308,26 +7346,26 @@
         <v>37.6</v>
       </c>
       <c r="T82" s="1">
-        <f t="shared" si="150"/>
+        <f t="shared" si="144"/>
         <v>40.800000000000004</v>
       </c>
       <c r="U82" s="1">
-        <f t="shared" si="151"/>
+        <f t="shared" si="145"/>
         <v>-43.000000000000007</v>
       </c>
       <c r="V82" s="1">
-        <f t="shared" si="152"/>
+        <f t="shared" si="146"/>
         <v>-10.799999999999997</v>
       </c>
       <c r="W82" s="1">
         <v>4.5999999999999996</v>
       </c>
       <c r="X82" s="1">
-        <f t="shared" si="153"/>
+        <f t="shared" si="147"/>
         <v>2</v>
       </c>
       <c r="Y82" s="1">
-        <f t="shared" si="154"/>
+        <f t="shared" si="148"/>
         <v>14.4</v>
       </c>
       <c r="Z82" s="1">
@@ -7346,11 +7384,11 @@
         <v>-153.1</v>
       </c>
       <c r="AL82" s="1">
-        <f t="shared" ref="AL82:AL109" si="156">SUM(S82:V82)</f>
+        <f t="shared" ref="AL82:AL109" si="150">SUM(S82:V82)</f>
         <v>24.6</v>
       </c>
       <c r="AM82" s="1">
-        <f t="shared" ref="AM82:AM109" si="157">SUM(W82:Z82)</f>
+        <f t="shared" ref="AM82:AM109" si="151">SUM(W82:Z82)</f>
         <v>-38.5</v>
       </c>
       <c r="AN82" s="1">
@@ -7358,43 +7396,43 @@
         <v>-39.270000000000003</v>
       </c>
       <c r="AO82" s="1">
-        <f t="shared" ref="AO82:AX82" si="158">AN82*1.02</f>
+        <f t="shared" ref="AO82:AX82" si="152">AN82*1.02</f>
         <v>-40.055400000000006</v>
       </c>
       <c r="AP82" s="1">
-        <f t="shared" si="158"/>
+        <f t="shared" si="152"/>
         <v>-40.856508000000005</v>
       </c>
       <c r="AQ82" s="1">
-        <f t="shared" si="158"/>
+        <f t="shared" si="152"/>
         <v>-41.673638160000003</v>
       </c>
       <c r="AR82" s="1">
-        <f t="shared" si="158"/>
+        <f t="shared" si="152"/>
         <v>-42.507110923200003</v>
       </c>
       <c r="AS82" s="1">
-        <f t="shared" si="158"/>
+        <f t="shared" si="152"/>
         <v>-43.357253141664003</v>
       </c>
       <c r="AT82" s="1">
-        <f t="shared" si="158"/>
+        <f t="shared" si="152"/>
         <v>-44.224398204497284</v>
       </c>
       <c r="AU82" s="1">
-        <f t="shared" si="158"/>
+        <f t="shared" si="152"/>
         <v>-45.108886168587233</v>
       </c>
       <c r="AV82" s="1">
-        <f t="shared" si="158"/>
+        <f t="shared" si="152"/>
         <v>-46.011063891958976</v>
       </c>
       <c r="AW82" s="1">
-        <f t="shared" si="158"/>
+        <f t="shared" si="152"/>
         <v>-46.931285169798159</v>
       </c>
       <c r="AX82" s="1">
-        <f t="shared" si="158"/>
+        <f t="shared" si="152"/>
         <v>-47.869910873194122</v>
       </c>
     </row>
@@ -7406,26 +7444,26 @@
         <v>1</v>
       </c>
       <c r="T83" s="1">
-        <f t="shared" si="150"/>
+        <f t="shared" si="144"/>
         <v>0.8</v>
       </c>
       <c r="U83" s="1">
-        <f t="shared" si="151"/>
+        <f t="shared" si="145"/>
         <v>0.59999999999999987</v>
       </c>
       <c r="V83" s="1">
-        <f t="shared" si="152"/>
+        <f t="shared" si="146"/>
         <v>1.8000000000000007</v>
       </c>
       <c r="W83" s="1">
         <v>-0.3</v>
       </c>
       <c r="X83" s="1">
-        <f t="shared" si="153"/>
+        <f t="shared" si="147"/>
         <v>0.4</v>
       </c>
       <c r="Y83" s="1">
-        <f t="shared" si="154"/>
+        <f t="shared" si="148"/>
         <v>-0.39999999999999997</v>
       </c>
       <c r="Z83" s="1">
@@ -7444,11 +7482,11 @@
         <v>3.6</v>
       </c>
       <c r="AL83" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="150"/>
         <v>4.2000000000000011</v>
       </c>
       <c r="AM83" s="1">
-        <f t="shared" si="157"/>
+        <f t="shared" si="151"/>
         <v>-0.39999999999999991</v>
       </c>
       <c r="AN83" s="1">
@@ -7493,26 +7531,26 @@
         <v>-131.6</v>
       </c>
       <c r="T84" s="1">
-        <f t="shared" si="150"/>
+        <f t="shared" si="144"/>
         <v>-44.200000000000017</v>
       </c>
       <c r="U84" s="1">
-        <f t="shared" si="151"/>
+        <f t="shared" si="145"/>
         <v>-31.399999999999977</v>
       </c>
       <c r="V84" s="1">
-        <f t="shared" si="152"/>
+        <f t="shared" si="146"/>
         <v>11.799999999999983</v>
       </c>
       <c r="W84" s="1">
         <v>11.4</v>
       </c>
       <c r="X84" s="1">
-        <f t="shared" si="153"/>
+        <f t="shared" si="147"/>
         <v>59.199999999999996</v>
       </c>
       <c r="Y84" s="1">
-        <f t="shared" si="154"/>
+        <f t="shared" si="148"/>
         <v>26.600000000000009</v>
       </c>
       <c r="Z84" s="1">
@@ -7531,11 +7569,11 @@
         <v>-382.7</v>
       </c>
       <c r="AL84" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="150"/>
         <v>-195.4</v>
       </c>
       <c r="AM84" s="1">
-        <f t="shared" si="157"/>
+        <f t="shared" si="151"/>
         <v>174.10000000000002</v>
       </c>
       <c r="AN84" s="1">
@@ -7580,26 +7618,26 @@
         <v>-2.4</v>
       </c>
       <c r="T85" s="1">
-        <f t="shared" si="150"/>
+        <f t="shared" si="144"/>
         <v>7.5</v>
       </c>
       <c r="U85" s="1">
-        <f t="shared" si="151"/>
+        <f t="shared" si="145"/>
         <v>21.4</v>
       </c>
       <c r="V85" s="1">
-        <f t="shared" si="152"/>
+        <f t="shared" si="146"/>
         <v>-20.7</v>
       </c>
       <c r="W85" s="1">
         <v>16.100000000000001</v>
       </c>
       <c r="X85" s="1">
-        <f t="shared" si="153"/>
+        <f t="shared" si="147"/>
         <v>23.9</v>
       </c>
       <c r="Y85" s="1">
-        <f t="shared" si="154"/>
+        <f t="shared" si="148"/>
         <v>24.5</v>
       </c>
       <c r="Z85" s="1">
@@ -7618,11 +7656,11 @@
         <v>18.8</v>
       </c>
       <c r="AL85" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="150"/>
         <v>5.8000000000000007</v>
       </c>
       <c r="AM85" s="1">
-        <f t="shared" si="157"/>
+        <f t="shared" si="151"/>
         <v>61.2</v>
       </c>
       <c r="AN85" s="1">
@@ -7630,43 +7668,43 @@
         <v>61.812000000000005</v>
       </c>
       <c r="AO85" s="1">
-        <f t="shared" ref="AO85:AX85" si="159">AN85*1.01</f>
+        <f t="shared" ref="AO85:AX85" si="153">AN85*1.01</f>
         <v>62.430120000000002</v>
       </c>
       <c r="AP85" s="1">
-        <f t="shared" si="159"/>
+        <f t="shared" si="153"/>
         <v>63.0544212</v>
       </c>
       <c r="AQ85" s="1">
-        <f t="shared" si="159"/>
+        <f t="shared" si="153"/>
         <v>63.684965412000004</v>
       </c>
       <c r="AR85" s="1">
-        <f t="shared" si="159"/>
+        <f t="shared" si="153"/>
         <v>64.32181506612001</v>
       </c>
       <c r="AS85" s="1">
-        <f t="shared" si="159"/>
+        <f t="shared" si="153"/>
         <v>64.965033216781208</v>
       </c>
       <c r="AT85" s="1">
-        <f t="shared" si="159"/>
+        <f t="shared" si="153"/>
         <v>65.614683548949017</v>
       </c>
       <c r="AU85" s="1">
-        <f t="shared" si="159"/>
+        <f t="shared" si="153"/>
         <v>66.270830384438511</v>
       </c>
       <c r="AV85" s="1">
-        <f t="shared" si="159"/>
+        <f t="shared" si="153"/>
         <v>66.933538688282894</v>
       </c>
       <c r="AW85" s="1">
-        <f t="shared" si="159"/>
+        <f t="shared" si="153"/>
         <v>67.60287407516573</v>
       </c>
       <c r="AX85" s="1">
-        <f t="shared" si="159"/>
+        <f t="shared" si="153"/>
         <v>68.278902815917391</v>
       </c>
     </row>
@@ -7678,26 +7716,26 @@
         <v>70.099999999999994</v>
       </c>
       <c r="T86" s="1">
-        <f t="shared" si="150"/>
+        <f t="shared" si="144"/>
         <v>50.400000000000006</v>
       </c>
       <c r="U86" s="1">
-        <f t="shared" si="151"/>
+        <f t="shared" si="145"/>
         <v>61.099999999999994</v>
       </c>
       <c r="V86" s="1">
-        <f t="shared" si="152"/>
+        <f t="shared" si="146"/>
         <v>69.599999999999994</v>
       </c>
       <c r="W86" s="1">
         <v>25.8</v>
       </c>
       <c r="X86" s="1">
-        <f t="shared" si="153"/>
+        <f t="shared" si="147"/>
         <v>64.400000000000006</v>
       </c>
       <c r="Y86" s="1">
-        <f t="shared" si="154"/>
+        <f t="shared" si="148"/>
         <v>68.2</v>
       </c>
       <c r="Z86" s="1">
@@ -7716,56 +7754,55 @@
         <v>189.1</v>
       </c>
       <c r="AL86" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="150"/>
         <v>251.2</v>
       </c>
       <c r="AM86" s="1">
-        <f t="shared" si="157"/>
+        <f t="shared" si="151"/>
         <v>232.7</v>
       </c>
       <c r="AN86" s="1">
-        <f>AM86*0.99</f>
-        <v>230.37299999999999</v>
+        <v>300</v>
       </c>
       <c r="AO86" s="1">
-        <f t="shared" ref="AO86:AQ86" si="160">AN86*0.99</f>
-        <v>228.06926999999999</v>
+        <f>AN86*0.95</f>
+        <v>285</v>
       </c>
       <c r="AP86" s="1">
-        <f t="shared" si="160"/>
-        <v>225.78857729999999</v>
+        <f t="shared" ref="AP86:AX86" si="154">AO86*0.95</f>
+        <v>270.75</v>
       </c>
       <c r="AQ86" s="1">
-        <f t="shared" si="160"/>
-        <v>223.53069152699999</v>
+        <f t="shared" si="154"/>
+        <v>257.21249999999998</v>
       </c>
       <c r="AR86" s="1">
-        <f>AQ86*0.95</f>
-        <v>212.35415695064998</v>
+        <f t="shared" si="154"/>
+        <v>244.35187499999998</v>
       </c>
       <c r="AS86" s="1">
-        <f t="shared" ref="AS86:AX86" si="161">AR86*0.95</f>
-        <v>201.73644910311748</v>
+        <f t="shared" si="154"/>
+        <v>232.13428124999996</v>
       </c>
       <c r="AT86" s="1">
-        <f t="shared" si="161"/>
-        <v>191.64962664796158</v>
+        <f t="shared" si="154"/>
+        <v>220.52756718749995</v>
       </c>
       <c r="AU86" s="1">
-        <f t="shared" si="161"/>
-        <v>182.06714531556349</v>
+        <f t="shared" si="154"/>
+        <v>209.50118882812495</v>
       </c>
       <c r="AV86" s="1">
-        <f t="shared" si="161"/>
-        <v>172.96378804978531</v>
+        <f t="shared" si="154"/>
+        <v>199.02612938671871</v>
       </c>
       <c r="AW86" s="1">
-        <f t="shared" si="161"/>
-        <v>164.31559864729604</v>
+        <f t="shared" si="154"/>
+        <v>189.07482291738276</v>
       </c>
       <c r="AX86" s="1">
-        <f t="shared" si="161"/>
-        <v>156.09981871493125</v>
+        <f t="shared" si="154"/>
+        <v>179.62108177151362</v>
       </c>
     </row>
     <row r="87" spans="2:50" x14ac:dyDescent="0.3">
@@ -7776,26 +7813,26 @@
         <v>10.9</v>
       </c>
       <c r="T87" s="1">
-        <f t="shared" si="150"/>
+        <f t="shared" si="144"/>
         <v>21.6</v>
       </c>
       <c r="U87" s="1">
-        <f t="shared" si="151"/>
+        <f t="shared" si="145"/>
         <v>67.099999999999994</v>
       </c>
       <c r="V87" s="1">
-        <f t="shared" si="152"/>
+        <f t="shared" si="146"/>
         <v>60.6</v>
       </c>
       <c r="W87" s="1">
         <v>54.2</v>
       </c>
       <c r="X87" s="1">
-        <f t="shared" si="153"/>
+        <f t="shared" si="147"/>
         <v>48.3</v>
       </c>
       <c r="Y87" s="1">
-        <f t="shared" si="154"/>
+        <f t="shared" si="148"/>
         <v>16.5</v>
       </c>
       <c r="Z87" s="1">
@@ -7814,11 +7851,11 @@
         <v>88.6</v>
       </c>
       <c r="AL87" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="150"/>
         <v>160.19999999999999</v>
       </c>
       <c r="AM87" s="1">
-        <f t="shared" si="157"/>
+        <f t="shared" si="151"/>
         <v>143.5</v>
       </c>
       <c r="AN87" s="1">
@@ -7826,44 +7863,44 @@
         <v>146.37</v>
       </c>
       <c r="AO87" s="1">
-        <f t="shared" ref="AO87:AX87" si="162">AN87*1.02</f>
-        <v>149.29740000000001</v>
+        <f>AN87*1.01</f>
+        <v>147.83369999999999</v>
       </c>
       <c r="AP87" s="1">
-        <f t="shared" si="162"/>
-        <v>152.28334800000002</v>
+        <f t="shared" ref="AP87:AX87" si="155">AO87*1.01</f>
+        <v>149.312037</v>
       </c>
       <c r="AQ87" s="1">
-        <f t="shared" si="162"/>
-        <v>155.32901496000002</v>
+        <f t="shared" si="155"/>
+        <v>150.80515737000002</v>
       </c>
       <c r="AR87" s="1">
-        <f t="shared" si="162"/>
-        <v>158.43559525920003</v>
+        <f t="shared" si="155"/>
+        <v>152.31320894370003</v>
       </c>
       <c r="AS87" s="1">
-        <f t="shared" si="162"/>
-        <v>161.60430716438404</v>
+        <f t="shared" si="155"/>
+        <v>153.83634103313705</v>
       </c>
       <c r="AT87" s="1">
-        <f t="shared" si="162"/>
-        <v>164.83639330767173</v>
+        <f t="shared" si="155"/>
+        <v>155.37470444346843</v>
       </c>
       <c r="AU87" s="1">
-        <f t="shared" si="162"/>
-        <v>168.13312117382517</v>
+        <f t="shared" si="155"/>
+        <v>156.92845148790312</v>
       </c>
       <c r="AV87" s="1">
-        <f t="shared" si="162"/>
-        <v>171.49578359730168</v>
+        <f t="shared" si="155"/>
+        <v>158.49773600278215</v>
       </c>
       <c r="AW87" s="1">
-        <f t="shared" si="162"/>
-        <v>174.92569926924773</v>
+        <f t="shared" si="155"/>
+        <v>160.08271336280998</v>
       </c>
       <c r="AX87" s="1">
-        <f t="shared" si="162"/>
-        <v>178.42421325463269</v>
+        <f t="shared" si="155"/>
+        <v>161.68354049643807</v>
       </c>
     </row>
     <row r="88" spans="2:50" x14ac:dyDescent="0.3">
@@ -7874,26 +7911,26 @@
         <v>14.9</v>
       </c>
       <c r="T88" s="1">
-        <f t="shared" si="150"/>
+        <f t="shared" si="144"/>
         <v>30.200000000000003</v>
       </c>
       <c r="U88" s="1">
-        <f t="shared" si="151"/>
+        <f t="shared" si="145"/>
         <v>8.1</v>
       </c>
       <c r="V88" s="1">
-        <f t="shared" si="152"/>
+        <f t="shared" si="146"/>
         <v>12.999999999999998</v>
       </c>
       <c r="W88" s="1">
         <v>6.1</v>
       </c>
       <c r="X88" s="1">
-        <f t="shared" si="153"/>
+        <f t="shared" si="147"/>
         <v>8.2000000000000011</v>
       </c>
       <c r="Y88" s="1">
-        <f t="shared" si="154"/>
+        <f t="shared" si="148"/>
         <v>-8.5</v>
       </c>
       <c r="Z88" s="1">
@@ -7912,11 +7949,11 @@
         <v>25.3</v>
       </c>
       <c r="AL88" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="150"/>
         <v>66.2</v>
       </c>
       <c r="AM88" s="1">
-        <f t="shared" si="157"/>
+        <f t="shared" si="151"/>
         <v>29.400000000000002</v>
       </c>
       <c r="AN88" s="1">
@@ -7975,7 +8012,7 @@
       <c r="AK89" s="1"/>
       <c r="AL89" s="1"/>
       <c r="AM89" s="1">
-        <f t="shared" si="157"/>
+        <f t="shared" si="151"/>
         <v>3558</v>
       </c>
       <c r="AN89" s="1">
@@ -8020,26 +8057,26 @@
         <v>1.2</v>
       </c>
       <c r="T90" s="1">
-        <f t="shared" ref="T90:T109" si="163">T129-S90</f>
+        <f t="shared" ref="T90:T109" si="156">T129-S90</f>
         <v>0</v>
       </c>
       <c r="U90" s="1">
-        <f t="shared" ref="U90:U109" si="164">U129-T90-S90</f>
+        <f t="shared" ref="U90:U109" si="157">U129-T90-S90</f>
         <v>1.2</v>
       </c>
       <c r="V90" s="1">
-        <f t="shared" ref="V90:V109" si="165">V129-U90-T90-S90</f>
+        <f t="shared" ref="V90:V109" si="158">V129-U90-T90-S90</f>
         <v>1.3</v>
       </c>
       <c r="W90" s="1">
         <v>1.3</v>
       </c>
       <c r="X90" s="1">
-        <f t="shared" ref="X90:X109" si="166">X129-W90</f>
+        <f t="shared" ref="X90:X109" si="159">X129-W90</f>
         <v>1.4999999999999998</v>
       </c>
       <c r="Y90" s="1">
-        <f t="shared" ref="Y90:Y109" si="167">Y129-X90-W90</f>
+        <f t="shared" ref="Y90:Y109" si="160">Y129-X90-W90</f>
         <v>0.99999999999999978</v>
       </c>
       <c r="Z90" s="1">
@@ -8058,11 +8095,11 @@
         <v>3.9</v>
       </c>
       <c r="AL90" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="150"/>
         <v>3.7</v>
       </c>
       <c r="AM90" s="1">
-        <f t="shared" si="157"/>
+        <f t="shared" si="151"/>
         <v>-0.20000000000000018</v>
       </c>
       <c r="AN90" s="1">
@@ -8107,26 +8144,26 @@
         <v>0</v>
       </c>
       <c r="T91" s="1">
-        <f t="shared" si="163"/>
+        <f t="shared" si="156"/>
         <v>0</v>
       </c>
       <c r="U91" s="1">
-        <f t="shared" si="164"/>
+        <f t="shared" si="157"/>
         <v>0</v>
       </c>
       <c r="V91" s="1">
-        <f t="shared" si="165"/>
+        <f t="shared" si="158"/>
         <v>10.9</v>
       </c>
       <c r="W91" s="1">
         <v>53</v>
       </c>
       <c r="X91" s="1">
-        <f t="shared" si="166"/>
+        <f t="shared" si="159"/>
         <v>0</v>
       </c>
       <c r="Y91" s="1">
-        <f t="shared" si="167"/>
+        <f t="shared" si="160"/>
         <v>0</v>
       </c>
       <c r="Z91" s="1">
@@ -8145,11 +8182,11 @@
         <v>20.3</v>
       </c>
       <c r="AL91" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="150"/>
         <v>10.9</v>
       </c>
       <c r="AM91" s="1">
-        <f t="shared" si="157"/>
+        <f t="shared" si="151"/>
         <v>58.3</v>
       </c>
       <c r="AN91" s="1">
@@ -8194,26 +8231,26 @@
         <v>85.8</v>
       </c>
       <c r="T92" s="1">
-        <f t="shared" si="163"/>
+        <f t="shared" si="156"/>
         <v>8.2000000000000028</v>
       </c>
       <c r="U92" s="1">
-        <f t="shared" si="164"/>
+        <f t="shared" si="157"/>
         <v>2.5999999999999943</v>
       </c>
       <c r="V92" s="1">
-        <f t="shared" si="165"/>
+        <f t="shared" si="158"/>
         <v>0</v>
       </c>
       <c r="W92" s="1">
         <v>-16.8</v>
       </c>
       <c r="X92" s="1">
-        <f t="shared" si="166"/>
+        <f t="shared" si="159"/>
         <v>-189.79999999999998</v>
       </c>
       <c r="Y92" s="1">
-        <f t="shared" si="167"/>
+        <f t="shared" si="160"/>
         <v>-4.300000000000022</v>
       </c>
       <c r="Z92" s="1">
@@ -8232,11 +8269,11 @@
         <v>1179.5</v>
       </c>
       <c r="AL92" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="150"/>
         <v>96.6</v>
       </c>
       <c r="AM92" s="1">
-        <f t="shared" si="157"/>
+        <f t="shared" si="151"/>
         <v>-441.5</v>
       </c>
       <c r="AN92" s="1">
@@ -8281,26 +8318,26 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="T93" s="1">
-        <f t="shared" si="163"/>
+        <f t="shared" si="156"/>
         <v>4</v>
       </c>
       <c r="U93" s="1">
-        <f t="shared" si="164"/>
+        <f t="shared" si="157"/>
         <v>4.5</v>
       </c>
       <c r="V93" s="1">
-        <f t="shared" si="165"/>
+        <f t="shared" si="158"/>
         <v>7.2000000000000011</v>
       </c>
       <c r="W93" s="1">
         <v>10.6</v>
       </c>
       <c r="X93" s="1">
-        <f t="shared" si="166"/>
+        <f t="shared" si="159"/>
         <v>-3.3999999999999995</v>
       </c>
       <c r="Y93" s="1">
-        <f t="shared" si="167"/>
+        <f t="shared" si="160"/>
         <v>245.4</v>
       </c>
       <c r="Z93" s="1">
@@ -8319,11 +8356,11 @@
         <v>90.8</v>
       </c>
       <c r="AL93" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="150"/>
         <v>20.3</v>
       </c>
       <c r="AM93" s="1">
-        <f t="shared" si="157"/>
+        <f t="shared" si="151"/>
         <v>486</v>
       </c>
       <c r="AN93" s="1">
@@ -8366,24 +8403,24 @@
       </c>
       <c r="S94" s="1"/>
       <c r="T94" s="1">
-        <f t="shared" si="163"/>
+        <f t="shared" si="156"/>
         <v>0</v>
       </c>
       <c r="U94" s="1">
-        <f t="shared" si="164"/>
+        <f t="shared" si="157"/>
         <v>0</v>
       </c>
       <c r="V94" s="1">
-        <f t="shared" si="165"/>
+        <f t="shared" si="158"/>
         <v>0</v>
       </c>
       <c r="W94" s="1"/>
       <c r="X94" s="1">
-        <f t="shared" si="166"/>
+        <f t="shared" si="159"/>
         <v>-5.7</v>
       </c>
       <c r="Y94" s="1">
-        <f t="shared" si="167"/>
+        <f t="shared" si="160"/>
         <v>-1.7999999999999998</v>
       </c>
       <c r="Z94" s="1">
@@ -8402,11 +8439,11 @@
         <v>0</v>
       </c>
       <c r="AL94" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="150"/>
         <v>0</v>
       </c>
       <c r="AM94" s="1">
-        <f t="shared" si="157"/>
+        <f t="shared" si="151"/>
         <v>-7.4</v>
       </c>
       <c r="AN94" s="1">
@@ -8449,24 +8486,24 @@
       </c>
       <c r="S95" s="1"/>
       <c r="T95" s="1">
-        <f t="shared" si="163"/>
+        <f t="shared" si="156"/>
         <v>1.2</v>
       </c>
       <c r="U95" s="1">
-        <f t="shared" si="164"/>
+        <f t="shared" si="157"/>
         <v>0</v>
       </c>
       <c r="V95" s="1">
-        <f t="shared" si="165"/>
+        <f t="shared" si="158"/>
         <v>0</v>
       </c>
       <c r="W95" s="1"/>
       <c r="X95" s="1">
-        <f t="shared" si="166"/>
+        <f t="shared" si="159"/>
         <v>0</v>
       </c>
       <c r="Y95" s="1">
-        <f t="shared" si="167"/>
+        <f t="shared" si="160"/>
         <v>0</v>
       </c>
       <c r="Z95" s="1">
@@ -8479,11 +8516,11 @@
       <c r="AJ95" s="1"/>
       <c r="AK95" s="1"/>
       <c r="AL95" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="150"/>
         <v>1.2</v>
       </c>
       <c r="AM95" s="1">
-        <f t="shared" si="157"/>
+        <f t="shared" si="151"/>
         <v>0</v>
       </c>
       <c r="AN95" s="1">
@@ -8528,26 +8565,26 @@
         <v>2616</v>
       </c>
       <c r="T96" s="1">
-        <f t="shared" si="163"/>
+        <f t="shared" si="156"/>
         <v>1284.8000000000002</v>
       </c>
       <c r="U96" s="1">
-        <f t="shared" si="164"/>
+        <f t="shared" si="157"/>
         <v>-1713.7000000000003</v>
       </c>
       <c r="V96" s="1">
-        <f t="shared" si="165"/>
+        <f t="shared" si="158"/>
         <v>-2154.8000000000002</v>
       </c>
       <c r="W96" s="1">
         <v>-1963</v>
       </c>
       <c r="X96" s="1">
-        <f t="shared" si="166"/>
+        <f t="shared" si="159"/>
         <v>-395.90000000000009</v>
       </c>
       <c r="Y96" s="1">
-        <f t="shared" si="167"/>
+        <f t="shared" si="160"/>
         <v>1853.5</v>
       </c>
       <c r="Z96" s="1">
@@ -8567,11 +8604,11 @@
         <v>740.2</v>
       </c>
       <c r="AL96" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="150"/>
         <v>32.299999999999727</v>
       </c>
       <c r="AM96" s="1">
-        <f t="shared" si="157"/>
+        <f t="shared" si="151"/>
         <v>-2981.8</v>
       </c>
       <c r="AN96" s="1">
@@ -8616,26 +8653,26 @@
         <v>2</v>
       </c>
       <c r="T97" s="1">
-        <f t="shared" si="163"/>
+        <f t="shared" si="156"/>
         <v>9.6</v>
       </c>
       <c r="U97" s="1">
-        <f t="shared" si="164"/>
+        <f t="shared" si="157"/>
         <v>0.40000000000000036</v>
       </c>
       <c r="V97" s="1">
-        <f t="shared" si="165"/>
+        <f t="shared" si="158"/>
         <v>8.2999999999999989</v>
       </c>
       <c r="W97" s="1">
         <v>10.3</v>
       </c>
       <c r="X97" s="1">
-        <f t="shared" si="166"/>
+        <f t="shared" si="159"/>
         <v>-2.6000000000000005</v>
       </c>
       <c r="Y97" s="1">
-        <f t="shared" si="167"/>
+        <f t="shared" si="160"/>
         <v>15.8</v>
       </c>
       <c r="Z97" s="1">
@@ -8654,11 +8691,11 @@
         <v>12.9</v>
       </c>
       <c r="AL97" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="150"/>
         <v>20.299999999999997</v>
       </c>
       <c r="AM97" s="1">
-        <f t="shared" si="157"/>
+        <f t="shared" si="151"/>
         <v>28</v>
       </c>
       <c r="AN97" s="1">
@@ -8703,26 +8740,26 @@
         <v>-50.7</v>
       </c>
       <c r="T98" s="1">
-        <f t="shared" si="163"/>
+        <f t="shared" si="156"/>
         <v>-9.3999999999999986</v>
       </c>
       <c r="U98" s="1">
-        <f t="shared" si="164"/>
+        <f t="shared" si="157"/>
         <v>216.60000000000002</v>
       </c>
       <c r="V98" s="1">
-        <f t="shared" si="165"/>
+        <f t="shared" si="158"/>
         <v>-17.500000000000014</v>
       </c>
       <c r="W98" s="1">
         <v>-63.4</v>
       </c>
       <c r="X98" s="1">
-        <f t="shared" si="166"/>
+        <f t="shared" si="159"/>
         <v>54.599999999999994</v>
       </c>
       <c r="Y98" s="1">
-        <f t="shared" si="167"/>
+        <f t="shared" si="160"/>
         <v>-19.29999999999999</v>
       </c>
       <c r="Z98" s="1">
@@ -8741,11 +8778,11 @@
         <v>261.89999999999998</v>
       </c>
       <c r="AL98" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="150"/>
         <v>139</v>
       </c>
       <c r="AM98" s="1">
-        <f t="shared" si="157"/>
+        <f t="shared" si="151"/>
         <v>-0.29999999999999361</v>
       </c>
       <c r="AN98" s="1">
@@ -8790,26 +8827,26 @@
         <v>26.8</v>
       </c>
       <c r="T99" s="1">
-        <f t="shared" si="163"/>
+        <f t="shared" si="156"/>
         <v>19.8</v>
       </c>
       <c r="U99" s="1">
-        <f t="shared" si="164"/>
+        <f t="shared" si="157"/>
         <v>20.100000000000005</v>
       </c>
       <c r="V99" s="1">
-        <f t="shared" si="165"/>
+        <f t="shared" si="158"/>
         <v>-25.400000000000009</v>
       </c>
       <c r="W99" s="1">
         <v>-14</v>
       </c>
       <c r="X99" s="1">
-        <f t="shared" si="166"/>
+        <f t="shared" si="159"/>
         <v>82.4</v>
       </c>
       <c r="Y99" s="1">
-        <f t="shared" si="167"/>
+        <f t="shared" si="160"/>
         <v>19.5</v>
       </c>
       <c r="Z99" s="1">
@@ -8828,11 +8865,11 @@
         <v>153</v>
       </c>
       <c r="AL99" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="150"/>
         <v>41.3</v>
       </c>
       <c r="AM99" s="1">
-        <f t="shared" si="157"/>
+        <f t="shared" si="151"/>
         <v>54.500000000000007</v>
       </c>
       <c r="AN99" s="1">
@@ -8877,26 +8914,26 @@
         <v>-18.399999999999999</v>
       </c>
       <c r="T100" s="1">
-        <f t="shared" si="163"/>
+        <f t="shared" si="156"/>
         <v>7.8999999999999986</v>
       </c>
       <c r="U100" s="1">
-        <f t="shared" si="164"/>
+        <f t="shared" si="157"/>
         <v>55.3</v>
       </c>
       <c r="V100" s="1">
-        <f t="shared" si="165"/>
+        <f t="shared" si="158"/>
         <v>160.30000000000001</v>
       </c>
       <c r="W100" s="1">
         <v>-184.1</v>
       </c>
       <c r="X100" s="1">
-        <f t="shared" si="166"/>
+        <f t="shared" si="159"/>
         <v>169.4</v>
       </c>
       <c r="Y100" s="1">
-        <f t="shared" si="167"/>
+        <f t="shared" si="160"/>
         <v>-14.100000000000023</v>
       </c>
       <c r="Z100" s="1">
@@ -8915,11 +8952,11 @@
         <v>707.5</v>
       </c>
       <c r="AL100" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="150"/>
         <v>205.10000000000002</v>
       </c>
       <c r="AM100" s="1">
-        <f t="shared" si="157"/>
+        <f t="shared" si="151"/>
         <v>810.8</v>
       </c>
       <c r="AN100" s="1">
@@ -8964,26 +9001,26 @@
         <v>0</v>
       </c>
       <c r="T101" s="1">
-        <f t="shared" si="163"/>
+        <f t="shared" si="156"/>
         <v>0</v>
       </c>
       <c r="U101" s="1">
-        <f t="shared" si="164"/>
+        <f t="shared" si="157"/>
         <v>0</v>
       </c>
       <c r="V101" s="1">
-        <f t="shared" si="165"/>
+        <f t="shared" si="158"/>
         <v>-312.8</v>
       </c>
       <c r="W101" s="1">
         <v>-193.1</v>
       </c>
       <c r="X101" s="1">
-        <f t="shared" si="166"/>
+        <f t="shared" si="159"/>
         <v>-121.29999999999998</v>
       </c>
       <c r="Y101" s="1">
-        <f t="shared" si="167"/>
+        <f t="shared" si="160"/>
         <v>-149.20000000000007</v>
       </c>
       <c r="Z101" s="1">
@@ -8996,11 +9033,11 @@
       <c r="AJ101" s="1"/>
       <c r="AK101" s="1"/>
       <c r="AL101" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="150"/>
         <v>-312.8</v>
       </c>
       <c r="AM101" s="1">
-        <f t="shared" si="157"/>
+        <f t="shared" si="151"/>
         <v>-670.8</v>
       </c>
       <c r="AN101" s="1">
@@ -9045,26 +9082,26 @@
         <v>-2367.4</v>
       </c>
       <c r="T102" s="1">
-        <f t="shared" si="163"/>
+        <f t="shared" si="156"/>
         <v>-1427.1</v>
       </c>
       <c r="U102" s="1">
-        <f t="shared" si="164"/>
+        <f t="shared" si="157"/>
         <v>153.19999999999982</v>
       </c>
       <c r="V102" s="1">
-        <f t="shared" si="165"/>
+        <f t="shared" si="158"/>
         <v>259.20000000000027</v>
       </c>
       <c r="W102" s="1">
         <v>-1778.7</v>
       </c>
       <c r="X102" s="1">
-        <f t="shared" si="166"/>
+        <f t="shared" si="159"/>
         <v>-2238</v>
       </c>
       <c r="Y102" s="1">
-        <f t="shared" si="167"/>
+        <f t="shared" si="160"/>
         <v>-3682</v>
       </c>
       <c r="Z102" s="1">
@@ -9084,11 +9121,11 @@
         <v>-3633.9</v>
       </c>
       <c r="AL102" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="150"/>
         <v>-3382.1</v>
       </c>
       <c r="AM102" s="1">
-        <f t="shared" si="157"/>
+        <f t="shared" si="151"/>
         <v>-8507.2999999999993</v>
       </c>
       <c r="AN102" s="1">
@@ -9099,39 +9136,39 @@
         <v>0</v>
       </c>
       <c r="AP102" s="1">
-        <f t="shared" ref="AP102:AX102" si="168">AO102*0.9</f>
+        <f t="shared" ref="AP102:AX102" si="161">AO102*0.9</f>
         <v>0</v>
       </c>
       <c r="AQ102" s="1">
-        <f t="shared" si="168"/>
+        <f t="shared" si="161"/>
         <v>0</v>
       </c>
       <c r="AR102" s="1">
-        <f t="shared" si="168"/>
+        <f t="shared" si="161"/>
         <v>0</v>
       </c>
       <c r="AS102" s="1">
-        <f t="shared" si="168"/>
+        <f t="shared" si="161"/>
         <v>0</v>
       </c>
       <c r="AT102" s="1">
-        <f t="shared" si="168"/>
+        <f t="shared" si="161"/>
         <v>0</v>
       </c>
       <c r="AU102" s="1">
-        <f t="shared" si="168"/>
+        <f t="shared" si="161"/>
         <v>0</v>
       </c>
       <c r="AV102" s="1">
-        <f t="shared" si="168"/>
+        <f t="shared" si="161"/>
         <v>0</v>
       </c>
       <c r="AW102" s="1">
-        <f t="shared" si="168"/>
+        <f t="shared" si="161"/>
         <v>0</v>
       </c>
       <c r="AX102" s="1">
-        <f t="shared" si="168"/>
+        <f t="shared" si="161"/>
         <v>0</v>
       </c>
     </row>
@@ -9143,26 +9180,26 @@
         <v>74.099999999999994</v>
       </c>
       <c r="T103" s="1">
-        <f t="shared" si="163"/>
+        <f t="shared" si="156"/>
         <v>18.5</v>
       </c>
       <c r="U103" s="1">
-        <f t="shared" si="164"/>
+        <f t="shared" si="157"/>
         <v>-26.099999999999994</v>
       </c>
       <c r="V103" s="1">
-        <f t="shared" si="165"/>
+        <f t="shared" si="158"/>
         <v>103.30000000000001</v>
       </c>
       <c r="W103" s="1">
         <v>156.1</v>
       </c>
       <c r="X103" s="1">
-        <f t="shared" si="166"/>
+        <f t="shared" si="159"/>
         <v>54.200000000000017</v>
       </c>
       <c r="Y103" s="1">
-        <f t="shared" si="167"/>
+        <f t="shared" si="160"/>
         <v>-374.8</v>
       </c>
       <c r="Z103" s="1">
@@ -9181,11 +9218,11 @@
         <v>137.80000000000001</v>
       </c>
       <c r="AL103" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="150"/>
         <v>169.8</v>
       </c>
       <c r="AM103" s="1">
-        <f t="shared" si="157"/>
+        <f t="shared" si="151"/>
         <v>-6.3000000000000114</v>
       </c>
       <c r="AN103" s="1">
@@ -9230,26 +9267,26 @@
         <v>-74.900000000000006</v>
       </c>
       <c r="T104" s="1">
-        <f t="shared" si="163"/>
+        <f t="shared" si="156"/>
         <v>67.300000000000011</v>
       </c>
       <c r="U104" s="1">
-        <f t="shared" si="164"/>
+        <f t="shared" si="157"/>
         <v>74.199999999999989</v>
       </c>
       <c r="V104" s="1">
-        <f t="shared" si="165"/>
+        <f t="shared" si="158"/>
         <v>-47.3</v>
       </c>
       <c r="W104" s="1">
         <v>-116.1</v>
       </c>
       <c r="X104" s="1">
-        <f t="shared" si="166"/>
+        <f t="shared" si="159"/>
         <v>84.6</v>
       </c>
       <c r="Y104" s="1">
-        <f t="shared" si="167"/>
+        <f t="shared" si="160"/>
         <v>88.7</v>
       </c>
       <c r="Z104" s="1">
@@ -9268,11 +9305,11 @@
         <v>195.3</v>
       </c>
       <c r="AL104" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="150"/>
         <v>19.299999999999997</v>
       </c>
       <c r="AM104" s="1">
-        <f t="shared" si="157"/>
+        <f t="shared" si="151"/>
         <v>30.000000000000004</v>
       </c>
       <c r="AN104" s="1">
@@ -9317,26 +9354,26 @@
         <v>-15.6</v>
       </c>
       <c r="T105" s="1">
-        <f t="shared" si="163"/>
+        <f t="shared" si="156"/>
         <v>-1.2999999999999989</v>
       </c>
       <c r="U105" s="1">
-        <f t="shared" si="164"/>
+        <f t="shared" si="157"/>
         <v>-10.9</v>
       </c>
       <c r="V105" s="1">
-        <f t="shared" si="165"/>
+        <f t="shared" si="158"/>
         <v>-6.2000000000000046</v>
       </c>
       <c r="W105" s="1">
         <v>-7.4</v>
       </c>
       <c r="X105" s="1">
-        <f t="shared" si="166"/>
+        <f t="shared" si="159"/>
         <v>-22.200000000000003</v>
       </c>
       <c r="Y105" s="1">
-        <f t="shared" si="167"/>
+        <f t="shared" si="160"/>
         <v>-15.299999999999995</v>
       </c>
       <c r="Z105" s="1">
@@ -9355,11 +9392,11 @@
         <v>-10</v>
       </c>
       <c r="AL105" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="150"/>
         <v>-34</v>
       </c>
       <c r="AM105" s="1">
-        <f t="shared" si="157"/>
+        <f t="shared" si="151"/>
         <v>-58.9</v>
       </c>
       <c r="AN105" s="1">
@@ -9404,26 +9441,26 @@
         <v>1.2</v>
       </c>
       <c r="T106" s="1">
-        <f t="shared" si="163"/>
+        <f t="shared" si="156"/>
         <v>-3.3</v>
       </c>
       <c r="U106" s="1">
-        <f t="shared" si="164"/>
+        <f t="shared" si="157"/>
         <v>-32.699999999999996</v>
       </c>
       <c r="V106" s="1">
-        <f t="shared" si="165"/>
+        <f t="shared" si="158"/>
         <v>-45.20000000000001</v>
       </c>
       <c r="W106" s="1">
         <v>80.5</v>
       </c>
       <c r="X106" s="1">
-        <f t="shared" si="166"/>
+        <f t="shared" si="159"/>
         <v>80.300000000000011</v>
       </c>
       <c r="Y106" s="1">
-        <f t="shared" si="167"/>
+        <f t="shared" si="160"/>
         <v>64.099999999999994</v>
       </c>
       <c r="Z106" s="1">
@@ -9442,11 +9479,11 @@
         <v>323.60000000000002</v>
       </c>
       <c r="AL106" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="150"/>
         <v>-80</v>
       </c>
       <c r="AM106" s="1">
-        <f t="shared" si="157"/>
+        <f t="shared" si="151"/>
         <v>361.70000000000005</v>
       </c>
       <c r="AN106" s="1">
@@ -9491,26 +9528,26 @@
         <v>-133.4</v>
       </c>
       <c r="T107" s="1">
-        <f t="shared" si="163"/>
+        <f t="shared" si="156"/>
         <v>-303.70000000000005</v>
       </c>
       <c r="U107" s="1">
-        <f t="shared" si="164"/>
+        <f t="shared" si="157"/>
         <v>-43.099999999999937</v>
       </c>
       <c r="V107" s="1">
-        <f t="shared" si="165"/>
+        <f t="shared" si="158"/>
         <v>-269.20000000000005</v>
       </c>
       <c r="W107" s="1">
         <v>-51.2</v>
       </c>
       <c r="X107" s="1">
-        <f t="shared" si="166"/>
+        <f t="shared" si="159"/>
         <v>-262.3</v>
       </c>
       <c r="Y107" s="1">
-        <f t="shared" si="167"/>
+        <f t="shared" si="160"/>
         <v>-266.29999999999995</v>
       </c>
       <c r="Z107" s="1">
@@ -9529,45 +9566,56 @@
         <v>-430.4</v>
       </c>
       <c r="AL107" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="150"/>
         <v>-749.4</v>
       </c>
       <c r="AM107" s="1">
-        <f t="shared" si="157"/>
+        <f t="shared" si="151"/>
         <v>-782.4</v>
       </c>
       <c r="AN107" s="1">
-        <v>0</v>
+        <f>AM107*1.05</f>
+        <v>-821.52</v>
       </c>
       <c r="AO107" s="1">
-        <v>0</v>
+        <f>AN107*1.03</f>
+        <v>-846.16560000000004</v>
       </c>
       <c r="AP107" s="1">
-        <v>0</v>
+        <f t="shared" ref="AP107:AX107" si="162">AO107*1.02</f>
+        <v>-863.08891200000005</v>
       </c>
       <c r="AQ107" s="1">
-        <v>0</v>
+        <f t="shared" si="162"/>
+        <v>-880.35069024000006</v>
       </c>
       <c r="AR107" s="1">
-        <v>0</v>
+        <f t="shared" si="162"/>
+        <v>-897.95770404480004</v>
       </c>
       <c r="AS107" s="1">
-        <v>0</v>
+        <f t="shared" si="162"/>
+        <v>-915.91685812569608</v>
       </c>
       <c r="AT107" s="1">
-        <v>0</v>
+        <f t="shared" si="162"/>
+        <v>-934.23519528820998</v>
       </c>
       <c r="AU107" s="1">
-        <v>0</v>
+        <f t="shared" si="162"/>
+        <v>-952.91989919397417</v>
       </c>
       <c r="AV107" s="1">
-        <v>0</v>
+        <f t="shared" si="162"/>
+        <v>-971.97829717785362</v>
       </c>
       <c r="AW107" s="1">
-        <v>0</v>
+        <f t="shared" si="162"/>
+        <v>-991.41786312141073</v>
       </c>
       <c r="AX107" s="1">
-        <v>0</v>
+        <f t="shared" si="162"/>
+        <v>-1011.2462203838389</v>
       </c>
     </row>
     <row r="108" spans="2:50" x14ac:dyDescent="0.3">
@@ -9578,26 +9626,26 @@
         <v>606.79999999999995</v>
       </c>
       <c r="T108" s="1">
-        <f t="shared" si="163"/>
+        <f t="shared" si="156"/>
         <v>538.90000000000009</v>
       </c>
       <c r="U108" s="1">
-        <f t="shared" si="164"/>
+        <f t="shared" si="157"/>
         <v>679.3</v>
       </c>
       <c r="V108" s="1">
-        <f t="shared" si="165"/>
+        <f t="shared" si="158"/>
         <v>941.90000000000032</v>
       </c>
       <c r="W108" s="1">
         <v>958.2</v>
       </c>
       <c r="X108" s="1">
-        <f t="shared" si="166"/>
+        <f t="shared" si="159"/>
         <v>1080.7</v>
       </c>
       <c r="Y108" s="1">
-        <f t="shared" si="167"/>
+        <f t="shared" si="160"/>
         <v>1203.8</v>
       </c>
       <c r="Z108" s="1">
@@ -9616,45 +9664,56 @@
         <v>2058.6999999999998</v>
       </c>
       <c r="AL108" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="150"/>
         <v>2766.9000000000005</v>
       </c>
       <c r="AM108" s="1">
-        <f t="shared" si="157"/>
+        <f t="shared" si="151"/>
         <v>4578.2</v>
       </c>
       <c r="AN108" s="1">
-        <v>0</v>
+        <f>AM108*1.01</f>
+        <v>4623.982</v>
       </c>
       <c r="AO108" s="1">
-        <v>0</v>
+        <f t="shared" ref="AO108:AX108" si="163">AN108*1.01</f>
+        <v>4670.2218199999998</v>
       </c>
       <c r="AP108" s="1">
-        <v>0</v>
+        <f t="shared" si="163"/>
+        <v>4716.9240381999998</v>
       </c>
       <c r="AQ108" s="1">
-        <v>0</v>
+        <f t="shared" si="163"/>
+        <v>4764.0932785819996</v>
       </c>
       <c r="AR108" s="1">
-        <v>0</v>
+        <f t="shared" si="163"/>
+        <v>4811.7342113678196</v>
       </c>
       <c r="AS108" s="1">
-        <v>0</v>
+        <f t="shared" si="163"/>
+        <v>4859.8515534814978</v>
       </c>
       <c r="AT108" s="1">
-        <v>0</v>
+        <f t="shared" si="163"/>
+        <v>4908.4500690163131</v>
       </c>
       <c r="AU108" s="1">
-        <v>0</v>
+        <f t="shared" si="163"/>
+        <v>4957.5345697064768</v>
       </c>
       <c r="AV108" s="1">
-        <v>0</v>
+        <f t="shared" si="163"/>
+        <v>5007.1099154035419</v>
       </c>
       <c r="AW108" s="1">
-        <v>0</v>
+        <f t="shared" si="163"/>
+        <v>5057.1810145575773</v>
       </c>
       <c r="AX108" s="1">
-        <v>0</v>
+        <f t="shared" si="163"/>
+        <v>5107.7528247031532</v>
       </c>
     </row>
     <row r="109" spans="2:50" x14ac:dyDescent="0.3">
@@ -9665,26 +9724,26 @@
         <v>-28.4</v>
       </c>
       <c r="T109" s="1">
-        <f t="shared" si="163"/>
+        <f t="shared" si="156"/>
         <v>-18.899999999999999</v>
       </c>
       <c r="U109" s="1">
-        <f t="shared" si="164"/>
+        <f t="shared" si="157"/>
         <v>-36.000000000000007</v>
       </c>
       <c r="V109" s="1">
-        <f t="shared" si="165"/>
+        <f t="shared" si="158"/>
         <v>-32.799999999999997</v>
       </c>
       <c r="W109" s="1">
         <v>-64.2</v>
       </c>
       <c r="X109" s="1">
-        <f t="shared" si="166"/>
+        <f t="shared" si="159"/>
         <v>-11.399999999999991</v>
       </c>
       <c r="Y109" s="1">
-        <f t="shared" si="167"/>
+        <f t="shared" si="160"/>
         <v>-44</v>
       </c>
       <c r="Z109" s="1">
@@ -9703,45 +9762,56 @@
         <v>-191.1</v>
       </c>
       <c r="AL109" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="150"/>
         <v>-116.10000000000001</v>
       </c>
       <c r="AM109" s="1">
-        <f t="shared" si="157"/>
+        <f t="shared" si="151"/>
         <v>-174</v>
       </c>
       <c r="AN109" s="1">
-        <v>0</v>
+        <f>AM109*1.01</f>
+        <v>-175.74</v>
       </c>
       <c r="AO109" s="1">
-        <v>0</v>
+        <f t="shared" ref="AO109:AX109" si="164">AN109*1.01</f>
+        <v>-177.4974</v>
       </c>
       <c r="AP109" s="1">
-        <v>0</v>
+        <f t="shared" si="164"/>
+        <v>-179.27237400000001</v>
       </c>
       <c r="AQ109" s="1">
-        <v>0</v>
+        <f t="shared" si="164"/>
+        <v>-181.06509774000003</v>
       </c>
       <c r="AR109" s="1">
-        <v>0</v>
+        <f t="shared" si="164"/>
+        <v>-182.87574871740003</v>
       </c>
       <c r="AS109" s="1">
-        <v>0</v>
+        <f t="shared" si="164"/>
+        <v>-184.70450620457402</v>
       </c>
       <c r="AT109" s="1">
-        <v>0</v>
+        <f t="shared" si="164"/>
+        <v>-186.55155126661975</v>
       </c>
       <c r="AU109" s="1">
-        <v>0</v>
+        <f t="shared" si="164"/>
+        <v>-188.41706677928596</v>
       </c>
       <c r="AV109" s="1">
-        <v>0</v>
+        <f t="shared" si="164"/>
+        <v>-190.30123744707882</v>
       </c>
       <c r="AW109" s="1">
-        <v>0</v>
+        <f t="shared" si="164"/>
+        <v>-192.20424982154961</v>
       </c>
       <c r="AX109" s="1">
-        <v>0</v>
+        <f t="shared" si="164"/>
+        <v>-194.1262923197651</v>
       </c>
     </row>
     <row r="110" spans="2:50" s="7" customFormat="1" x14ac:dyDescent="0.3">
@@ -9749,43 +9819,43 @@
         <v>118</v>
       </c>
       <c r="O110" s="9">
-        <f t="shared" ref="O110:X110" si="169">O80+SUM(O81:O109)</f>
+        <f t="shared" ref="O110:X110" si="165">O80+SUM(O81:O109)</f>
         <v>-313.09999999999997</v>
       </c>
       <c r="P110" s="9">
-        <f t="shared" si="169"/>
+        <f t="shared" si="165"/>
         <v>-487.40000000000015</v>
       </c>
       <c r="Q110" s="9">
-        <f t="shared" si="169"/>
+        <f t="shared" si="165"/>
         <v>202.49999999999997</v>
       </c>
       <c r="R110" s="9">
-        <f t="shared" si="169"/>
+        <f t="shared" si="165"/>
         <v>78.899999999999949</v>
       </c>
       <c r="S110" s="9">
-        <f t="shared" si="169"/>
+        <f t="shared" si="165"/>
         <v>1168.4000000000001</v>
       </c>
       <c r="T110" s="9">
-        <f t="shared" si="169"/>
+        <f t="shared" si="165"/>
         <v>830.80000000000018</v>
       </c>
       <c r="U110" s="9">
-        <f t="shared" si="169"/>
+        <f t="shared" si="165"/>
         <v>60.399999999999352</v>
       </c>
       <c r="V110" s="9">
-        <f t="shared" si="169"/>
+        <f t="shared" si="165"/>
         <v>-416.09999999999991</v>
       </c>
       <c r="W110" s="9">
-        <f t="shared" si="169"/>
+        <f t="shared" si="165"/>
         <v>-2473.9999999999995</v>
       </c>
       <c r="X110" s="9">
-        <f t="shared" si="169"/>
+        <f t="shared" si="165"/>
         <v>-718.10000000000014</v>
       </c>
       <c r="Y110" s="9">
@@ -9804,68 +9874,68 @@
       <c r="AC110" s="9"/>
       <c r="AD110" s="9"/>
       <c r="AI110" s="9">
-        <f t="shared" ref="AI110" si="170">AI80+SUM(AI81:AI109)</f>
+        <f t="shared" ref="AI110" si="166">AI80+SUM(AI81:AI109)</f>
         <v>73.099999999999568</v>
       </c>
       <c r="AJ110" s="9">
-        <f t="shared" ref="AJ110:AK110" si="171">AJ80+SUM(AJ81:AJ109)</f>
+        <f t="shared" ref="AJ110:AK110" si="167">AJ80+SUM(AJ81:AJ109)</f>
         <v>3625.7000000000007</v>
       </c>
       <c r="AK110" s="9">
-        <f t="shared" si="171"/>
+        <f t="shared" si="167"/>
         <v>1690.8000000000011</v>
       </c>
       <c r="AL110" s="9">
-        <f t="shared" ref="AL110:AN110" si="172">AL80+SUM(AL81:AL109)</f>
+        <f t="shared" ref="AL110:AN110" si="168">AL80+SUM(AL81:AL109)</f>
         <v>1643.500000000002</v>
       </c>
       <c r="AM110" s="9">
-        <f t="shared" si="172"/>
+        <f t="shared" si="168"/>
         <v>-3627.199999999998</v>
       </c>
       <c r="AN110" s="9">
-        <f t="shared" si="172"/>
-        <v>3821.687256000002</v>
+        <f t="shared" si="168"/>
+        <v>7399.2412639999984</v>
       </c>
       <c r="AO110" s="9">
-        <f t="shared" ref="AO110:AX110" si="173">AO80+SUM(AO81:AO109)</f>
-        <v>4394.9048545799997</v>
+        <f t="shared" ref="AO110:AX110" si="169">AO80+SUM(AO81:AO109)</f>
+        <v>7999.7363480611994</v>
       </c>
       <c r="AP110" s="9">
-        <f t="shared" si="173"/>
-        <v>4659.1618627902008</v>
+        <f t="shared" si="169"/>
+        <v>8351.1282727417474</v>
       </c>
       <c r="AQ110" s="9">
-        <f t="shared" si="173"/>
-        <v>4856.3441305543265</v>
+        <f t="shared" si="169"/>
+        <v>8625.3771188002447</v>
       </c>
       <c r="AR110" s="9">
-        <f t="shared" si="173"/>
-        <v>4961.1970886837335</v>
+        <f t="shared" si="169"/>
+        <v>8840.9496505648294</v>
       </c>
       <c r="AS110" s="9">
-        <f t="shared" si="173"/>
-        <v>5057.4322870186743</v>
+        <f t="shared" si="169"/>
+        <v>9006.2289826375072</v>
       </c>
       <c r="AT110" s="9">
-        <f t="shared" si="173"/>
-        <v>5097.3182772300088</v>
+        <f t="shared" si="169"/>
+        <v>9155.0225292501073</v>
       </c>
       <c r="AU110" s="9">
-        <f t="shared" si="173"/>
-        <v>5085.4747343541885</v>
+        <f t="shared" si="169"/>
+        <v>9244.1198243696654</v>
       </c>
       <c r="AV110" s="9">
-        <f t="shared" si="173"/>
-        <v>5073.6209550381946</v>
+        <f t="shared" si="169"/>
+        <v>9335.1908828170745</v>
       </c>
       <c r="AW110" s="9">
-        <f t="shared" si="173"/>
-        <v>5061.7143049596998</v>
+        <f t="shared" si="169"/>
+        <v>9428.2369562399836</v>
       </c>
       <c r="AX110" s="9">
-        <f t="shared" si="173"/>
-        <v>5049.7129640262683</v>
+        <f t="shared" si="169"/>
+        <v>9523.2614396921235</v>
       </c>
     </row>
     <row r="111" spans="2:50" x14ac:dyDescent="0.3">
@@ -9917,11 +9987,11 @@
         <v>417.7</v>
       </c>
       <c r="AL111" s="1">
-        <f t="shared" ref="AL111:AL112" si="174">SUM(S111:V111)</f>
+        <f t="shared" ref="AL111:AL112" si="170">SUM(S111:V111)</f>
         <v>736.2</v>
       </c>
       <c r="AM111" s="1">
-        <f t="shared" ref="AM111:AM112" si="175">SUM(W111:Z111)</f>
+        <f t="shared" ref="AM111:AM112" si="171">SUM(W111:Z111)</f>
         <v>764.5</v>
       </c>
       <c r="AN111" s="1">
@@ -9929,7 +9999,7 @@
         <v>779.79</v>
       </c>
       <c r="AO111" s="1">
-        <f t="shared" ref="AO111:AR112" si="176">AN111*1.02</f>
+        <f t="shared" ref="AO111:AR112" si="172">AN111*1.02</f>
         <v>795.38580000000002</v>
       </c>
       <c r="AP111" s="1">
@@ -9937,35 +10007,35 @@
         <v>803.33965799999999</v>
       </c>
       <c r="AQ111" s="1">
-        <f t="shared" ref="AQ111:AX111" si="177">AP111*1.01</f>
+        <f t="shared" ref="AQ111:AX111" si="173">AP111*1.01</f>
         <v>811.37305458000003</v>
       </c>
       <c r="AR111" s="1">
-        <f t="shared" si="177"/>
+        <f t="shared" si="173"/>
         <v>819.4867851258</v>
       </c>
       <c r="AS111" s="1">
-        <f t="shared" si="177"/>
+        <f t="shared" si="173"/>
         <v>827.68165297705798</v>
       </c>
       <c r="AT111" s="1">
-        <f t="shared" si="177"/>
+        <f t="shared" si="173"/>
         <v>835.95846950682858</v>
       </c>
       <c r="AU111" s="1">
-        <f t="shared" si="177"/>
+        <f t="shared" si="173"/>
         <v>844.31805420189687</v>
       </c>
       <c r="AV111" s="1">
-        <f t="shared" si="177"/>
+        <f t="shared" si="173"/>
         <v>852.76123474391579</v>
       </c>
       <c r="AW111" s="1">
-        <f t="shared" si="177"/>
+        <f t="shared" si="173"/>
         <v>861.28884709135491</v>
       </c>
       <c r="AX111" s="1">
-        <f t="shared" si="177"/>
+        <f t="shared" si="173"/>
         <v>869.90173556226841</v>
       </c>
     </row>
@@ -10018,11 +10088,11 @@
         <v>305.5</v>
       </c>
       <c r="AL112" s="1">
-        <f t="shared" si="174"/>
+        <f t="shared" si="170"/>
         <v>474.1</v>
       </c>
       <c r="AM112" s="1">
-        <f t="shared" si="175"/>
+        <f t="shared" si="171"/>
         <v>507.2</v>
       </c>
       <c r="AN112" s="1">
@@ -10034,15 +10104,15 @@
         <v>455.26272</v>
       </c>
       <c r="AP112" s="1">
-        <f t="shared" si="176"/>
+        <f t="shared" si="172"/>
         <v>464.36797440000004</v>
       </c>
       <c r="AQ112" s="1">
-        <f t="shared" si="176"/>
+        <f t="shared" si="172"/>
         <v>473.65533388800003</v>
       </c>
       <c r="AR112" s="1">
-        <f t="shared" si="176"/>
+        <f t="shared" si="172"/>
         <v>483.12844056576006</v>
       </c>
       <c r="AS112" s="1">
@@ -10050,23 +10120,23 @@
         <v>487.95972497141764</v>
       </c>
       <c r="AT112" s="1">
-        <f t="shared" ref="AT112:AX112" si="178">AS112*1.01</f>
+        <f t="shared" ref="AT112:AX112" si="174">AS112*1.01</f>
         <v>492.83932222113185</v>
       </c>
       <c r="AU112" s="1">
-        <f t="shared" si="178"/>
+        <f t="shared" si="174"/>
         <v>497.76771544334315</v>
       </c>
       <c r="AV112" s="1">
-        <f t="shared" si="178"/>
+        <f t="shared" si="174"/>
         <v>502.74539259777657</v>
       </c>
       <c r="AW112" s="1">
-        <f t="shared" si="178"/>
+        <f t="shared" si="174"/>
         <v>507.77284652375437</v>
       </c>
       <c r="AX112" s="1">
-        <f t="shared" si="178"/>
+        <f t="shared" si="174"/>
         <v>512.85057498899187</v>
       </c>
     </row>
@@ -10079,102 +10149,102 @@
         <v>416.4</v>
       </c>
       <c r="T113" s="1">
-        <f t="shared" ref="T113:Z113" si="179">T111+T112</f>
+        <f t="shared" ref="T113:Z113" si="175">T111+T112</f>
         <v>332.2</v>
       </c>
       <c r="U113" s="1">
-        <f t="shared" si="179"/>
+        <f t="shared" si="175"/>
         <v>176.39999999999995</v>
       </c>
       <c r="V113" s="1">
-        <f t="shared" si="179"/>
+        <f t="shared" si="175"/>
         <v>285.30000000000007</v>
       </c>
       <c r="W113" s="1">
-        <f t="shared" si="179"/>
+        <f t="shared" si="175"/>
         <v>306.60000000000002</v>
       </c>
       <c r="X113" s="1">
-        <f t="shared" si="179"/>
+        <f t="shared" si="175"/>
         <v>344.6</v>
       </c>
       <c r="Y113" s="1">
-        <f t="shared" si="179"/>
+        <f t="shared" si="175"/>
         <v>298.10000000000002</v>
       </c>
       <c r="Z113" s="1">
-        <f t="shared" si="179"/>
+        <f t="shared" si="175"/>
         <v>322.39999999999998</v>
       </c>
       <c r="AA113" s="1">
-        <f t="shared" ref="AA113" si="180">AA111+AA112</f>
+        <f t="shared" ref="AA113" si="176">AA111+AA112</f>
         <v>287.5</v>
       </c>
       <c r="AB113" s="1"/>
       <c r="AC113" s="1"/>
       <c r="AD113" s="1"/>
       <c r="AI113" s="1">
-        <f t="shared" ref="AI113:AK113" si="181">AI111+AI112</f>
+        <f t="shared" ref="AI113:AK113" si="177">AI111+AI112</f>
         <v>455.1</v>
       </c>
       <c r="AJ113" s="1">
-        <f t="shared" si="181"/>
+        <f t="shared" si="177"/>
         <v>1298.7</v>
       </c>
       <c r="AK113" s="1">
-        <f t="shared" si="181"/>
+        <f t="shared" si="177"/>
         <v>723.2</v>
       </c>
       <c r="AL113" s="1">
-        <f t="shared" ref="AL113" si="182">AL111+AL112</f>
+        <f t="shared" ref="AL113" si="178">AL111+AL112</f>
         <v>1210.3000000000002</v>
       </c>
       <c r="AM113" s="1">
-        <f t="shared" ref="AM113" si="183">AM111+AM112</f>
+        <f t="shared" ref="AM113" si="179">AM111+AM112</f>
         <v>1271.7</v>
       </c>
       <c r="AN113" s="1">
-        <f t="shared" ref="AN113" si="184">AN111+AN112</f>
+        <f t="shared" ref="AN113" si="180">AN111+AN112</f>
         <v>1226.126</v>
       </c>
       <c r="AO113" s="1">
-        <f t="shared" ref="AO113" si="185">AO111+AO112</f>
+        <f t="shared" ref="AO113" si="181">AO111+AO112</f>
         <v>1250.64852</v>
       </c>
       <c r="AP113" s="1">
-        <f t="shared" ref="AP113" si="186">AP111+AP112</f>
+        <f t="shared" ref="AP113" si="182">AP111+AP112</f>
         <v>1267.7076324</v>
       </c>
       <c r="AQ113" s="1">
-        <f t="shared" ref="AQ113" si="187">AQ111+AQ112</f>
+        <f t="shared" ref="AQ113" si="183">AQ111+AQ112</f>
         <v>1285.028388468</v>
       </c>
       <c r="AR113" s="1">
-        <f t="shared" ref="AR113" si="188">AR111+AR112</f>
+        <f t="shared" ref="AR113" si="184">AR111+AR112</f>
         <v>1302.61522569156</v>
       </c>
       <c r="AS113" s="1">
-        <f t="shared" ref="AS113" si="189">AS111+AS112</f>
+        <f t="shared" ref="AS113" si="185">AS111+AS112</f>
         <v>1315.6413779484756</v>
       </c>
       <c r="AT113" s="1">
-        <f t="shared" ref="AT113" si="190">AT111+AT112</f>
+        <f t="shared" ref="AT113" si="186">AT111+AT112</f>
         <v>1328.7977917279604</v>
       </c>
       <c r="AU113" s="1">
-        <f t="shared" ref="AU113" si="191">AU111+AU112</f>
+        <f t="shared" ref="AU113" si="187">AU111+AU112</f>
         <v>1342.0857696452399</v>
       </c>
       <c r="AV113" s="1">
-        <f t="shared" ref="AV113" si="192">AV111+AV112</f>
+        <f t="shared" ref="AV113" si="188">AV111+AV112</f>
         <v>1355.5066273416924</v>
       </c>
       <c r="AW113" s="1">
-        <f t="shared" ref="AW113" si="193">AW111+AW112</f>
+        <f t="shared" ref="AW113" si="189">AW111+AW112</f>
         <v>1369.0616936151093</v>
       </c>
       <c r="AX113" s="1">
-        <f t="shared" ref="AX113" si="194">AX111+AX112</f>
+        <f t="shared" ref="AX113" si="190">AX111+AX112</f>
         <v>1382.7523105512603</v>
       </c>
     </row>
@@ -10183,19 +10253,19 @@
         <v>119</v>
       </c>
       <c r="O114" s="9">
-        <f t="shared" ref="O114:R114" si="195">O110+O111+O112</f>
+        <f t="shared" ref="O114:R114" si="191">O110+O111+O112</f>
         <v>-313.09999999999997</v>
       </c>
       <c r="P114" s="9">
-        <f t="shared" si="195"/>
+        <f t="shared" si="191"/>
         <v>-487.40000000000015</v>
       </c>
       <c r="Q114" s="9">
-        <f t="shared" si="195"/>
+        <f t="shared" si="191"/>
         <v>202.49999999999997</v>
       </c>
       <c r="R114" s="9">
-        <f t="shared" si="195"/>
+        <f t="shared" si="191"/>
         <v>78.899999999999949</v>
       </c>
       <c r="S114" s="9">
@@ -10203,495 +10273,495 @@
         <v>752.00000000000011</v>
       </c>
       <c r="T114" s="9">
-        <f t="shared" ref="T114:Z114" si="196">T110-T113</f>
+        <f t="shared" ref="T114:Z114" si="192">T110-T113</f>
         <v>498.60000000000019</v>
       </c>
       <c r="U114" s="9">
-        <f t="shared" si="196"/>
+        <f t="shared" si="192"/>
         <v>-116.0000000000006</v>
       </c>
       <c r="V114" s="9">
-        <f t="shared" si="196"/>
+        <f t="shared" si="192"/>
         <v>-701.4</v>
       </c>
       <c r="W114" s="9">
-        <f t="shared" si="196"/>
+        <f t="shared" si="192"/>
         <v>-2780.5999999999995</v>
       </c>
       <c r="X114" s="9">
-        <f t="shared" si="196"/>
+        <f t="shared" si="192"/>
         <v>-1062.7000000000003</v>
       </c>
       <c r="Y114" s="9">
-        <f t="shared" si="196"/>
+        <f t="shared" si="192"/>
         <v>-432.50000000000011</v>
       </c>
       <c r="Z114" s="9">
-        <f t="shared" si="196"/>
+        <f t="shared" si="192"/>
         <v>-623.10000000000025</v>
       </c>
       <c r="AA114" s="9">
-        <f t="shared" ref="AA114" si="197">AA110-AA113</f>
+        <f t="shared" ref="AA114" si="193">AA110-AA113</f>
         <v>334.5999999999998</v>
       </c>
       <c r="AB114" s="9"/>
       <c r="AC114" s="9"/>
       <c r="AD114" s="9"/>
       <c r="AI114" s="9">
-        <f t="shared" ref="AI114:AK114" si="198">AI110-AI113</f>
+        <f t="shared" ref="AI114:AK114" si="194">AI110-AI113</f>
         <v>-382.00000000000045</v>
       </c>
       <c r="AJ114" s="9">
-        <f t="shared" si="198"/>
+        <f t="shared" si="194"/>
         <v>2327.0000000000009</v>
       </c>
       <c r="AK114" s="9">
-        <f t="shared" si="198"/>
+        <f t="shared" si="194"/>
         <v>967.60000000000105</v>
       </c>
       <c r="AL114" s="9">
-        <f t="shared" ref="AL114" si="199">AL110-AL113</f>
+        <f t="shared" ref="AL114" si="195">AL110-AL113</f>
         <v>433.20000000000186</v>
       </c>
       <c r="AM114" s="9">
-        <f t="shared" ref="AM114" si="200">AM110-AM113</f>
+        <f t="shared" ref="AM114" si="196">AM110-AM113</f>
         <v>-4898.8999999999978</v>
       </c>
       <c r="AN114" s="9">
-        <f t="shared" ref="AN114" si="201">AN110-AN113</f>
-        <v>2595.5612560000018</v>
+        <f t="shared" ref="AN114" si="197">AN110-AN113</f>
+        <v>6173.1152639999982</v>
       </c>
       <c r="AO114" s="9">
-        <f t="shared" ref="AO114" si="202">AO110-AO113</f>
-        <v>3144.2563345799999</v>
+        <f t="shared" ref="AO114" si="198">AO110-AO113</f>
+        <v>6749.0878280611996</v>
       </c>
       <c r="AP114" s="9">
-        <f t="shared" ref="AP114" si="203">AP110-AP113</f>
-        <v>3391.4542303902008</v>
+        <f t="shared" ref="AP114" si="199">AP110-AP113</f>
+        <v>7083.4206403417475</v>
       </c>
       <c r="AQ114" s="9">
-        <f t="shared" ref="AQ114" si="204">AQ110-AQ113</f>
-        <v>3571.3157420863263</v>
+        <f t="shared" ref="AQ114" si="200">AQ110-AQ113</f>
+        <v>7340.3487303322445</v>
       </c>
       <c r="AR114" s="9">
-        <f t="shared" ref="AR114" si="205">AR110-AR113</f>
-        <v>3658.5818629921732</v>
+        <f t="shared" ref="AR114" si="201">AR110-AR113</f>
+        <v>7538.3344248732692</v>
       </c>
       <c r="AS114" s="9">
-        <f t="shared" ref="AS114" si="206">AS110-AS113</f>
-        <v>3741.7909090701987</v>
+        <f t="shared" ref="AS114" si="202">AS110-AS113</f>
+        <v>7690.5876046890317</v>
       </c>
       <c r="AT114" s="9">
-        <f t="shared" ref="AT114" si="207">AT110-AT113</f>
-        <v>3768.5204855020484</v>
+        <f t="shared" ref="AT114" si="203">AT110-AT113</f>
+        <v>7826.2247375221468</v>
       </c>
       <c r="AU114" s="9">
-        <f t="shared" ref="AU114" si="208">AU110-AU113</f>
-        <v>3743.3889647089486</v>
+        <f t="shared" ref="AU114" si="204">AU110-AU113</f>
+        <v>7902.034054724425</v>
       </c>
       <c r="AV114" s="9">
-        <f t="shared" ref="AV114" si="209">AV110-AV113</f>
-        <v>3718.1143276965022</v>
+        <f t="shared" ref="AV114" si="205">AV110-AV113</f>
+        <v>7979.6842554753821</v>
       </c>
       <c r="AW114" s="9">
-        <f t="shared" ref="AW114" si="210">AW110-AW113</f>
-        <v>3692.6526113445907</v>
+        <f t="shared" ref="AW114" si="206">AW110-AW113</f>
+        <v>8059.1752626248744</v>
       </c>
       <c r="AX114" s="9">
-        <f t="shared" ref="AX114" si="211">AX110-AX113</f>
-        <v>3666.9606534750083</v>
+        <f t="shared" ref="AX114" si="207">AX110-AX113</f>
+        <v>8140.5091291408635</v>
       </c>
       <c r="AY114" s="7">
         <f>AX114*(1+$BC$23)</f>
-        <v>3630.2910469402582</v>
+        <v>8059.1040378494545</v>
       </c>
       <c r="AZ114" s="7">
-        <f t="shared" ref="AZ114:DK114" si="212">AY114*(1+$BC$23)</f>
-        <v>3593.9881364708554</v>
+        <f t="shared" ref="AZ114:DK114" si="208">AY114*(1+$BC$23)</f>
+        <v>7978.5129974709598</v>
       </c>
       <c r="BA114" s="7">
-        <f t="shared" si="212"/>
-        <v>3558.0482551061468</v>
+        <f t="shared" si="208"/>
+        <v>7898.7278674962499</v>
       </c>
       <c r="BB114" s="7">
-        <f t="shared" si="212"/>
-        <v>3522.4677725550855</v>
+        <f t="shared" si="208"/>
+        <v>7819.740588821287</v>
       </c>
       <c r="BC114" s="7">
-        <f t="shared" si="212"/>
-        <v>3487.2430948295346</v>
+        <f t="shared" si="208"/>
+        <v>7741.5431829330737</v>
       </c>
       <c r="BD114" s="7">
-        <f t="shared" si="212"/>
-        <v>3452.3706638812391</v>
+        <f t="shared" si="208"/>
+        <v>7664.1277511037433</v>
       </c>
       <c r="BE114" s="7">
-        <f t="shared" si="212"/>
-        <v>3417.8469572424269</v>
+        <f t="shared" si="208"/>
+        <v>7587.4864735927058</v>
       </c>
       <c r="BF114" s="7">
-        <f t="shared" si="212"/>
-        <v>3383.6684876700028</v>
+        <f t="shared" si="208"/>
+        <v>7511.6116088567787</v>
       </c>
       <c r="BG114" s="7">
-        <f t="shared" si="212"/>
-        <v>3349.8318027933028</v>
+        <f t="shared" si="208"/>
+        <v>7436.4954927682111</v>
       </c>
       <c r="BH114" s="7">
-        <f t="shared" si="212"/>
-        <v>3316.3334847653696</v>
+        <f t="shared" si="208"/>
+        <v>7362.1305378405286</v>
       </c>
       <c r="BI114" s="7">
-        <f t="shared" si="212"/>
-        <v>3283.1701499177157</v>
+        <f t="shared" si="208"/>
+        <v>7288.5092324621237</v>
       </c>
       <c r="BJ114" s="7">
-        <f t="shared" si="212"/>
-        <v>3250.3384484185385</v>
+        <f t="shared" si="208"/>
+        <v>7215.6241401375028</v>
       </c>
       <c r="BK114" s="7">
-        <f t="shared" si="212"/>
-        <v>3217.835063934353</v>
+        <f t="shared" si="208"/>
+        <v>7143.4678987361276</v>
       </c>
       <c r="BL114" s="7">
-        <f t="shared" si="212"/>
-        <v>3185.6567132950095</v>
+        <f t="shared" si="208"/>
+        <v>7072.033219748766</v>
       </c>
       <c r="BM114" s="7">
-        <f t="shared" si="212"/>
-        <v>3153.8001461620593</v>
+        <f t="shared" si="208"/>
+        <v>7001.3128875512784</v>
       </c>
       <c r="BN114" s="7">
-        <f t="shared" si="212"/>
-        <v>3122.2621447004385</v>
+        <f t="shared" si="208"/>
+        <v>6931.2997586757656</v>
       </c>
       <c r="BO114" s="7">
-        <f t="shared" si="212"/>
-        <v>3091.0395232534343</v>
+        <f t="shared" si="208"/>
+        <v>6861.9867610890078</v>
       </c>
       <c r="BP114" s="7">
-        <f t="shared" si="212"/>
-        <v>3060.1291280208998</v>
+        <f t="shared" si="208"/>
+        <v>6793.3668934781181</v>
       </c>
       <c r="BQ114" s="7">
-        <f t="shared" si="212"/>
-        <v>3029.5278367406909</v>
+        <f t="shared" si="208"/>
+        <v>6725.433224543337</v>
       </c>
       <c r="BR114" s="7">
-        <f t="shared" si="212"/>
-        <v>2999.2325583732841</v>
+        <f t="shared" si="208"/>
+        <v>6658.178892297904</v>
       </c>
       <c r="BS114" s="7">
-        <f t="shared" si="212"/>
-        <v>2969.2402327895511</v>
+        <f t="shared" si="208"/>
+        <v>6591.5971033749247</v>
       </c>
       <c r="BT114" s="7">
-        <f t="shared" si="212"/>
-        <v>2939.5478304616554</v>
+        <f t="shared" si="208"/>
+        <v>6525.6811323411757</v>
       </c>
       <c r="BU114" s="7">
-        <f t="shared" si="212"/>
-        <v>2910.1523521570389</v>
+        <f t="shared" si="208"/>
+        <v>6460.4243210177638</v>
       </c>
       <c r="BV114" s="7">
-        <f t="shared" si="212"/>
-        <v>2881.0508286354684</v>
+        <f t="shared" si="208"/>
+        <v>6395.8200778075861</v>
       </c>
       <c r="BW114" s="7">
-        <f t="shared" si="212"/>
-        <v>2852.2403203491135</v>
+        <f t="shared" si="208"/>
+        <v>6331.8618770295107</v>
       </c>
       <c r="BX114" s="7">
-        <f t="shared" si="212"/>
-        <v>2823.7179171456223</v>
+        <f t="shared" si="208"/>
+        <v>6268.5432582592157</v>
       </c>
       <c r="BY114" s="7">
-        <f t="shared" si="212"/>
-        <v>2795.480737974166</v>
+        <f t="shared" si="208"/>
+        <v>6205.8578256766232</v>
       </c>
       <c r="BZ114" s="7">
-        <f t="shared" si="212"/>
-        <v>2767.5259305944242</v>
+        <f t="shared" si="208"/>
+        <v>6143.7992474198572</v>
       </c>
       <c r="CA114" s="7">
-        <f t="shared" si="212"/>
-        <v>2739.85067128848</v>
+        <f t="shared" si="208"/>
+        <v>6082.3612549456584</v>
       </c>
       <c r="CB114" s="7">
-        <f t="shared" si="212"/>
-        <v>2712.4521645755954</v>
+        <f t="shared" si="208"/>
+        <v>6021.5376423962016</v>
       </c>
       <c r="CC114" s="7">
-        <f t="shared" si="212"/>
-        <v>2685.3276429298394</v>
+        <f t="shared" si="208"/>
+        <v>5961.3222659722396</v>
       </c>
       <c r="CD114" s="7">
-        <f t="shared" si="212"/>
-        <v>2658.4743665005408</v>
+        <f t="shared" si="208"/>
+        <v>5901.7090433125168</v>
       </c>
       <c r="CE114" s="7">
-        <f t="shared" si="212"/>
-        <v>2631.8896228355352</v>
+        <f t="shared" si="208"/>
+        <v>5842.6919528793915</v>
       </c>
       <c r="CF114" s="7">
-        <f t="shared" si="212"/>
-        <v>2605.5707266071799</v>
+        <f t="shared" si="208"/>
+        <v>5784.2650333505972</v>
       </c>
       <c r="CG114" s="7">
-        <f t="shared" si="212"/>
-        <v>2579.5150193411082</v>
+        <f t="shared" si="208"/>
+        <v>5726.4223830170913</v>
       </c>
       <c r="CH114" s="7">
-        <f t="shared" si="212"/>
-        <v>2553.719869147697</v>
+        <f t="shared" si="208"/>
+        <v>5669.1581591869208</v>
       </c>
       <c r="CI114" s="7">
-        <f t="shared" si="212"/>
-        <v>2528.18267045622</v>
+        <f t="shared" si="208"/>
+        <v>5612.4665775950516</v>
       </c>
       <c r="CJ114" s="7">
-        <f t="shared" si="212"/>
-        <v>2502.9008437516577</v>
+        <f t="shared" si="208"/>
+        <v>5556.3419118191014</v>
       </c>
       <c r="CK114" s="7">
-        <f t="shared" si="212"/>
-        <v>2477.8718353141412</v>
+        <f t="shared" si="208"/>
+        <v>5500.7784927009106</v>
       </c>
       <c r="CL114" s="7">
-        <f t="shared" si="212"/>
-        <v>2453.0931169609999</v>
+        <f t="shared" si="208"/>
+        <v>5445.7707077739014</v>
       </c>
       <c r="CM114" s="7">
-        <f t="shared" si="212"/>
-        <v>2428.5621857913898</v>
+        <f t="shared" si="208"/>
+        <v>5391.3130006961628</v>
       </c>
       <c r="CN114" s="7">
-        <f t="shared" si="212"/>
-        <v>2404.2765639334757</v>
+        <f t="shared" si="208"/>
+        <v>5337.3998706892007</v>
       </c>
       <c r="CO114" s="7">
-        <f t="shared" si="212"/>
-        <v>2380.2337982941408</v>
+        <f t="shared" si="208"/>
+        <v>5284.0258719823087</v>
       </c>
       <c r="CP114" s="7">
-        <f t="shared" si="212"/>
-        <v>2356.4314603111993</v>
+        <f t="shared" si="208"/>
+        <v>5231.1856132624853</v>
       </c>
       <c r="CQ114" s="7">
-        <f t="shared" si="212"/>
-        <v>2332.8671457080873</v>
+        <f t="shared" si="208"/>
+        <v>5178.8737571298607</v>
       </c>
       <c r="CR114" s="7">
-        <f t="shared" si="212"/>
-        <v>2309.5384742510064</v>
+        <f t="shared" si="208"/>
+        <v>5127.0850195585617</v>
       </c>
       <c r="CS114" s="7">
-        <f t="shared" si="212"/>
-        <v>2286.4430895084961</v>
+        <f t="shared" si="208"/>
+        <v>5075.8141693629759</v>
       </c>
       <c r="CT114" s="7">
-        <f t="shared" si="212"/>
-        <v>2263.5786586134109</v>
+        <f t="shared" si="208"/>
+        <v>5025.0560276693459</v>
       </c>
       <c r="CU114" s="7">
-        <f t="shared" si="212"/>
-        <v>2240.9428720272767</v>
+        <f t="shared" si="208"/>
+        <v>4974.8054673926526</v>
       </c>
       <c r="CV114" s="7">
-        <f t="shared" si="212"/>
-        <v>2218.5334433070038</v>
+        <f t="shared" si="208"/>
+        <v>4925.0574127187265</v>
       </c>
       <c r="CW114" s="7">
-        <f t="shared" si="212"/>
-        <v>2196.3481088739336</v>
+        <f t="shared" si="208"/>
+        <v>4875.8068385915394</v>
       </c>
       <c r="CX114" s="7">
-        <f t="shared" si="212"/>
-        <v>2174.3846277851944</v>
+        <f t="shared" si="208"/>
+        <v>4827.0487702056244</v>
       </c>
       <c r="CY114" s="7">
-        <f t="shared" si="212"/>
-        <v>2152.6407815073426</v>
+        <f t="shared" si="208"/>
+        <v>4778.7782825035683</v>
       </c>
       <c r="CZ114" s="7">
-        <f t="shared" si="212"/>
-        <v>2131.1143736922691</v>
+        <f t="shared" si="208"/>
+        <v>4730.9904996785326</v>
       </c>
       <c r="DA114" s="7">
-        <f t="shared" si="212"/>
-        <v>2109.8032299553465</v>
+        <f t="shared" si="208"/>
+        <v>4683.6805946817476</v>
       </c>
       <c r="DB114" s="7">
-        <f t="shared" si="212"/>
-        <v>2088.7051976557932</v>
+        <f t="shared" si="208"/>
+        <v>4636.8437887349301</v>
       </c>
       <c r="DC114" s="7">
-        <f t="shared" si="212"/>
-        <v>2067.8181456792354</v>
+        <f t="shared" si="208"/>
+        <v>4590.4753508475806</v>
       </c>
       <c r="DD114" s="7">
-        <f t="shared" si="212"/>
-        <v>2047.139964222443</v>
+        <f t="shared" si="208"/>
+        <v>4544.570597339105</v>
       </c>
       <c r="DE114" s="7">
-        <f t="shared" si="212"/>
-        <v>2026.6685645802186</v>
+        <f t="shared" si="208"/>
+        <v>4499.1248913657137</v>
       </c>
       <c r="DF114" s="7">
-        <f t="shared" si="212"/>
-        <v>2006.4018789344163</v>
+        <f t="shared" si="208"/>
+        <v>4454.1336424520568</v>
       </c>
       <c r="DG114" s="7">
-        <f t="shared" si="212"/>
-        <v>1986.3378601450722</v>
+        <f t="shared" si="208"/>
+        <v>4409.5923060275363</v>
       </c>
       <c r="DH114" s="7">
-        <f t="shared" si="212"/>
-        <v>1966.4744815436216</v>
+        <f t="shared" si="208"/>
+        <v>4365.4963829672606</v>
       </c>
       <c r="DI114" s="7">
-        <f t="shared" si="212"/>
-        <v>1946.8097367281853</v>
+        <f t="shared" si="208"/>
+        <v>4321.8414191375878</v>
       </c>
       <c r="DJ114" s="7">
-        <f t="shared" si="212"/>
-        <v>1927.3416393609034</v>
+        <f t="shared" si="208"/>
+        <v>4278.6230049462119</v>
       </c>
       <c r="DK114" s="7">
-        <f t="shared" si="212"/>
-        <v>1908.0682229672943</v>
+        <f t="shared" si="208"/>
+        <v>4235.8367748967494</v>
       </c>
       <c r="DL114" s="7">
-        <f t="shared" ref="DL114:ER114" si="213">DK114*(1+$BC$23)</f>
-        <v>1888.9875407376214</v>
+        <f t="shared" ref="DL114:ER114" si="209">DK114*(1+$BC$23)</f>
+        <v>4193.4784071477816</v>
       </c>
       <c r="DM114" s="7">
-        <f t="shared" si="213"/>
-        <v>1870.0976653302453</v>
+        <f t="shared" si="209"/>
+        <v>4151.5436230763034</v>
       </c>
       <c r="DN114" s="7">
-        <f t="shared" si="213"/>
-        <v>1851.3966886769429</v>
+        <f t="shared" si="209"/>
+        <v>4110.0281868455404</v>
       </c>
       <c r="DO114" s="7">
-        <f t="shared" si="213"/>
-        <v>1832.8827217901735</v>
+        <f t="shared" si="209"/>
+        <v>4068.9279049770848</v>
       </c>
       <c r="DP114" s="7">
-        <f t="shared" si="213"/>
-        <v>1814.5538945722717</v>
+        <f t="shared" si="209"/>
+        <v>4028.2386259273139</v>
       </c>
       <c r="DQ114" s="7">
-        <f t="shared" si="213"/>
-        <v>1796.4083556265489</v>
+        <f t="shared" si="209"/>
+        <v>3987.9562396680408</v>
       </c>
       <c r="DR114" s="7">
-        <f t="shared" si="213"/>
-        <v>1778.4442720702834</v>
+        <f t="shared" si="209"/>
+        <v>3948.0766772713605</v>
       </c>
       <c r="DS114" s="7">
-        <f t="shared" si="213"/>
-        <v>1760.6598293495806</v>
+        <f t="shared" si="209"/>
+        <v>3908.5959104986468</v>
       </c>
       <c r="DT114" s="7">
-        <f t="shared" si="213"/>
-        <v>1743.0532310560848</v>
+        <f t="shared" si="209"/>
+        <v>3869.5099513936602</v>
       </c>
       <c r="DU114" s="7">
-        <f t="shared" si="213"/>
-        <v>1725.6226987455238</v>
+        <f t="shared" si="209"/>
+        <v>3830.8148518797234</v>
       </c>
       <c r="DV114" s="7">
-        <f t="shared" si="213"/>
-        <v>1708.3664717580687</v>
+        <f t="shared" si="209"/>
+        <v>3792.5067033609262</v>
       </c>
       <c r="DW114" s="7">
-        <f t="shared" si="213"/>
-        <v>1691.282807040488</v>
+        <f t="shared" si="209"/>
+        <v>3754.581636327317</v>
       </c>
       <c r="DX114" s="7">
-        <f t="shared" si="213"/>
-        <v>1674.3699789700831</v>
+        <f t="shared" si="209"/>
+        <v>3717.0358199640436</v>
       </c>
       <c r="DY114" s="7">
-        <f t="shared" si="213"/>
-        <v>1657.6262791803822</v>
+        <f t="shared" si="209"/>
+        <v>3679.8654617644033</v>
       </c>
       <c r="DZ114" s="7">
-        <f t="shared" si="213"/>
-        <v>1641.0500163885783</v>
+        <f t="shared" si="209"/>
+        <v>3643.0668071467594</v>
       </c>
       <c r="EA114" s="7">
-        <f t="shared" si="213"/>
-        <v>1624.6395162246924</v>
+        <f t="shared" si="209"/>
+        <v>3606.6361390752918</v>
       </c>
       <c r="EB114" s="7">
-        <f t="shared" si="213"/>
-        <v>1608.3931210624455</v>
+        <f t="shared" si="209"/>
+        <v>3570.5697776845386</v>
       </c>
       <c r="EC114" s="7">
-        <f t="shared" si="213"/>
-        <v>1592.309189851821</v>
+        <f t="shared" si="209"/>
+        <v>3534.8640799076934</v>
       </c>
       <c r="ED114" s="7">
-        <f t="shared" si="213"/>
-        <v>1576.3860979533029</v>
+        <f t="shared" si="209"/>
+        <v>3499.5154391086166</v>
       </c>
       <c r="EE114" s="7">
-        <f t="shared" si="213"/>
-        <v>1560.6222369737698</v>
+        <f t="shared" si="209"/>
+        <v>3464.5202847175306</v>
       </c>
       <c r="EF114" s="7">
-        <f t="shared" si="213"/>
-        <v>1545.0160146040321</v>
+        <f t="shared" si="209"/>
+        <v>3429.8750818703552</v>
       </c>
       <c r="EG114" s="7">
-        <f t="shared" si="213"/>
-        <v>1529.5658544579917</v>
+        <f t="shared" si="209"/>
+        <v>3395.5763310516518</v>
       </c>
       <c r="EH114" s="7">
-        <f t="shared" si="213"/>
-        <v>1514.2701959134117</v>
+        <f t="shared" si="209"/>
+        <v>3361.6205677411353</v>
       </c>
       <c r="EI114" s="7">
-        <f t="shared" si="213"/>
-        <v>1499.1274939542775</v>
+        <f t="shared" si="209"/>
+        <v>3328.0043620637239</v>
       </c>
       <c r="EJ114" s="7">
-        <f t="shared" si="213"/>
-        <v>1484.1362190147347</v>
+        <f t="shared" si="209"/>
+        <v>3294.7243184430868</v>
       </c>
       <c r="EK114" s="7">
-        <f t="shared" si="213"/>
-        <v>1469.2948568245874</v>
+        <f t="shared" si="209"/>
+        <v>3261.7770752586557</v>
       </c>
       <c r="EL114" s="7">
-        <f t="shared" si="213"/>
-        <v>1454.6019082563416</v>
+        <f t="shared" si="209"/>
+        <v>3229.159304506069</v>
       </c>
       <c r="EM114" s="7">
-        <f t="shared" si="213"/>
-        <v>1440.0558891737783</v>
+        <f t="shared" si="209"/>
+        <v>3196.8677114610082</v>
       </c>
       <c r="EN114" s="7">
-        <f t="shared" si="213"/>
-        <v>1425.6553302820405</v>
+        <f t="shared" si="209"/>
+        <v>3164.8990343463979</v>
       </c>
       <c r="EO114" s="7">
-        <f t="shared" si="213"/>
-        <v>1411.39877697922</v>
+        <f t="shared" si="209"/>
+        <v>3133.2500440029339</v>
       </c>
       <c r="EP114" s="7">
-        <f t="shared" si="213"/>
-        <v>1397.2847892094278</v>
+        <f t="shared" si="209"/>
+        <v>3101.9175435629045</v>
       </c>
       <c r="EQ114" s="7">
-        <f t="shared" si="213"/>
-        <v>1383.3119413173335</v>
+        <f t="shared" si="209"/>
+        <v>3070.8983681272753</v>
       </c>
       <c r="ER114" s="7">
-        <f t="shared" si="213"/>
-        <v>1369.4788219041602</v>
+        <f t="shared" si="209"/>
+        <v>3040.1893844460024</v>
       </c>
     </row>
     <row r="115" spans="2:148" x14ac:dyDescent="0.3">
@@ -10699,15 +10769,15 @@
     </row>
     <row r="116" spans="2:148" x14ac:dyDescent="0.3">
       <c r="W116" s="10">
-        <f t="shared" ref="W116:Y116" si="214">W111/S111-1</f>
+        <f t="shared" ref="W116:Y116" si="210">W111/S111-1</f>
         <v>-0.46929180135174853</v>
       </c>
       <c r="X116" s="10">
-        <f t="shared" si="214"/>
+        <f t="shared" si="210"/>
         <v>7.1865443425076503E-2</v>
       </c>
       <c r="Y116" s="10">
-        <f t="shared" si="214"/>
+        <f t="shared" si="210"/>
         <v>2.0777576853526258</v>
       </c>
       <c r="Z116" s="10">
@@ -10722,23 +10792,23 @@
     </row>
     <row r="117" spans="2:148" x14ac:dyDescent="0.3">
       <c r="W117" s="10">
-        <f t="shared" ref="W117:AA117" si="215">W112/S112-1</f>
+        <f t="shared" ref="W117:AA117" si="211">W112/S112-1</f>
         <v>0.65571616294349555</v>
       </c>
       <c r="X117" s="10">
-        <f t="shared" si="215"/>
+        <f t="shared" si="211"/>
         <v>-1.2499999999999956E-2</v>
       </c>
       <c r="Y117" s="10">
-        <f t="shared" si="215"/>
+        <f t="shared" si="211"/>
         <v>5.6151940545003942E-2</v>
       </c>
       <c r="Z117" s="10">
-        <f t="shared" si="215"/>
+        <f t="shared" si="211"/>
         <v>-0.15542938254080907</v>
       </c>
       <c r="AA117" s="10">
-        <f t="shared" si="215"/>
+        <f t="shared" si="211"/>
         <v>-0.14841269841269844</v>
       </c>
       <c r="BA117" s="10"/>
@@ -10749,7 +10819,7 @@
       </c>
       <c r="BA118" s="14">
         <f>NPV(BC24,AN114:ER114)</f>
-        <v>22618.244104935922</v>
+        <v>48760.366149468857</v>
       </c>
     </row>
     <row r="119" spans="2:148" x14ac:dyDescent="0.3">
@@ -10758,7 +10828,7 @@
       </c>
       <c r="BA119" s="1">
         <f>BA118/Main!D13</f>
-        <v>3996.1562022854987</v>
+        <v>8996.3775183521884</v>
       </c>
     </row>
     <row r="120" spans="2:148" x14ac:dyDescent="0.3">
@@ -10822,7 +10892,7 @@
       </c>
       <c r="BA120" s="1">
         <f>Main!D10</f>
-        <v>-1344.0106007067136</v>
+        <v>-1571.0701107011073</v>
       </c>
     </row>
     <row r="121" spans="2:148" x14ac:dyDescent="0.3">
@@ -10852,7 +10922,7 @@
       </c>
       <c r="BA121" s="1">
         <f>BA119+BA120</f>
-        <v>2652.1456015787853</v>
+        <v>7425.3074076510811</v>
       </c>
     </row>
     <row r="122" spans="2:148" x14ac:dyDescent="0.3">
@@ -10882,7 +10952,7 @@
       </c>
       <c r="BA122" s="2">
         <f>BA121/AX19</f>
-        <v>9.4787190907033061</v>
+        <v>27.079895724475133</v>
       </c>
     </row>
     <row r="123" spans="2:148" x14ac:dyDescent="0.3">
@@ -10912,7 +10982,7 @@
       </c>
       <c r="BA123" s="2">
         <f>Main!D3</f>
-        <v>13.28</v>
+        <v>15.35</v>
       </c>
     </row>
     <row r="124" spans="2:148" x14ac:dyDescent="0.3">
@@ -10942,7 +11012,7 @@
       </c>
       <c r="BA124" s="11">
         <f>BA122/BA123-1</f>
-        <v>-0.28624103232655829</v>
+        <v>0.76416258791368952</v>
       </c>
     </row>
     <row r="125" spans="2:148" x14ac:dyDescent="0.3">
@@ -11503,28 +11573,28 @@
       </c>
       <c r="O149" s="1"/>
       <c r="P149" s="1">
-        <f t="shared" ref="P149:V149" si="216">P120+SUM(P121:P148)</f>
+        <f t="shared" ref="P149:V149" si="212">P120+SUM(P121:P148)</f>
         <v>-800.50000000000011</v>
       </c>
       <c r="Q149" s="1">
-        <f t="shared" si="216"/>
+        <f t="shared" si="212"/>
         <v>-598.00000000000023</v>
       </c>
       <c r="R149" s="1">
-        <f t="shared" si="216"/>
+        <f t="shared" si="212"/>
         <v>1690.9999999999998</v>
       </c>
       <c r="S149" s="1"/>
       <c r="T149" s="1">
-        <f t="shared" si="216"/>
+        <f t="shared" si="212"/>
         <v>1999.2000000000005</v>
       </c>
       <c r="U149" s="1">
-        <f t="shared" si="216"/>
+        <f t="shared" si="212"/>
         <v>2059.5999999999995</v>
       </c>
       <c r="V149" s="1">
-        <f t="shared" si="216"/>
+        <f t="shared" si="212"/>
         <v>1643.5</v>
       </c>
       <c r="W149" s="1"/>
@@ -11588,5 +11658,6 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>